--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4738149-39F6-47CE-BA08-7D070B310112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926C9651-424F-488E-B8B4-B8BE9A5A0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926C9651-424F-488E-B8B4-B8BE9A5A0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA89B78-F210-4A06-89C7-C1F923E95B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1022">
   <si>
     <t>Company</t>
   </si>
@@ -3002,6 +3002,90 @@
   </si>
   <si>
     <t>78970153027720209</t>
+  </si>
+  <si>
+    <t>78970152027720144</t>
+  </si>
+  <si>
+    <t>СВ5723НB</t>
+  </si>
+  <si>
+    <t>МЕЖДУНАРОДНИ ПРЕВОЗИ КАНОТРАНС ООД</t>
+  </si>
+  <si>
+    <t>78970153027721272</t>
+  </si>
+  <si>
+    <t>78970153027721280</t>
+  </si>
+  <si>
+    <t>78970153027721298</t>
+  </si>
+  <si>
+    <t>78970153027721306</t>
+  </si>
+  <si>
+    <t>78970153027721314</t>
+  </si>
+  <si>
+    <t>78970153027721322</t>
+  </si>
+  <si>
+    <t>78970153027721330</t>
+  </si>
+  <si>
+    <t>78970153027721348</t>
+  </si>
+  <si>
+    <t>78970153027721355</t>
+  </si>
+  <si>
+    <t>78970153027721363</t>
+  </si>
+  <si>
+    <t>78970153027721371</t>
+  </si>
+  <si>
+    <t>78970153027721389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В0303ТМ </t>
+  </si>
+  <si>
+    <t>В3838ХК</t>
+  </si>
+  <si>
+    <t>В1551ТН</t>
+  </si>
+  <si>
+    <t>В3030ХВ</t>
+  </si>
+  <si>
+    <t>В6633ХВ</t>
+  </si>
+  <si>
+    <t>В6655ТЕ</t>
+  </si>
+  <si>
+    <t>В7227ТТ</t>
+  </si>
+  <si>
+    <t>В7337ТТ</t>
+  </si>
+  <si>
+    <t>В1155НН</t>
+  </si>
+  <si>
+    <t>В9922ТМ</t>
+  </si>
+  <si>
+    <t>В9955ТХ</t>
+  </si>
+  <si>
+    <t>К99</t>
+  </si>
+  <si>
+    <t>103082651</t>
   </si>
 </sst>
 </file>
@@ -3049,7 +3133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3058,6 +3142,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3360,7 +3446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E456"/>
+  <dimension ref="A1:E469"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.42578125" bestFit="1" customWidth="1"/>
@@ -4534,16 +4620,16 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>925</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>160</v>
+        <v>921</v>
+      </c>
+      <c r="B84" t="s">
+        <v>995</v>
+      </c>
+      <c r="C84" t="s">
+        <v>994</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -4551,10 +4637,10 @@
         <v>925</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>926</v>
@@ -4562,44 +4648,44 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C88" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -4607,10 +4693,10 @@
         <v>931</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="C89" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>932</v>
@@ -4618,16 +4704,16 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>171</v>
+        <v>51</v>
+      </c>
+      <c r="C90" t="s">
+        <v>169</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -4635,10 +4721,10 @@
         <v>933</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>934</v>
@@ -4646,16 +4732,16 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -4663,10 +4749,10 @@
         <v>935</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>936</v>
@@ -4677,10 +4763,10 @@
         <v>935</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>936</v>
@@ -4688,16 +4774,16 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -4705,10 +4791,10 @@
         <v>937</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>938</v>
@@ -4719,10 +4805,10 @@
         <v>937</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>938</v>
@@ -4733,10 +4819,10 @@
         <v>937</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>938</v>
@@ -4744,16 +4830,16 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4761,10 +4847,10 @@
         <v>940</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>939</v>
@@ -4775,10 +4861,10 @@
         <v>940</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>939</v>
@@ -4786,13 +4872,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>939</v>
@@ -4803,10 +4889,10 @@
         <v>941</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>939</v>
@@ -4817,10 +4903,10 @@
         <v>941</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>939</v>
@@ -4831,10 +4917,10 @@
         <v>941</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>939</v>
@@ -4845,10 +4931,10 @@
         <v>941</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>939</v>
@@ -4859,10 +4945,10 @@
         <v>941</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>939</v>
@@ -4873,10 +4959,10 @@
         <v>941</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>939</v>
@@ -4887,10 +4973,10 @@
         <v>941</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>939</v>
@@ -4901,10 +4987,10 @@
         <v>941</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>939</v>
@@ -4915,10 +5001,10 @@
         <v>941</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>939</v>
@@ -4929,10 +5015,10 @@
         <v>941</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>939</v>
@@ -4943,10 +5029,10 @@
         <v>941</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>939</v>
@@ -4957,10 +5043,10 @@
         <v>941</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>939</v>
@@ -4971,10 +5057,10 @@
         <v>941</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>939</v>
@@ -4985,10 +5071,10 @@
         <v>941</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>939</v>
@@ -4999,10 +5085,10 @@
         <v>941</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>939</v>
@@ -5013,10 +5099,10 @@
         <v>941</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>939</v>
@@ -5027,10 +5113,10 @@
         <v>941</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>939</v>
@@ -5041,10 +5127,10 @@
         <v>941</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>939</v>
@@ -5055,10 +5141,10 @@
         <v>941</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>939</v>
@@ -5069,10 +5155,10 @@
         <v>941</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>939</v>
@@ -5083,10 +5169,10 @@
         <v>941</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>939</v>
@@ -5097,10 +5183,10 @@
         <v>941</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>939</v>
@@ -5111,10 +5197,10 @@
         <v>941</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>939</v>
@@ -5125,10 +5211,10 @@
         <v>941</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>939</v>
@@ -5139,10 +5225,10 @@
         <v>941</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>939</v>
@@ -5153,10 +5239,10 @@
         <v>941</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>939</v>
@@ -5164,13 +5250,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>939</v>
@@ -5181,10 +5267,10 @@
         <v>942</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>939</v>
@@ -5195,10 +5281,10 @@
         <v>942</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>939</v>
@@ -5209,10 +5295,10 @@
         <v>942</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>939</v>
@@ -5223,10 +5309,10 @@
         <v>942</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>939</v>
@@ -5237,10 +5323,10 @@
         <v>942</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>939</v>
@@ -5251,10 +5337,10 @@
         <v>942</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>939</v>
@@ -5265,10 +5351,10 @@
         <v>942</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>939</v>
@@ -5279,10 +5365,10 @@
         <v>942</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>939</v>
@@ -5293,10 +5379,10 @@
         <v>942</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>939</v>
@@ -5307,10 +5393,10 @@
         <v>942</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>939</v>
@@ -5321,10 +5407,10 @@
         <v>942</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>939</v>
@@ -5335,10 +5421,10 @@
         <v>942</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>939</v>
@@ -5349,10 +5435,10 @@
         <v>942</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>939</v>
@@ -5363,10 +5449,10 @@
         <v>942</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>939</v>
@@ -5377,10 +5463,10 @@
         <v>942</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>939</v>
@@ -5391,10 +5477,10 @@
         <v>942</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>939</v>
@@ -5405,10 +5491,10 @@
         <v>942</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>939</v>
@@ -5419,10 +5505,10 @@
         <v>942</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>939</v>
@@ -5433,10 +5519,10 @@
         <v>942</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>939</v>
@@ -5444,16 +5530,16 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -5461,10 +5547,10 @@
         <v>943</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>944</v>
@@ -5475,10 +5561,10 @@
         <v>943</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>944</v>
@@ -5489,10 +5575,10 @@
         <v>943</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>944</v>
@@ -5503,10 +5589,10 @@
         <v>943</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>944</v>
@@ -5517,10 +5603,10 @@
         <v>943</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>944</v>
@@ -5531,10 +5617,10 @@
         <v>943</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>944</v>
@@ -5545,10 +5631,10 @@
         <v>943</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>944</v>
@@ -5559,10 +5645,10 @@
         <v>943</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>944</v>
@@ -5573,10 +5659,10 @@
         <v>943</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>944</v>
@@ -5587,10 +5673,10 @@
         <v>943</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>944</v>
@@ -5601,10 +5687,10 @@
         <v>943</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>944</v>
@@ -5615,10 +5701,10 @@
         <v>943</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>944</v>
@@ -5629,10 +5715,10 @@
         <v>943</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>944</v>
@@ -5643,10 +5729,10 @@
         <v>943</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>944</v>
@@ -5657,10 +5743,10 @@
         <v>943</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>944</v>
@@ -5671,10 +5757,10 @@
         <v>943</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>944</v>
@@ -5685,10 +5771,10 @@
         <v>943</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>944</v>
@@ -5699,10 +5785,10 @@
         <v>943</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>944</v>
@@ -5713,10 +5799,10 @@
         <v>943</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>944</v>
@@ -5727,10 +5813,10 @@
         <v>943</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>944</v>
@@ -5741,10 +5827,10 @@
         <v>943</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>944</v>
@@ -5755,10 +5841,10 @@
         <v>943</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>944</v>
@@ -5769,10 +5855,10 @@
         <v>943</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>944</v>
@@ -5783,10 +5869,10 @@
         <v>943</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>944</v>
@@ -5797,10 +5883,10 @@
         <v>943</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>944</v>
@@ -5811,10 +5897,10 @@
         <v>943</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>944</v>
@@ -5825,10 +5911,10 @@
         <v>943</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>944</v>
@@ -5839,10 +5925,10 @@
         <v>943</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>944</v>
@@ -5853,10 +5939,10 @@
         <v>943</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>944</v>
@@ -5867,10 +5953,10 @@
         <v>943</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>944</v>
@@ -5881,10 +5967,10 @@
         <v>943</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>944</v>
@@ -5895,10 +5981,10 @@
         <v>943</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>944</v>
@@ -5909,10 +5995,10 @@
         <v>943</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>944</v>
@@ -5923,10 +6009,10 @@
         <v>943</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>944</v>
@@ -5937,10 +6023,10 @@
         <v>943</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>944</v>
@@ -5951,10 +6037,10 @@
         <v>943</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>944</v>
@@ -5965,10 +6051,10 @@
         <v>943</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>944</v>
@@ -5979,10 +6065,10 @@
         <v>943</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>944</v>
@@ -5993,10 +6079,10 @@
         <v>943</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>944</v>
@@ -6004,16 +6090,16 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -6021,10 +6107,10 @@
         <v>945</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>946</v>
@@ -6035,10 +6121,10 @@
         <v>945</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>946</v>
@@ -6046,16 +6132,16 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -6063,10 +6149,10 @@
         <v>947</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>948</v>
@@ -6077,10 +6163,10 @@
         <v>947</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>948</v>
@@ -6091,10 +6177,10 @@
         <v>947</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>948</v>
@@ -6105,10 +6191,10 @@
         <v>947</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>948</v>
@@ -6119,10 +6205,10 @@
         <v>947</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>948</v>
@@ -6133,10 +6219,10 @@
         <v>947</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>948</v>
@@ -6144,16 +6230,16 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -6161,10 +6247,10 @@
         <v>949</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>950</v>
@@ -6172,16 +6258,16 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -6189,10 +6275,10 @@
         <v>951</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>952</v>
@@ -6203,10 +6289,10 @@
         <v>951</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>952</v>
@@ -6217,10 +6303,10 @@
         <v>951</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>952</v>
@@ -6231,10 +6317,10 @@
         <v>951</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>952</v>
@@ -6245,10 +6331,10 @@
         <v>951</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>952</v>
@@ -6259,10 +6345,10 @@
         <v>951</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>952</v>
@@ -6273,10 +6359,10 @@
         <v>951</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>952</v>
@@ -6287,10 +6373,10 @@
         <v>951</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>952</v>
@@ -6301,10 +6387,10 @@
         <v>951</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>952</v>
@@ -6315,10 +6401,10 @@
         <v>951</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>952</v>
@@ -6326,16 +6412,16 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -6343,10 +6429,10 @@
         <v>953</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>954</v>
@@ -6357,10 +6443,10 @@
         <v>953</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>954</v>
@@ -6371,10 +6457,10 @@
         <v>953</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>954</v>
@@ -6385,10 +6471,10 @@
         <v>953</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>954</v>
@@ -6399,10 +6485,10 @@
         <v>953</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>954</v>
@@ -6413,10 +6499,10 @@
         <v>953</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>954</v>
@@ -6427,10 +6513,10 @@
         <v>953</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>954</v>
@@ -6441,10 +6527,10 @@
         <v>953</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>954</v>
@@ -6455,10 +6541,10 @@
         <v>953</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>954</v>
@@ -6469,10 +6555,10 @@
         <v>953</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>954</v>
@@ -6483,10 +6569,10 @@
         <v>953</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>954</v>
@@ -6497,10 +6583,10 @@
         <v>953</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>954</v>
@@ -6511,10 +6597,10 @@
         <v>953</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>954</v>
@@ -6525,10 +6611,10 @@
         <v>953</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>954</v>
@@ -6539,10 +6625,10 @@
         <v>953</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>954</v>
@@ -6553,10 +6639,10 @@
         <v>953</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>954</v>
@@ -6567,10 +6653,10 @@
         <v>953</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>954</v>
@@ -6581,10 +6667,10 @@
         <v>953</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>954</v>
@@ -6595,10 +6681,10 @@
         <v>953</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>954</v>
@@ -6609,10 +6695,10 @@
         <v>953</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>954</v>
@@ -6623,10 +6709,10 @@
         <v>953</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>954</v>
@@ -6637,10 +6723,10 @@
         <v>953</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>954</v>
@@ -6651,10 +6737,10 @@
         <v>953</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>954</v>
@@ -6665,10 +6751,10 @@
         <v>953</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>954</v>
@@ -6679,10 +6765,10 @@
         <v>953</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>954</v>
@@ -6693,10 +6779,10 @@
         <v>953</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>954</v>
@@ -6707,10 +6793,10 @@
         <v>953</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>954</v>
@@ -6721,10 +6807,10 @@
         <v>953</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>954</v>
@@ -6735,10 +6821,10 @@
         <v>953</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>954</v>
@@ -6749,10 +6835,10 @@
         <v>953</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>954</v>
@@ -6760,16 +6846,16 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,10 +6863,10 @@
         <v>955</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>956</v>
@@ -6788,16 +6874,16 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -6805,10 +6891,10 @@
         <v>957</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>958</v>
@@ -6816,30 +6902,30 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -6847,10 +6933,10 @@
         <v>961</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>962</v>
@@ -6858,16 +6944,16 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -6875,10 +6961,10 @@
         <v>963</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>964</v>
@@ -6889,10 +6975,10 @@
         <v>963</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>964</v>
@@ -6903,10 +6989,10 @@
         <v>963</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>964</v>
@@ -6917,10 +7003,10 @@
         <v>963</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>964</v>
@@ -6931,10 +7017,10 @@
         <v>963</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>964</v>
@@ -6945,10 +7031,10 @@
         <v>963</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>964</v>
@@ -6959,10 +7045,10 @@
         <v>963</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>964</v>
@@ -6970,16 +7056,16 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6987,10 +7073,10 @@
         <v>965</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>966</v>
@@ -7001,10 +7087,10 @@
         <v>965</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>966</v>
@@ -7015,10 +7101,10 @@
         <v>965</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>966</v>
@@ -7029,10 +7115,10 @@
         <v>965</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>966</v>
@@ -7043,10 +7129,10 @@
         <v>965</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>966</v>
@@ -7054,16 +7140,16 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -7071,10 +7157,10 @@
         <v>967</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>968</v>
@@ -7085,10 +7171,10 @@
         <v>967</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>968</v>
@@ -7096,16 +7182,16 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -7113,10 +7199,10 @@
         <v>969</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>970</v>
@@ -7127,10 +7213,10 @@
         <v>969</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>970</v>
@@ -7141,10 +7227,10 @@
         <v>969</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>970</v>
@@ -7155,10 +7241,10 @@
         <v>969</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>970</v>
@@ -7169,10 +7255,10 @@
         <v>969</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>970</v>
@@ -7183,10 +7269,10 @@
         <v>969</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>970</v>
@@ -7197,10 +7283,10 @@
         <v>969</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>970</v>
@@ -7211,10 +7297,10 @@
         <v>969</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>970</v>
@@ -7225,10 +7311,10 @@
         <v>969</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>970</v>
@@ -7239,10 +7325,10 @@
         <v>969</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>970</v>
@@ -7253,10 +7339,10 @@
         <v>969</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>970</v>
@@ -7267,10 +7353,10 @@
         <v>969</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>970</v>
@@ -7281,10 +7367,10 @@
         <v>969</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>970</v>
@@ -7295,10 +7381,10 @@
         <v>969</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>970</v>
@@ -7309,10 +7395,10 @@
         <v>969</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>970</v>
@@ -7323,10 +7409,10 @@
         <v>969</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>970</v>
@@ -7337,10 +7423,10 @@
         <v>969</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>970</v>
@@ -7351,10 +7437,10 @@
         <v>969</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>970</v>
@@ -7365,10 +7451,10 @@
         <v>969</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>970</v>
@@ -7379,10 +7465,10 @@
         <v>969</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>970</v>
@@ -7393,10 +7479,10 @@
         <v>969</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>970</v>
@@ -7407,10 +7493,10 @@
         <v>969</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>970</v>
@@ -7421,10 +7507,10 @@
         <v>969</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>970</v>
@@ -7435,10 +7521,10 @@
         <v>969</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>970</v>
@@ -7449,10 +7535,10 @@
         <v>969</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>970</v>
@@ -7463,10 +7549,10 @@
         <v>969</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>970</v>
@@ -7477,10 +7563,10 @@
         <v>969</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>970</v>
@@ -7491,10 +7577,10 @@
         <v>969</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>970</v>
@@ -7505,10 +7591,10 @@
         <v>969</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>970</v>
@@ -7519,10 +7605,10 @@
         <v>969</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>970</v>
@@ -7533,10 +7619,10 @@
         <v>969</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>970</v>
@@ -7547,10 +7633,10 @@
         <v>969</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>970</v>
@@ -7561,10 +7647,10 @@
         <v>969</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>970</v>
@@ -7575,10 +7661,10 @@
         <v>969</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>970</v>
@@ -7589,10 +7675,10 @@
         <v>969</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>970</v>
@@ -7603,10 +7689,10 @@
         <v>969</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>970</v>
@@ -7617,10 +7703,10 @@
         <v>969</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>970</v>
@@ -7631,10 +7717,10 @@
         <v>969</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>970</v>
@@ -7645,10 +7731,10 @@
         <v>969</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>970</v>
@@ -7659,10 +7745,10 @@
         <v>969</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>970</v>
@@ -7673,10 +7759,10 @@
         <v>969</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>970</v>
@@ -7684,16 +7770,16 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -7701,10 +7787,10 @@
         <v>971</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>972</v>
@@ -7715,10 +7801,10 @@
         <v>971</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>972</v>
@@ -7729,10 +7815,10 @@
         <v>971</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>972</v>
@@ -7743,10 +7829,10 @@
         <v>971</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>972</v>
@@ -7757,10 +7843,10 @@
         <v>971</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>972</v>
@@ -7771,10 +7857,10 @@
         <v>971</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>972</v>
@@ -7785,10 +7871,10 @@
         <v>971</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>972</v>
@@ -7799,10 +7885,10 @@
         <v>971</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>972</v>
@@ -7813,10 +7899,10 @@
         <v>971</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>972</v>
@@ -7824,16 +7910,16 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -7841,10 +7927,10 @@
         <v>973</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>974</v>
@@ -7855,10 +7941,10 @@
         <v>973</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>974</v>
@@ -7866,16 +7952,16 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -7883,10 +7969,10 @@
         <v>976</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>978</v>
@@ -7897,10 +7983,10 @@
         <v>976</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>978</v>
@@ -7911,10 +7997,10 @@
         <v>976</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>978</v>
@@ -7925,10 +8011,10 @@
         <v>976</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>978</v>
@@ -7939,10 +8025,10 @@
         <v>976</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>978</v>
@@ -7953,10 +8039,10 @@
         <v>976</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>978</v>
@@ -7967,10 +8053,10 @@
         <v>976</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>978</v>
@@ -7981,10 +8067,10 @@
         <v>976</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>978</v>
@@ -7992,13 +8078,13 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>978</v>
@@ -8009,10 +8095,10 @@
         <v>975</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>978</v>
@@ -8023,10 +8109,10 @@
         <v>975</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>978</v>
@@ -8037,10 +8123,10 @@
         <v>975</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>978</v>
@@ -8051,10 +8137,10 @@
         <v>975</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>978</v>
@@ -8065,10 +8151,10 @@
         <v>975</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>978</v>
@@ -8079,10 +8165,10 @@
         <v>975</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>978</v>
@@ -8093,10 +8179,10 @@
         <v>975</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>978</v>
@@ -8104,16 +8190,16 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -8121,10 +8207,10 @@
         <v>977</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>979</v>
@@ -8135,10 +8221,10 @@
         <v>977</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>979</v>
@@ -8149,10 +8235,10 @@
         <v>977</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>979</v>
@@ -8160,16 +8246,16 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -8177,10 +8263,10 @@
         <v>980</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>991</v>
@@ -8191,10 +8277,10 @@
         <v>980</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>991</v>
@@ -8205,10 +8291,10 @@
         <v>980</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>991</v>
@@ -8219,10 +8305,10 @@
         <v>980</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>991</v>
@@ -8233,10 +8319,10 @@
         <v>980</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>991</v>
@@ -8247,10 +8333,10 @@
         <v>980</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>991</v>
@@ -8261,10 +8347,10 @@
         <v>980</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>991</v>
@@ -8275,10 +8361,10 @@
         <v>980</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>991</v>
@@ -8289,10 +8375,10 @@
         <v>980</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>991</v>
@@ -8303,10 +8389,10 @@
         <v>980</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>991</v>
@@ -8317,10 +8403,10 @@
         <v>980</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>991</v>
@@ -8331,10 +8417,10 @@
         <v>980</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>991</v>
@@ -8345,10 +8431,10 @@
         <v>980</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>991</v>
@@ -8359,10 +8445,10 @@
         <v>980</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>991</v>
@@ -8373,10 +8459,10 @@
         <v>980</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>991</v>
@@ -8384,13 +8470,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>991</v>
@@ -8401,10 +8487,10 @@
         <v>981</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>991</v>
@@ -8415,10 +8501,10 @@
         <v>981</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>991</v>
@@ -8429,10 +8515,10 @@
         <v>981</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>991</v>
@@ -8443,10 +8529,10 @@
         <v>981</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>991</v>
@@ -8457,10 +8543,10 @@
         <v>981</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>991</v>
@@ -8471,10 +8557,10 @@
         <v>981</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>991</v>
@@ -8485,10 +8571,10 @@
         <v>981</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>991</v>
@@ -8499,10 +8585,10 @@
         <v>981</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>991</v>
@@ -8513,10 +8599,10 @@
         <v>981</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>991</v>
@@ -8527,10 +8613,10 @@
         <v>981</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>991</v>
@@ -8541,10 +8627,10 @@
         <v>981</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>991</v>
@@ -8555,10 +8641,10 @@
         <v>981</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>991</v>
@@ -8569,10 +8655,10 @@
         <v>981</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>991</v>
@@ -8583,10 +8669,10 @@
         <v>981</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>991</v>
@@ -8597,10 +8683,10 @@
         <v>981</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>991</v>
@@ -8608,27 +8694,27 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>897</v>
+        <v>738</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>741</v>
+        <v>897</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>990</v>
@@ -8639,10 +8725,10 @@
         <v>988</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>990</v>
@@ -8653,10 +8739,10 @@
         <v>988</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>990</v>
@@ -8670,7 +8756,7 @@
         <v>744</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>879</v>
+        <v>745</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>990</v>
@@ -8681,10 +8767,10 @@
         <v>988</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>990</v>
@@ -8695,10 +8781,10 @@
         <v>988</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>990</v>
@@ -8706,13 +8792,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>990</v>
@@ -8726,7 +8812,7 @@
         <v>746</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>747</v>
+        <v>882</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>990</v>
@@ -8734,16 +8820,16 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>791</v>
+        <v>747</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -8751,10 +8837,10 @@
         <v>982</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>992</v>
@@ -8765,10 +8851,10 @@
         <v>982</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>790</v>
+        <v>813</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>992</v>
@@ -8779,10 +8865,10 @@
         <v>982</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>992</v>
@@ -8793,10 +8879,10 @@
         <v>982</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>992</v>
@@ -8807,10 +8893,10 @@
         <v>982</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C389" t="s">
-        <v>903</v>
+        <v>753</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>992</v>
@@ -8821,10 +8907,10 @@
         <v>982</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>802</v>
+        <v>754</v>
+      </c>
+      <c r="C390" t="s">
+        <v>903</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>992</v>
@@ -8835,10 +8921,10 @@
         <v>982</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>992</v>
@@ -8849,10 +8935,10 @@
         <v>982</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>992</v>
@@ -8863,10 +8949,10 @@
         <v>982</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>752</v>
+        <v>800</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>992</v>
@@ -8877,10 +8963,10 @@
         <v>982</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>806</v>
+        <v>752</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>992</v>
@@ -8891,10 +8977,10 @@
         <v>982</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>992</v>
@@ -8905,10 +8991,10 @@
         <v>982</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>992</v>
@@ -8919,10 +9005,10 @@
         <v>982</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>992</v>
@@ -8933,10 +9019,10 @@
         <v>982</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>812</v>
+        <v>763</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>992</v>
@@ -8947,10 +9033,10 @@
         <v>982</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="C399" t="s">
-        <v>902</v>
+        <v>764</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>812</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>992</v>
@@ -8961,10 +9047,10 @@
         <v>982</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>794</v>
+        <v>765</v>
+      </c>
+      <c r="C400" t="s">
+        <v>902</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>992</v>
@@ -8975,10 +9061,10 @@
         <v>982</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>992</v>
@@ -8989,10 +9075,10 @@
         <v>982</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>992</v>
@@ -9003,10 +9089,10 @@
         <v>982</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>841</v>
+        <v>795</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>992</v>
@@ -9017,10 +9103,10 @@
         <v>982</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>992</v>
@@ -9031,10 +9117,10 @@
         <v>982</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>992</v>
@@ -9045,10 +9131,10 @@
         <v>982</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>992</v>
@@ -9059,10 +9145,10 @@
         <v>982</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>992</v>
@@ -9073,10 +9159,10 @@
         <v>982</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>992</v>
@@ -9087,10 +9173,10 @@
         <v>982</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>992</v>
@@ -9101,7 +9187,7 @@
         <v>982</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>774</v>
@@ -9115,7 +9201,7 @@
         <v>982</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>774</v>
@@ -9129,7 +9215,7 @@
         <v>982</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>774</v>
@@ -9143,10 +9229,10 @@
         <v>982</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>807</v>
+        <v>774</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>992</v>
@@ -9157,10 +9243,10 @@
         <v>982</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>992</v>
@@ -9171,10 +9257,10 @@
         <v>982</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>992</v>
@@ -9185,10 +9271,10 @@
         <v>982</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>992</v>
@@ -9199,10 +9285,10 @@
         <v>982</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>992</v>
@@ -9212,11 +9298,11 @@
       <c r="A418" t="s">
         <v>982</v>
       </c>
-      <c r="B418" t="s">
-        <v>786</v>
-      </c>
-      <c r="C418" t="s">
-        <v>900</v>
+      <c r="B418" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>804</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>992</v>
@@ -9226,11 +9312,11 @@
       <c r="A419" t="s">
         <v>982</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>799</v>
+      <c r="B419" t="s">
+        <v>786</v>
+      </c>
+      <c r="C419" t="s">
+        <v>900</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>992</v>
@@ -9241,10 +9327,10 @@
         <v>982</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>992</v>
@@ -9255,10 +9341,10 @@
         <v>982</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>992</v>
@@ -9268,8 +9354,11 @@
       <c r="A422" t="s">
         <v>982</v>
       </c>
+      <c r="B422" s="1" t="s">
+        <v>789</v>
+      </c>
       <c r="C422" s="2" t="s">
-        <v>816</v>
+        <v>785</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>992</v>
@@ -9277,16 +9366,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>983</v>
-      </c>
-      <c r="B423" s="3" t="s">
-        <v>829</v>
+        <v>982</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -9294,10 +9380,10 @@
         <v>983</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D424" s="1" t="s">
         <v>984</v>
@@ -9308,10 +9394,10 @@
         <v>983</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>984</v>
@@ -9322,10 +9408,10 @@
         <v>983</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D426" s="1" t="s">
         <v>984</v>
@@ -9336,10 +9422,10 @@
         <v>983</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>984</v>
@@ -9350,10 +9436,10 @@
         <v>983</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>984</v>
@@ -9364,10 +9450,10 @@
         <v>983</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>984</v>
@@ -9378,10 +9464,10 @@
         <v>983</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>984</v>
@@ -9392,10 +9478,10 @@
         <v>983</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>984</v>
@@ -9406,10 +9492,10 @@
         <v>983</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>984</v>
@@ -9420,10 +9506,10 @@
         <v>983</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>984</v>
@@ -9434,10 +9520,10 @@
         <v>983</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>984</v>
@@ -9445,16 +9531,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>842</v>
-      </c>
-      <c r="B435" s="1" t="s">
-        <v>846</v>
+        <v>983</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>840</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>888</v>
+        <v>828</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -9462,10 +9548,10 @@
         <v>842</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>850</v>
+        <v>888</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>985</v>
@@ -9476,10 +9562,10 @@
         <v>842</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>985</v>
@@ -9490,10 +9576,10 @@
         <v>842</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>985</v>
@@ -9504,10 +9590,10 @@
         <v>842</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>985</v>
@@ -9518,10 +9604,10 @@
         <v>842</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>985</v>
@@ -9532,10 +9618,10 @@
         <v>842</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>985</v>
@@ -9543,50 +9629,47 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>884</v>
-      </c>
-      <c r="B442" s="1">
-        <v>3</v>
+        <v>842</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>874</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="E442" s="1" t="s">
-        <v>853</v>
+        <v>985</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>884</v>
       </c>
+      <c r="B443" s="1">
+        <v>3</v>
+      </c>
       <c r="C443" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>884</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>859</v>
-      </c>
       <c r="C444" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -9594,16 +9677,16 @@
         <v>884</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -9611,16 +9694,16 @@
         <v>884</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -9628,16 +9711,16 @@
         <v>884</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>51</v>
+        <v>863</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>864</v>
+        <v>883</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -9645,16 +9728,16 @@
         <v>884</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -9662,30 +9745,33 @@
         <v>884</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>884</v>
       </c>
+      <c r="B450" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="C450" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -9693,61 +9779,61 @@
         <v>884</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>884</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C452" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>884</v>
       </c>
-      <c r="B453" t="s">
-        <v>887</v>
+      <c r="B453" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>884</v>
       </c>
+      <c r="B454" t="s">
+        <v>887</v>
+      </c>
       <c r="C454" s="2" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -9755,13 +9841,13 @@
         <v>884</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -9769,13 +9855,195 @@
         <v>884</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>986</v>
       </c>
       <c r="E456" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>884</v>
+      </c>
+      <c r="C457" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="E457" s="1" t="s">
         <v>869</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>996</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D458" s="1" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D459" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C460" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="D460" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D461" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D462" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D463" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D464" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D465" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D466" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D467" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C468" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D468" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D469" s="5" t="s">
+        <v>1021</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA89B78-F210-4A06-89C7-C1F923E95B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FACB6DA-9B2B-47DE-ACA3-1A06F2B1BA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3133,7 +3133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3142,8 +3142,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9893,7 +9891,7 @@
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A459" s="4" t="s">
+      <c r="A459" t="s">
         <v>996</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -9902,12 +9900,12 @@
       <c r="C459" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="D459" s="5" t="s">
+      <c r="D459" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A460" s="4" t="s">
+      <c r="A460" t="s">
         <v>996</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -9916,12 +9914,12 @@
       <c r="C460" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D460" s="5" t="s">
+      <c r="D460" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A461" s="4" t="s">
+      <c r="A461" t="s">
         <v>996</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -9930,12 +9928,12 @@
       <c r="C461" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="D461" s="5" t="s">
+      <c r="D461" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="4" t="s">
+      <c r="A462" t="s">
         <v>996</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -9944,12 +9942,12 @@
       <c r="C462" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="D462" s="5" t="s">
+      <c r="D462" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="4" t="s">
+      <c r="A463" t="s">
         <v>996</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -9958,12 +9956,12 @@
       <c r="C463" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D463" s="5" t="s">
+      <c r="D463" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="4" t="s">
+      <c r="A464" t="s">
         <v>996</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -9972,12 +9970,12 @@
       <c r="C464" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="D464" s="5" t="s">
+      <c r="D464" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A465" s="4" t="s">
+      <c r="A465" t="s">
         <v>996</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -9986,12 +9984,12 @@
       <c r="C465" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="D465" s="5" t="s">
+      <c r="D465" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A466" s="4" t="s">
+      <c r="A466" t="s">
         <v>996</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -10000,12 +9998,12 @@
       <c r="C466" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="D466" s="5" t="s">
+      <c r="D466" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A467" s="4" t="s">
+      <c r="A467" t="s">
         <v>996</v>
       </c>
       <c r="B467" s="1" t="s">
@@ -10014,12 +10012,12 @@
       <c r="C467" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="D467" s="5" t="s">
+      <c r="D467" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A468" s="4" t="s">
+      <c r="A468" t="s">
         <v>996</v>
       </c>
       <c r="B468" s="1" t="s">
@@ -10028,12 +10026,12 @@
       <c r="C468" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D468" s="5" t="s">
+      <c r="D468" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="4" t="s">
+      <c r="A469" t="s">
         <v>996</v>
       </c>
       <c r="B469" s="1" t="s">
@@ -10042,7 +10040,7 @@
       <c r="C469" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="D469" s="5" t="s">
+      <c r="D469" s="1" t="s">
         <v>1021</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FACB6DA-9B2B-47DE-ACA3-1A06F2B1BA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE68E18-3231-4427-9116-A9B3CC54F4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1023">
   <si>
     <t>Company</t>
   </si>
@@ -2650,9 +2650,6 @@
     <t>78970110027720217</t>
   </si>
   <si>
-    <t>ЕНЕРДЖИ ПЛЮС</t>
-  </si>
-  <si>
     <t>78970110027720233</t>
   </si>
   <si>
@@ -3086,6 +3083,12 @@
   </si>
   <si>
     <t>103082651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	ЕНЕРДЖИ ПЛЮС ЕООД</t>
+  </si>
+  <si>
+    <t>104698653</t>
   </si>
 </sst>
 </file>
@@ -3465,12 +3468,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -3479,12 +3482,12 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -3493,12 +3496,12 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3507,12 +3510,12 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
@@ -3521,12 +3524,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -3535,12 +3538,12 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>13</v>
@@ -3549,12 +3552,12 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>15</v>
@@ -3563,40 +3566,40 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -3605,12 +3608,12 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -3619,26 +3622,26 @@
         <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>24</v>
@@ -3647,12 +3650,12 @@
         <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>26</v>
@@ -3661,26 +3664,26 @@
         <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>29</v>
@@ -3689,12 +3692,12 @@
         <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>31</v>
@@ -3703,12 +3706,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>33</v>
@@ -3717,12 +3720,12 @@
         <v>34</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>35</v>
@@ -3731,26 +3734,26 @@
         <v>36</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>38</v>
@@ -3759,12 +3762,12 @@
         <v>39</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>40</v>
@@ -3773,12 +3776,12 @@
         <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>42</v>
@@ -3787,12 +3790,12 @@
         <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>44</v>
@@ -3801,12 +3804,12 @@
         <v>45</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>46</v>
@@ -3815,12 +3818,12 @@
         <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>48</v>
@@ -3829,26 +3832,26 @@
         <v>49</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>52</v>
@@ -3857,12 +3860,12 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>54</v>
@@ -3871,12 +3874,12 @@
         <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>56</v>
@@ -3885,12 +3888,12 @@
         <v>57</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>58</v>
@@ -3899,12 +3902,12 @@
         <v>59</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>60</v>
@@ -3913,12 +3916,12 @@
         <v>61</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>62</v>
@@ -3927,12 +3930,12 @@
         <v>63</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>64</v>
@@ -3941,12 +3944,12 @@
         <v>65</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>66</v>
@@ -3955,26 +3958,26 @@
         <v>67</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>68</v>
@@ -3983,12 +3986,12 @@
         <v>69</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>70</v>
@@ -3997,12 +4000,12 @@
         <v>71</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>72</v>
@@ -4011,12 +4014,12 @@
         <v>73</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>74</v>
@@ -4025,12 +4028,12 @@
         <v>75</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>76</v>
@@ -4039,12 +4042,12 @@
         <v>77</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>78</v>
@@ -4053,12 +4056,12 @@
         <v>79</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>80</v>
@@ -4067,12 +4070,12 @@
         <v>81</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>82</v>
@@ -4081,12 +4084,12 @@
         <v>83</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>84</v>
@@ -4095,12 +4098,12 @@
         <v>85</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>86</v>
@@ -4109,12 +4112,12 @@
         <v>87</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>86</v>
@@ -4123,12 +4126,12 @@
         <v>88</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>89</v>
@@ -4137,12 +4140,12 @@
         <v>90</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>91</v>
@@ -4151,12 +4154,12 @@
         <v>92</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>93</v>
@@ -4165,12 +4168,12 @@
         <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>95</v>
@@ -4179,12 +4182,12 @@
         <v>96</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>97</v>
@@ -4193,12 +4196,12 @@
         <v>98</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>99</v>
@@ -4207,12 +4210,12 @@
         <v>100</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>101</v>
@@ -4221,12 +4224,12 @@
         <v>102</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>103</v>
@@ -4235,12 +4238,12 @@
         <v>104</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>105</v>
@@ -4249,12 +4252,12 @@
         <v>106</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>107</v>
@@ -4263,12 +4266,12 @@
         <v>108</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>109</v>
@@ -4277,12 +4280,12 @@
         <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>111</v>
@@ -4291,12 +4294,12 @@
         <v>112</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>113</v>
@@ -4305,12 +4308,12 @@
         <v>114</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>115</v>
@@ -4319,12 +4322,12 @@
         <v>116</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>117</v>
@@ -4333,12 +4336,12 @@
         <v>118</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>119</v>
@@ -4347,12 +4350,12 @@
         <v>120</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>121</v>
@@ -4361,12 +4364,12 @@
         <v>122</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>123</v>
@@ -4375,12 +4378,12 @@
         <v>124</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>125</v>
@@ -4389,12 +4392,12 @@
         <v>126</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>127</v>
@@ -4403,12 +4406,12 @@
         <v>128</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>129</v>
@@ -4417,12 +4420,12 @@
         <v>130</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>131</v>
@@ -4431,12 +4434,12 @@
         <v>132</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>133</v>
@@ -4445,12 +4448,12 @@
         <v>134</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>135</v>
@@ -4459,12 +4462,12 @@
         <v>136</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>137</v>
@@ -4473,12 +4476,12 @@
         <v>138</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>139</v>
@@ -4487,12 +4490,12 @@
         <v>140</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>141</v>
@@ -4501,12 +4504,12 @@
         <v>142</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>143</v>
@@ -4515,12 +4518,12 @@
         <v>144</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>145</v>
@@ -4529,12 +4532,12 @@
         <v>146</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>147</v>
@@ -4543,12 +4546,12 @@
         <v>148</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>149</v>
@@ -4557,12 +4560,12 @@
         <v>150</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>151</v>
@@ -4571,12 +4574,12 @@
         <v>152</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>153</v>
@@ -4585,12 +4588,12 @@
         <v>154</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>155</v>
@@ -4599,12 +4602,12 @@
         <v>156</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>157</v>
@@ -4613,26 +4616,26 @@
         <v>158</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>920</v>
+      </c>
+      <c r="B84" t="s">
+        <v>994</v>
+      </c>
+      <c r="C84" t="s">
+        <v>993</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="B84" t="s">
-        <v>995</v>
-      </c>
-      <c r="C84" t="s">
-        <v>994</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
@@ -4641,12 +4644,12 @@
         <v>160</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>161</v>
@@ -4655,12 +4658,12 @@
         <v>162</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>163</v>
@@ -4669,12 +4672,12 @@
         <v>164</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>165</v>
@@ -4683,12 +4686,12 @@
         <v>166</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>167</v>
@@ -4697,12 +4700,12 @@
         <v>168</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>51</v>
@@ -4711,12 +4714,12 @@
         <v>169</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>170</v>
@@ -4725,12 +4728,12 @@
         <v>171</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>172</v>
@@ -4739,12 +4742,12 @@
         <v>173</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>174</v>
@@ -4753,12 +4756,12 @@
         <v>175</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>101</v>
@@ -4767,12 +4770,12 @@
         <v>176</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>177</v>
@@ -4781,12 +4784,12 @@
         <v>178</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>179</v>
@@ -4795,12 +4798,12 @@
         <v>180</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>181</v>
@@ -4809,12 +4812,12 @@
         <v>182</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>183</v>
@@ -4823,12 +4826,12 @@
         <v>184</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>185</v>
@@ -4837,12 +4840,12 @@
         <v>186</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>187</v>
@@ -4851,12 +4854,12 @@
         <v>188</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>189</v>
@@ -4865,12 +4868,12 @@
         <v>190</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>191</v>
@@ -4879,12 +4882,12 @@
         <v>192</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>193</v>
@@ -4893,12 +4896,12 @@
         <v>194</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>195</v>
@@ -4907,12 +4910,12 @@
         <v>196</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>197</v>
@@ -4921,12 +4924,12 @@
         <v>198</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>199</v>
@@ -4935,12 +4938,12 @@
         <v>200</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>201</v>
@@ -4949,12 +4952,12 @@
         <v>202</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>203</v>
@@ -4963,12 +4966,12 @@
         <v>204</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>205</v>
@@ -4977,12 +4980,12 @@
         <v>206</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>207</v>
@@ -4991,12 +4994,12 @@
         <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>209</v>
@@ -5005,12 +5008,12 @@
         <v>210</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>211</v>
@@ -5019,12 +5022,12 @@
         <v>212</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>213</v>
@@ -5033,12 +5036,12 @@
         <v>214</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>215</v>
@@ -5047,12 +5050,12 @@
         <v>216</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>217</v>
@@ -5061,12 +5064,12 @@
         <v>218</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>219</v>
@@ -5075,12 +5078,12 @@
         <v>220</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>221</v>
@@ -5089,12 +5092,12 @@
         <v>222</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>223</v>
@@ -5103,12 +5106,12 @@
         <v>224</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>225</v>
@@ -5117,12 +5120,12 @@
         <v>226</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>227</v>
@@ -5131,12 +5134,12 @@
         <v>228</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>229</v>
@@ -5145,12 +5148,12 @@
         <v>230</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>231</v>
@@ -5159,12 +5162,12 @@
         <v>232</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>233</v>
@@ -5173,12 +5176,12 @@
         <v>234</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>235</v>
@@ -5187,12 +5190,12 @@
         <v>236</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>237</v>
@@ -5201,12 +5204,12 @@
         <v>238</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>239</v>
@@ -5215,12 +5218,12 @@
         <v>240</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>241</v>
@@ -5229,12 +5232,12 @@
         <v>242</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>243</v>
@@ -5243,12 +5246,12 @@
         <v>244</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>245</v>
@@ -5257,12 +5260,12 @@
         <v>246</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>247</v>
@@ -5271,12 +5274,12 @@
         <v>248</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>249</v>
@@ -5285,12 +5288,12 @@
         <v>250</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>251</v>
@@ -5299,12 +5302,12 @@
         <v>252</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>253</v>
@@ -5313,12 +5316,12 @@
         <v>254</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>255</v>
@@ -5327,12 +5330,12 @@
         <v>256</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>257</v>
@@ -5341,12 +5344,12 @@
         <v>258</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>259</v>
@@ -5355,12 +5358,12 @@
         <v>260</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>261</v>
@@ -5369,12 +5372,12 @@
         <v>262</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>263</v>
@@ -5383,12 +5386,12 @@
         <v>264</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>265</v>
@@ -5397,12 +5400,12 @@
         <v>266</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>267</v>
@@ -5411,12 +5414,12 @@
         <v>268</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>269</v>
@@ -5425,12 +5428,12 @@
         <v>270</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>271</v>
@@ -5439,12 +5442,12 @@
         <v>272</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>273</v>
@@ -5453,12 +5456,12 @@
         <v>274</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>275</v>
@@ -5467,12 +5470,12 @@
         <v>276</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>277</v>
@@ -5481,12 +5484,12 @@
         <v>278</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>279</v>
@@ -5495,12 +5498,12 @@
         <v>280</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>281</v>
@@ -5509,12 +5512,12 @@
         <v>282</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>283</v>
@@ -5523,12 +5526,12 @@
         <v>284</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>285</v>
@@ -5537,12 +5540,12 @@
         <v>286</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>287</v>
@@ -5551,12 +5554,12 @@
         <v>288</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>289</v>
@@ -5565,12 +5568,12 @@
         <v>290</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>291</v>
@@ -5579,12 +5582,12 @@
         <v>292</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>293</v>
@@ -5593,12 +5596,12 @@
         <v>294</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>295</v>
@@ -5607,12 +5610,12 @@
         <v>296</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>297</v>
@@ -5621,12 +5624,12 @@
         <v>298</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>299</v>
@@ -5635,12 +5638,12 @@
         <v>300</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>301</v>
@@ -5649,12 +5652,12 @@
         <v>302</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>303</v>
@@ -5663,12 +5666,12 @@
         <v>304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>305</v>
@@ -5677,12 +5680,12 @@
         <v>306</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>307</v>
@@ -5691,12 +5694,12 @@
         <v>308</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>309</v>
@@ -5705,12 +5708,12 @@
         <v>310</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>311</v>
@@ -5719,12 +5722,12 @@
         <v>312</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>313</v>
@@ -5733,12 +5736,12 @@
         <v>314</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>315</v>
@@ -5747,12 +5750,12 @@
         <v>316</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>317</v>
@@ -5761,12 +5764,12 @@
         <v>318</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>319</v>
@@ -5775,12 +5778,12 @@
         <v>320</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>321</v>
@@ -5789,12 +5792,12 @@
         <v>322</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>323</v>
@@ -5803,12 +5806,12 @@
         <v>324</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>325</v>
@@ -5817,12 +5820,12 @@
         <v>326</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>327</v>
@@ -5831,12 +5834,12 @@
         <v>328</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>329</v>
@@ -5845,12 +5848,12 @@
         <v>330</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>331</v>
@@ -5859,12 +5862,12 @@
         <v>332</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>333</v>
@@ -5873,12 +5876,12 @@
         <v>334</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>335</v>
@@ -5887,12 +5890,12 @@
         <v>336</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>337</v>
@@ -5901,12 +5904,12 @@
         <v>338</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>339</v>
@@ -5915,12 +5918,12 @@
         <v>340</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>341</v>
@@ -5929,12 +5932,12 @@
         <v>342</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>343</v>
@@ -5943,12 +5946,12 @@
         <v>344</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>345</v>
@@ -5957,12 +5960,12 @@
         <v>346</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>347</v>
@@ -5971,12 +5974,12 @@
         <v>348</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>349</v>
@@ -5985,12 +5988,12 @@
         <v>350</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>351</v>
@@ -5999,12 +6002,12 @@
         <v>352</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>353</v>
@@ -6013,12 +6016,12 @@
         <v>354</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>355</v>
@@ -6027,12 +6030,12 @@
         <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>357</v>
@@ -6041,12 +6044,12 @@
         <v>358</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>359</v>
@@ -6055,12 +6058,12 @@
         <v>360</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>361</v>
@@ -6069,12 +6072,12 @@
         <v>362</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>363</v>
@@ -6083,12 +6086,12 @@
         <v>364</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>365</v>
@@ -6097,12 +6100,12 @@
         <v>366</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>367</v>
@@ -6111,12 +6114,12 @@
         <v>368</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>369</v>
@@ -6125,12 +6128,12 @@
         <v>370</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>371</v>
@@ -6139,12 +6142,12 @@
         <v>372</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>373</v>
@@ -6153,12 +6156,12 @@
         <v>374</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>375</v>
@@ -6167,12 +6170,12 @@
         <v>376</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>377</v>
@@ -6181,12 +6184,12 @@
         <v>378</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>379</v>
@@ -6195,12 +6198,12 @@
         <v>380</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>381</v>
@@ -6209,12 +6212,12 @@
         <v>382</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>383</v>
@@ -6223,12 +6226,12 @@
         <v>384</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>385</v>
@@ -6237,12 +6240,12 @@
         <v>386</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>387</v>
@@ -6251,12 +6254,12 @@
         <v>388</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>389</v>
@@ -6265,12 +6268,12 @@
         <v>390</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>391</v>
@@ -6279,12 +6282,12 @@
         <v>392</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>393</v>
@@ -6293,12 +6296,12 @@
         <v>394</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>395</v>
@@ -6307,12 +6310,12 @@
         <v>396</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>397</v>
@@ -6321,12 +6324,12 @@
         <v>398</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>399</v>
@@ -6335,12 +6338,12 @@
         <v>400</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>401</v>
@@ -6349,12 +6352,12 @@
         <v>402</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>403</v>
@@ -6363,12 +6366,12 @@
         <v>404</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>405</v>
@@ -6377,12 +6380,12 @@
         <v>406</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>407</v>
@@ -6391,12 +6394,12 @@
         <v>408</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>409</v>
@@ -6405,12 +6408,12 @@
         <v>410</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>411</v>
@@ -6419,12 +6422,12 @@
         <v>412</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>413</v>
@@ -6433,12 +6436,12 @@
         <v>414</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>415</v>
@@ -6447,12 +6450,12 @@
         <v>416</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>417</v>
@@ -6461,12 +6464,12 @@
         <v>418</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>419</v>
@@ -6475,12 +6478,12 @@
         <v>420</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>421</v>
@@ -6489,12 +6492,12 @@
         <v>422</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>423</v>
@@ -6503,12 +6506,12 @@
         <v>424</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>425</v>
@@ -6517,12 +6520,12 @@
         <v>426</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>427</v>
@@ -6531,12 +6534,12 @@
         <v>428</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>429</v>
@@ -6545,12 +6548,12 @@
         <v>430</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>431</v>
@@ -6559,12 +6562,12 @@
         <v>432</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>433</v>
@@ -6573,12 +6576,12 @@
         <v>434</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>435</v>
@@ -6587,12 +6590,12 @@
         <v>436</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>437</v>
@@ -6601,12 +6604,12 @@
         <v>438</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>439</v>
@@ -6615,12 +6618,12 @@
         <v>440</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>441</v>
@@ -6629,12 +6632,12 @@
         <v>442</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>443</v>
@@ -6643,12 +6646,12 @@
         <v>444</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>445</v>
@@ -6657,12 +6660,12 @@
         <v>446</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>447</v>
@@ -6671,12 +6674,12 @@
         <v>448</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>449</v>
@@ -6685,12 +6688,12 @@
         <v>450</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>451</v>
@@ -6699,12 +6702,12 @@
         <v>452</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>453</v>
@@ -6713,12 +6716,12 @@
         <v>454</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>455</v>
@@ -6727,12 +6730,12 @@
         <v>456</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>457</v>
@@ -6741,12 +6744,12 @@
         <v>458</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>459</v>
@@ -6755,12 +6758,12 @@
         <v>460</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>461</v>
@@ -6769,12 +6772,12 @@
         <v>462</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>463</v>
@@ -6783,12 +6786,12 @@
         <v>464</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>465</v>
@@ -6797,12 +6800,12 @@
         <v>466</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>467</v>
@@ -6811,12 +6814,12 @@
         <v>468</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>469</v>
@@ -6825,12 +6828,12 @@
         <v>470</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>471</v>
@@ -6839,12 +6842,12 @@
         <v>472</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>473</v>
@@ -6853,12 +6856,12 @@
         <v>474</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>475</v>
@@ -6867,12 +6870,12 @@
         <v>476</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>477</v>
@@ -6881,12 +6884,12 @@
         <v>478</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>479</v>
@@ -6895,12 +6898,12 @@
         <v>480</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>481</v>
@@ -6909,12 +6912,12 @@
         <v>482</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>483</v>
@@ -6923,12 +6926,12 @@
         <v>484</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>485</v>
@@ -6937,12 +6940,12 @@
         <v>486</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>487</v>
@@ -6951,12 +6954,12 @@
         <v>488</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>489</v>
@@ -6965,12 +6968,12 @@
         <v>490</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>491</v>
@@ -6979,12 +6982,12 @@
         <v>492</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>493</v>
@@ -6993,12 +6996,12 @@
         <v>494</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>495</v>
@@ -7007,12 +7010,12 @@
         <v>496</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>497</v>
@@ -7021,12 +7024,12 @@
         <v>498</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>499</v>
@@ -7035,12 +7038,12 @@
         <v>500</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>501</v>
@@ -7049,12 +7052,12 @@
         <v>502</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>503</v>
@@ -7063,12 +7066,12 @@
         <v>504</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>505</v>
@@ -7077,12 +7080,12 @@
         <v>506</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>507</v>
@@ -7091,12 +7094,12 @@
         <v>508</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>509</v>
@@ -7105,12 +7108,12 @@
         <v>510</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>511</v>
@@ -7119,12 +7122,12 @@
         <v>512</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>513</v>
@@ -7133,12 +7136,12 @@
         <v>514</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>515</v>
@@ -7147,12 +7150,12 @@
         <v>516</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>517</v>
@@ -7161,12 +7164,12 @@
         <v>518</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>519</v>
@@ -7175,12 +7178,12 @@
         <v>520</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>521</v>
@@ -7189,12 +7192,12 @@
         <v>522</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>523</v>
@@ -7203,12 +7206,12 @@
         <v>524</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>525</v>
@@ -7217,12 +7220,12 @@
         <v>526</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>527</v>
@@ -7231,12 +7234,12 @@
         <v>528</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>529</v>
@@ -7245,12 +7248,12 @@
         <v>530</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>531</v>
@@ -7259,12 +7262,12 @@
         <v>532</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>533</v>
@@ -7273,12 +7276,12 @@
         <v>534</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>535</v>
@@ -7287,12 +7290,12 @@
         <v>536</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>537</v>
@@ -7301,12 +7304,12 @@
         <v>538</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>539</v>
@@ -7315,12 +7318,12 @@
         <v>540</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>541</v>
@@ -7329,12 +7332,12 @@
         <v>542</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>543</v>
@@ -7343,12 +7346,12 @@
         <v>544</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>545</v>
@@ -7357,12 +7360,12 @@
         <v>546</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>547</v>
@@ -7371,12 +7374,12 @@
         <v>548</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>549</v>
@@ -7385,12 +7388,12 @@
         <v>550</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>551</v>
@@ -7399,12 +7402,12 @@
         <v>552</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>553</v>
@@ -7413,12 +7416,12 @@
         <v>554</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>555</v>
@@ -7427,12 +7430,12 @@
         <v>556</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>557</v>
@@ -7441,12 +7444,12 @@
         <v>558</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>559</v>
@@ -7455,12 +7458,12 @@
         <v>560</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>561</v>
@@ -7469,12 +7472,12 @@
         <v>562</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>563</v>
@@ -7483,12 +7486,12 @@
         <v>564</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>565</v>
@@ -7497,12 +7500,12 @@
         <v>566</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>567</v>
@@ -7511,12 +7514,12 @@
         <v>568</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>569</v>
@@ -7525,12 +7528,12 @@
         <v>570</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>571</v>
@@ -7539,12 +7542,12 @@
         <v>572</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>573</v>
@@ -7553,12 +7556,12 @@
         <v>574</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>575</v>
@@ -7567,12 +7570,12 @@
         <v>576</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>577</v>
@@ -7581,12 +7584,12 @@
         <v>578</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>579</v>
@@ -7595,12 +7598,12 @@
         <v>580</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>581</v>
@@ -7609,12 +7612,12 @@
         <v>582</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>583</v>
@@ -7623,12 +7626,12 @@
         <v>584</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>585</v>
@@ -7637,12 +7640,12 @@
         <v>586</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>587</v>
@@ -7651,12 +7654,12 @@
         <v>588</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>589</v>
@@ -7665,12 +7668,12 @@
         <v>590</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>591</v>
@@ -7679,12 +7682,12 @@
         <v>592</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>593</v>
@@ -7693,12 +7696,12 @@
         <v>594</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>595</v>
@@ -7707,12 +7710,12 @@
         <v>596</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>597</v>
@@ -7721,12 +7724,12 @@
         <v>598</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>599</v>
@@ -7735,12 +7738,12 @@
         <v>600</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>601</v>
@@ -7749,12 +7752,12 @@
         <v>602</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>603</v>
@@ -7763,12 +7766,12 @@
         <v>604</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>605</v>
@@ -7777,12 +7780,12 @@
         <v>606</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>607</v>
@@ -7791,12 +7794,12 @@
         <v>608</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>609</v>
@@ -7805,12 +7808,12 @@
         <v>610</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>611</v>
@@ -7819,12 +7822,12 @@
         <v>612</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>613</v>
@@ -7833,12 +7836,12 @@
         <v>614</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>615</v>
@@ -7847,12 +7850,12 @@
         <v>616</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>617</v>
@@ -7861,12 +7864,12 @@
         <v>618</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>619</v>
@@ -7875,12 +7878,12 @@
         <v>620</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>621</v>
@@ -7889,12 +7892,12 @@
         <v>622</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>623</v>
@@ -7903,12 +7906,12 @@
         <v>624</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>625</v>
@@ -7917,12 +7920,12 @@
         <v>626</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>627</v>
@@ -7931,12 +7934,12 @@
         <v>628</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>629</v>
@@ -7945,12 +7948,12 @@
         <v>630</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>631</v>
@@ -7959,12 +7962,12 @@
         <v>632</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>633</v>
@@ -7973,12 +7976,12 @@
         <v>634</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>635</v>
@@ -7987,12 +7990,12 @@
         <v>636</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>637</v>
@@ -8001,12 +8004,12 @@
         <v>638</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>639</v>
@@ -8015,12 +8018,12 @@
         <v>640</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>641</v>
@@ -8029,12 +8032,12 @@
         <v>642</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>643</v>
@@ -8043,12 +8046,12 @@
         <v>644</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>645</v>
@@ -8057,12 +8060,12 @@
         <v>646</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>647</v>
@@ -8071,12 +8074,12 @@
         <v>648</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>649</v>
@@ -8085,12 +8088,12 @@
         <v>650</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>651</v>
@@ -8099,12 +8102,12 @@
         <v>652</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>653</v>
@@ -8113,12 +8116,12 @@
         <v>654</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>655</v>
@@ -8127,12 +8130,12 @@
         <v>656</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>657</v>
@@ -8141,12 +8144,12 @@
         <v>658</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>659</v>
@@ -8155,12 +8158,12 @@
         <v>660</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>661</v>
@@ -8169,12 +8172,12 @@
         <v>662</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>663</v>
@@ -8183,12 +8186,12 @@
         <v>664</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>665</v>
@@ -8197,12 +8200,12 @@
         <v>666</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>667</v>
@@ -8211,12 +8214,12 @@
         <v>668</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>669</v>
@@ -8225,12 +8228,12 @@
         <v>670</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>671</v>
@@ -8239,12 +8242,12 @@
         <v>672</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>673</v>
@@ -8253,12 +8256,12 @@
         <v>674</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>675</v>
@@ -8267,12 +8270,12 @@
         <v>676</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>677</v>
@@ -8281,12 +8284,12 @@
         <v>678</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>679</v>
@@ -8295,12 +8298,12 @@
         <v>680</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>681</v>
@@ -8309,12 +8312,12 @@
         <v>682</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>683</v>
@@ -8323,12 +8326,12 @@
         <v>684</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>685</v>
@@ -8337,12 +8340,12 @@
         <v>686</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>687</v>
@@ -8351,12 +8354,12 @@
         <v>688</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>689</v>
@@ -8365,12 +8368,12 @@
         <v>690</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>691</v>
@@ -8379,12 +8382,12 @@
         <v>692</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>693</v>
@@ -8393,12 +8396,12 @@
         <v>694</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>695</v>
@@ -8407,12 +8410,12 @@
         <v>696</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>697</v>
@@ -8421,12 +8424,12 @@
         <v>698</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>699</v>
@@ -8435,12 +8438,12 @@
         <v>700</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>701</v>
@@ -8449,12 +8452,12 @@
         <v>702</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>703</v>
@@ -8463,12 +8466,12 @@
         <v>704</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>705</v>
@@ -8477,12 +8480,12 @@
         <v>706</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>707</v>
@@ -8491,12 +8494,12 @@
         <v>708</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>709</v>
@@ -8505,12 +8508,12 @@
         <v>710</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>711</v>
@@ -8519,12 +8522,12 @@
         <v>712</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>713</v>
@@ -8533,12 +8536,12 @@
         <v>714</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>715</v>
@@ -8547,12 +8550,12 @@
         <v>716</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>717</v>
@@ -8561,12 +8564,12 @@
         <v>718</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>719</v>
@@ -8575,12 +8578,12 @@
         <v>720</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>721</v>
@@ -8589,12 +8592,12 @@
         <v>722</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>723</v>
@@ -8603,12 +8606,12 @@
         <v>724</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>725</v>
@@ -8617,12 +8620,12 @@
         <v>726</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>727</v>
@@ -8631,12 +8634,12 @@
         <v>728</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>729</v>
@@ -8645,12 +8648,12 @@
         <v>730</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>731</v>
@@ -8659,12 +8662,12 @@
         <v>732</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>733</v>
@@ -8673,12 +8676,12 @@
         <v>734</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>735</v>
@@ -8687,12 +8690,12 @@
         <v>736</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>737</v>
@@ -8701,26 +8704,26 @@
         <v>738</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>739</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>740</v>
@@ -8729,12 +8732,12 @@
         <v>741</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>742</v>
@@ -8743,12 +8746,12 @@
         <v>743</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>744</v>
@@ -8757,68 +8760,68 @@
         <v>745</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>744</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>740</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>742</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>746</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>746</v>
@@ -8827,12 +8830,12 @@
         <v>747</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>748</v>
@@ -8841,12 +8844,12 @@
         <v>791</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>749</v>
@@ -8855,12 +8858,12 @@
         <v>813</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>750</v>
@@ -8869,12 +8872,12 @@
         <v>790</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>751</v>
@@ -8883,12 +8886,12 @@
         <v>810</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>753</v>
@@ -8897,26 +8900,26 @@
         <v>803</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>754</v>
       </c>
       <c r="C390" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>755</v>
@@ -8925,12 +8928,12 @@
         <v>802</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>756</v>
@@ -8939,12 +8942,12 @@
         <v>793</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>757</v>
@@ -8953,12 +8956,12 @@
         <v>800</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>758</v>
@@ -8967,12 +8970,12 @@
         <v>752</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>759</v>
@@ -8981,12 +8984,12 @@
         <v>806</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>760</v>
@@ -8995,12 +8998,12 @@
         <v>808</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>761</v>
@@ -9009,12 +9012,12 @@
         <v>752</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>762</v>
@@ -9023,12 +9026,12 @@
         <v>763</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>764</v>
@@ -9037,26 +9040,26 @@
         <v>812</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>765</v>
       </c>
       <c r="C400" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>766</v>
@@ -9065,12 +9068,12 @@
         <v>794</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>767</v>
@@ -9079,12 +9082,12 @@
         <v>815</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>768</v>
@@ -9093,12 +9096,12 @@
         <v>795</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>769</v>
@@ -9107,12 +9110,12 @@
         <v>841</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>770</v>
@@ -9121,12 +9124,12 @@
         <v>811</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>771</v>
@@ -9135,12 +9138,12 @@
         <v>798</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>772</v>
@@ -9149,12 +9152,12 @@
         <v>796</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>773</v>
@@ -9163,12 +9166,12 @@
         <v>805</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>775</v>
@@ -9177,12 +9180,12 @@
         <v>814</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>776</v>
@@ -9191,12 +9194,12 @@
         <v>774</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>777</v>
@@ -9205,12 +9208,12 @@
         <v>774</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>778</v>
@@ -9219,12 +9222,12 @@
         <v>774</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>779</v>
@@ -9233,12 +9236,12 @@
         <v>774</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>780</v>
@@ -9247,12 +9250,12 @@
         <v>807</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>781</v>
@@ -9261,12 +9264,12 @@
         <v>797</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>782</v>
@@ -9275,12 +9278,12 @@
         <v>792</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>783</v>
@@ -9289,12 +9292,12 @@
         <v>809</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>784</v>
@@ -9303,26 +9306,26 @@
         <v>804</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B419" t="s">
         <v>786</v>
       </c>
       <c r="C419" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>787</v>
@@ -9331,12 +9334,12 @@
         <v>799</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>788</v>
@@ -9345,12 +9348,12 @@
         <v>801</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>789</v>
@@ -9359,23 +9362,23 @@
         <v>785</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>816</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>829</v>
@@ -9384,12 +9387,12 @@
         <v>817</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>830</v>
@@ -9398,12 +9401,12 @@
         <v>818</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>831</v>
@@ -9412,12 +9415,12 @@
         <v>819</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>832</v>
@@ -9426,12 +9429,12 @@
         <v>820</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>833</v>
@@ -9440,12 +9443,12 @@
         <v>821</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>834</v>
@@ -9454,12 +9457,12 @@
         <v>822</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>835</v>
@@ -9468,12 +9471,12 @@
         <v>823</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>836</v>
@@ -9482,12 +9485,12 @@
         <v>824</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>837</v>
@@ -9496,12 +9499,12 @@
         <v>825</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>838</v>
@@ -9510,12 +9513,12 @@
         <v>826</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>839</v>
@@ -9524,12 +9527,12 @@
         <v>827</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>840</v>
@@ -9538,7 +9541,7 @@
         <v>828</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -9549,10 +9552,10 @@
         <v>846</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -9566,7 +9569,7 @@
         <v>850</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -9580,7 +9583,7 @@
         <v>848</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -9594,7 +9597,7 @@
         <v>849</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -9608,7 +9611,7 @@
         <v>851</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -9622,7 +9625,7 @@
         <v>852</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -9636,12 +9639,12 @@
         <v>873</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B443" s="1">
         <v>3</v>
@@ -9650,7 +9653,7 @@
         <v>854</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>853</v>
@@ -9658,13 +9661,13 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>856</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>855</v>
@@ -9672,7 +9675,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>859</v>
@@ -9681,7 +9684,7 @@
         <v>858</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>857</v>
@@ -9689,7 +9692,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>862</v>
@@ -9698,7 +9701,7 @@
         <v>861</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>860</v>
@@ -9706,7 +9709,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>863</v>
@@ -9715,15 +9718,15 @@
         <v>865</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>51</v>
@@ -9732,7 +9735,7 @@
         <v>866</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>864</v>
@@ -9740,7 +9743,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>174</v>
@@ -9749,7 +9752,7 @@
         <v>867</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>868</v>
@@ -9757,7 +9760,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>177</v>
@@ -9766,7 +9769,7 @@
         <v>870</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>869</v>
@@ -9774,13 +9777,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>871</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>872</v>
@@ -9788,97 +9791,97 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>884</v>
+        <v>883</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
+        <v>883</v>
+      </c>
+      <c r="B453" t="s">
+        <v>886</v>
+      </c>
+      <c r="C453" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="B453" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>877</v>
-      </c>
       <c r="D453" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>884</v>
-      </c>
-      <c r="B454" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>893</v>
+        <v>869</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>884</v>
+        <v>995</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>1008</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>898</v>
+        <v>996</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="E457" s="1" t="s">
-        <v>869</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>1009</v>
@@ -9887,40 +9890,40 @@
         <v>997</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>998</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>999</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>1011</v>
@@ -9929,12 +9932,12 @@
         <v>1000</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>1012</v>
@@ -9943,12 +9946,12 @@
         <v>1001</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1013</v>
@@ -9957,12 +9960,12 @@
         <v>1002</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>1014</v>
@@ -9971,12 +9974,12 @@
         <v>1003</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>1015</v>
@@ -9985,26 +9988,26 @@
         <v>1004</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>1005</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>1018</v>
@@ -10013,12 +10016,12 @@
         <v>1006</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>1019</v>
@@ -10027,21 +10030,21 @@
         <v>1007</v>
       </c>
       <c r="D468" s="1" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" s="1" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
-        <v>996</v>
-      </c>
       <c r="B469" s="1" t="s">
-        <v>1020</v>
+        <v>181</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1008</v>
+        <v>875</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE68E18-3231-4427-9116-A9B3CC54F4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD42553-3804-4DD3-B6CD-C86E0E912E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="1025">
   <si>
     <t>Company</t>
   </si>
@@ -3089,6 +3089,12 @@
   </si>
   <si>
     <t>104698653</t>
+  </si>
+  <si>
+    <t>СВ0495СО</t>
+  </si>
+  <si>
+    <t>78970152027720136</t>
   </si>
 </sst>
 </file>
@@ -3447,7 +3453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E469"/>
+  <dimension ref="A1:E470"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.42578125" bestFit="1" customWidth="1"/>
@@ -8093,13 +8099,13 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>651</v>
+        <v>1023</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>652</v>
+        <v>1024</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>977</v>
@@ -8110,10 +8116,10 @@
         <v>974</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>977</v>
@@ -8124,10 +8130,10 @@
         <v>974</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>977</v>
@@ -8138,10 +8144,10 @@
         <v>974</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>977</v>
@@ -8152,10 +8158,10 @@
         <v>974</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>977</v>
@@ -8166,10 +8172,10 @@
         <v>974</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>977</v>
@@ -8180,10 +8186,10 @@
         <v>974</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>977</v>
@@ -8194,10 +8200,10 @@
         <v>974</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>977</v>
@@ -8205,16 +8211,16 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -8222,10 +8228,10 @@
         <v>976</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>978</v>
@@ -8236,10 +8242,10 @@
         <v>976</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>978</v>
@@ -8250,10 +8256,10 @@
         <v>976</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>978</v>
@@ -8261,16 +8267,16 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -8278,10 +8284,10 @@
         <v>979</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>990</v>
@@ -8292,10 +8298,10 @@
         <v>979</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>990</v>
@@ -8306,10 +8312,10 @@
         <v>979</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>990</v>
@@ -8320,10 +8326,10 @@
         <v>979</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>990</v>
@@ -8334,10 +8340,10 @@
         <v>979</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>990</v>
@@ -8348,10 +8354,10 @@
         <v>979</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>990</v>
@@ -8362,10 +8368,10 @@
         <v>979</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>990</v>
@@ -8376,10 +8382,10 @@
         <v>979</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>990</v>
@@ -8390,10 +8396,10 @@
         <v>979</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>990</v>
@@ -8404,10 +8410,10 @@
         <v>979</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>990</v>
@@ -8418,10 +8424,10 @@
         <v>979</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>990</v>
@@ -8432,10 +8438,10 @@
         <v>979</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>990</v>
@@ -8446,10 +8452,10 @@
         <v>979</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>990</v>
@@ -8460,10 +8466,10 @@
         <v>979</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>990</v>
@@ -8474,10 +8480,10 @@
         <v>979</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>990</v>
@@ -8485,13 +8491,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>990</v>
@@ -8502,10 +8508,10 @@
         <v>980</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>990</v>
@@ -8516,10 +8522,10 @@
         <v>980</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>990</v>
@@ -8530,10 +8536,10 @@
         <v>980</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>990</v>
@@ -8544,10 +8550,10 @@
         <v>980</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>990</v>
@@ -8558,10 +8564,10 @@
         <v>980</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>990</v>
@@ -8572,10 +8578,10 @@
         <v>980</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>990</v>
@@ -8586,10 +8592,10 @@
         <v>980</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>990</v>
@@ -8600,10 +8606,10 @@
         <v>980</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>990</v>
@@ -8614,10 +8620,10 @@
         <v>980</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>990</v>
@@ -8628,10 +8634,10 @@
         <v>980</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>990</v>
@@ -8642,10 +8648,10 @@
         <v>980</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>990</v>
@@ -8656,10 +8662,10 @@
         <v>980</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>990</v>
@@ -8670,10 +8676,10 @@
         <v>980</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>990</v>
@@ -8684,10 +8690,10 @@
         <v>980</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>990</v>
@@ -8698,10 +8704,10 @@
         <v>980</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>990</v>
@@ -8709,27 +8715,27 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>896</v>
+        <v>738</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>741</v>
+        <v>896</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>989</v>
@@ -8740,10 +8746,10 @@
         <v>987</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>989</v>
@@ -8754,10 +8760,10 @@
         <v>987</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>989</v>
@@ -8771,7 +8777,7 @@
         <v>744</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>878</v>
+        <v>745</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>989</v>
@@ -8782,10 +8788,10 @@
         <v>987</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>989</v>
@@ -8796,10 +8802,10 @@
         <v>987</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>989</v>
@@ -8807,13 +8813,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>989</v>
@@ -8827,7 +8833,7 @@
         <v>746</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>747</v>
+        <v>881</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>989</v>
@@ -8835,16 +8841,16 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>791</v>
+        <v>747</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -8852,10 +8858,10 @@
         <v>981</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>991</v>
@@ -8866,10 +8872,10 @@
         <v>981</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>790</v>
+        <v>813</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>991</v>
@@ -8880,10 +8886,10 @@
         <v>981</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>991</v>
@@ -8894,10 +8900,10 @@
         <v>981</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>991</v>
@@ -8908,10 +8914,10 @@
         <v>981</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C390" t="s">
-        <v>902</v>
+        <v>753</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>991</v>
@@ -8922,10 +8928,10 @@
         <v>981</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C391" s="2" t="s">
-        <v>802</v>
+        <v>754</v>
+      </c>
+      <c r="C391" t="s">
+        <v>902</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>991</v>
@@ -8936,10 +8942,10 @@
         <v>981</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>991</v>
@@ -8950,10 +8956,10 @@
         <v>981</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>991</v>
@@ -8964,10 +8970,10 @@
         <v>981</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>752</v>
+        <v>800</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>991</v>
@@ -8978,10 +8984,10 @@
         <v>981</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>806</v>
+        <v>752</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>991</v>
@@ -8992,10 +8998,10 @@
         <v>981</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>991</v>
@@ -9006,10 +9012,10 @@
         <v>981</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>991</v>
@@ -9020,10 +9026,10 @@
         <v>981</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>991</v>
@@ -9034,10 +9040,10 @@
         <v>981</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>812</v>
+        <v>763</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>991</v>
@@ -9048,10 +9054,10 @@
         <v>981</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="C400" t="s">
-        <v>901</v>
+        <v>764</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>812</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>991</v>
@@ -9062,10 +9068,10 @@
         <v>981</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>794</v>
+        <v>765</v>
+      </c>
+      <c r="C401" t="s">
+        <v>901</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>991</v>
@@ -9076,10 +9082,10 @@
         <v>981</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>991</v>
@@ -9090,10 +9096,10 @@
         <v>981</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>991</v>
@@ -9104,10 +9110,10 @@
         <v>981</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>841</v>
+        <v>795</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>991</v>
@@ -9118,10 +9124,10 @@
         <v>981</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>991</v>
@@ -9132,10 +9138,10 @@
         <v>981</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>991</v>
@@ -9146,10 +9152,10 @@
         <v>981</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>991</v>
@@ -9160,10 +9166,10 @@
         <v>981</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>991</v>
@@ -9174,10 +9180,10 @@
         <v>981</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>991</v>
@@ -9188,10 +9194,10 @@
         <v>981</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="D410" s="1" t="s">
         <v>991</v>
@@ -9202,7 +9208,7 @@
         <v>981</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>774</v>
@@ -9216,7 +9222,7 @@
         <v>981</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>774</v>
@@ -9230,7 +9236,7 @@
         <v>981</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>774</v>
@@ -9244,10 +9250,10 @@
         <v>981</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>807</v>
+        <v>774</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>991</v>
@@ -9258,10 +9264,10 @@
         <v>981</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>991</v>
@@ -9272,10 +9278,10 @@
         <v>981</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>991</v>
@@ -9286,10 +9292,10 @@
         <v>981</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>991</v>
@@ -9300,10 +9306,10 @@
         <v>981</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>991</v>
@@ -9313,11 +9319,11 @@
       <c r="A419" t="s">
         <v>981</v>
       </c>
-      <c r="B419" t="s">
-        <v>786</v>
-      </c>
-      <c r="C419" t="s">
-        <v>899</v>
+      <c r="B419" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>804</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>991</v>
@@ -9327,11 +9333,11 @@
       <c r="A420" t="s">
         <v>981</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C420" s="2" t="s">
-        <v>799</v>
+      <c r="B420" t="s">
+        <v>786</v>
+      </c>
+      <c r="C420" t="s">
+        <v>899</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>991</v>
@@ -9342,10 +9348,10 @@
         <v>981</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>991</v>
@@ -9356,10 +9362,10 @@
         <v>981</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>991</v>
@@ -9369,8 +9375,11 @@
       <c r="A423" t="s">
         <v>981</v>
       </c>
+      <c r="B423" s="1" t="s">
+        <v>789</v>
+      </c>
       <c r="C423" s="2" t="s">
-        <v>816</v>
+        <v>785</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>991</v>
@@ -9378,16 +9387,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>982</v>
-      </c>
-      <c r="B424" s="3" t="s">
-        <v>829</v>
+        <v>981</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -9395,10 +9401,10 @@
         <v>982</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>983</v>
@@ -9409,10 +9415,10 @@
         <v>982</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D426" s="1" t="s">
         <v>983</v>
@@ -9423,10 +9429,10 @@
         <v>982</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>983</v>
@@ -9437,10 +9443,10 @@
         <v>982</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>983</v>
@@ -9451,10 +9457,10 @@
         <v>982</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>983</v>
@@ -9465,10 +9471,10 @@
         <v>982</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>983</v>
@@ -9479,10 +9485,10 @@
         <v>982</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>983</v>
@@ -9493,10 +9499,10 @@
         <v>982</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>983</v>
@@ -9507,10 +9513,10 @@
         <v>982</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>983</v>
@@ -9521,10 +9527,10 @@
         <v>982</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>983</v>
@@ -9535,10 +9541,10 @@
         <v>982</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>983</v>
@@ -9546,16 +9552,16 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>842</v>
-      </c>
-      <c r="B436" s="1" t="s">
-        <v>846</v>
+        <v>982</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>840</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>887</v>
+        <v>828</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -9563,10 +9569,10 @@
         <v>842</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>850</v>
+        <v>887</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>984</v>
@@ -9577,10 +9583,10 @@
         <v>842</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>984</v>
@@ -9591,10 +9597,10 @@
         <v>842</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>984</v>
@@ -9605,10 +9611,10 @@
         <v>842</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>984</v>
@@ -9619,10 +9625,10 @@
         <v>842</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>984</v>
@@ -9633,10 +9639,10 @@
         <v>842</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>984</v>
@@ -9644,50 +9650,47 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>883</v>
-      </c>
-      <c r="B443" s="1">
-        <v>3</v>
+        <v>842</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>874</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>853</v>
+        <v>984</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>883</v>
       </c>
+      <c r="B444" s="1">
+        <v>3</v>
+      </c>
       <c r="C444" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>883</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>859</v>
-      </c>
       <c r="C445" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -9695,16 +9698,16 @@
         <v>883</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -9712,16 +9715,16 @@
         <v>883</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -9729,16 +9732,16 @@
         <v>883</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>51</v>
+        <v>863</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -9746,16 +9749,16 @@
         <v>883</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -9763,78 +9766,81 @@
         <v>883</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>883</v>
       </c>
+      <c r="B451" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="C451" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>883</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C452" s="2" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>883</v>
       </c>
-      <c r="B453" t="s">
-        <v>886</v>
+      <c r="B453" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>883</v>
       </c>
+      <c r="B454" t="s">
+        <v>886</v>
+      </c>
       <c r="C454" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -9842,13 +9848,13 @@
         <v>883</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -9856,27 +9862,27 @@
         <v>883</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>985</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>869</v>
+        <v>892</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>995</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>1008</v>
+        <v>883</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>996</v>
+        <v>897</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>1020</v>
+        <v>985</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -9884,10 +9890,10 @@
         <v>995</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>1020</v>
@@ -9898,10 +9904,10 @@
         <v>995</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>1020</v>
@@ -9912,10 +9918,10 @@
         <v>995</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>1020</v>
@@ -9926,10 +9932,10 @@
         <v>995</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D461" s="1" t="s">
         <v>1020</v>
@@ -9940,10 +9946,10 @@
         <v>995</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D462" s="1" t="s">
         <v>1020</v>
@@ -9954,10 +9960,10 @@
         <v>995</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D463" s="1" t="s">
         <v>1020</v>
@@ -9968,10 +9974,10 @@
         <v>995</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D464" s="1" t="s">
         <v>1020</v>
@@ -9982,10 +9988,10 @@
         <v>995</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D465" s="1" t="s">
         <v>1020</v>
@@ -9996,10 +10002,10 @@
         <v>995</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D466" s="1" t="s">
         <v>1020</v>
@@ -10010,10 +10016,10 @@
         <v>995</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D467" s="1" t="s">
         <v>1020</v>
@@ -10024,26 +10030,40 @@
         <v>995</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D468" s="1" t="s">
         <v>1020</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="1" t="s">
+      <c r="A469" t="s">
+        <v>995</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="B469" s="1" t="s">
+      <c r="B470" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C469" s="2" t="s">
+      <c r="C470" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="D469" s="1" t="s">
+      <c r="D470" s="1" t="s">
         <v>1022</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD42553-3804-4DD3-B6CD-C86E0E912E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE76C77-584A-40B7-B568-15289063413D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C223BE-BD94-4D92-8986-21FBF1F0F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB85560-2D49-422C-97E4-DFB430093D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB85560-2D49-422C-97E4-DFB430093D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1D7669-2A61-41D5-9D49-7BF0A48D8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1D7669-2A61-41D5-9D49-7BF0A48D8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0E0593-B36D-4114-8B6B-F94D5D848208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2759" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="1549">
   <si>
     <t>Company</t>
   </si>
@@ -4481,6 +4481,192 @@
   </si>
   <si>
     <t>0000934420042</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО % 1</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО % 2</t>
+  </si>
+  <si>
+    <t>В 6613 КС</t>
+  </si>
+  <si>
+    <t>В 9933 СМ</t>
+  </si>
+  <si>
+    <t>В 8636 СТ</t>
+  </si>
+  <si>
+    <t>В 3762 РА</t>
+  </si>
+  <si>
+    <t>В 9922 РА</t>
+  </si>
+  <si>
+    <t>В 4685 РС</t>
+  </si>
+  <si>
+    <t>В 2278 РВ</t>
+  </si>
+  <si>
+    <t>В 4692 РС</t>
+  </si>
+  <si>
+    <t>В 1839 ТМ</t>
+  </si>
+  <si>
+    <t>В 5328 РМ</t>
+  </si>
+  <si>
+    <t>В 5116 РС</t>
+  </si>
+  <si>
+    <t>В 5117 РС</t>
+  </si>
+  <si>
+    <t>В 6476 ВС</t>
+  </si>
+  <si>
+    <t>В 6915 ВХ</t>
+  </si>
+  <si>
+    <t>В 5654 ВН</t>
+  </si>
+  <si>
+    <t>В 3535 СТ</t>
+  </si>
+  <si>
+    <t>В 4239 ВТ</t>
+  </si>
+  <si>
+    <t>В 1283 НТ</t>
+  </si>
+  <si>
+    <t>В 9999 РX</t>
+  </si>
+  <si>
+    <t>В 6431 НР</t>
+  </si>
+  <si>
+    <t>В 5119 РС</t>
+  </si>
+  <si>
+    <t>В 5163ХВ</t>
+  </si>
+  <si>
+    <t>В 5089 РВ</t>
+  </si>
+  <si>
+    <t>В 7341 ВС</t>
+  </si>
+  <si>
+    <t>В 2429 ТТ</t>
+  </si>
+  <si>
+    <t>B 6947 НТ</t>
+  </si>
+  <si>
+    <t>В 6196 РС</t>
+  </si>
+  <si>
+    <t>В 1293 НН</t>
+  </si>
+  <si>
+    <t>В 09 805</t>
+  </si>
+  <si>
+    <t>ТУБА</t>
+  </si>
+  <si>
+    <t>78970155027722168</t>
+  </si>
+  <si>
+    <t>78970155027722176</t>
+  </si>
+  <si>
+    <t>78970155027722184</t>
+  </si>
+  <si>
+    <t>78970155027722192</t>
+  </si>
+  <si>
+    <t>78970155027722200</t>
+  </si>
+  <si>
+    <t>78970155027722218</t>
+  </si>
+  <si>
+    <t>78970155027722226</t>
+  </si>
+  <si>
+    <t>78970155027722234</t>
+  </si>
+  <si>
+    <t>78970155027722242</t>
+  </si>
+  <si>
+    <t>78970155027722259</t>
+  </si>
+  <si>
+    <t>78970155027722267</t>
+  </si>
+  <si>
+    <t>78970155027722275</t>
+  </si>
+  <si>
+    <t>78970155027722283</t>
+  </si>
+  <si>
+    <t>78970155027722291</t>
+  </si>
+  <si>
+    <t>78970155027722309</t>
+  </si>
+  <si>
+    <t>78970155027722317</t>
+  </si>
+  <si>
+    <t>78970155027722325</t>
+  </si>
+  <si>
+    <t>78970155027722333</t>
+  </si>
+  <si>
+    <t>78970155027722341</t>
+  </si>
+  <si>
+    <t>78970155027722358</t>
+  </si>
+  <si>
+    <t>78970155027722366</t>
+  </si>
+  <si>
+    <t>78970155027722374</t>
+  </si>
+  <si>
+    <t>78970155027722382</t>
+  </si>
+  <si>
+    <t>78970155027722390</t>
+  </si>
+  <si>
+    <t>78970155027722408</t>
+  </si>
+  <si>
+    <t>78970155027722416</t>
+  </si>
+  <si>
+    <t>78970155027722424</t>
+  </si>
+  <si>
+    <t>78970155027722432</t>
+  </si>
+  <si>
+    <t>78970155027722440</t>
+  </si>
+  <si>
+    <t>78970155027722457</t>
   </si>
 </sst>
 </file>
@@ -4529,7 +4715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4549,6 +4735,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4852,7 +5041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E688"/>
+  <dimension ref="A1:E718"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" bestFit="1" customWidth="1"/>
@@ -14518,6 +14707,336 @@
         <v>1486</v>
       </c>
     </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C689" s="8" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C690" s="8" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C691" s="8" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C692" s="8" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C693" s="8" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C694" s="8" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C695" s="8" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C696" s="8" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C697" s="8" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C698" s="8" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C699" s="8" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C700" s="8" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C701" s="8" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C702" s="8" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C703" s="8" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C704" s="8" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C705" s="8" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C706" s="8" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C707" s="8" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C708" s="8" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C709" s="8" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C710" s="8" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C711" s="8" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C712" s="8" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C713" s="8" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C714" s="8" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C715" s="8" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C716" s="8" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C717" s="8" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C718" s="8" t="s">
+        <v>1548</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0E0593-B36D-4114-8B6B-F94D5D848208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C5E5B3-FCA9-4E3D-A520-563599CCA168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="1549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="1550">
   <si>
     <t>Company</t>
   </si>
@@ -4489,93 +4489,6 @@
     <t>ОБЩИНА АКСАКОВО % 2</t>
   </si>
   <si>
-    <t>В 6613 КС</t>
-  </si>
-  <si>
-    <t>В 9933 СМ</t>
-  </si>
-  <si>
-    <t>В 8636 СТ</t>
-  </si>
-  <si>
-    <t>В 3762 РА</t>
-  </si>
-  <si>
-    <t>В 9922 РА</t>
-  </si>
-  <si>
-    <t>В 4685 РС</t>
-  </si>
-  <si>
-    <t>В 2278 РВ</t>
-  </si>
-  <si>
-    <t>В 4692 РС</t>
-  </si>
-  <si>
-    <t>В 1839 ТМ</t>
-  </si>
-  <si>
-    <t>В 5328 РМ</t>
-  </si>
-  <si>
-    <t>В 5116 РС</t>
-  </si>
-  <si>
-    <t>В 5117 РС</t>
-  </si>
-  <si>
-    <t>В 6476 ВС</t>
-  </si>
-  <si>
-    <t>В 6915 ВХ</t>
-  </si>
-  <si>
-    <t>В 5654 ВН</t>
-  </si>
-  <si>
-    <t>В 3535 СТ</t>
-  </si>
-  <si>
-    <t>В 4239 ВТ</t>
-  </si>
-  <si>
-    <t>В 1283 НТ</t>
-  </si>
-  <si>
-    <t>В 9999 РX</t>
-  </si>
-  <si>
-    <t>В 6431 НР</t>
-  </si>
-  <si>
-    <t>В 5119 РС</t>
-  </si>
-  <si>
-    <t>В 5163ХВ</t>
-  </si>
-  <si>
-    <t>В 5089 РВ</t>
-  </si>
-  <si>
-    <t>В 7341 ВС</t>
-  </si>
-  <si>
-    <t>В 2429 ТТ</t>
-  </si>
-  <si>
-    <t>B 6947 НТ</t>
-  </si>
-  <si>
-    <t>В 6196 РС</t>
-  </si>
-  <si>
-    <t>В 1293 НН</t>
-  </si>
-  <si>
-    <t>В 09 805</t>
-  </si>
-  <si>
     <t>ТУБА</t>
   </si>
   <si>
@@ -4667,6 +4580,96 @@
   </si>
   <si>
     <t>78970155027722457</t>
+  </si>
+  <si>
+    <t>В6613КС</t>
+  </si>
+  <si>
+    <t>В9933СМ</t>
+  </si>
+  <si>
+    <t>В8636СТ</t>
+  </si>
+  <si>
+    <t>В3762РА</t>
+  </si>
+  <si>
+    <t>В9922РА</t>
+  </si>
+  <si>
+    <t>В4685РС</t>
+  </si>
+  <si>
+    <t>В2278РВ</t>
+  </si>
+  <si>
+    <t>В4692РС</t>
+  </si>
+  <si>
+    <t>В1839ТМ</t>
+  </si>
+  <si>
+    <t>В5328РМ</t>
+  </si>
+  <si>
+    <t>В5116РС</t>
+  </si>
+  <si>
+    <t>В5117РС</t>
+  </si>
+  <si>
+    <t>В6476ВС</t>
+  </si>
+  <si>
+    <t>В6915ВХ</t>
+  </si>
+  <si>
+    <t>В5654ВН</t>
+  </si>
+  <si>
+    <t>В3535СТ</t>
+  </si>
+  <si>
+    <t>В4239ВТ</t>
+  </si>
+  <si>
+    <t>В1283НТ</t>
+  </si>
+  <si>
+    <t>В9999РX</t>
+  </si>
+  <si>
+    <t>В6431НР</t>
+  </si>
+  <si>
+    <t>В5119РС</t>
+  </si>
+  <si>
+    <t>В5163ХВ</t>
+  </si>
+  <si>
+    <t>В5089РВ</t>
+  </si>
+  <si>
+    <t>В7341ВС</t>
+  </si>
+  <si>
+    <t>В2429ТТ</t>
+  </si>
+  <si>
+    <t>B6947НТ</t>
+  </si>
+  <si>
+    <t>В6196РС</t>
+  </si>
+  <si>
+    <t>В1293НН</t>
+  </si>
+  <si>
+    <t>В09805</t>
+  </si>
+  <si>
+    <t>000093385</t>
   </si>
 </sst>
 </file>
@@ -4715,7 +4718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4735,9 +4738,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14707,334 +14707,424 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>1487</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C689" s="8" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1520</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D689" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>1487</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C690" s="8" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1521</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D690" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1487</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1491</v>
-      </c>
-      <c r="C691" s="8" t="s">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1522</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D691" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>1487</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C692" s="8" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1523</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D692" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>1487</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C693" s="8" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1524</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D693" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1487</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C694" s="8" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1525</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D694" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>1487</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C695" s="8" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1526</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D695" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1487</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1496</v>
-      </c>
-      <c r="C696" s="8" t="s">
-        <v>1526</v>
-      </c>
-    </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1527</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D696" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>1487</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1497</v>
-      </c>
-      <c r="C697" s="8" t="s">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1528</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D697" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>1487</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C698" s="8" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1529</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D698" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>1487</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C699" s="8" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1530</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D699" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>1487</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1500</v>
-      </c>
-      <c r="C700" s="8" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1531</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D700" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>1487</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1501</v>
-      </c>
-      <c r="C701" s="8" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1532</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D701" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>1487</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C702" s="8" t="s">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1533</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D702" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>1487</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C703" s="8" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1534</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D703" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>1487</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1504</v>
-      </c>
-      <c r="C704" s="8" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1535</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D704" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>1487</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C705" s="8" t="s">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1536</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D705" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>1487</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C706" s="8" t="s">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1537</v>
+      </c>
+      <c r="C706" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D706" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>1487</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C707" s="8" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1538</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D707" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>1487</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C708" s="8" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1539</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D708" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>1487</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1509</v>
-      </c>
-      <c r="C709" s="8" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1540</v>
+      </c>
+      <c r="C709" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>1487</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1510</v>
-      </c>
-      <c r="C710" s="8" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1541</v>
+      </c>
+      <c r="C710" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D710" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>1487</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1511</v>
-      </c>
-      <c r="C711" s="8" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1542</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D711" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>1487</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1512</v>
-      </c>
-      <c r="C712" s="8" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1543</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>1487</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="C713" s="8" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1544</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>1487</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>1514</v>
-      </c>
-      <c r="C714" s="8" t="s">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1545</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>1487</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C715" s="8" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1546</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>1487</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1516</v>
-      </c>
-      <c r="C716" s="8" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1547</v>
+      </c>
+      <c r="C716" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>1487</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1517</v>
-      </c>
-      <c r="C717" s="8" t="s">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1548</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D717" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>1488</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1518</v>
-      </c>
-      <c r="C718" s="8" t="s">
-        <v>1548</v>
+        <v>1489</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D718" s="2" t="s">
+        <v>1549</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C5E5B3-FCA9-4E3D-A520-563599CCA168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A6DADB-1035-4A08-BA84-9A4B6EF673CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3301,1375 +3301,1375 @@
     <t>В8894ХВ</t>
   </si>
   <si>
+    <t xml:space="preserve">В5786КН </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В0843ТМ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В8990ВР </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В4930РА </t>
+  </si>
+  <si>
+    <t>ТУБА ВЛ 1</t>
+  </si>
+  <si>
+    <t>0000934420076</t>
+  </si>
+  <si>
+    <t>78970155027720386</t>
+  </si>
+  <si>
+    <t>78970155027720394</t>
+  </si>
+  <si>
+    <t>78970155027720402</t>
+  </si>
+  <si>
+    <t>78970155027720410</t>
+  </si>
+  <si>
+    <t>78970155027720428</t>
+  </si>
+  <si>
+    <t>78970155027720436</t>
+  </si>
+  <si>
+    <t>78970155027720444</t>
+  </si>
+  <si>
+    <t>78970155027720451</t>
+  </si>
+  <si>
+    <t>78970155027720469</t>
+  </si>
+  <si>
+    <t>78970155027720477</t>
+  </si>
+  <si>
+    <t>78970155027720485</t>
+  </si>
+  <si>
+    <t>78970155027720261</t>
+  </si>
+  <si>
+    <t>78970155027720279</t>
+  </si>
+  <si>
+    <t>78970155027720287</t>
+  </si>
+  <si>
+    <t>78970155027720295</t>
+  </si>
+  <si>
+    <t>78970155027720303</t>
+  </si>
+  <si>
+    <t>78970155027720311</t>
+  </si>
+  <si>
+    <t>78970155027720329</t>
+  </si>
+  <si>
+    <t>78970155027720337</t>
+  </si>
+  <si>
+    <t>78970155027720345</t>
+  </si>
+  <si>
+    <t>78970155027720352</t>
+  </si>
+  <si>
+    <t>78970155027720360</t>
+  </si>
+  <si>
+    <t>78970155027720378</t>
+  </si>
+  <si>
+    <t>78970155027720493</t>
+  </si>
+  <si>
+    <t>78970155027720501</t>
+  </si>
+  <si>
+    <t>78970155027720519</t>
+  </si>
+  <si>
+    <t>78970155027720527</t>
+  </si>
+  <si>
+    <t>78970155027720238</t>
+  </si>
+  <si>
+    <t>78970155027720246</t>
+  </si>
+  <si>
+    <t>78970155027720253</t>
+  </si>
+  <si>
+    <t>78970155027720592</t>
+  </si>
+  <si>
+    <t>78970155027720600</t>
+  </si>
+  <si>
+    <t>78970155027720618</t>
+  </si>
+  <si>
+    <t>78970155027720626</t>
+  </si>
+  <si>
+    <t>78970155027720634</t>
+  </si>
+  <si>
+    <t>78970155027720642</t>
+  </si>
+  <si>
+    <t>78970155027720659</t>
+  </si>
+  <si>
+    <t>78970155027720667</t>
+  </si>
+  <si>
+    <t>78970155027720675</t>
+  </si>
+  <si>
+    <t>78970155027720683</t>
+  </si>
+  <si>
+    <t>78970155027720691</t>
+  </si>
+  <si>
+    <t>78970155027720584</t>
+  </si>
+  <si>
+    <t>78970155027720709</t>
+  </si>
+  <si>
+    <t>78970155027720717</t>
+  </si>
+  <si>
+    <t>78970155027720725</t>
+  </si>
+  <si>
+    <t>78970155027720733</t>
+  </si>
+  <si>
+    <t>78970155027720535</t>
+  </si>
+  <si>
+    <t>78970155027720543</t>
+  </si>
+  <si>
+    <t>78970155027720550</t>
+  </si>
+  <si>
+    <t>78970155027720568</t>
+  </si>
+  <si>
+    <t>78970155027720576</t>
+  </si>
+  <si>
+    <t>78970155027720741</t>
+  </si>
+  <si>
+    <t>78970155027720758</t>
+  </si>
+  <si>
+    <t>78970155027720766</t>
+  </si>
+  <si>
+    <t>78970155027720774</t>
+  </si>
+  <si>
+    <t>78970155027720782</t>
+  </si>
+  <si>
+    <t>КСУБЛС</t>
+  </si>
+  <si>
+    <t>КСУДС</t>
+  </si>
+  <si>
+    <t>КМЕТСТВО КАМЕНАР</t>
+  </si>
+  <si>
+    <t>КМЕТСТВО КОНСТАНТИНОВО</t>
+  </si>
+  <si>
+    <t>КМЕТСТВО ТОПОЛИ</t>
+  </si>
+  <si>
+    <t>КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
+  </si>
+  <si>
+    <t>КСУДМ</t>
+  </si>
+  <si>
+    <t>ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ</t>
+  </si>
+  <si>
+    <t>ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
+  </si>
+  <si>
+    <t>РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
+  </si>
+  <si>
+    <t>КМЕТСТВО ЗВЕЗДИЦА</t>
+  </si>
+  <si>
+    <t>ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА</t>
+  </si>
+  <si>
+    <t>РАЙОН ОДЕСОС</t>
+  </si>
+  <si>
+    <t>В8986ВР</t>
+  </si>
+  <si>
+    <t>В9053ВТ</t>
+  </si>
+  <si>
+    <t>78970155027720873</t>
+  </si>
+  <si>
+    <t>78970155027720881</t>
+  </si>
+  <si>
+    <t>В5689ВН</t>
+  </si>
+  <si>
+    <t>В3650ВХ</t>
+  </si>
+  <si>
+    <t>78970155027720790</t>
+  </si>
+  <si>
+    <t>78970155027720808</t>
+  </si>
+  <si>
+    <t>В3914РТ</t>
+  </si>
+  <si>
+    <t>ТУБА КАМ 1</t>
+  </si>
+  <si>
+    <t>78970155027720816</t>
+  </si>
+  <si>
+    <t>78970155027720824</t>
+  </si>
+  <si>
+    <t>В0587ВТ</t>
+  </si>
+  <si>
+    <t>ТУБА КОН 1</t>
+  </si>
+  <si>
+    <t>78970155027720832</t>
+  </si>
+  <si>
+    <t>78970155027720840</t>
+  </si>
+  <si>
+    <t>В0584ВТ</t>
+  </si>
+  <si>
+    <t>ТУБА ТОП 1</t>
+  </si>
+  <si>
+    <t>78970155027720857</t>
+  </si>
+  <si>
+    <t>78970155027720865</t>
+  </si>
+  <si>
+    <t>В7580ТЕ</t>
+  </si>
+  <si>
+    <t>В8972ВР</t>
+  </si>
+  <si>
+    <t>В3018ХЕ</t>
+  </si>
+  <si>
+    <t>ТУБА КСУВХ 1</t>
+  </si>
+  <si>
+    <t>78970155027721335</t>
+  </si>
+  <si>
+    <t>78970155027721343</t>
+  </si>
+  <si>
+    <t>78970155027721350</t>
+  </si>
+  <si>
+    <t>78970155027721368</t>
+  </si>
+  <si>
+    <t>В3270ВН</t>
+  </si>
+  <si>
+    <t>В4450ТТ</t>
+  </si>
+  <si>
+    <t>78970155027721152</t>
+  </si>
+  <si>
+    <t>78970155027721160</t>
+  </si>
+  <si>
+    <t>78970155027720899</t>
+  </si>
+  <si>
+    <t>78970155027720907</t>
+  </si>
+  <si>
+    <t>78970155027720915</t>
+  </si>
+  <si>
+    <t>78970155027720923</t>
+  </si>
+  <si>
+    <t>78970155027720931</t>
+  </si>
+  <si>
+    <t>78970155027720949</t>
+  </si>
+  <si>
+    <t>78970155027720956</t>
+  </si>
+  <si>
+    <t>78970155027720964</t>
+  </si>
+  <si>
+    <t>78970155027720972</t>
+  </si>
+  <si>
+    <t>78970155027720980</t>
+  </si>
+  <si>
+    <t>78970155027720998</t>
+  </si>
+  <si>
+    <t>78970155027721004</t>
+  </si>
+  <si>
+    <t>78970155027721012</t>
+  </si>
+  <si>
+    <t>78970155027721020</t>
+  </si>
+  <si>
+    <t>78970155027721038</t>
+  </si>
+  <si>
+    <t>78970155027721046</t>
+  </si>
+  <si>
+    <t>78970155027721053</t>
+  </si>
+  <si>
+    <t>78970155027721061</t>
+  </si>
+  <si>
+    <t>78970155027721079</t>
+  </si>
+  <si>
+    <t>78970155027721087</t>
+  </si>
+  <si>
+    <t>78970155027721095</t>
+  </si>
+  <si>
+    <t>78970155027721103</t>
+  </si>
+  <si>
+    <t>78970155027721111</t>
+  </si>
+  <si>
+    <t>78970155027721129</t>
+  </si>
+  <si>
+    <t>78970155027721137</t>
+  </si>
+  <si>
+    <t>78970155027721145</t>
+  </si>
+  <si>
+    <t>78970155027722069</t>
+  </si>
+  <si>
+    <t>78970155027722077</t>
+  </si>
+  <si>
+    <t>78970155027722085</t>
+  </si>
+  <si>
+    <t>78970155027722093</t>
+  </si>
+  <si>
+    <t>78970155027722101</t>
+  </si>
+  <si>
+    <t>78970155027722119</t>
+  </si>
+  <si>
+    <t>78970155027722127</t>
+  </si>
+  <si>
+    <t>78970155027722135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТУБА - 8332 </t>
+  </si>
+  <si>
+    <t>ТУБА 10 Л</t>
+  </si>
+  <si>
+    <t>В8084СТ</t>
+  </si>
+  <si>
+    <t>В3752РМ</t>
+  </si>
+  <si>
+    <t>В3759РМ</t>
+  </si>
+  <si>
+    <t>В0588ВТ</t>
+  </si>
+  <si>
+    <t>В3537НВ</t>
+  </si>
+  <si>
+    <t>В5134НА</t>
+  </si>
+  <si>
+    <t>В5136НА</t>
+  </si>
+  <si>
+    <t>В0548НТ</t>
+  </si>
+  <si>
+    <t>В0549НТ</t>
+  </si>
+  <si>
+    <t>В0551НТ</t>
+  </si>
+  <si>
+    <t>В0552НТ</t>
+  </si>
+  <si>
+    <t>В0553НТ</t>
+  </si>
+  <si>
+    <t>В0554НТ</t>
+  </si>
+  <si>
+    <t>В0555НТ</t>
+  </si>
+  <si>
+    <t>В7481ВС</t>
+  </si>
+  <si>
+    <t>В7473ВС</t>
+  </si>
+  <si>
+    <t>В10528</t>
+  </si>
+  <si>
+    <t>В3572ТХ</t>
+  </si>
+  <si>
+    <t>ТУБА - 1 196025</t>
+  </si>
+  <si>
+    <t>ТУБА - 2 196026</t>
+  </si>
+  <si>
+    <t>ТУБА - 3 206025</t>
+  </si>
+  <si>
+    <t>ТУБА - 4 206026</t>
+  </si>
+  <si>
+    <t>ТУБА - 5 БЕНЗИН</t>
+  </si>
+  <si>
+    <t>0023043 - 1</t>
+  </si>
+  <si>
+    <t>0023042 - 2</t>
+  </si>
+  <si>
+    <t>0023041 - 3</t>
+  </si>
+  <si>
+    <t>0023413 - 4</t>
+  </si>
+  <si>
+    <t>0024345 - 5</t>
+  </si>
+  <si>
+    <t>ТУБА - 6 </t>
+  </si>
+  <si>
+    <t>В14021</t>
+  </si>
+  <si>
+    <t>В1518ХК</t>
+  </si>
+  <si>
+    <t>В1519ХК</t>
+  </si>
+  <si>
+    <t>B2207PP</t>
+  </si>
+  <si>
+    <t>B9208BM</t>
+  </si>
+  <si>
+    <t>B7846TP</t>
+  </si>
+  <si>
+    <t>B0452TC</t>
+  </si>
+  <si>
+    <t>B5773PX</t>
+  </si>
+  <si>
+    <t>B5770PX</t>
+  </si>
+  <si>
+    <t>B5383XE</t>
+  </si>
+  <si>
+    <t>B5379XE</t>
+  </si>
+  <si>
+    <t>B7845TP</t>
+  </si>
+  <si>
+    <t>B8917BP</t>
+  </si>
+  <si>
+    <t>B5392PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B4161TK </t>
+  </si>
+  <si>
+    <t>B4160TK</t>
+  </si>
+  <si>
+    <t>B6386HH</t>
+  </si>
+  <si>
+    <t>B5289РХ</t>
+  </si>
+  <si>
+    <t>B8930КА</t>
+  </si>
+  <si>
+    <t>78970155027721178</t>
+  </si>
+  <si>
+    <t>78970155027721186</t>
+  </si>
+  <si>
+    <t>78970155027721194</t>
+  </si>
+  <si>
+    <t>78970155027721202</t>
+  </si>
+  <si>
+    <t>78970155027721210</t>
+  </si>
+  <si>
+    <t>78970155027721228</t>
+  </si>
+  <si>
+    <t>78970155027721236</t>
+  </si>
+  <si>
+    <t>78970155027721244</t>
+  </si>
+  <si>
+    <t>78970155027721251</t>
+  </si>
+  <si>
+    <t>78970155027721269</t>
+  </si>
+  <si>
+    <t>78970155027721277</t>
+  </si>
+  <si>
+    <t>78970155027721285</t>
+  </si>
+  <si>
+    <t>78970155027721293</t>
+  </si>
+  <si>
+    <t>78970155027721301</t>
+  </si>
+  <si>
+    <t>78970155027721319</t>
+  </si>
+  <si>
+    <t>78970155027721327</t>
+  </si>
+  <si>
+    <t>В5782КН</t>
+  </si>
+  <si>
+    <t>В6514КС</t>
+  </si>
+  <si>
+    <t>В8981ВР</t>
+  </si>
+  <si>
+    <t>В7241ВР</t>
+  </si>
+  <si>
+    <t>78970155027721376</t>
+  </si>
+  <si>
+    <t>78970155027721384</t>
+  </si>
+  <si>
+    <t>78970155027721392</t>
+  </si>
+  <si>
+    <t>78970155027721400</t>
+  </si>
+  <si>
+    <t>В8973ВР</t>
+  </si>
+  <si>
+    <t>В7229ВР</t>
+  </si>
+  <si>
+    <t>ТУБА КАЗ 1</t>
+  </si>
+  <si>
+    <t>В0541НХ</t>
+  </si>
+  <si>
+    <t>В0586ВТ</t>
+  </si>
+  <si>
+    <t>В0589ВТ</t>
+  </si>
+  <si>
+    <t>В0591ВТ</t>
+  </si>
+  <si>
+    <t>В0592ВТ</t>
+  </si>
+  <si>
+    <t>В0594ВТ</t>
+  </si>
+  <si>
+    <t>В0595ВТ</t>
+  </si>
+  <si>
+    <t>В0804ТР</t>
+  </si>
+  <si>
+    <t>В0805ТР</t>
+  </si>
+  <si>
+    <t>В1071КК</t>
+  </si>
+  <si>
+    <t>В1111КС</t>
+  </si>
+  <si>
+    <t>В1422РХ</t>
+  </si>
+  <si>
+    <t>В1440СР</t>
+  </si>
+  <si>
+    <t>В1560НР</t>
+  </si>
+  <si>
+    <t>В1977ВМ</t>
+  </si>
+  <si>
+    <t>В2650КВ</t>
+  </si>
+  <si>
+    <t>В2802ТХ</t>
+  </si>
+  <si>
+    <t>В2852РК</t>
+  </si>
+  <si>
+    <t>В2971НР</t>
+  </si>
+  <si>
+    <t>В3432ВТ</t>
+  </si>
+  <si>
+    <t>В4582РР</t>
+  </si>
+  <si>
+    <t>В4814КВ</t>
+  </si>
+  <si>
+    <t>В5987РР</t>
+  </si>
+  <si>
+    <t>В6049НХ</t>
+  </si>
+  <si>
+    <t>В6511КС</t>
+  </si>
+  <si>
+    <t>В6512КС</t>
+  </si>
+  <si>
+    <t>В6565КМ</t>
+  </si>
+  <si>
+    <t>В6633СН</t>
+  </si>
+  <si>
+    <t>В7106НН</t>
+  </si>
+  <si>
+    <t>В7224ВР</t>
+  </si>
+  <si>
+    <t>В7230ВР</t>
+  </si>
+  <si>
+    <t>В7233ВР</t>
+  </si>
+  <si>
+    <t>В7234ВР</t>
+  </si>
+  <si>
+    <t>В7236ВР</t>
+  </si>
+  <si>
+    <t>В7242ВР</t>
+  </si>
+  <si>
+    <t>В7447РХ</t>
+  </si>
+  <si>
+    <t>В7721ВВ</t>
+  </si>
+  <si>
+    <t>В7948РТ</t>
+  </si>
+  <si>
+    <t>В8819ВТ</t>
+  </si>
+  <si>
+    <t>В8974ВР</t>
+  </si>
+  <si>
+    <t>В8975ВР</t>
+  </si>
+  <si>
+    <t>В8976ВР</t>
+  </si>
+  <si>
+    <t>В8978ВР</t>
+  </si>
+  <si>
+    <t>В8979ВР</t>
+  </si>
+  <si>
+    <t>В8985ВР</t>
+  </si>
+  <si>
+    <t>В9337НК</t>
+  </si>
+  <si>
+    <t>В9347РН</t>
+  </si>
+  <si>
+    <t>В8853ХК</t>
+  </si>
+  <si>
+    <t>В2410В</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА ОВ 1</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА ОВ 2</t>
+  </si>
+  <si>
+    <t>ТУБА ОВ 1</t>
+  </si>
+  <si>
+    <t>ТУБА ОВ 2</t>
+  </si>
+  <si>
+    <t>78970155027721418</t>
+  </si>
+  <si>
+    <t>78970155027721426</t>
+  </si>
+  <si>
+    <t>78970155027721434</t>
+  </si>
+  <si>
+    <t>78970155027721442</t>
+  </si>
+  <si>
+    <t>78970155027721459</t>
+  </si>
+  <si>
+    <t>78970155027721467</t>
+  </si>
+  <si>
+    <t>78970155027721475</t>
+  </si>
+  <si>
+    <t>78970155027721483</t>
+  </si>
+  <si>
+    <t>78970155027721491</t>
+  </si>
+  <si>
+    <t>78970155027721509</t>
+  </si>
+  <si>
+    <t>78970155027721517</t>
+  </si>
+  <si>
+    <t>78970155027721525</t>
+  </si>
+  <si>
+    <t>78970155027721533</t>
+  </si>
+  <si>
+    <t>78970155027721541</t>
+  </si>
+  <si>
+    <t>78970155027721558</t>
+  </si>
+  <si>
+    <t>78970155027721566</t>
+  </si>
+  <si>
+    <t>78970155027721574</t>
+  </si>
+  <si>
+    <t>78970155027721582</t>
+  </si>
+  <si>
+    <t>78970155027721590</t>
+  </si>
+  <si>
+    <t>78970155027721608</t>
+  </si>
+  <si>
+    <t>78970155027721616</t>
+  </si>
+  <si>
+    <t>78970155027721624</t>
+  </si>
+  <si>
+    <t>78970155027721632</t>
+  </si>
+  <si>
+    <t>78970155027721640</t>
+  </si>
+  <si>
+    <t>78970155027721657</t>
+  </si>
+  <si>
+    <t>78970155027721665</t>
+  </si>
+  <si>
+    <t>78970155027721673</t>
+  </si>
+  <si>
+    <t>78970155027721681</t>
+  </si>
+  <si>
+    <t>78970155027721699</t>
+  </si>
+  <si>
+    <t>78970155027721707</t>
+  </si>
+  <si>
+    <t>78970155027721715</t>
+  </si>
+  <si>
+    <t>78970155027721723</t>
+  </si>
+  <si>
+    <t>78970155027721731</t>
+  </si>
+  <si>
+    <t>78970155027721749</t>
+  </si>
+  <si>
+    <t>78970155027721756</t>
+  </si>
+  <si>
+    <t>78970155027721764</t>
+  </si>
+  <si>
+    <t>78970155027721772</t>
+  </si>
+  <si>
+    <t>78970155027721780</t>
+  </si>
+  <si>
+    <t>78970155027721798</t>
+  </si>
+  <si>
+    <t>В7237ВР</t>
+  </si>
+  <si>
+    <t>В8971ВР</t>
+  </si>
+  <si>
+    <t>В8977ВР</t>
+  </si>
+  <si>
+    <t>В8980ВР</t>
+  </si>
+  <si>
+    <t>В8982ВР</t>
+  </si>
+  <si>
+    <t>В8991ВР</t>
+  </si>
+  <si>
+    <t>В3171К</t>
+  </si>
+  <si>
+    <t>В3173К</t>
+  </si>
+  <si>
+    <t>В5896ВМ</t>
+  </si>
+  <si>
+    <t>В8330НТ</t>
+  </si>
+  <si>
+    <t>78970155027721988</t>
+  </si>
+  <si>
+    <t>В0583ВТ</t>
+  </si>
+  <si>
+    <t>78970155027721806</t>
+  </si>
+  <si>
+    <t>ТУБА КОСАЧКА</t>
+  </si>
+  <si>
+    <t>В0084ХМ</t>
+  </si>
+  <si>
+    <t>ТУБА ГЕНЕРАТОР</t>
+  </si>
+  <si>
+    <t>В4835НР</t>
+  </si>
+  <si>
+    <t>В4837НР</t>
+  </si>
+  <si>
+    <t>В4839НР</t>
+  </si>
+  <si>
+    <t>В4840НР</t>
+  </si>
+  <si>
+    <t>В4792НР</t>
+  </si>
+  <si>
+    <t>В2881РХ</t>
+  </si>
+  <si>
+    <t>В4244АТ</t>
+  </si>
+  <si>
+    <t>В1708ВК</t>
+  </si>
+  <si>
+    <t>В7492КТ</t>
+  </si>
+  <si>
+    <t>В7493КТ</t>
+  </si>
+  <si>
+    <t>В4287НТ</t>
+  </si>
+  <si>
+    <t>В4289НТ</t>
+  </si>
+  <si>
+    <t>В4291НТ</t>
+  </si>
+  <si>
+    <t>78970155027721814</t>
+  </si>
+  <si>
+    <t>78970155027721822</t>
+  </si>
+  <si>
+    <t>78970155027721830</t>
+  </si>
+  <si>
+    <t>78970155027721848</t>
+  </si>
+  <si>
+    <t>78970155027721855</t>
+  </si>
+  <si>
+    <t>78970155027721863</t>
+  </si>
+  <si>
+    <t>78970155027721871</t>
+  </si>
+  <si>
+    <t>78970155027721889</t>
+  </si>
+  <si>
+    <t>78970155027721897</t>
+  </si>
+  <si>
+    <t>78970155027721905</t>
+  </si>
+  <si>
+    <t>78970155027721913</t>
+  </si>
+  <si>
+    <t>78970155027721921</t>
+  </si>
+  <si>
+    <t>78970155027721939</t>
+  </si>
+  <si>
+    <t>78970155027721947</t>
+  </si>
+  <si>
+    <t>78970155027721954</t>
+  </si>
+  <si>
+    <t>78970155027721962</t>
+  </si>
+  <si>
+    <t>78970155027721970</t>
+  </si>
+  <si>
+    <t>B5779KH</t>
+  </si>
+  <si>
+    <t>B0593BT</t>
+  </si>
+  <si>
+    <t>B7235BP</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
+  </si>
+  <si>
+    <t>В2763ТА</t>
+  </si>
+  <si>
+    <t>В2764ТА</t>
+  </si>
+  <si>
+    <t>78970155027721996</t>
+  </si>
+  <si>
+    <t>78970155027722002</t>
+  </si>
+  <si>
+    <t>78970155027722010</t>
+  </si>
+  <si>
+    <t>78970155027722028</t>
+  </si>
+  <si>
+    <t>78970155027722036</t>
+  </si>
+  <si>
+    <t>78970155027722044</t>
+  </si>
+  <si>
+    <t>78970155027722051</t>
+  </si>
+  <si>
+    <t>0000934421683</t>
+  </si>
+  <si>
+    <t>0000934421607</t>
+  </si>
+  <si>
+    <t>0000934420080</t>
+  </si>
+  <si>
+    <t>0000934421454</t>
+  </si>
+  <si>
+    <t>0000934420061</t>
+  </si>
+  <si>
+    <t>0000934421488</t>
+  </si>
+  <si>
+    <t>0000934421729</t>
+  </si>
+  <si>
+    <t>0000934421504</t>
+  </si>
+  <si>
+    <t>0000934421469</t>
+  </si>
+  <si>
+    <t>0000934420019</t>
+  </si>
+  <si>
+    <t>0000934421714</t>
+  </si>
+  <si>
+    <t>0000934421435</t>
+  </si>
+  <si>
+    <t>000093442</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 1</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 3 - ОИЦ</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 4 - УА</t>
+  </si>
+  <si>
+    <t>0000934420057</t>
+  </si>
+  <si>
+    <t>0000934421679</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 5 - ПГД</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 6 - УА</t>
+  </si>
+  <si>
+    <t>0000934420042</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО % 1</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО % 2</t>
+  </si>
+  <si>
+    <t>ТУБА</t>
+  </si>
+  <si>
+    <t>78970155027722168</t>
+  </si>
+  <si>
+    <t>78970155027722176</t>
+  </si>
+  <si>
+    <t>78970155027722184</t>
+  </si>
+  <si>
+    <t>78970155027722192</t>
+  </si>
+  <si>
+    <t>78970155027722200</t>
+  </si>
+  <si>
+    <t>78970155027722218</t>
+  </si>
+  <si>
+    <t>78970155027722226</t>
+  </si>
+  <si>
+    <t>78970155027722234</t>
+  </si>
+  <si>
+    <t>78970155027722242</t>
+  </si>
+  <si>
+    <t>78970155027722259</t>
+  </si>
+  <si>
+    <t>78970155027722267</t>
+  </si>
+  <si>
+    <t>78970155027722275</t>
+  </si>
+  <si>
+    <t>78970155027722283</t>
+  </si>
+  <si>
+    <t>78970155027722291</t>
+  </si>
+  <si>
+    <t>78970155027722309</t>
+  </si>
+  <si>
+    <t>78970155027722317</t>
+  </si>
+  <si>
+    <t>78970155027722325</t>
+  </si>
+  <si>
+    <t>78970155027722333</t>
+  </si>
+  <si>
+    <t>78970155027722341</t>
+  </si>
+  <si>
+    <t>78970155027722358</t>
+  </si>
+  <si>
+    <t>78970155027722366</t>
+  </si>
+  <si>
+    <t>78970155027722374</t>
+  </si>
+  <si>
+    <t>78970155027722382</t>
+  </si>
+  <si>
+    <t>78970155027722390</t>
+  </si>
+  <si>
+    <t>78970155027722408</t>
+  </si>
+  <si>
+    <t>78970155027722416</t>
+  </si>
+  <si>
+    <t>78970155027722424</t>
+  </si>
+  <si>
+    <t>78970155027722432</t>
+  </si>
+  <si>
+    <t>78970155027722440</t>
+  </si>
+  <si>
+    <t>78970155027722457</t>
+  </si>
+  <si>
+    <t>В6613КС</t>
+  </si>
+  <si>
+    <t>В9933СМ</t>
+  </si>
+  <si>
+    <t>В8636СТ</t>
+  </si>
+  <si>
+    <t>В3762РА</t>
+  </si>
+  <si>
+    <t>В9922РА</t>
+  </si>
+  <si>
+    <t>В4685РС</t>
+  </si>
+  <si>
+    <t>В2278РВ</t>
+  </si>
+  <si>
+    <t>В4692РС</t>
+  </si>
+  <si>
+    <t>В1839ТМ</t>
+  </si>
+  <si>
+    <t>В5328РМ</t>
+  </si>
+  <si>
+    <t>В5116РС</t>
+  </si>
+  <si>
+    <t>В5117РС</t>
+  </si>
+  <si>
+    <t>В6476ВС</t>
+  </si>
+  <si>
+    <t>В6915ВХ</t>
+  </si>
+  <si>
+    <t>В5654ВН</t>
+  </si>
+  <si>
+    <t>В3535СТ</t>
+  </si>
+  <si>
+    <t>В4239ВТ</t>
+  </si>
+  <si>
+    <t>В1283НТ</t>
+  </si>
+  <si>
+    <t>В9999РX</t>
+  </si>
+  <si>
+    <t>В6431НР</t>
+  </si>
+  <si>
+    <t>В5119РС</t>
+  </si>
+  <si>
+    <t>В5163ХВ</t>
+  </si>
+  <si>
+    <t>В5089РВ</t>
+  </si>
+  <si>
+    <t>В7341ВС</t>
+  </si>
+  <si>
+    <t>В2429ТТ</t>
+  </si>
+  <si>
+    <t>B6947НТ</t>
+  </si>
+  <si>
+    <t>В6196РС</t>
+  </si>
+  <si>
+    <t>В1293НН</t>
+  </si>
+  <si>
+    <t>В09805</t>
+  </si>
+  <si>
+    <t>000093385</t>
+  </si>
+  <si>
     <t>РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В5786КН </t>
-  </si>
-  <si>
-    <t xml:space="preserve">В0843ТМ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">В8990ВР </t>
-  </si>
-  <si>
-    <t xml:space="preserve">В4930РА </t>
-  </si>
-  <si>
-    <t>ТУБА ВЛ 1</t>
-  </si>
-  <si>
-    <t>0000934420076</t>
-  </si>
-  <si>
-    <t>78970155027720386</t>
-  </si>
-  <si>
-    <t>78970155027720394</t>
-  </si>
-  <si>
-    <t>78970155027720402</t>
-  </si>
-  <si>
-    <t>78970155027720410</t>
-  </si>
-  <si>
-    <t>78970155027720428</t>
-  </si>
-  <si>
-    <t>78970155027720436</t>
-  </si>
-  <si>
-    <t>78970155027720444</t>
-  </si>
-  <si>
-    <t>78970155027720451</t>
-  </si>
-  <si>
-    <t>78970155027720469</t>
-  </si>
-  <si>
-    <t>78970155027720477</t>
-  </si>
-  <si>
-    <t>78970155027720485</t>
-  </si>
-  <si>
-    <t>78970155027720261</t>
-  </si>
-  <si>
-    <t>78970155027720279</t>
-  </si>
-  <si>
-    <t>78970155027720287</t>
-  </si>
-  <si>
-    <t>78970155027720295</t>
-  </si>
-  <si>
-    <t>78970155027720303</t>
-  </si>
-  <si>
-    <t>78970155027720311</t>
-  </si>
-  <si>
-    <t>78970155027720329</t>
-  </si>
-  <si>
-    <t>78970155027720337</t>
-  </si>
-  <si>
-    <t>78970155027720345</t>
-  </si>
-  <si>
-    <t>78970155027720352</t>
-  </si>
-  <si>
-    <t>78970155027720360</t>
-  </si>
-  <si>
-    <t>78970155027720378</t>
-  </si>
-  <si>
-    <t>78970155027720493</t>
-  </si>
-  <si>
-    <t>78970155027720501</t>
-  </si>
-  <si>
-    <t>78970155027720519</t>
-  </si>
-  <si>
-    <t>78970155027720527</t>
-  </si>
-  <si>
-    <t>78970155027720238</t>
-  </si>
-  <si>
-    <t>78970155027720246</t>
-  </si>
-  <si>
-    <t>78970155027720253</t>
-  </si>
-  <si>
-    <t>78970155027720592</t>
-  </si>
-  <si>
-    <t>78970155027720600</t>
-  </si>
-  <si>
-    <t>78970155027720618</t>
-  </si>
-  <si>
-    <t>78970155027720626</t>
-  </si>
-  <si>
-    <t>78970155027720634</t>
-  </si>
-  <si>
-    <t>78970155027720642</t>
-  </si>
-  <si>
-    <t>78970155027720659</t>
-  </si>
-  <si>
-    <t>78970155027720667</t>
-  </si>
-  <si>
-    <t>78970155027720675</t>
-  </si>
-  <si>
-    <t>78970155027720683</t>
-  </si>
-  <si>
-    <t>78970155027720691</t>
-  </si>
-  <si>
-    <t>78970155027720584</t>
-  </si>
-  <si>
-    <t>78970155027720709</t>
-  </si>
-  <si>
-    <t>78970155027720717</t>
-  </si>
-  <si>
-    <t>78970155027720725</t>
-  </si>
-  <si>
-    <t>78970155027720733</t>
-  </si>
-  <si>
-    <t>78970155027720535</t>
-  </si>
-  <si>
-    <t>78970155027720543</t>
-  </si>
-  <si>
-    <t>78970155027720550</t>
-  </si>
-  <si>
-    <t>78970155027720568</t>
-  </si>
-  <si>
-    <t>78970155027720576</t>
-  </si>
-  <si>
-    <t>78970155027720741</t>
-  </si>
-  <si>
-    <t>78970155027720758</t>
-  </si>
-  <si>
-    <t>78970155027720766</t>
-  </si>
-  <si>
-    <t>78970155027720774</t>
-  </si>
-  <si>
-    <t>78970155027720782</t>
-  </si>
-  <si>
-    <t>КСУБЛС</t>
-  </si>
-  <si>
-    <t>КСУДС</t>
-  </si>
-  <si>
-    <t>КМЕТСТВО КАМЕНАР</t>
-  </si>
-  <si>
-    <t>КМЕТСТВО КОНСТАНТИНОВО</t>
-  </si>
-  <si>
-    <t>КМЕТСТВО ТОПОЛИ</t>
-  </si>
-  <si>
-    <t>КСУВХ ГЕРГАНА ДСХ И ДПЛФУ</t>
-  </si>
-  <si>
-    <t>КСУДМ</t>
-  </si>
-  <si>
-    <t>ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ</t>
-  </si>
-  <si>
-    <t>ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
-  </si>
-  <si>
-    <t>РАЙОН ПРИМОРСКИ – ОБЩИНА ВАРНА</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА - ДИРЕКЦИЯ СПОРТ</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
-  </si>
-  <si>
-    <t>КМЕТСТВО ЗВЕЗДИЦА</t>
-  </si>
-  <si>
-    <t>ОП ОБЩИНСКИ ПАРКИНГИ И СИНЯ ЗОНА</t>
-  </si>
-  <si>
-    <t>РАЙОН ОДЕСОС</t>
-  </si>
-  <si>
-    <t>В8986ВР</t>
-  </si>
-  <si>
-    <t>В9053ВТ</t>
-  </si>
-  <si>
-    <t>78970155027720873</t>
-  </si>
-  <si>
-    <t>78970155027720881</t>
-  </si>
-  <si>
-    <t>В5689ВН</t>
-  </si>
-  <si>
-    <t>В3650ВХ</t>
-  </si>
-  <si>
-    <t>78970155027720790</t>
-  </si>
-  <si>
-    <t>78970155027720808</t>
-  </si>
-  <si>
-    <t>В3914РТ</t>
-  </si>
-  <si>
-    <t>ТУБА КАМ 1</t>
-  </si>
-  <si>
-    <t>78970155027720816</t>
-  </si>
-  <si>
-    <t>78970155027720824</t>
-  </si>
-  <si>
-    <t>В0587ВТ</t>
-  </si>
-  <si>
-    <t>ТУБА КОН 1</t>
-  </si>
-  <si>
-    <t>78970155027720832</t>
-  </si>
-  <si>
-    <t>78970155027720840</t>
-  </si>
-  <si>
-    <t>В0584ВТ</t>
-  </si>
-  <si>
-    <t>ТУБА ТОП 1</t>
-  </si>
-  <si>
-    <t>78970155027720857</t>
-  </si>
-  <si>
-    <t>78970155027720865</t>
-  </si>
-  <si>
-    <t>В7580ТЕ</t>
-  </si>
-  <si>
-    <t>В8972ВР</t>
-  </si>
-  <si>
-    <t>В3018ХЕ</t>
-  </si>
-  <si>
-    <t>ТУБА КСУВХ 1</t>
-  </si>
-  <si>
-    <t>78970155027721335</t>
-  </si>
-  <si>
-    <t>78970155027721343</t>
-  </si>
-  <si>
-    <t>78970155027721350</t>
-  </si>
-  <si>
-    <t>78970155027721368</t>
-  </si>
-  <si>
-    <t>В3270ВН</t>
-  </si>
-  <si>
-    <t>В4450ТТ</t>
-  </si>
-  <si>
-    <t>78970155027721152</t>
-  </si>
-  <si>
-    <t>78970155027721160</t>
-  </si>
-  <si>
-    <t>78970155027720899</t>
-  </si>
-  <si>
-    <t>78970155027720907</t>
-  </si>
-  <si>
-    <t>78970155027720915</t>
-  </si>
-  <si>
-    <t>78970155027720923</t>
-  </si>
-  <si>
-    <t>78970155027720931</t>
-  </si>
-  <si>
-    <t>78970155027720949</t>
-  </si>
-  <si>
-    <t>78970155027720956</t>
-  </si>
-  <si>
-    <t>78970155027720964</t>
-  </si>
-  <si>
-    <t>78970155027720972</t>
-  </si>
-  <si>
-    <t>78970155027720980</t>
-  </si>
-  <si>
-    <t>78970155027720998</t>
-  </si>
-  <si>
-    <t>78970155027721004</t>
-  </si>
-  <si>
-    <t>78970155027721012</t>
-  </si>
-  <si>
-    <t>78970155027721020</t>
-  </si>
-  <si>
-    <t>78970155027721038</t>
-  </si>
-  <si>
-    <t>78970155027721046</t>
-  </si>
-  <si>
-    <t>78970155027721053</t>
-  </si>
-  <si>
-    <t>78970155027721061</t>
-  </si>
-  <si>
-    <t>78970155027721079</t>
-  </si>
-  <si>
-    <t>78970155027721087</t>
-  </si>
-  <si>
-    <t>78970155027721095</t>
-  </si>
-  <si>
-    <t>78970155027721103</t>
-  </si>
-  <si>
-    <t>78970155027721111</t>
-  </si>
-  <si>
-    <t>78970155027721129</t>
-  </si>
-  <si>
-    <t>78970155027721137</t>
-  </si>
-  <si>
-    <t>78970155027721145</t>
-  </si>
-  <si>
-    <t>78970155027722069</t>
-  </si>
-  <si>
-    <t>78970155027722077</t>
-  </si>
-  <si>
-    <t>78970155027722085</t>
-  </si>
-  <si>
-    <t>78970155027722093</t>
-  </si>
-  <si>
-    <t>78970155027722101</t>
-  </si>
-  <si>
-    <t>78970155027722119</t>
-  </si>
-  <si>
-    <t>78970155027722127</t>
-  </si>
-  <si>
-    <t>78970155027722135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТУБА - 8332 </t>
-  </si>
-  <si>
-    <t>ТУБА 10 Л</t>
-  </si>
-  <si>
-    <t>В8084СТ</t>
-  </si>
-  <si>
-    <t>В3752РМ</t>
-  </si>
-  <si>
-    <t>В3759РМ</t>
-  </si>
-  <si>
-    <t>В0588ВТ</t>
-  </si>
-  <si>
-    <t>В3537НВ</t>
-  </si>
-  <si>
-    <t>В5134НА</t>
-  </si>
-  <si>
-    <t>В5136НА</t>
-  </si>
-  <si>
-    <t>В0548НТ</t>
-  </si>
-  <si>
-    <t>В0549НТ</t>
-  </si>
-  <si>
-    <t>В0551НТ</t>
-  </si>
-  <si>
-    <t>В0552НТ</t>
-  </si>
-  <si>
-    <t>В0553НТ</t>
-  </si>
-  <si>
-    <t>В0554НТ</t>
-  </si>
-  <si>
-    <t>В0555НТ</t>
-  </si>
-  <si>
-    <t>В7481ВС</t>
-  </si>
-  <si>
-    <t>В7473ВС</t>
-  </si>
-  <si>
-    <t>В10528</t>
-  </si>
-  <si>
-    <t>В3572ТХ</t>
-  </si>
-  <si>
-    <t>ТУБА - 1 196025</t>
-  </si>
-  <si>
-    <t>ТУБА - 2 196026</t>
-  </si>
-  <si>
-    <t>ТУБА - 3 206025</t>
-  </si>
-  <si>
-    <t>ТУБА - 4 206026</t>
-  </si>
-  <si>
-    <t>ТУБА - 5 БЕНЗИН</t>
-  </si>
-  <si>
-    <t>0023043 - 1</t>
-  </si>
-  <si>
-    <t>0023042 - 2</t>
-  </si>
-  <si>
-    <t>0023041 - 3</t>
-  </si>
-  <si>
-    <t>0023413 - 4</t>
-  </si>
-  <si>
-    <t>0024345 - 5</t>
-  </si>
-  <si>
-    <t>ТУБА - 6 </t>
-  </si>
-  <si>
-    <t>В14021</t>
-  </si>
-  <si>
-    <t>В1518ХК</t>
-  </si>
-  <si>
-    <t>В1519ХК</t>
-  </si>
-  <si>
-    <t>B2207PP</t>
-  </si>
-  <si>
-    <t>B9208BM</t>
-  </si>
-  <si>
-    <t>B7846TP</t>
-  </si>
-  <si>
-    <t>B0452TC</t>
-  </si>
-  <si>
-    <t>B5773PX</t>
-  </si>
-  <si>
-    <t>B5770PX</t>
-  </si>
-  <si>
-    <t>B5383XE</t>
-  </si>
-  <si>
-    <t>B5379XE</t>
-  </si>
-  <si>
-    <t>B7845TP</t>
-  </si>
-  <si>
-    <t>B8917BP</t>
-  </si>
-  <si>
-    <t>B5392PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B4161TK </t>
-  </si>
-  <si>
-    <t>B4160TK</t>
-  </si>
-  <si>
-    <t>B6386HH</t>
-  </si>
-  <si>
-    <t>B5289РХ</t>
-  </si>
-  <si>
-    <t>B8930КА</t>
-  </si>
-  <si>
-    <t>78970155027721178</t>
-  </si>
-  <si>
-    <t>78970155027721186</t>
-  </si>
-  <si>
-    <t>78970155027721194</t>
-  </si>
-  <si>
-    <t>78970155027721202</t>
-  </si>
-  <si>
-    <t>78970155027721210</t>
-  </si>
-  <si>
-    <t>78970155027721228</t>
-  </si>
-  <si>
-    <t>78970155027721236</t>
-  </si>
-  <si>
-    <t>78970155027721244</t>
-  </si>
-  <si>
-    <t>78970155027721251</t>
-  </si>
-  <si>
-    <t>78970155027721269</t>
-  </si>
-  <si>
-    <t>78970155027721277</t>
-  </si>
-  <si>
-    <t>78970155027721285</t>
-  </si>
-  <si>
-    <t>78970155027721293</t>
-  </si>
-  <si>
-    <t>78970155027721301</t>
-  </si>
-  <si>
-    <t>78970155027721319</t>
-  </si>
-  <si>
-    <t>78970155027721327</t>
-  </si>
-  <si>
-    <t>В5782КН</t>
-  </si>
-  <si>
-    <t>В6514КС</t>
-  </si>
-  <si>
-    <t>В8981ВР</t>
-  </si>
-  <si>
-    <t>В7241ВР</t>
-  </si>
-  <si>
-    <t>78970155027721376</t>
-  </si>
-  <si>
-    <t>78970155027721384</t>
-  </si>
-  <si>
-    <t>78970155027721392</t>
-  </si>
-  <si>
-    <t>78970155027721400</t>
-  </si>
-  <si>
-    <t>В8973ВР</t>
-  </si>
-  <si>
-    <t>В7229ВР</t>
-  </si>
-  <si>
-    <t>ТУБА КАЗ 1</t>
-  </si>
-  <si>
-    <t>В0541НХ</t>
-  </si>
-  <si>
-    <t>В0586ВТ</t>
-  </si>
-  <si>
-    <t>В0589ВТ</t>
-  </si>
-  <si>
-    <t>В0591ВТ</t>
-  </si>
-  <si>
-    <t>В0592ВТ</t>
-  </si>
-  <si>
-    <t>В0594ВТ</t>
-  </si>
-  <si>
-    <t>В0595ВТ</t>
-  </si>
-  <si>
-    <t>В0804ТР</t>
-  </si>
-  <si>
-    <t>В0805ТР</t>
-  </si>
-  <si>
-    <t>В1071КК</t>
-  </si>
-  <si>
-    <t>В1111КС</t>
-  </si>
-  <si>
-    <t>В1422РХ</t>
-  </si>
-  <si>
-    <t>В1440СР</t>
-  </si>
-  <si>
-    <t>В1560НР</t>
-  </si>
-  <si>
-    <t>В1977ВМ</t>
-  </si>
-  <si>
-    <t>В2650КВ</t>
-  </si>
-  <si>
-    <t>В2802ТХ</t>
-  </si>
-  <si>
-    <t>В2852РК</t>
-  </si>
-  <si>
-    <t>В2971НР</t>
-  </si>
-  <si>
-    <t>В3432ВТ</t>
-  </si>
-  <si>
-    <t>В4582РР</t>
-  </si>
-  <si>
-    <t>В4814КВ</t>
-  </si>
-  <si>
-    <t>В5987РР</t>
-  </si>
-  <si>
-    <t>В6049НХ</t>
-  </si>
-  <si>
-    <t>В6511КС</t>
-  </si>
-  <si>
-    <t>В6512КС</t>
-  </si>
-  <si>
-    <t>В6565КМ</t>
-  </si>
-  <si>
-    <t>В6633СН</t>
-  </si>
-  <si>
-    <t>В7106НН</t>
-  </si>
-  <si>
-    <t>В7224ВР</t>
-  </si>
-  <si>
-    <t>В7230ВР</t>
-  </si>
-  <si>
-    <t>В7233ВР</t>
-  </si>
-  <si>
-    <t>В7234ВР</t>
-  </si>
-  <si>
-    <t>В7236ВР</t>
-  </si>
-  <si>
-    <t>В7242ВР</t>
-  </si>
-  <si>
-    <t>В7447РХ</t>
-  </si>
-  <si>
-    <t>В7721ВВ</t>
-  </si>
-  <si>
-    <t>В7948РТ</t>
-  </si>
-  <si>
-    <t>В8819ВТ</t>
-  </si>
-  <si>
-    <t>В8974ВР</t>
-  </si>
-  <si>
-    <t>В8975ВР</t>
-  </si>
-  <si>
-    <t>В8976ВР</t>
-  </si>
-  <si>
-    <t>В8978ВР</t>
-  </si>
-  <si>
-    <t>В8979ВР</t>
-  </si>
-  <si>
-    <t>В8985ВР</t>
-  </si>
-  <si>
-    <t>В9337НК</t>
-  </si>
-  <si>
-    <t>В9347РН</t>
-  </si>
-  <si>
-    <t>В8853ХК</t>
-  </si>
-  <si>
-    <t>В2410В</t>
-  </si>
-  <si>
-    <t>СЛУЖЕБНА ОВ 1</t>
-  </si>
-  <si>
-    <t>СЛУЖЕБНА ОВ 2</t>
-  </si>
-  <si>
-    <t>ТУБА ОВ 1</t>
-  </si>
-  <si>
-    <t>ТУБА ОВ 2</t>
-  </si>
-  <si>
-    <t>78970155027721418</t>
-  </si>
-  <si>
-    <t>78970155027721426</t>
-  </si>
-  <si>
-    <t>78970155027721434</t>
-  </si>
-  <si>
-    <t>78970155027721442</t>
-  </si>
-  <si>
-    <t>78970155027721459</t>
-  </si>
-  <si>
-    <t>78970155027721467</t>
-  </si>
-  <si>
-    <t>78970155027721475</t>
-  </si>
-  <si>
-    <t>78970155027721483</t>
-  </si>
-  <si>
-    <t>78970155027721491</t>
-  </si>
-  <si>
-    <t>78970155027721509</t>
-  </si>
-  <si>
-    <t>78970155027721517</t>
-  </si>
-  <si>
-    <t>78970155027721525</t>
-  </si>
-  <si>
-    <t>78970155027721533</t>
-  </si>
-  <si>
-    <t>78970155027721541</t>
-  </si>
-  <si>
-    <t>78970155027721558</t>
-  </si>
-  <si>
-    <t>78970155027721566</t>
-  </si>
-  <si>
-    <t>78970155027721574</t>
-  </si>
-  <si>
-    <t>78970155027721582</t>
-  </si>
-  <si>
-    <t>78970155027721590</t>
-  </si>
-  <si>
-    <t>78970155027721608</t>
-  </si>
-  <si>
-    <t>78970155027721616</t>
-  </si>
-  <si>
-    <t>78970155027721624</t>
-  </si>
-  <si>
-    <t>78970155027721632</t>
-  </si>
-  <si>
-    <t>78970155027721640</t>
-  </si>
-  <si>
-    <t>78970155027721657</t>
-  </si>
-  <si>
-    <t>78970155027721665</t>
-  </si>
-  <si>
-    <t>78970155027721673</t>
-  </si>
-  <si>
-    <t>78970155027721681</t>
-  </si>
-  <si>
-    <t>78970155027721699</t>
-  </si>
-  <si>
-    <t>78970155027721707</t>
-  </si>
-  <si>
-    <t>78970155027721715</t>
-  </si>
-  <si>
-    <t>78970155027721723</t>
-  </si>
-  <si>
-    <t>78970155027721731</t>
-  </si>
-  <si>
-    <t>78970155027721749</t>
-  </si>
-  <si>
-    <t>78970155027721756</t>
-  </si>
-  <si>
-    <t>78970155027721764</t>
-  </si>
-  <si>
-    <t>78970155027721772</t>
-  </si>
-  <si>
-    <t>78970155027721780</t>
-  </si>
-  <si>
-    <t>78970155027721798</t>
-  </si>
-  <si>
-    <t>В7237ВР</t>
-  </si>
-  <si>
-    <t>В8971ВР</t>
-  </si>
-  <si>
-    <t>В8977ВР</t>
-  </si>
-  <si>
-    <t>В8980ВР</t>
-  </si>
-  <si>
-    <t>В8982ВР</t>
-  </si>
-  <si>
-    <t>В8991ВР</t>
-  </si>
-  <si>
-    <t>В3171К</t>
-  </si>
-  <si>
-    <t>В3173К</t>
-  </si>
-  <si>
-    <t>В5896ВМ</t>
-  </si>
-  <si>
-    <t>В8330НТ</t>
-  </si>
-  <si>
-    <t>78970155027721988</t>
-  </si>
-  <si>
-    <t>В0583ВТ</t>
-  </si>
-  <si>
-    <t>78970155027721806</t>
-  </si>
-  <si>
-    <t>ТУБА КОСАЧКА</t>
-  </si>
-  <si>
-    <t>В0084ХМ</t>
-  </si>
-  <si>
-    <t>ТУБА ГЕНЕРАТОР</t>
-  </si>
-  <si>
-    <t>В4835НР</t>
-  </si>
-  <si>
-    <t>В4837НР</t>
-  </si>
-  <si>
-    <t>В4839НР</t>
-  </si>
-  <si>
-    <t>В4840НР</t>
-  </si>
-  <si>
-    <t>В4792НР</t>
-  </si>
-  <si>
-    <t>В2881РХ</t>
-  </si>
-  <si>
-    <t>В4244АТ</t>
-  </si>
-  <si>
-    <t>В1708ВК</t>
-  </si>
-  <si>
-    <t>В7492КТ</t>
-  </si>
-  <si>
-    <t>В7493КТ</t>
-  </si>
-  <si>
-    <t>В4287НТ</t>
-  </si>
-  <si>
-    <t>В4289НТ</t>
-  </si>
-  <si>
-    <t>В4291НТ</t>
-  </si>
-  <si>
-    <t>78970155027721814</t>
-  </si>
-  <si>
-    <t>78970155027721822</t>
-  </si>
-  <si>
-    <t>78970155027721830</t>
-  </si>
-  <si>
-    <t>78970155027721848</t>
-  </si>
-  <si>
-    <t>78970155027721855</t>
-  </si>
-  <si>
-    <t>78970155027721863</t>
-  </si>
-  <si>
-    <t>78970155027721871</t>
-  </si>
-  <si>
-    <t>78970155027721889</t>
-  </si>
-  <si>
-    <t>78970155027721897</t>
-  </si>
-  <si>
-    <t>78970155027721905</t>
-  </si>
-  <si>
-    <t>78970155027721913</t>
-  </si>
-  <si>
-    <t>78970155027721921</t>
-  </si>
-  <si>
-    <t>78970155027721939</t>
-  </si>
-  <si>
-    <t>78970155027721947</t>
-  </si>
-  <si>
-    <t>78970155027721954</t>
-  </si>
-  <si>
-    <t>78970155027721962</t>
-  </si>
-  <si>
-    <t>78970155027721970</t>
-  </si>
-  <si>
-    <t>B5779KH</t>
-  </si>
-  <si>
-    <t>B0593BT</t>
-  </si>
-  <si>
-    <t>B7235BP</t>
-  </si>
-  <si>
-    <t>B8984BP</t>
-  </si>
-  <si>
-    <t>В2763ТА</t>
-  </si>
-  <si>
-    <t>В2764ТА</t>
-  </si>
-  <si>
-    <t>78970155027721996</t>
-  </si>
-  <si>
-    <t>78970155027722002</t>
-  </si>
-  <si>
-    <t>78970155027722010</t>
-  </si>
-  <si>
-    <t>78970155027722028</t>
-  </si>
-  <si>
-    <t>78970155027722036</t>
-  </si>
-  <si>
-    <t>78970155027722044</t>
-  </si>
-  <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
-    <t>0000934421683</t>
-  </si>
-  <si>
-    <t>0000934421607</t>
-  </si>
-  <si>
-    <t>0000934420080</t>
-  </si>
-  <si>
-    <t>0000934421454</t>
-  </si>
-  <si>
-    <t>0000934420061</t>
-  </si>
-  <si>
-    <t>0000934421488</t>
-  </si>
-  <si>
-    <t>0000934421729</t>
-  </si>
-  <si>
-    <t>0000934421504</t>
-  </si>
-  <si>
-    <t>0000934421469</t>
-  </si>
-  <si>
-    <t>0000934420019</t>
-  </si>
-  <si>
-    <t>0000934421714</t>
-  </si>
-  <si>
-    <t>0000934421435</t>
-  </si>
-  <si>
-    <t>000093442</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 1</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 3 - ОИЦ</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 4 - УА</t>
-  </si>
-  <si>
-    <t>0000934420057</t>
-  </si>
-  <si>
-    <t>0000934421679</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 5 - ПГД</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 6 - УА</t>
-  </si>
-  <si>
-    <t>0000934420042</t>
-  </si>
-  <si>
-    <t>ОБЩИНА АКСАКОВО % 1</t>
-  </si>
-  <si>
-    <t>ОБЩИНА АКСАКОВО % 2</t>
-  </si>
-  <si>
-    <t>ТУБА</t>
-  </si>
-  <si>
-    <t>78970155027722168</t>
-  </si>
-  <si>
-    <t>78970155027722176</t>
-  </si>
-  <si>
-    <t>78970155027722184</t>
-  </si>
-  <si>
-    <t>78970155027722192</t>
-  </si>
-  <si>
-    <t>78970155027722200</t>
-  </si>
-  <si>
-    <t>78970155027722218</t>
-  </si>
-  <si>
-    <t>78970155027722226</t>
-  </si>
-  <si>
-    <t>78970155027722234</t>
-  </si>
-  <si>
-    <t>78970155027722242</t>
-  </si>
-  <si>
-    <t>78970155027722259</t>
-  </si>
-  <si>
-    <t>78970155027722267</t>
-  </si>
-  <si>
-    <t>78970155027722275</t>
-  </si>
-  <si>
-    <t>78970155027722283</t>
-  </si>
-  <si>
-    <t>78970155027722291</t>
-  </si>
-  <si>
-    <t>78970155027722309</t>
-  </si>
-  <si>
-    <t>78970155027722317</t>
-  </si>
-  <si>
-    <t>78970155027722325</t>
-  </si>
-  <si>
-    <t>78970155027722333</t>
-  </si>
-  <si>
-    <t>78970155027722341</t>
-  </si>
-  <si>
-    <t>78970155027722358</t>
-  </si>
-  <si>
-    <t>78970155027722366</t>
-  </si>
-  <si>
-    <t>78970155027722374</t>
-  </si>
-  <si>
-    <t>78970155027722382</t>
-  </si>
-  <si>
-    <t>78970155027722390</t>
-  </si>
-  <si>
-    <t>78970155027722408</t>
-  </si>
-  <si>
-    <t>78970155027722416</t>
-  </si>
-  <si>
-    <t>78970155027722424</t>
-  </si>
-  <si>
-    <t>78970155027722432</t>
-  </si>
-  <si>
-    <t>78970155027722440</t>
-  </si>
-  <si>
-    <t>78970155027722457</t>
-  </si>
-  <si>
-    <t>В6613КС</t>
-  </si>
-  <si>
-    <t>В9933СМ</t>
-  </si>
-  <si>
-    <t>В8636СТ</t>
-  </si>
-  <si>
-    <t>В3762РА</t>
-  </si>
-  <si>
-    <t>В9922РА</t>
-  </si>
-  <si>
-    <t>В4685РС</t>
-  </si>
-  <si>
-    <t>В2278РВ</t>
-  </si>
-  <si>
-    <t>В4692РС</t>
-  </si>
-  <si>
-    <t>В1839ТМ</t>
-  </si>
-  <si>
-    <t>В5328РМ</t>
-  </si>
-  <si>
-    <t>В5116РС</t>
-  </si>
-  <si>
-    <t>В5117РС</t>
-  </si>
-  <si>
-    <t>В6476ВС</t>
-  </si>
-  <si>
-    <t>В6915ВХ</t>
-  </si>
-  <si>
-    <t>В5654ВН</t>
-  </si>
-  <si>
-    <t>В3535СТ</t>
-  </si>
-  <si>
-    <t>В4239ВТ</t>
-  </si>
-  <si>
-    <t>В1283НТ</t>
-  </si>
-  <si>
-    <t>В9999РX</t>
-  </si>
-  <si>
-    <t>В6431НР</t>
-  </si>
-  <si>
-    <t>В5119РС</t>
-  </si>
-  <si>
-    <t>В5163ХВ</t>
-  </si>
-  <si>
-    <t>В5089РВ</t>
-  </si>
-  <si>
-    <t>В7341ВС</t>
-  </si>
-  <si>
-    <t>В2429ТТ</t>
-  </si>
-  <si>
-    <t>B6947НТ</t>
-  </si>
-  <si>
-    <t>В6196РС</t>
-  </si>
-  <si>
-    <t>В1293НН</t>
-  </si>
-  <si>
-    <t>В09805</t>
-  </si>
-  <si>
-    <t>000093385</t>
   </si>
 </sst>
 </file>
@@ -11663,7 +11663,7 @@
         <v>1025</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>1036</v>
@@ -11677,7 +11677,7 @@
         <v>1026</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>1036</v>
@@ -11691,7 +11691,7 @@
         <v>1027</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>1036</v>
@@ -11705,7 +11705,7 @@
         <v>1028</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>1036</v>
@@ -11719,7 +11719,7 @@
         <v>1029</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D475" s="2" t="s">
         <v>1036</v>
@@ -11733,7 +11733,7 @@
         <v>1030</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>1036</v>
@@ -11747,7 +11747,7 @@
         <v>1031</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D477" s="2" t="s">
         <v>1036</v>
@@ -11761,7 +11761,7 @@
         <v>1032</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D478" s="2" t="s">
         <v>1036</v>
@@ -11775,7 +11775,7 @@
         <v>1033</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>1036</v>
@@ -11789,7 +11789,7 @@
         <v>1034</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D480" s="2" t="s">
         <v>1036</v>
@@ -11803,7 +11803,7 @@
         <v>1035</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D481" s="2" t="s">
         <v>1036</v>
@@ -11817,7 +11817,7 @@
         <v>1040</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D482" s="2" t="s">
         <v>1039</v>
@@ -11831,7 +11831,7 @@
         <v>1041</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D483" s="2" t="s">
         <v>1039</v>
@@ -11845,7 +11845,7 @@
         <v>1042</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D484" s="2" t="s">
         <v>1039</v>
@@ -11859,7 +11859,7 @@
         <v>1043</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>1039</v>
@@ -11873,7 +11873,7 @@
         <v>1044</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>1039</v>
@@ -11887,7 +11887,7 @@
         <v>1045</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>1039</v>
@@ -11901,7 +11901,7 @@
         <v>1046</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>1039</v>
@@ -11915,7 +11915,7 @@
         <v>1047</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>1039</v>
@@ -11929,7 +11929,7 @@
         <v>1048</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D490" s="2" t="s">
         <v>1039</v>
@@ -11943,7 +11943,7 @@
         <v>1051</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>1049</v>
@@ -11957,7 +11957,7 @@
         <v>1050</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D492" s="2" t="s">
         <v>1049</v>
@@ -11971,7 +11971,7 @@
         <v>1052</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>1049</v>
@@ -11985,7 +11985,7 @@
         <v>1054</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D494" s="2" t="s">
         <v>1053</v>
@@ -11999,7 +11999,7 @@
         <v>1055</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D495" s="2" t="s">
         <v>1053</v>
@@ -12013,7 +12013,7 @@
         <v>1056</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D496" s="2" t="s">
         <v>1053</v>
@@ -12027,7 +12027,7 @@
         <v>1057</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D497" s="2" t="s">
         <v>1053</v>
@@ -12041,7 +12041,7 @@
         <v>1062</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>1061</v>
@@ -12055,7 +12055,7 @@
         <v>1063</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>1061</v>
@@ -12069,7 +12069,7 @@
         <v>1063</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D500" s="2" t="s">
         <v>1061</v>
@@ -12083,7 +12083,7 @@
         <v>1066</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>1065</v>
@@ -12097,7 +12097,7 @@
         <v>1067</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>1065</v>
@@ -12111,7 +12111,7 @@
         <v>1068</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>1065</v>
@@ -12125,7 +12125,7 @@
         <v>1069</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>1065</v>
@@ -12139,7 +12139,7 @@
         <v>1070</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>1065</v>
@@ -12153,7 +12153,7 @@
         <v>1071</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>1065</v>
@@ -12167,7 +12167,7 @@
         <v>1072</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>1065</v>
@@ -12181,7 +12181,7 @@
         <v>1073</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>1065</v>
@@ -12195,7 +12195,7 @@
         <v>1074</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D509" s="2" t="s">
         <v>1065</v>
@@ -12209,7 +12209,7 @@
         <v>1075</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D510" s="2" t="s">
         <v>1065</v>
@@ -12223,7 +12223,7 @@
         <v>1076</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>1065</v>
@@ -12237,7 +12237,7 @@
         <v>1078</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D512" s="2" t="s">
         <v>1079</v>
@@ -12251,7 +12251,7 @@
         <v>1081</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>1085</v>
@@ -12265,7 +12265,7 @@
         <v>1082</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>1085</v>
@@ -12279,7 +12279,7 @@
         <v>1083</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>1085</v>
@@ -12293,7 +12293,7 @@
         <v>1084</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>1085</v>
@@ -12307,7 +12307,7 @@
         <v>1088</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>1087</v>
@@ -12321,7 +12321,7 @@
         <v>1089</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>1087</v>
@@ -12335,7 +12335,7 @@
         <v>1090</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D519" s="2" t="s">
         <v>1087</v>
@@ -12349,7 +12349,7 @@
         <v>1091</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>1087</v>
@@ -12363,7 +12363,7 @@
         <v>1092</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D521" s="2" t="s">
         <v>1087</v>
@@ -12371,2760 +12371,2760 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="B522" s="1" t="s">
-        <v>1094</v>
-      </c>
       <c r="C522" s="5" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1093</v>
+        <v>1549</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1093</v>
+        <v>1549</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1093</v>
+        <v>1549</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1093</v>
+        <v>1549</v>
       </c>
       <c r="B526" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>1098</v>
-      </c>
-      <c r="C526" s="5" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B543" s="6" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B544" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B546" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B547" s="6" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B548" s="6" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B549" s="6" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B550" s="6" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B551" s="6" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B552" s="6" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B553" s="6" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B554" s="6" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B555" s="6" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B556" s="6" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B557" s="6" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B558" s="6" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B559" s="6" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B560" s="6" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B561" s="6" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B562" s="6" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B563" s="6" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B564" s="6" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B566" s="6" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B567" s="6" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B568" s="6" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B569" s="6" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B570" s="6" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B571" s="6" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B572" s="6" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B573" s="6" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B574" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B575" s="6" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B576" s="6" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C595" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D600" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D603" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C604" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D604" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D605" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C607" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D607" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D609" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D612" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D613" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D614" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B615" s="7" t="s">
         <v>1081</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D615" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D616" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D617" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D618" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D619" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C620" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D620" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D624" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D625" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D626" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C663" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="C663" s="1" t="s">
-        <v>1416</v>
-      </c>
       <c r="D663" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C664" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="C664" s="1" t="s">
-        <v>1418</v>
-      </c>
       <c r="D664" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D671" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D678" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D679" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D680" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D685" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D691" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D692" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D694" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D695" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D696" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D697" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D698" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C699" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D699" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C700" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D700" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D702" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C703" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C704" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C705" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C706" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C707" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C708" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C709" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C710" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C711" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C712" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C713" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D713" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C714" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D714" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C715" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C716" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B717" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D717" s="2" t="s">
         <v>1548</v>
-      </c>
-      <c r="C717" s="1" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D717" s="2" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B718" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="B718" s="1" t="s">
-        <v>1489</v>
-      </c>
       <c r="C718" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D718" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A500ACE6-81B8-4D9C-950B-173025B0BE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05D213-B31B-44AA-BE35-1281E4B60B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1568">
   <si>
     <t>Company</t>
   </si>
@@ -4721,6 +4721,9 @@
   </si>
   <si>
     <t>78970154027720504</t>
+  </si>
+  <si>
+    <t>78970155027722549</t>
   </si>
 </sst>
 </file>
@@ -5092,7 +5095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E722"/>
+  <dimension ref="A1:E723"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" bestFit="1" customWidth="1"/>
@@ -13534,24 +13537,21 @@
         <v>1310</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D601" s="2" t="s">
-        <v>1474</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
@@ -13559,10 +13559,10 @@
         <v>1166</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>1475</v>
@@ -13570,16 +13570,16 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1477</v>
-      </c>
-      <c r="B604" s="7" t="s">
-        <v>1313</v>
+        <v>1166</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>1312</v>
       </c>
       <c r="C604" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D604" s="2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
@@ -13587,10 +13587,10 @@
         <v>1477</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>1476</v>
@@ -13601,10 +13601,10 @@
         <v>1477</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>1476</v>
@@ -13615,10 +13615,10 @@
         <v>1477</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C607" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>1476</v>
@@ -13629,10 +13629,10 @@
         <v>1477</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1563</v>
+        <v>1298</v>
       </c>
       <c r="D608" s="2" t="s">
         <v>1476</v>
@@ -13643,10 +13643,10 @@
         <v>1477</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1300</v>
+        <v>1563</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>1476</v>
@@ -13657,10 +13657,10 @@
         <v>1477</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>1476</v>
@@ -13671,10 +13671,10 @@
         <v>1477</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1562</v>
+        <v>1301</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>1476</v>
@@ -13685,10 +13685,10 @@
         <v>1477</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>1195</v>
+        <v>1562</v>
       </c>
       <c r="D612" s="2" t="s">
         <v>1476</v>
@@ -13699,10 +13699,10 @@
         <v>1477</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>1476</v>
@@ -13713,10 +13713,10 @@
         <v>1477</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>1476</v>
@@ -13727,10 +13727,10 @@
         <v>1477</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1306</v>
+        <v>1197</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>1476</v>
@@ -13741,10 +13741,10 @@
         <v>1477</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>1476</v>
@@ -13755,10 +13755,10 @@
         <v>1477</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>1476</v>
@@ -13769,10 +13769,10 @@
         <v>1477</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>1476</v>
@@ -13783,10 +13783,10 @@
         <v>1477</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1081</v>
+        <v>1327</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1366</v>
+        <v>1309</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>1476</v>
@@ -13797,10 +13797,10 @@
         <v>1477</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1328</v>
+        <v>1081</v>
       </c>
       <c r="C620" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>1476</v>
@@ -13811,10 +13811,10 @@
         <v>1477</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>1476</v>
@@ -13825,10 +13825,10 @@
         <v>1477</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>1476</v>
@@ -13839,10 +13839,10 @@
         <v>1477</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D623" s="2" t="s">
         <v>1476</v>
@@ -13853,10 +13853,10 @@
         <v>1477</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D624" s="2" t="s">
         <v>1476</v>
@@ -13867,10 +13867,10 @@
         <v>1477</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>1476</v>
@@ -13881,10 +13881,10 @@
         <v>1477</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D626" s="2" t="s">
         <v>1476</v>
@@ -13895,10 +13895,10 @@
         <v>1477</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>1476</v>
@@ -13909,10 +13909,10 @@
         <v>1477</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D628" s="2" t="s">
         <v>1476</v>
@@ -13923,10 +13923,10 @@
         <v>1477</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D629" s="2" t="s">
         <v>1476</v>
@@ -13937,10 +13937,10 @@
         <v>1477</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D630" s="2" t="s">
         <v>1476</v>
@@ -13951,10 +13951,10 @@
         <v>1477</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>1476</v>
@@ -13965,10 +13965,10 @@
         <v>1477</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>1476</v>
@@ -13979,10 +13979,10 @@
         <v>1477</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>1476</v>
@@ -13993,10 +13993,10 @@
         <v>1477</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>1476</v>
@@ -14007,10 +14007,10 @@
         <v>1477</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>1476</v>
@@ -14021,10 +14021,10 @@
         <v>1477</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D636" s="2" t="s">
         <v>1476</v>
@@ -14035,10 +14035,10 @@
         <v>1477</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>1476</v>
@@ -14049,10 +14049,10 @@
         <v>1477</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>1476</v>
@@ -14063,10 +14063,10 @@
         <v>1477</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>1476</v>
@@ -14077,10 +14077,10 @@
         <v>1477</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>1476</v>
@@ -14091,10 +14091,10 @@
         <v>1477</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D641" s="2" t="s">
         <v>1476</v>
@@ -14105,10 +14105,10 @@
         <v>1477</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>1476</v>
@@ -14119,10 +14119,10 @@
         <v>1477</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>1476</v>
@@ -14133,10 +14133,10 @@
         <v>1477</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>1476</v>
@@ -14147,10 +14147,10 @@
         <v>1477</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>1476</v>
@@ -14161,10 +14161,10 @@
         <v>1477</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>1476</v>
@@ -14175,10 +14175,10 @@
         <v>1477</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D647" s="2" t="s">
         <v>1476</v>
@@ -14189,10 +14189,10 @@
         <v>1477</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D648" s="2" t="s">
         <v>1476</v>
@@ -14203,10 +14203,10 @@
         <v>1477</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>1476</v>
@@ -14217,10 +14217,10 @@
         <v>1477</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>1476</v>
@@ -14231,10 +14231,10 @@
         <v>1477</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="D651" s="2" t="s">
         <v>1476</v>
@@ -14245,10 +14245,10 @@
         <v>1477</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D652" s="2" t="s">
         <v>1476</v>
@@ -14259,10 +14259,10 @@
         <v>1477</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D653" s="2" t="s">
         <v>1476</v>
@@ -14273,10 +14273,10 @@
         <v>1477</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D654" s="2" t="s">
         <v>1476</v>
@@ -14287,10 +14287,10 @@
         <v>1477</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>1476</v>
@@ -14301,10 +14301,10 @@
         <v>1477</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D656" s="2" t="s">
         <v>1476</v>
@@ -14315,10 +14315,10 @@
         <v>1477</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D657" s="2" t="s">
         <v>1476</v>
@@ -14326,13 +14326,13 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1478</v>
-      </c>
-      <c r="B658" s="1" t="s">
-        <v>1405</v>
+        <v>1477</v>
+      </c>
+      <c r="B658" s="7" t="s">
+        <v>1365</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>1554</v>
+        <v>1404</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>1476</v>
@@ -14343,10 +14343,10 @@
         <v>1478</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>1476</v>
@@ -14357,10 +14357,10 @@
         <v>1478</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D660" s="2" t="s">
         <v>1476</v>
@@ -14371,10 +14371,10 @@
         <v>1478</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D661" s="2" t="s">
         <v>1476</v>
@@ -14385,10 +14385,10 @@
         <v>1478</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>1476</v>
@@ -14399,10 +14399,10 @@
         <v>1478</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>1476</v>
@@ -14413,10 +14413,10 @@
         <v>1478</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>1476</v>
@@ -14427,10 +14427,10 @@
         <v>1478</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>1476</v>
@@ -14438,13 +14438,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>1292</v>
+        <v>1561</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>1476</v>
@@ -14452,13 +14452,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>1415</v>
+        <v>1292</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>1476</v>
@@ -14466,30 +14466,30 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1167</v>
+        <v>1480</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>1434</v>
+        <v>1417</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
@@ -14497,10 +14497,10 @@
         <v>1168</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>1482</v>
@@ -14511,10 +14511,10 @@
         <v>1168</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>1482</v>
@@ -14525,10 +14525,10 @@
         <v>1168</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>1482</v>
@@ -14539,10 +14539,10 @@
         <v>1168</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>1482</v>
@@ -14553,10 +14553,10 @@
         <v>1168</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>1482</v>
@@ -14567,10 +14567,10 @@
         <v>1168</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>1482</v>
@@ -14581,10 +14581,10 @@
         <v>1168</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>1482</v>
@@ -14595,10 +14595,10 @@
         <v>1168</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>1482</v>
@@ -14609,10 +14609,10 @@
         <v>1168</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>1482</v>
@@ -14623,10 +14623,10 @@
         <v>1168</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D679" s="2" t="s">
         <v>1482</v>
@@ -14637,10 +14637,10 @@
         <v>1168</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>1482</v>
@@ -14651,10 +14651,10 @@
         <v>1168</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D681" s="2" t="s">
         <v>1482</v>
@@ -14665,10 +14665,10 @@
         <v>1168</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D682" s="2" t="s">
         <v>1482</v>
@@ -14679,10 +14679,10 @@
         <v>1168</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>1482</v>
@@ -14693,10 +14693,10 @@
         <v>1168</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D684" s="2" t="s">
         <v>1482</v>
@@ -14707,10 +14707,10 @@
         <v>1168</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D685" s="2" t="s">
         <v>1482</v>
@@ -14718,16 +14718,16 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1483</v>
+        <v>1168</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1455</v>
+        <v>1420</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
@@ -14735,10 +14735,10 @@
         <v>1483</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D687" s="2" t="s">
         <v>1476</v>
@@ -14746,13 +14746,13 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1414</v>
+        <v>1456</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D688" s="2" t="s">
         <v>1476</v>
@@ -14760,16 +14760,16 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1169</v>
+        <v>1484</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1451</v>
+        <v>1414</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
@@ -14777,10 +14777,10 @@
         <v>1169</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D690" s="2" t="s">
         <v>1485</v>
@@ -14791,10 +14791,10 @@
         <v>1169</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D691" s="2" t="s">
         <v>1485</v>
@@ -14805,10 +14805,10 @@
         <v>1169</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D692" s="2" t="s">
         <v>1485</v>
@@ -14816,16 +14816,16 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1486</v>
+        <v>1169</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1519</v>
+        <v>1454</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>1489</v>
+        <v>1463</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>1548</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
@@ -14833,10 +14833,10 @@
         <v>1486</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D694" s="2" t="s">
         <v>1548</v>
@@ -14847,10 +14847,10 @@
         <v>1486</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D695" s="2" t="s">
         <v>1548</v>
@@ -14861,10 +14861,10 @@
         <v>1486</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D696" s="2" t="s">
         <v>1548</v>
@@ -14875,10 +14875,10 @@
         <v>1486</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D697" s="2" t="s">
         <v>1548</v>
@@ -14889,10 +14889,10 @@
         <v>1486</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D698" s="2" t="s">
         <v>1548</v>
@@ -14903,10 +14903,10 @@
         <v>1486</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C699" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D699" s="2" t="s">
         <v>1548</v>
@@ -14917,10 +14917,10 @@
         <v>1486</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C700" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D700" s="2" t="s">
         <v>1548</v>
@@ -14931,10 +14931,10 @@
         <v>1486</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D701" s="2" t="s">
         <v>1548</v>
@@ -14945,10 +14945,10 @@
         <v>1486</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D702" s="2" t="s">
         <v>1548</v>
@@ -14959,10 +14959,10 @@
         <v>1486</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C703" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D703" s="2" t="s">
         <v>1548</v>
@@ -14973,10 +14973,10 @@
         <v>1486</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C704" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D704" s="2" t="s">
         <v>1548</v>
@@ -14987,10 +14987,10 @@
         <v>1486</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C705" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>1548</v>
@@ -15001,10 +15001,10 @@
         <v>1486</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C706" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D706" s="2" t="s">
         <v>1548</v>
@@ -15015,10 +15015,10 @@
         <v>1486</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C707" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D707" s="2" t="s">
         <v>1548</v>
@@ -15029,10 +15029,10 @@
         <v>1486</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C708" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D708" s="2" t="s">
         <v>1548</v>
@@ -15043,10 +15043,10 @@
         <v>1486</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C709" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D709" s="2" t="s">
         <v>1548</v>
@@ -15057,10 +15057,10 @@
         <v>1486</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C710" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D710" s="2" t="s">
         <v>1548</v>
@@ -15071,10 +15071,10 @@
         <v>1486</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C711" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D711" s="2" t="s">
         <v>1548</v>
@@ -15085,10 +15085,10 @@
         <v>1486</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C712" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D712" s="2" t="s">
         <v>1548</v>
@@ -15099,10 +15099,10 @@
         <v>1486</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C713" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D713" s="2" t="s">
         <v>1548</v>
@@ -15113,10 +15113,10 @@
         <v>1486</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C714" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D714" s="2" t="s">
         <v>1548</v>
@@ -15127,10 +15127,10 @@
         <v>1486</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C715" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D715" s="2" t="s">
         <v>1548</v>
@@ -15141,10 +15141,10 @@
         <v>1486</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C716" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D716" s="2" t="s">
         <v>1548</v>
@@ -15155,10 +15155,10 @@
         <v>1486</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C717" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D717" s="2" t="s">
         <v>1548</v>
@@ -15169,10 +15169,10 @@
         <v>1486</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C718" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D718" s="2" t="s">
         <v>1548</v>
@@ -15183,10 +15183,10 @@
         <v>1486</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C719" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>1548</v>
@@ -15197,10 +15197,10 @@
         <v>1486</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C720" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>1548</v>
@@ -15211,10 +15211,10 @@
         <v>1486</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C721" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D721" s="2" t="s">
         <v>1548</v>
@@ -15222,15 +15222,29 @@
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C722" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D722" s="2" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
         <v>1487</v>
       </c>
-      <c r="B722" s="1" t="s">
+      <c r="B723" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="C722" s="1" t="s">
+      <c r="C723" s="1" t="s">
         <v>1518</v>
       </c>
-      <c r="D722" s="2" t="s">
+      <c r="D723" s="2" t="s">
         <v>1548</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F265123E-B353-4F25-8959-C75AAE134471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B0CBA3-80C6-420A-A4D4-CAD7C74C9E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2903" uniqueCount="1590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="1591">
   <si>
     <t>Company</t>
   </si>
@@ -4790,6 +4790,9 @@
   </si>
   <si>
     <t>78970151027720906</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -11500,6 +11503,9 @@
       <c r="A450" s="1" t="s">
         <v>881</v>
       </c>
+      <c r="B450" s="2" t="s">
+        <v>1590</v>
+      </c>
       <c r="C450" s="2" t="s">
         <v>854</v>
       </c>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B0CBA3-80C6-420A-A4D4-CAD7C74C9E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6367615-70D1-4471-A4F7-B859B230ECB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6367615-70D1-4471-A4F7-B859B230ECB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0E6FAB-8338-400C-BFA1-B27B865AFF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0E6FAB-8338-400C-BFA1-B27B865AFF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D678430B-D0C8-442E-BD4B-29F97367D05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4444,18 +4444,9 @@
     <t>000093442</t>
   </si>
   <si>
-    <t>ОБЩИНА ВАРНА % 1</t>
-  </si>
-  <si>
     <t>ОБЩИНА ВАРНА % 2 - ОБЩИНСКА ПОЛИЦИЯ</t>
   </si>
   <si>
-    <t>ОБЩИНА ВАРНА % 3 - ОИЦ</t>
-  </si>
-  <si>
-    <t>ОБЩИНА ВАРНА % 4 - УА</t>
-  </si>
-  <si>
     <t>0000934420057</t>
   </si>
   <si>
@@ -4793,6 +4784,15 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 3 - РАЗХОД ПО ПРОЕКТ ОИЦ ВАРНА</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 1 - АВТОПАРК</t>
   </si>
 </sst>
 </file>
@@ -5974,7 +5974,7 @@
         <v>912</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>913</v>
@@ -6041,10 +6041,10 @@
         <v>916</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>917</v>
@@ -6055,10 +6055,10 @@
         <v>916</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>917</v>
@@ -6069,10 +6069,10 @@
         <v>918</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>919</v>
@@ -9236,7 +9236,7 @@
         <v>555</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>967</v>
@@ -11000,7 +11000,7 @@
         <v>773</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>989</v>
@@ -11042,7 +11042,7 @@
         <v>776</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>989</v>
@@ -11056,7 +11056,7 @@
         <v>777</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>989</v>
@@ -11070,7 +11070,7 @@
         <v>778</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>989</v>
@@ -11196,7 +11196,7 @@
         <v>787</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>989</v>
@@ -11207,7 +11207,7 @@
         <v>979</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>814</v>
@@ -11504,7 +11504,7 @@
         <v>881</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>854</v>
@@ -12606,7 +12606,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>1091</v>
@@ -12620,7 +12620,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>1092</v>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>1093</v>
@@ -12648,7 +12648,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>1094</v>
@@ -12662,7 +12662,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>1095</v>
@@ -13662,7 +13662,7 @@
         <v>1308</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1471</v>
@@ -13676,7 +13676,7 @@
         <v>1309</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1472</v>
@@ -13690,7 +13690,7 @@
         <v>1310</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1472</v>
@@ -13698,13 +13698,13 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B605" s="7" t="s">
         <v>1311</v>
       </c>
       <c r="C605" s="8" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1473</v>
@@ -13712,13 +13712,13 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B606" s="7" t="s">
         <v>1312</v>
       </c>
       <c r="C606" s="8" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D606" s="3" t="s">
         <v>1473</v>
@@ -13726,13 +13726,13 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>1313</v>
       </c>
       <c r="C607" s="8" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D607" s="3" t="s">
         <v>1473</v>
@@ -13740,13 +13740,13 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B608" s="7" t="s">
         <v>1314</v>
       </c>
       <c r="C608" s="8" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1473</v>
@@ -13754,13 +13754,13 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B609" s="7" t="s">
         <v>1315</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1473</v>
@@ -13768,13 +13768,13 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B610" s="7" t="s">
         <v>1316</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1473</v>
@@ -13782,13 +13782,13 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B611" s="7" t="s">
         <v>1317</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1473</v>
@@ -13796,13 +13796,13 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B612" s="7" t="s">
         <v>1318</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1473</v>
@@ -13810,13 +13810,13 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B613" s="7" t="s">
         <v>1319</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1473</v>
@@ -13824,13 +13824,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B614" s="7" t="s">
         <v>1320</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1473</v>
@@ -13838,13 +13838,13 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B615" s="7" t="s">
         <v>1321</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1473</v>
@@ -13852,13 +13852,13 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B616" s="7" t="s">
         <v>1322</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1473</v>
@@ -13866,13 +13866,13 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B617" s="7" t="s">
         <v>1323</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1473</v>
@@ -13880,13 +13880,13 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>1324</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1473</v>
@@ -13894,13 +13894,13 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B619" s="7" t="s">
         <v>1325</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1473</v>
@@ -13908,7 +13908,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B620" s="7" t="s">
         <v>1079</v>
@@ -13922,7 +13922,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B621" s="7" t="s">
         <v>1326</v>
@@ -13936,7 +13936,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B622" s="7" t="s">
         <v>1327</v>
@@ -13950,7 +13950,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B623" s="7" t="s">
         <v>1328</v>
@@ -13964,7 +13964,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B624" s="7" t="s">
         <v>1329</v>
@@ -13978,7 +13978,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B625" s="7" t="s">
         <v>1330</v>
@@ -13992,7 +13992,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B626" s="7" t="s">
         <v>1331</v>
@@ -14006,7 +14006,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B627" s="7" t="s">
         <v>1332</v>
@@ -14020,7 +14020,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B628" s="7" t="s">
         <v>1333</v>
@@ -14034,7 +14034,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>1334</v>
@@ -14048,7 +14048,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B630" s="7" t="s">
         <v>1335</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B631" s="7" t="s">
         <v>1336</v>
@@ -14076,7 +14076,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B632" s="7" t="s">
         <v>1337</v>
@@ -14090,7 +14090,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B633" s="7" t="s">
         <v>1338</v>
@@ -14104,7 +14104,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B634" s="7" t="s">
         <v>1339</v>
@@ -14118,7 +14118,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B635" s="7" t="s">
         <v>1340</v>
@@ -14132,7 +14132,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B636" s="7" t="s">
         <v>1341</v>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B637" s="7" t="s">
         <v>1342</v>
@@ -14160,7 +14160,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B638" s="7" t="s">
         <v>1343</v>
@@ -14174,7 +14174,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B639" s="7" t="s">
         <v>1344</v>
@@ -14188,7 +14188,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>1345</v>
@@ -14202,7 +14202,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B641" s="7" t="s">
         <v>1346</v>
@@ -14216,7 +14216,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B642" s="7" t="s">
         <v>1347</v>
@@ -14230,7 +14230,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B643" s="7" t="s">
         <v>1348</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B644" s="7" t="s">
         <v>1349</v>
@@ -14258,7 +14258,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B645" s="7" t="s">
         <v>1350</v>
@@ -14272,7 +14272,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B646" s="7" t="s">
         <v>1351</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B647" s="7" t="s">
         <v>1352</v>
@@ -14300,7 +14300,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B648" s="7" t="s">
         <v>1353</v>
@@ -14314,7 +14314,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B649" s="7" t="s">
         <v>1354</v>
@@ -14328,7 +14328,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B650" s="7" t="s">
         <v>1355</v>
@@ -14342,7 +14342,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>1356</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B652" s="7" t="s">
         <v>1357</v>
@@ -14370,7 +14370,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B653" s="7" t="s">
         <v>1358</v>
@@ -14384,7 +14384,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B654" s="7" t="s">
         <v>1359</v>
@@ -14398,7 +14398,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B655" s="7" t="s">
         <v>1360</v>
@@ -14412,7 +14412,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B656" s="7" t="s">
         <v>1361</v>
@@ -14426,7 +14426,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B657" s="7" t="s">
         <v>1362</v>
@@ -14440,13 +14440,13 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1474</v>
+        <v>1590</v>
       </c>
       <c r="B658" s="7" t="s">
         <v>1363</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1473</v>
@@ -14454,13 +14454,13 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>1402</v>
       </c>
       <c r="C659" s="8" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1473</v>
@@ -14468,13 +14468,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>1403</v>
       </c>
       <c r="C660" s="8" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1473</v>
@@ -14482,13 +14482,13 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="C661" s="8" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1473</v>
@@ -14496,13 +14496,13 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C662" s="8" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1473</v>
@@ -14510,13 +14510,13 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>1406</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1473</v>
@@ -14524,13 +14524,13 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1473</v>
@@ -14538,13 +14538,13 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>1408</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1473</v>
@@ -14552,13 +14552,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>1409</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1473</v>
@@ -14566,13 +14566,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1476</v>
+        <v>1588</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>1410</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1473</v>
@@ -14580,7 +14580,7 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1477</v>
+        <v>1589</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>1411</v>
@@ -14603,7 +14603,7 @@
         <v>1414</v>
       </c>
       <c r="D669" s="3" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
@@ -14611,13 +14611,13 @@
         <v>1165</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="C670" s="9" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="D670" s="3" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
@@ -14631,7 +14631,7 @@
         <v>1431</v>
       </c>
       <c r="D671" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
@@ -14645,7 +14645,7 @@
         <v>1432</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
@@ -14659,7 +14659,7 @@
         <v>1433</v>
       </c>
       <c r="D673" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
@@ -14673,7 +14673,7 @@
         <v>1434</v>
       </c>
       <c r="D674" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
@@ -14687,7 +14687,7 @@
         <v>1435</v>
       </c>
       <c r="D675" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
@@ -14701,7 +14701,7 @@
         <v>1436</v>
       </c>
       <c r="D676" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
@@ -14715,7 +14715,7 @@
         <v>1437</v>
       </c>
       <c r="D677" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
@@ -14729,7 +14729,7 @@
         <v>1438</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
@@ -14743,7 +14743,7 @@
         <v>1439</v>
       </c>
       <c r="D679" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
@@ -14757,7 +14757,7 @@
         <v>1440</v>
       </c>
       <c r="D680" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
@@ -14771,7 +14771,7 @@
         <v>1441</v>
       </c>
       <c r="D681" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
@@ -14785,7 +14785,7 @@
         <v>1442</v>
       </c>
       <c r="D682" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
@@ -14799,7 +14799,7 @@
         <v>1443</v>
       </c>
       <c r="D683" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
@@ -14813,7 +14813,7 @@
         <v>1444</v>
       </c>
       <c r="D684" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
@@ -14827,7 +14827,7 @@
         <v>1445</v>
       </c>
       <c r="D685" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
@@ -14841,7 +14841,7 @@
         <v>1446</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
@@ -14855,12 +14855,12 @@
         <v>1447</v>
       </c>
       <c r="D687" s="3" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>1452</v>
@@ -14874,7 +14874,7 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>1453</v>
@@ -14888,7 +14888,7 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>1411</v>
@@ -14911,7 +14911,7 @@
         <v>1457</v>
       </c>
       <c r="D691" s="3" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
@@ -14925,7 +14925,7 @@
         <v>1458</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
@@ -14939,7 +14939,7 @@
         <v>1459</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
@@ -14953,427 +14953,427 @@
         <v>1460</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C695" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="B695" s="2" t="s">
-        <v>1516</v>
-      </c>
-      <c r="C695" s="2" t="s">
-        <v>1486</v>
-      </c>
       <c r="D695" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="D697" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="D698" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="D699" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="D701" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="D703" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="D704" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="D705" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D707" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="D709" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B721" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C721" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D721" s="3" t="s">
         <v>1542</v>
-      </c>
-      <c r="C721" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D721" s="3" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="D723" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="D724" s="3" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBD1461-58B6-4EFB-BAD6-3578456EB50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0278384-C322-47D2-88E4-CA98F5F25899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4820,7 +4820,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4837,12 +4837,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -4912,15 +4906,15 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10817,17 +10811,17 @@
         <v>988</v>
       </c>
     </row>
-    <row r="400" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="11" t="s">
+    <row r="400" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A400" s="13" t="s">
         <v>978</v>
       </c>
-      <c r="B400" s="12" t="s">
+      <c r="B400" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="C400" s="12" t="s">
+      <c r="C400" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="D400" s="13" t="s">
+      <c r="D400" s="15" t="s">
         <v>988</v>
       </c>
     </row>
@@ -10859,17 +10853,17 @@
         <v>988</v>
       </c>
     </row>
-    <row r="403" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="11" t="s">
+    <row r="403" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A403" s="13" t="s">
         <v>978</v>
       </c>
-      <c r="B403" s="12" t="s">
+      <c r="B403" s="14" t="s">
         <v>760</v>
       </c>
-      <c r="C403" s="12" t="s">
+      <c r="C403" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="D403" s="13" t="s">
+      <c r="D403" s="15" t="s">
         <v>988</v>
       </c>
     </row>
@@ -12503,10 +12497,10 @@
       <c r="A518" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="B518" s="14" t="s">
+      <c r="B518" s="11" t="s">
         <v>1591</v>
       </c>
-      <c r="C518" s="15" t="s">
+      <c r="C518" s="12" t="s">
         <v>1592</v>
       </c>
       <c r="D518" s="3" t="s">

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0278384-C322-47D2-88E4-CA98F5F25899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B461D627-E2F6-41F2-AB82-B4B87B999880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1594">
   <si>
     <t>Company</t>
   </si>
@@ -3187,9 +3187,6 @@
     <t>В2071ХК</t>
   </si>
   <si>
-    <t>КСУДПЛУ  СВ. ЙОАН  ЗЛАТОУСТ</t>
-  </si>
-  <si>
     <t>РАЙОН АСПАРУХОВО</t>
   </si>
   <si>
@@ -4799,6 +4796,12 @@
   </si>
   <si>
     <t>78970155027722754</t>
+  </si>
+  <si>
+    <t>КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
+  </si>
+  <si>
+    <t>КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
   </si>
 </sst>
 </file>
@@ -4878,7 +4881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4910,11 +4913,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5264,7 +5262,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>901</v>
@@ -5989,7 +5987,7 @@
         <v>911</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>912</v>
@@ -6056,10 +6054,10 @@
         <v>915</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>916</v>
@@ -6070,10 +6068,10 @@
         <v>915</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>916</v>
@@ -6084,10 +6082,10 @@
         <v>917</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>918</v>
@@ -9251,7 +9249,7 @@
         <v>554</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>966</v>
@@ -10811,17 +10809,17 @@
         <v>988</v>
       </c>
     </row>
-    <row r="400" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="13" t="s">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B400" s="14" t="s">
+      <c r="B400" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="C400" s="14" t="s">
+      <c r="C400" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="D400" s="15" t="s">
+      <c r="D400" s="3" t="s">
         <v>988</v>
       </c>
     </row>
@@ -10853,17 +10851,17 @@
         <v>988</v>
       </c>
     </row>
-    <row r="403" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="13" t="s">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B403" s="14" t="s">
+      <c r="B403" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="C403" s="14" t="s">
+      <c r="C403" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="D403" s="15" t="s">
+      <c r="D403" s="3" t="s">
         <v>988</v>
       </c>
     </row>
@@ -11015,7 +11013,7 @@
         <v>772</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11057,7 +11055,7 @@
         <v>775</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11071,7 +11069,7 @@
         <v>776</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11085,7 +11083,7 @@
         <v>777</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11211,7 +11209,7 @@
         <v>786</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11222,7 +11220,7 @@
         <v>978</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>813</v>
@@ -11519,7 +11517,7 @@
         <v>880</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>853</v>
@@ -11913,7 +11911,7 @@
         <v>1022</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D476" s="3" t="s">
         <v>1033</v>
@@ -11927,7 +11925,7 @@
         <v>1023</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1033</v>
@@ -11941,7 +11939,7 @@
         <v>1024</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>1033</v>
@@ -11955,7 +11953,7 @@
         <v>1025</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>1033</v>
@@ -11969,7 +11967,7 @@
         <v>1026</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>1033</v>
@@ -11983,7 +11981,7 @@
         <v>1027</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D481" s="3" t="s">
         <v>1033</v>
@@ -11997,7 +11995,7 @@
         <v>1028</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>1033</v>
@@ -12011,7 +12009,7 @@
         <v>1029</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>1033</v>
@@ -12025,7 +12023,7 @@
         <v>1030</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D484" s="3" t="s">
         <v>1033</v>
@@ -12039,7 +12037,7 @@
         <v>1031</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1033</v>
@@ -12053,7 +12051,7 @@
         <v>1032</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1033</v>
@@ -12067,7 +12065,7 @@
         <v>1037</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D487" s="3" t="s">
         <v>1036</v>
@@ -12081,7 +12079,7 @@
         <v>1038</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1036</v>
@@ -12095,7 +12093,7 @@
         <v>1039</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1036</v>
@@ -12109,7 +12107,7 @@
         <v>1040</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1036</v>
@@ -12123,7 +12121,7 @@
         <v>1041</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D491" s="3" t="s">
         <v>1036</v>
@@ -12137,7 +12135,7 @@
         <v>1042</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D492" s="3" t="s">
         <v>1036</v>
@@ -12151,7 +12149,7 @@
         <v>1043</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>1036</v>
@@ -12165,7 +12163,7 @@
         <v>1044</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1036</v>
@@ -12179,7 +12177,7 @@
         <v>1045</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>1036</v>
@@ -12187,13 +12185,13 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>1055</v>
+        <v>1592</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>1048</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>1046</v>
@@ -12201,13 +12199,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>1055</v>
+        <v>1593</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>1047</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>1046</v>
@@ -12215,13 +12213,13 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>1055</v>
+        <v>1593</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>1049</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1046</v>
@@ -12229,13 +12227,13 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>1051</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D499" s="3" t="s">
         <v>1050</v>
@@ -12243,13 +12241,13 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>1052</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D500" s="3" t="s">
         <v>1050</v>
@@ -12257,13 +12255,13 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>1053</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>1050</v>
@@ -12271,13 +12269,13 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>1054</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>1050</v>
@@ -12285,3124 +12283,3124 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C503" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D503" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C503" s="6" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D503" s="3" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C504" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D504" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="B504" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C504" s="6" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D504" s="3" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C505" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D505" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="B505" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C505" s="6" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D505" s="3" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C506" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D506" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B506" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C506" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D506" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C507" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D507" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B507" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C507" s="6" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D507" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C508" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D508" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C508" s="6" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D508" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C509" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D509" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C509" s="6" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D509" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C510" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D510" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B510" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C510" s="6" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D510" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C511" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D511" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B511" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C511" s="6" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D511" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C512" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D512" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C512" s="6" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D512" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C513" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D513" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B513" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C513" s="6" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D513" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C514" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D514" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C514" s="6" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D514" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C515" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D515" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B515" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C515" s="6" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D515" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C516" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D516" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B516" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C516" s="6" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D516" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B517" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="C517" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D517" s="3" t="s">
         <v>1075</v>
-      </c>
-      <c r="C517" s="6" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D517" s="3" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="518" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B518" s="11" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C518" s="12" t="s">
         <v>1591</v>
       </c>
-      <c r="C518" s="12" t="s">
-        <v>1592</v>
-      </c>
       <c r="D518" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B519" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="B519" s="2" t="s">
-        <v>1078</v>
-      </c>
       <c r="C519" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B522" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C522" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D522" s="3" t="s">
         <v>1081</v>
-      </c>
-      <c r="C522" s="6" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D522" s="3" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C523" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D523" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="B523" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C523" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D523" s="3" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C524" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D524" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="B524" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C524" s="6" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D524" s="3" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C525" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D525" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="B525" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C525" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D525" s="3" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C526" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D526" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="B526" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C526" s="6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D526" s="3" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C527" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D527" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="B527" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C527" s="6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D527" s="3" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B532" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C532" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D532" s="3" t="s">
         <v>1094</v>
-      </c>
-      <c r="C532" s="6" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D532" s="3" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D536" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B549" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B550" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B551" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B555" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D563" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D564" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D565" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D566" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D569" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D573" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D574" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D579" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D580" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D583" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D589" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D590" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D591" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D592" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D594" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D595" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D596" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D597" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D598" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D599" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D600" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D601" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D602" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D603" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D604" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D605" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C606" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D606" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C607" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C608" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D609" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D610" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D611" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D612" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D614" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D615" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D616" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D617" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D618" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D619" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D620" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C621" s="9" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D621" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D622" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C623" s="9" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D623" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D624" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C625" s="9" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D625" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D626" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C627" s="9" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D627" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D628" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C629" s="9" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D629" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D630" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C631" s="9" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D631" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D632" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C633" s="9" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D633" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D634" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C635" s="9" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D635" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D636" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C637" s="9" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D637" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D638" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C639" s="9" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D639" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C640" s="10" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D640" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C641" s="9" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D641" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C642" s="10" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D642" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C643" s="9" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D643" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C644" s="10" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="D644" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C645" s="9" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C646" s="10" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D646" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C647" s="9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D647" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C648" s="10" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="D648" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C649" s="9" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D649" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C650" s="10" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D650" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C651" s="9" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D651" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C652" s="10" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D652" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C653" s="9" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D653" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C654" s="10" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D654" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C655" s="9" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D655" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C656" s="10" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="D656" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C657" s="9" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D657" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C658" s="10" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D658" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D659" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C660" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D660" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C661" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D661" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C662" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D662" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D663" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D664" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D665" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D666" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D667" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D668" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B669" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C669" s="9" t="s">
         <v>1410</v>
       </c>
-      <c r="C669" s="9" t="s">
-        <v>1411</v>
-      </c>
       <c r="D669" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B670" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C670" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="C670" s="2" t="s">
-        <v>1413</v>
-      </c>
       <c r="D670" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C671" s="9" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D671" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C672" s="10" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C673" s="9" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="D673" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C674" s="10" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D674" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C675" s="9" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D675" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C676" s="10" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D676" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C677" s="9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D677" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C678" s="10" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C679" s="9" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D679" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C680" s="10" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D680" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C681" s="9" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D681" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C682" s="10" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D682" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C683" s="9" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D683" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C684" s="10" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D684" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C685" s="9" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D685" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C686" s="10" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C687" s="9" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D687" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C688" s="10" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D688" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C689" s="10" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D689" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C690" s="9" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D690" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D691" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D695" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D697" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D698" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D699" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D701" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D703" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D704" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D705" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D707" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D709" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D721" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D723" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B724" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D724" s="3" t="s">
         <v>1540</v>
-      </c>
-      <c r="C724" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D724" s="3" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B725" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="B725" s="2" t="s">
-        <v>1481</v>
-      </c>
       <c r="C725" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D725" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B461D627-E2F6-41F2-AB82-B4B87B999880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066F32F-CFBA-46A4-A4DF-F1457F2C6B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1593">
   <si>
     <t>Company</t>
   </si>
@@ -4447,9 +4447,6 @@
     <t>0000934421679</t>
   </si>
   <si>
-    <t>ОБЩИНА ВАРНА % 5 - ПГД</t>
-  </si>
-  <si>
     <t>ОБЩИНА ВАРНА % 6 - УА</t>
   </si>
   <si>
@@ -4801,7 +4798,7 @@
     <t>КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
   </si>
   <si>
-    <t>КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
+    <t>ОБЩИНА ВАРНА % 5 - ПДГ</t>
   </si>
 </sst>
 </file>
@@ -5262,7 +5259,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>901</v>
@@ -5987,7 +5984,7 @@
         <v>911</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>912</v>
@@ -6054,10 +6051,10 @@
         <v>915</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>916</v>
@@ -6068,10 +6065,10 @@
         <v>915</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>916</v>
@@ -6082,10 +6079,10 @@
         <v>917</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>918</v>
@@ -9249,7 +9246,7 @@
         <v>554</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>966</v>
@@ -11013,7 +11010,7 @@
         <v>772</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11055,7 +11052,7 @@
         <v>775</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11069,7 +11066,7 @@
         <v>776</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11083,7 +11080,7 @@
         <v>777</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11209,7 +11206,7 @@
         <v>786</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11220,7 +11217,7 @@
         <v>978</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>813</v>
@@ -11517,7 +11514,7 @@
         <v>880</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>853</v>
@@ -12185,7 +12182,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>1048</v>
@@ -12199,7 +12196,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>1047</v>
@@ -12213,7 +12210,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>1049</v>
@@ -12496,10 +12493,10 @@
         <v>1073</v>
       </c>
       <c r="B518" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C518" s="12" t="s">
         <v>1590</v>
-      </c>
-      <c r="C518" s="12" t="s">
-        <v>1591</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>1075</v>
@@ -12633,7 +12630,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>1089</v>
@@ -12647,7 +12644,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>1090</v>
@@ -12661,7 +12658,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>1091</v>
@@ -12675,7 +12672,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>1092</v>
@@ -12689,7 +12686,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>1093</v>
@@ -13689,7 +13686,7 @@
         <v>1306</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1469</v>
@@ -13703,7 +13700,7 @@
         <v>1307</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1470</v>
@@ -13717,7 +13714,7 @@
         <v>1308</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1470</v>
@@ -13725,13 +13722,13 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B606" s="7" t="s">
         <v>1309</v>
       </c>
       <c r="C606" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D606" s="3" t="s">
         <v>1471</v>
@@ -13739,13 +13736,13 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>1310</v>
       </c>
       <c r="C607" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D607" s="3" t="s">
         <v>1471</v>
@@ -13753,13 +13750,13 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B608" s="7" t="s">
         <v>1311</v>
       </c>
       <c r="C608" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1471</v>
@@ -13767,13 +13764,13 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B609" s="7" t="s">
         <v>1312</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1471</v>
@@ -13781,13 +13778,13 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B610" s="7" t="s">
         <v>1313</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1471</v>
@@ -13795,13 +13792,13 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B611" s="7" t="s">
         <v>1314</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1471</v>
@@ -13809,13 +13806,13 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B612" s="7" t="s">
         <v>1315</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1471</v>
@@ -13823,13 +13820,13 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B613" s="7" t="s">
         <v>1316</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1471</v>
@@ -13837,13 +13834,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B614" s="7" t="s">
         <v>1317</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1471</v>
@@ -13851,13 +13848,13 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B615" s="7" t="s">
         <v>1318</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1471</v>
@@ -13865,13 +13862,13 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
         <v>1319</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -13879,13 +13876,13 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
         <v>1320</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -13893,13 +13890,13 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>1321</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -13907,13 +13904,13 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
         <v>1322</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -13921,13 +13918,13 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
         <v>1323</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -13935,7 +13932,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
         <v>1077</v>
@@ -13949,7 +13946,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
         <v>1324</v>
@@ -13963,7 +13960,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
         <v>1325</v>
@@ -13977,7 +13974,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
         <v>1326</v>
@@ -13991,7 +13988,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
         <v>1327</v>
@@ -14005,7 +14002,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
         <v>1328</v>
@@ -14019,7 +14016,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
         <v>1329</v>
@@ -14033,7 +14030,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
         <v>1330</v>
@@ -14047,7 +14044,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>1331</v>
@@ -14061,7 +14058,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
         <v>1332</v>
@@ -14075,7 +14072,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
         <v>1333</v>
@@ -14089,7 +14086,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
         <v>1334</v>
@@ -14103,7 +14100,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
         <v>1335</v>
@@ -14117,7 +14114,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
         <v>1336</v>
@@ -14131,7 +14128,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
         <v>1337</v>
@@ -14145,7 +14142,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
         <v>1338</v>
@@ -14159,7 +14156,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
         <v>1339</v>
@@ -14173,7 +14170,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
         <v>1340</v>
@@ -14187,7 +14184,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
         <v>1341</v>
@@ -14201,7 +14198,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>1342</v>
@@ -14215,7 +14212,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
         <v>1343</v>
@@ -14229,7 +14226,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
         <v>1344</v>
@@ -14243,7 +14240,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
         <v>1345</v>
@@ -14257,7 +14254,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
         <v>1346</v>
@@ -14271,7 +14268,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
         <v>1347</v>
@@ -14285,7 +14282,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
         <v>1348</v>
@@ -14299,7 +14296,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
         <v>1349</v>
@@ -14313,7 +14310,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
         <v>1350</v>
@@ -14327,7 +14324,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
         <v>1351</v>
@@ -14341,7 +14338,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
         <v>1352</v>
@@ -14355,7 +14352,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>1353</v>
@@ -14369,7 +14366,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
         <v>1354</v>
@@ -14383,7 +14380,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
         <v>1355</v>
@@ -14397,7 +14394,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
         <v>1356</v>
@@ -14411,7 +14408,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
         <v>1357</v>
@@ -14425,7 +14422,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
         <v>1358</v>
@@ -14439,7 +14436,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
         <v>1359</v>
@@ -14453,7 +14450,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
         <v>1360</v>
@@ -14467,13 +14464,13 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
         <v>1361</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -14487,7 +14484,7 @@
         <v>1400</v>
       </c>
       <c r="C660" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -14501,7 +14498,7 @@
         <v>1401</v>
       </c>
       <c r="C661" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -14515,7 +14512,7 @@
         <v>1402</v>
       </c>
       <c r="C662" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -14529,7 +14526,7 @@
         <v>1403</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -14543,7 +14540,7 @@
         <v>1404</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -14557,7 +14554,7 @@
         <v>1405</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -14571,7 +14568,7 @@
         <v>1406</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -14585,7 +14582,7 @@
         <v>1407</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -14593,13 +14590,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>1408</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -14607,7 +14604,7 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>1409</v>
@@ -14638,10 +14635,10 @@
         <v>1163</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C671" s="9" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1473</v>
@@ -14887,7 +14884,7 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1475</v>
+        <v>1592</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>1450</v>
@@ -14901,7 +14898,7 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1475</v>
+        <v>1592</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>1451</v>
@@ -14915,7 +14912,7 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>1409</v>
@@ -14938,7 +14935,7 @@
         <v>1455</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
@@ -14952,7 +14949,7 @@
         <v>1456</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
@@ -14966,7 +14963,7 @@
         <v>1457</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
@@ -14980,427 +14977,427 @@
         <v>1458</v>
       </c>
       <c r="D695" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D697" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D698" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D699" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D701" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D703" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D704" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D705" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D707" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D709" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D721" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D723" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D724" s="3" t="s">
         <v>1539</v>
-      </c>
-      <c r="C724" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D724" s="3" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B725" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="B725" s="2" t="s">
-        <v>1480</v>
-      </c>
       <c r="C725" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D725" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066F32F-CFBA-46A4-A4DF-F1457F2C6B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039FEA89-6CD9-4647-81A0-1FAE892BDFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039FEA89-6CD9-4647-81A0-1FAE892BDFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E73D5F-FCBF-488F-8009-834E3058FD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="1611">
   <si>
     <t>Company</t>
   </si>
@@ -4799,6 +4799,60 @@
   </si>
   <si>
     <t>ОБЩИНА ВАРНА % 5 - ПДГ</t>
+  </si>
+  <si>
+    <t>CA1823СM</t>
+  </si>
+  <si>
+    <t>78970155027722770</t>
+  </si>
+  <si>
+    <t>ФЕНИКС ИМПОРТ М ЕООД</t>
+  </si>
+  <si>
+    <t>203538369</t>
+  </si>
+  <si>
+    <t>CB8180KM</t>
+  </si>
+  <si>
+    <t>B8417BM</t>
+  </si>
+  <si>
+    <t>CA7394XA</t>
+  </si>
+  <si>
+    <t>B0835TK</t>
+  </si>
+  <si>
+    <t>B2899BK</t>
+  </si>
+  <si>
+    <t>Company card 6</t>
+  </si>
+  <si>
+    <t>Company card 7</t>
+  </si>
+  <si>
+    <t>78970155027722796</t>
+  </si>
+  <si>
+    <t>78970155027722804</t>
+  </si>
+  <si>
+    <t>78970155027722812</t>
+  </si>
+  <si>
+    <t>78970155027722820</t>
+  </si>
+  <si>
+    <t>78970155027722838</t>
+  </si>
+  <si>
+    <t>78970155027722846</t>
+  </si>
+  <si>
+    <t>78970155027722853</t>
   </si>
 </sst>
 </file>
@@ -5212,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E725"/>
+  <dimension ref="A1:E733"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
@@ -9803,10 +9857,10 @@
         <v>972</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>632</v>
+        <v>1593</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>633</v>
+        <v>1594</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>974</v>
@@ -9817,10 +9871,10 @@
         <v>972</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>974</v>
@@ -9831,10 +9885,10 @@
         <v>972</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>974</v>
@@ -9845,10 +9899,10 @@
         <v>972</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>974</v>
@@ -9859,10 +9913,10 @@
         <v>972</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>974</v>
@@ -9873,10 +9927,10 @@
         <v>972</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>974</v>
@@ -9887,10 +9941,10 @@
         <v>972</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>974</v>
@@ -9901,10 +9955,10 @@
         <v>972</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>974</v>
@@ -9915,10 +9969,10 @@
         <v>972</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>974</v>
@@ -9929,10 +9983,10 @@
         <v>972</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1020</v>
+        <v>648</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>1021</v>
+        <v>649</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>974</v>
@@ -9940,13 +9994,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>650</v>
+        <v>1020</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>651</v>
+        <v>1021</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>974</v>
@@ -9957,10 +10011,10 @@
         <v>971</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>974</v>
@@ -9971,10 +10025,10 @@
         <v>971</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>974</v>
@@ -9985,10 +10039,10 @@
         <v>971</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>974</v>
@@ -9999,10 +10053,10 @@
         <v>971</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>974</v>
@@ -10013,10 +10067,10 @@
         <v>971</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>974</v>
@@ -10027,10 +10081,10 @@
         <v>971</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>974</v>
@@ -10041,10 +10095,10 @@
         <v>971</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>974</v>
@@ -10052,16 +10106,16 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -10069,10 +10123,10 @@
         <v>973</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>975</v>
@@ -10083,10 +10137,10 @@
         <v>973</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>975</v>
@@ -10097,10 +10151,10 @@
         <v>973</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>975</v>
@@ -10108,16 +10162,16 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -10125,10 +10179,10 @@
         <v>976</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>987</v>
@@ -10139,10 +10193,10 @@
         <v>976</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>987</v>
@@ -10153,10 +10207,10 @@
         <v>976</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>987</v>
@@ -10167,10 +10221,10 @@
         <v>976</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>987</v>
@@ -10181,10 +10235,10 @@
         <v>976</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>987</v>
@@ -10195,10 +10249,10 @@
         <v>976</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D356" s="3" t="s">
         <v>987</v>
@@ -10209,10 +10263,10 @@
         <v>976</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>987</v>
@@ -10223,10 +10277,10 @@
         <v>976</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>987</v>
@@ -10237,10 +10291,10 @@
         <v>976</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>987</v>
@@ -10251,10 +10305,10 @@
         <v>976</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>987</v>
@@ -10265,10 +10319,10 @@
         <v>976</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>987</v>
@@ -10279,10 +10333,10 @@
         <v>976</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>987</v>
@@ -10293,10 +10347,10 @@
         <v>976</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>987</v>
@@ -10307,10 +10361,10 @@
         <v>976</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>987</v>
@@ -10321,10 +10375,10 @@
         <v>976</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>987</v>
@@ -10332,13 +10386,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>987</v>
@@ -10349,10 +10403,10 @@
         <v>977</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>987</v>
@@ -10363,10 +10417,10 @@
         <v>977</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>987</v>
@@ -10377,10 +10431,10 @@
         <v>977</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>987</v>
@@ -10391,10 +10445,10 @@
         <v>977</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>987</v>
@@ -10405,10 +10459,10 @@
         <v>977</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>987</v>
@@ -10419,10 +10473,10 @@
         <v>977</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>987</v>
@@ -10433,10 +10487,10 @@
         <v>977</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>987</v>
@@ -10447,10 +10501,10 @@
         <v>977</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>987</v>
@@ -10461,10 +10515,10 @@
         <v>977</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>987</v>
@@ -10475,10 +10529,10 @@
         <v>977</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>987</v>
@@ -10489,10 +10543,10 @@
         <v>977</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>987</v>
@@ -10503,10 +10557,10 @@
         <v>977</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>987</v>
@@ -10517,10 +10571,10 @@
         <v>977</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>987</v>
@@ -10531,10 +10585,10 @@
         <v>977</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>987</v>
@@ -10545,10 +10599,10 @@
         <v>977</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>987</v>
@@ -10556,27 +10610,27 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>893</v>
+        <v>737</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>740</v>
+        <v>893</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>986</v>
@@ -10587,10 +10641,10 @@
         <v>984</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>986</v>
@@ -10601,10 +10655,10 @@
         <v>984</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>986</v>
@@ -10618,7 +10672,7 @@
         <v>743</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>875</v>
+        <v>744</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>986</v>
@@ -10629,10 +10683,10 @@
         <v>984</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>986</v>
@@ -10643,10 +10697,10 @@
         <v>984</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>986</v>
@@ -10654,13 +10708,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>986</v>
@@ -10674,7 +10728,7 @@
         <v>745</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>746</v>
+        <v>878</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>986</v>
@@ -10682,16 +10736,16 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>788</v>
+        <v>746</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -10699,10 +10753,10 @@
         <v>978</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>810</v>
+        <v>788</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>988</v>
@@ -10713,10 +10767,10 @@
         <v>978</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>988</v>
@@ -10727,10 +10781,10 @@
         <v>978</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>988</v>
@@ -10741,10 +10795,10 @@
         <v>978</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>988</v>
@@ -10755,10 +10809,10 @@
         <v>978</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>988</v>
@@ -10769,10 +10823,10 @@
         <v>978</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>988</v>
@@ -10783,10 +10837,10 @@
         <v>978</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>988</v>
@@ -10797,10 +10851,10 @@
         <v>978</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>988</v>
@@ -10811,10 +10865,10 @@
         <v>978</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>988</v>
@@ -10825,10 +10879,10 @@
         <v>978</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>803</v>
+        <v>751</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>988</v>
@@ -10839,10 +10893,10 @@
         <v>978</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>988</v>
@@ -10853,10 +10907,10 @@
         <v>978</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>751</v>
+        <v>805</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>988</v>
@@ -10867,10 +10921,10 @@
         <v>978</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>988</v>
@@ -10881,10 +10935,10 @@
         <v>978</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>809</v>
+        <v>762</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>988</v>
@@ -10895,10 +10949,10 @@
         <v>978</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>898</v>
+        <v>809</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>988</v>
@@ -10909,10 +10963,10 @@
         <v>978</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>791</v>
+        <v>898</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>988</v>
@@ -10923,10 +10977,10 @@
         <v>978</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>988</v>
@@ -10937,10 +10991,10 @@
         <v>978</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>988</v>
@@ -10951,10 +11005,10 @@
         <v>978</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>838</v>
+        <v>792</v>
       </c>
       <c r="D410" s="3" t="s">
         <v>988</v>
@@ -10965,10 +11019,10 @@
         <v>978</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>988</v>
@@ -10979,10 +11033,10 @@
         <v>978</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="D412" s="3" t="s">
         <v>988</v>
@@ -10993,10 +11047,10 @@
         <v>978</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>988</v>
@@ -11007,10 +11061,10 @@
         <v>978</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1583</v>
+        <v>793</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11021,10 +11075,10 @@
         <v>978</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>811</v>
+        <v>1583</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>988</v>
@@ -11035,10 +11089,10 @@
         <v>978</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>988</v>
@@ -11049,10 +11103,10 @@
         <v>978</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1578</v>
+        <v>802</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11063,10 +11117,10 @@
         <v>978</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11077,10 +11131,10 @@
         <v>978</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11091,10 +11145,10 @@
         <v>978</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>804</v>
+        <v>1580</v>
       </c>
       <c r="D420" s="3" t="s">
         <v>988</v>
@@ -11105,10 +11159,10 @@
         <v>978</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="D421" s="3" t="s">
         <v>988</v>
@@ -11119,10 +11173,10 @@
         <v>978</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>988</v>
@@ -11133,10 +11187,10 @@
         <v>978</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>988</v>
@@ -11147,10 +11201,10 @@
         <v>978</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>988</v>
@@ -11160,11 +11214,11 @@
       <c r="A425" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B425" s="4" t="s">
-        <v>783</v>
+      <c r="B425" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>896</v>
+        <v>801</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>988</v>
@@ -11174,11 +11228,11 @@
       <c r="A426" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B426" s="2" t="s">
-        <v>784</v>
+      <c r="B426" s="4" t="s">
+        <v>783</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>796</v>
+        <v>896</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>988</v>
@@ -11189,10 +11243,10 @@
         <v>978</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>988</v>
@@ -11203,10 +11257,10 @@
         <v>978</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1581</v>
+        <v>798</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11217,10 +11271,10 @@
         <v>978</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1582</v>
+        <v>786</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>813</v>
+        <v>1581</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>988</v>
@@ -11228,16 +11282,16 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B430" s="5" t="s">
-        <v>826</v>
+        <v>978</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>1582</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -11245,10 +11299,10 @@
         <v>979</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D431" s="3" t="s">
         <v>980</v>
@@ -11259,10 +11313,10 @@
         <v>979</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>980</v>
@@ -11273,10 +11327,10 @@
         <v>979</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>980</v>
@@ -11287,10 +11341,10 @@
         <v>979</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>980</v>
@@ -11301,10 +11355,10 @@
         <v>979</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D435" s="3" t="s">
         <v>980</v>
@@ -11315,10 +11369,10 @@
         <v>979</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D436" s="3" t="s">
         <v>980</v>
@@ -11329,10 +11383,10 @@
         <v>979</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D437" s="3" t="s">
         <v>980</v>
@@ -11343,10 +11397,10 @@
         <v>979</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>980</v>
@@ -11357,10 +11411,10 @@
         <v>979</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>980</v>
@@ -11371,10 +11425,10 @@
         <v>979</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D440" s="3" t="s">
         <v>980</v>
@@ -11385,10 +11439,10 @@
         <v>979</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D441" s="3" t="s">
         <v>980</v>
@@ -11396,16 +11450,16 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>843</v>
+        <v>979</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>837</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>884</v>
+        <v>825</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -11413,10 +11467,10 @@
         <v>839</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="D443" s="3" t="s">
         <v>981</v>
@@ -11427,10 +11481,10 @@
         <v>839</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>981</v>
@@ -11441,10 +11495,10 @@
         <v>839</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>981</v>
@@ -11455,10 +11509,10 @@
         <v>839</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D446" s="3" t="s">
         <v>981</v>
@@ -11469,10 +11523,10 @@
         <v>839</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D447" s="3" t="s">
         <v>981</v>
@@ -11483,10 +11537,10 @@
         <v>839</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>871</v>
+        <v>844</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="D448" s="3" t="s">
         <v>981</v>
@@ -11494,36 +11548,33 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="B449" s="2">
-        <v>3</v>
+        <v>839</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E449" s="3" t="s">
-        <v>850</v>
+        <v>981</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B450" s="2" t="s">
-        <v>1584</v>
+      <c r="B450" s="2">
+        <v>3</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D450" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -11531,16 +11582,16 @@
         <v>880</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>856</v>
+        <v>1584</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D451" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -11548,16 +11599,16 @@
         <v>880</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -11565,16 +11616,16 @@
         <v>880</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D453" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>879</v>
+        <v>857</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -11582,16 +11633,16 @@
         <v>880</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>50</v>
+        <v>860</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -11599,16 +11650,16 @@
         <v>880</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -11616,78 +11667,81 @@
         <v>880</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B457" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C457" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B458" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="C458" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B459" s="4" t="s">
-        <v>883</v>
+      <c r="B459" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="D459" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B460" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="C460" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -11695,13 +11749,13 @@
         <v>880</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -11709,27 +11763,27 @@
         <v>880</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D462" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B463" s="2" t="s">
-        <v>1005</v>
+        <v>880</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>993</v>
+        <v>894</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
+      </c>
+      <c r="E463" s="3" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
@@ -11737,10 +11791,10 @@
         <v>992</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D464" s="3" t="s">
         <v>1017</v>
@@ -11751,10 +11805,10 @@
         <v>992</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D465" s="3" t="s">
         <v>1017</v>
@@ -11765,10 +11819,10 @@
         <v>992</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>1017</v>
@@ -11779,10 +11833,10 @@
         <v>992</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D467" s="3" t="s">
         <v>1017</v>
@@ -11793,10 +11847,10 @@
         <v>992</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D468" s="3" t="s">
         <v>1017</v>
@@ -11807,10 +11861,10 @@
         <v>992</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D469" s="3" t="s">
         <v>1017</v>
@@ -11821,10 +11875,10 @@
         <v>992</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D470" s="3" t="s">
         <v>1017</v>
@@ -11835,10 +11889,10 @@
         <v>992</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D471" s="3" t="s">
         <v>1017</v>
@@ -11849,10 +11903,10 @@
         <v>992</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D472" s="3" t="s">
         <v>1017</v>
@@ -11863,10 +11917,10 @@
         <v>992</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>1017</v>
@@ -11877,41 +11931,41 @@
         <v>992</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A475" s="3" t="s">
+      <c r="A475" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C475" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D475" s="3" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="B475" s="2" t="s">
+      <c r="B476" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C475" s="2" t="s">
+      <c r="C476" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="D475" s="3" t="s">
+      <c r="D476" s="3" t="s">
         <v>1019</v>
-      </c>
-    </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A476" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C476" s="6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D476" s="3" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -11919,10 +11973,10 @@
         <v>1034</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1033</v>
@@ -11933,10 +11987,10 @@
         <v>1034</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>1033</v>
@@ -11947,10 +12001,10 @@
         <v>1034</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>1033</v>
@@ -11961,10 +12015,10 @@
         <v>1034</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>1033</v>
@@ -11975,10 +12029,10 @@
         <v>1034</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D481" s="3" t="s">
         <v>1033</v>
@@ -11989,10 +12043,10 @@
         <v>1034</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>1033</v>
@@ -12003,10 +12057,10 @@
         <v>1034</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>1033</v>
@@ -12017,10 +12071,10 @@
         <v>1034</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D484" s="3" t="s">
         <v>1033</v>
@@ -12031,10 +12085,10 @@
         <v>1034</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1033</v>
@@ -12045,10 +12099,10 @@
         <v>1034</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1033</v>
@@ -12056,16 +12110,16 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -12073,10 +12127,10 @@
         <v>1035</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1036</v>
@@ -12087,10 +12141,10 @@
         <v>1035</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1036</v>
@@ -12101,10 +12155,10 @@
         <v>1035</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1036</v>
@@ -12115,10 +12169,10 @@
         <v>1035</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D491" s="3" t="s">
         <v>1036</v>
@@ -12129,10 +12183,10 @@
         <v>1035</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D492" s="3" t="s">
         <v>1036</v>
@@ -12143,10 +12197,10 @@
         <v>1035</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>1036</v>
@@ -12157,10 +12211,10 @@
         <v>1035</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1036</v>
@@ -12171,10 +12225,10 @@
         <v>1035</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>1036</v>
@@ -12182,16 +12236,16 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -12199,10 +12253,10 @@
         <v>1591</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>1046</v>
@@ -12213,10 +12267,10 @@
         <v>1591</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1046</v>
@@ -12224,16 +12278,16 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
@@ -12241,10 +12295,10 @@
         <v>1055</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D500" s="3" t="s">
         <v>1050</v>
@@ -12255,10 +12309,10 @@
         <v>1055</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>1050</v>
@@ -12269,10 +12323,10 @@
         <v>1055</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>1050</v>
@@ -12280,16 +12334,16 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -12297,10 +12351,10 @@
         <v>1056</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D504" s="3" t="s">
         <v>1057</v>
@@ -12314,7 +12368,7 @@
         <v>1059</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D505" s="3" t="s">
         <v>1057</v>
@@ -12322,16 +12376,16 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
@@ -12339,10 +12393,10 @@
         <v>1060</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D507" s="3" t="s">
         <v>1061</v>
@@ -12353,10 +12407,10 @@
         <v>1060</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>1061</v>
@@ -12367,10 +12421,10 @@
         <v>1060</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>1061</v>
@@ -12381,10 +12435,10 @@
         <v>1060</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D510" s="3" t="s">
         <v>1061</v>
@@ -12395,10 +12449,10 @@
         <v>1060</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>1061</v>
@@ -12409,10 +12463,10 @@
         <v>1060</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>1061</v>
@@ -12423,10 +12477,10 @@
         <v>1060</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D513" s="3" t="s">
         <v>1061</v>
@@ -12437,10 +12491,10 @@
         <v>1060</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D514" s="3" t="s">
         <v>1061</v>
@@ -12451,10 +12505,10 @@
         <v>1060</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>1061</v>
@@ -12465,10 +12519,10 @@
         <v>1060</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>1061</v>
@@ -12476,44 +12530,44 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="518" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="B518" s="11" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C518" s="12" t="s">
-        <v>1590</v>
+      <c r="B518" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C518" s="6" t="s">
+        <v>1136</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B519" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C519" s="6" t="s">
-        <v>1137</v>
+        <v>1073</v>
+      </c>
+      <c r="B519" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C519" s="12" t="s">
+        <v>1590</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
@@ -12521,10 +12575,10 @@
         <v>1076</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>1081</v>
@@ -12535,10 +12589,10 @@
         <v>1076</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>1081</v>
@@ -12549,10 +12603,10 @@
         <v>1076</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>1081</v>
@@ -12560,16 +12614,16 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
@@ -12577,10 +12631,10 @@
         <v>1082</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>1083</v>
@@ -12591,10 +12645,10 @@
         <v>1082</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>1083</v>
@@ -12605,10 +12659,10 @@
         <v>1082</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>1083</v>
@@ -12619,10 +12673,10 @@
         <v>1082</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>1083</v>
@@ -12630,16 +12684,16 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
@@ -12647,10 +12701,10 @@
         <v>1540</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>1094</v>
@@ -12661,10 +12715,10 @@
         <v>1540</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>1094</v>
@@ -12675,10 +12729,10 @@
         <v>1540</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D531" s="3" t="s">
         <v>1094</v>
@@ -12689,10 +12743,10 @@
         <v>1540</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>1094</v>
@@ -12700,16 +12754,16 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C533" s="2" t="s">
-        <v>1168</v>
+        <v>1093</v>
+      </c>
+      <c r="C533" s="6" t="s">
+        <v>1150</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
@@ -12717,10 +12771,10 @@
         <v>1151</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D534" s="3" t="s">
         <v>1459</v>
@@ -12728,16 +12782,16 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
@@ -12745,10 +12799,10 @@
         <v>1152</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D536" s="3" t="s">
         <v>1460</v>
@@ -12756,16 +12810,16 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
@@ -12773,10 +12827,10 @@
         <v>1153</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D538" s="3" t="s">
         <v>1461</v>
@@ -12784,16 +12838,16 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
@@ -12801,10 +12855,10 @@
         <v>1154</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>1462</v>
@@ -12812,16 +12866,16 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
@@ -12829,10 +12883,10 @@
         <v>1155</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D542" s="3" t="s">
         <v>1463</v>
@@ -12840,16 +12894,16 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
@@ -12857,10 +12911,10 @@
         <v>1156</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D544" s="3" t="s">
         <v>1464</v>
@@ -12871,10 +12925,10 @@
         <v>1156</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D545" s="3" t="s">
         <v>1464</v>
@@ -12885,10 +12939,10 @@
         <v>1156</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D546" s="3" t="s">
         <v>1464</v>
@@ -12896,16 +12950,16 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
@@ -12913,10 +12967,10 @@
         <v>1157</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D548" s="3" t="s">
         <v>1465</v>
@@ -12924,16 +12978,16 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B549" s="7" t="s">
-        <v>1234</v>
+        <v>1157</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>1195</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
@@ -12941,10 +12995,10 @@
         <v>1158</v>
       </c>
       <c r="B550" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D550" s="3" t="s">
         <v>1466</v>
@@ -12955,10 +13009,10 @@
         <v>1158</v>
       </c>
       <c r="B551" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>1466</v>
@@ -12969,10 +13023,10 @@
         <v>1158</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D552" s="3" t="s">
         <v>1466</v>
@@ -12983,10 +13037,10 @@
         <v>1158</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D553" s="3" t="s">
         <v>1466</v>
@@ -12997,10 +13051,10 @@
         <v>1158</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D554" s="3" t="s">
         <v>1466</v>
@@ -13011,10 +13065,10 @@
         <v>1158</v>
       </c>
       <c r="B555" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>1466</v>
@@ -13025,10 +13079,10 @@
         <v>1158</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D556" s="3" t="s">
         <v>1466</v>
@@ -13039,10 +13093,10 @@
         <v>1158</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D557" s="3" t="s">
         <v>1466</v>
@@ -13053,10 +13107,10 @@
         <v>1158</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D558" s="3" t="s">
         <v>1466</v>
@@ -13067,10 +13121,10 @@
         <v>1158</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D559" s="3" t="s">
         <v>1466</v>
@@ -13081,10 +13135,10 @@
         <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D560" s="3" t="s">
         <v>1466</v>
@@ -13095,10 +13149,10 @@
         <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D561" s="3" t="s">
         <v>1466</v>
@@ -13109,10 +13163,10 @@
         <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D562" s="3" t="s">
         <v>1466</v>
@@ -13123,10 +13177,10 @@
         <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1466</v>
@@ -13137,10 +13191,10 @@
         <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>1466</v>
@@ -13151,10 +13205,10 @@
         <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>1466</v>
@@ -13165,10 +13219,10 @@
         <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1466</v>
@@ -13179,10 +13233,10 @@
         <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1466</v>
@@ -13193,10 +13247,10 @@
         <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>1466</v>
@@ -13207,10 +13261,10 @@
         <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>1466</v>
@@ -13221,10 +13275,10 @@
         <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>1466</v>
@@ -13234,11 +13288,11 @@
       <c r="A571" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B571" s="4" t="s">
-        <v>1256</v>
+      <c r="B571" s="7" t="s">
+        <v>1255</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1466</v>
@@ -13248,11 +13302,11 @@
       <c r="A572" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B572" s="7" t="s">
-        <v>1257</v>
+      <c r="B572" s="4" t="s">
+        <v>1256</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1466</v>
@@ -13263,10 +13317,10 @@
         <v>1158</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>1466</v>
@@ -13277,10 +13331,10 @@
         <v>1158</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1466</v>
@@ -13291,10 +13345,10 @@
         <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>1466</v>
@@ -13305,10 +13359,10 @@
         <v>1158</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>1466</v>
@@ -13319,10 +13373,10 @@
         <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>1466</v>
@@ -13333,10 +13387,10 @@
         <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1232</v>
+        <v>1262</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>1466</v>
@@ -13347,10 +13401,10 @@
         <v>1158</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1263</v>
+        <v>1232</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>1466</v>
@@ -13361,10 +13415,10 @@
         <v>1158</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>1466</v>
@@ -13375,10 +13429,10 @@
         <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>1466</v>
@@ -13389,10 +13443,10 @@
         <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>1466</v>
@@ -13400,16 +13454,16 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1282</v>
+        <v>1231</v>
       </c>
       <c r="D583" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -13417,10 +13471,10 @@
         <v>1159</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>1467</v>
@@ -13431,10 +13485,10 @@
         <v>1159</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>1467</v>
@@ -13445,10 +13499,10 @@
         <v>1159</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>1467</v>
@@ -13459,10 +13513,10 @@
         <v>1159</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>1467</v>
@@ -13473,10 +13527,10 @@
         <v>1159</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1467</v>
@@ -13487,10 +13541,10 @@
         <v>1159</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1467</v>
@@ -13501,10 +13555,10 @@
         <v>1159</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>1467</v>
@@ -13515,10 +13569,10 @@
         <v>1159</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>1467</v>
@@ -13529,10 +13583,10 @@
         <v>1159</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1467</v>
@@ -13543,10 +13597,10 @@
         <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>1467</v>
@@ -13557,10 +13611,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -13571,10 +13625,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -13585,10 +13639,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -13599,10 +13653,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -13613,10 +13667,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -13624,16 +13678,16 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="D599" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -13641,10 +13695,10 @@
         <v>1160</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D600" s="3" t="s">
         <v>1468</v>
@@ -13655,10 +13709,10 @@
         <v>1160</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D601" s="3" t="s">
         <v>1468</v>
@@ -13669,10 +13723,10 @@
         <v>1160</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1468</v>
@@ -13680,30 +13734,30 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B603" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B603" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1558</v>
+        <v>1305</v>
       </c>
       <c r="D603" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="D604" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
@@ -13711,10 +13765,10 @@
         <v>1162</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1470</v>
@@ -13722,16 +13776,16 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B606" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C606" s="8" t="s">
-        <v>1560</v>
+        <v>1162</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D606" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
@@ -13739,10 +13793,10 @@
         <v>1587</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C607" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D607" s="3" t="s">
         <v>1471</v>
@@ -13753,10 +13807,10 @@
         <v>1587</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C608" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1471</v>
@@ -13767,10 +13821,10 @@
         <v>1587</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1471</v>
@@ -13781,10 +13835,10 @@
         <v>1587</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1471</v>
@@ -13795,10 +13849,10 @@
         <v>1587</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1471</v>
@@ -13809,10 +13863,10 @@
         <v>1587</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1471</v>
@@ -13823,10 +13877,10 @@
         <v>1587</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1471</v>
@@ -13837,10 +13891,10 @@
         <v>1587</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1566</v>
+        <v>1553</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1471</v>
@@ -13851,10 +13905,10 @@
         <v>1587</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1471</v>
@@ -13865,10 +13919,10 @@
         <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -13879,10 +13933,10 @@
         <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -13893,10 +13947,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -13907,10 +13961,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -13921,10 +13975,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -13935,10 +13989,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C621" s="9" t="s">
-        <v>1362</v>
+        <v>1323</v>
+      </c>
+      <c r="C621" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -13949,10 +14003,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C622" s="10" t="s">
-        <v>1363</v>
+        <v>1077</v>
+      </c>
+      <c r="C622" s="9" t="s">
+        <v>1362</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -13963,10 +14017,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C623" s="9" t="s">
-        <v>1364</v>
+        <v>1324</v>
+      </c>
+      <c r="C623" s="10" t="s">
+        <v>1363</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -13977,10 +14031,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C624" s="10" t="s">
-        <v>1365</v>
+        <v>1325</v>
+      </c>
+      <c r="C624" s="9" t="s">
+        <v>1364</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -13991,10 +14045,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C625" s="9" t="s">
-        <v>1366</v>
+        <v>1326</v>
+      </c>
+      <c r="C625" s="10" t="s">
+        <v>1365</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14005,10 +14059,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C626" s="10" t="s">
-        <v>1367</v>
+        <v>1327</v>
+      </c>
+      <c r="C626" s="9" t="s">
+        <v>1366</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14019,10 +14073,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C627" s="9" t="s">
-        <v>1368</v>
+        <v>1328</v>
+      </c>
+      <c r="C627" s="10" t="s">
+        <v>1367</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14033,10 +14087,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C628" s="10" t="s">
-        <v>1369</v>
+        <v>1329</v>
+      </c>
+      <c r="C628" s="9" t="s">
+        <v>1368</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14047,10 +14101,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C629" s="9" t="s">
-        <v>1370</v>
+        <v>1330</v>
+      </c>
+      <c r="C629" s="10" t="s">
+        <v>1369</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14061,10 +14115,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C630" s="10" t="s">
-        <v>1371</v>
+        <v>1331</v>
+      </c>
+      <c r="C630" s="9" t="s">
+        <v>1370</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14075,10 +14129,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C631" s="9" t="s">
-        <v>1372</v>
+        <v>1332</v>
+      </c>
+      <c r="C631" s="10" t="s">
+        <v>1371</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14089,10 +14143,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C632" s="10" t="s">
-        <v>1373</v>
+        <v>1333</v>
+      </c>
+      <c r="C632" s="9" t="s">
+        <v>1372</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14103,10 +14157,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C633" s="9" t="s">
-        <v>1374</v>
+        <v>1334</v>
+      </c>
+      <c r="C633" s="10" t="s">
+        <v>1373</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14117,10 +14171,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C634" s="10" t="s">
-        <v>1375</v>
+        <v>1335</v>
+      </c>
+      <c r="C634" s="9" t="s">
+        <v>1374</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14131,10 +14185,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C635" s="9" t="s">
-        <v>1376</v>
+        <v>1336</v>
+      </c>
+      <c r="C635" s="10" t="s">
+        <v>1375</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14145,10 +14199,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C636" s="10" t="s">
-        <v>1377</v>
+        <v>1337</v>
+      </c>
+      <c r="C636" s="9" t="s">
+        <v>1376</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14159,10 +14213,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C637" s="9" t="s">
-        <v>1378</v>
+        <v>1338</v>
+      </c>
+      <c r="C637" s="10" t="s">
+        <v>1377</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14173,10 +14227,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C638" s="10" t="s">
-        <v>1379</v>
+        <v>1339</v>
+      </c>
+      <c r="C638" s="9" t="s">
+        <v>1378</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14187,10 +14241,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C639" s="9" t="s">
-        <v>1380</v>
+        <v>1340</v>
+      </c>
+      <c r="C639" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14201,10 +14255,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C640" s="10" t="s">
-        <v>1381</v>
+        <v>1341</v>
+      </c>
+      <c r="C640" s="9" t="s">
+        <v>1380</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14215,10 +14269,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C641" s="9" t="s">
-        <v>1382</v>
+        <v>1342</v>
+      </c>
+      <c r="C641" s="10" t="s">
+        <v>1381</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14229,10 +14283,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C642" s="10" t="s">
-        <v>1383</v>
+        <v>1343</v>
+      </c>
+      <c r="C642" s="9" t="s">
+        <v>1382</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14243,10 +14297,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C643" s="9" t="s">
-        <v>1384</v>
+        <v>1344</v>
+      </c>
+      <c r="C643" s="10" t="s">
+        <v>1383</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14257,10 +14311,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C644" s="10" t="s">
-        <v>1385</v>
+        <v>1345</v>
+      </c>
+      <c r="C644" s="9" t="s">
+        <v>1384</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14271,10 +14325,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C645" s="9" t="s">
-        <v>1386</v>
+        <v>1346</v>
+      </c>
+      <c r="C645" s="10" t="s">
+        <v>1385</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14285,10 +14339,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C646" s="10" t="s">
-        <v>1387</v>
+        <v>1347</v>
+      </c>
+      <c r="C646" s="9" t="s">
+        <v>1386</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14299,10 +14353,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C647" s="9" t="s">
-        <v>1388</v>
+        <v>1348</v>
+      </c>
+      <c r="C647" s="10" t="s">
+        <v>1387</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14313,10 +14367,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C648" s="10" t="s">
-        <v>1389</v>
+        <v>1349</v>
+      </c>
+      <c r="C648" s="9" t="s">
+        <v>1388</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14327,10 +14381,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C649" s="9" t="s">
-        <v>1390</v>
+        <v>1350</v>
+      </c>
+      <c r="C649" s="10" t="s">
+        <v>1389</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14341,10 +14395,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C650" s="10" t="s">
-        <v>1391</v>
+        <v>1351</v>
+      </c>
+      <c r="C650" s="9" t="s">
+        <v>1390</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14355,10 +14409,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C651" s="9" t="s">
-        <v>1392</v>
+        <v>1352</v>
+      </c>
+      <c r="C651" s="10" t="s">
+        <v>1391</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14369,10 +14423,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C652" s="10" t="s">
-        <v>1393</v>
+        <v>1353</v>
+      </c>
+      <c r="C652" s="9" t="s">
+        <v>1392</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -14383,10 +14437,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C653" s="9" t="s">
-        <v>1394</v>
+        <v>1354</v>
+      </c>
+      <c r="C653" s="10" t="s">
+        <v>1393</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -14397,10 +14451,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C654" s="10" t="s">
-        <v>1395</v>
+        <v>1355</v>
+      </c>
+      <c r="C654" s="9" t="s">
+        <v>1394</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -14411,10 +14465,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C655" s="9" t="s">
-        <v>1396</v>
+        <v>1356</v>
+      </c>
+      <c r="C655" s="10" t="s">
+        <v>1395</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -14425,10 +14479,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C656" s="10" t="s">
-        <v>1397</v>
+        <v>1357</v>
+      </c>
+      <c r="C656" s="9" t="s">
+        <v>1396</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -14439,10 +14493,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C657" s="9" t="s">
-        <v>1398</v>
+        <v>1358</v>
+      </c>
+      <c r="C657" s="10" t="s">
+        <v>1397</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -14453,10 +14507,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C658" s="10" t="s">
-        <v>1399</v>
+        <v>1359</v>
+      </c>
+      <c r="C658" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -14467,10 +14521,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C659" s="2" t="s">
-        <v>1573</v>
+        <v>1360</v>
+      </c>
+      <c r="C659" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -14478,13 +14532,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B660" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C660" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -14495,10 +14549,10 @@
         <v>1472</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C661" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -14509,10 +14563,10 @@
         <v>1472</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C662" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -14523,10 +14577,10 @@
         <v>1472</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -14537,10 +14591,10 @@
         <v>1472</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -14551,10 +14605,10 @@
         <v>1472</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -14565,10 +14619,10 @@
         <v>1472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -14579,10 +14633,10 @@
         <v>1472</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -14590,13 +14644,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1574</v>
+        <v>1552</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -14604,13 +14658,13 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C669" s="9" t="s">
-        <v>1410</v>
+        <v>1408</v>
+      </c>
+      <c r="C669" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -14618,16 +14672,16 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1163</v>
+        <v>1586</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C670" s="2" t="s">
-        <v>1412</v>
+        <v>1409</v>
+      </c>
+      <c r="C670" s="9" t="s">
+        <v>1410</v>
       </c>
       <c r="D670" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
@@ -14635,10 +14689,10 @@
         <v>1163</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C671" s="9" t="s">
-        <v>1575</v>
+        <v>1411</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1473</v>
@@ -14646,16 +14700,16 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C672" s="10" t="s">
-        <v>1429</v>
+        <v>1479</v>
+      </c>
+      <c r="C672" s="9" t="s">
+        <v>1575</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
@@ -14663,10 +14717,10 @@
         <v>1164</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C673" s="9" t="s">
-        <v>1430</v>
+        <v>1414</v>
+      </c>
+      <c r="C673" s="10" t="s">
+        <v>1429</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1474</v>
@@ -14677,10 +14731,10 @@
         <v>1164</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C674" s="10" t="s">
-        <v>1431</v>
+        <v>1416</v>
+      </c>
+      <c r="C674" s="9" t="s">
+        <v>1430</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1474</v>
@@ -14691,10 +14745,10 @@
         <v>1164</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C675" s="9" t="s">
-        <v>1432</v>
+        <v>1417</v>
+      </c>
+      <c r="C675" s="10" t="s">
+        <v>1431</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>1474</v>
@@ -14705,10 +14759,10 @@
         <v>1164</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C676" s="10" t="s">
-        <v>1433</v>
+        <v>1418</v>
+      </c>
+      <c r="C676" s="9" t="s">
+        <v>1432</v>
       </c>
       <c r="D676" s="3" t="s">
         <v>1474</v>
@@ -14719,10 +14773,10 @@
         <v>1164</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C677" s="9" t="s">
-        <v>1434</v>
+        <v>1419</v>
+      </c>
+      <c r="C677" s="10" t="s">
+        <v>1433</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>1474</v>
@@ -14733,10 +14787,10 @@
         <v>1164</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C678" s="10" t="s">
-        <v>1435</v>
+        <v>1420</v>
+      </c>
+      <c r="C678" s="9" t="s">
+        <v>1434</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>1474</v>
@@ -14747,10 +14801,10 @@
         <v>1164</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C679" s="9" t="s">
-        <v>1436</v>
+        <v>1421</v>
+      </c>
+      <c r="C679" s="10" t="s">
+        <v>1435</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1474</v>
@@ -14761,10 +14815,10 @@
         <v>1164</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C680" s="10" t="s">
-        <v>1437</v>
+        <v>1422</v>
+      </c>
+      <c r="C680" s="9" t="s">
+        <v>1436</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1474</v>
@@ -14775,10 +14829,10 @@
         <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C681" s="9" t="s">
-        <v>1438</v>
+        <v>1423</v>
+      </c>
+      <c r="C681" s="10" t="s">
+        <v>1437</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1474</v>
@@ -14789,10 +14843,10 @@
         <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C682" s="10" t="s">
-        <v>1439</v>
+        <v>1424</v>
+      </c>
+      <c r="C682" s="9" t="s">
+        <v>1438</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1474</v>
@@ -14803,10 +14857,10 @@
         <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C683" s="9" t="s">
-        <v>1440</v>
+        <v>1425</v>
+      </c>
+      <c r="C683" s="10" t="s">
+        <v>1439</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1474</v>
@@ -14817,10 +14871,10 @@
         <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C684" s="10" t="s">
-        <v>1441</v>
+        <v>1426</v>
+      </c>
+      <c r="C684" s="9" t="s">
+        <v>1440</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1474</v>
@@ -14831,10 +14885,10 @@
         <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C685" s="9" t="s">
-        <v>1442</v>
+        <v>1427</v>
+      </c>
+      <c r="C685" s="10" t="s">
+        <v>1441</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1474</v>
@@ -14845,10 +14899,10 @@
         <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C686" s="10" t="s">
-        <v>1443</v>
+        <v>1428</v>
+      </c>
+      <c r="C686" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1474</v>
@@ -14859,10 +14913,10 @@
         <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C687" s="9" t="s">
-        <v>1444</v>
+        <v>1423</v>
+      </c>
+      <c r="C687" s="10" t="s">
+        <v>1443</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1474</v>
@@ -14873,10 +14927,10 @@
         <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C688" s="10" t="s">
-        <v>1445</v>
+        <v>1413</v>
+      </c>
+      <c r="C688" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1474</v>
@@ -14884,16 +14938,16 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1592</v>
+        <v>1164</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="C689" s="10" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
       <c r="D689" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
@@ -14901,10 +14955,10 @@
         <v>1592</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C690" s="9" t="s">
-        <v>1453</v>
+        <v>1450</v>
+      </c>
+      <c r="C690" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D690" s="3" t="s">
         <v>1471</v>
@@ -14912,13 +14966,13 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1475</v>
+        <v>1592</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C691" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
+      </c>
+      <c r="C691" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1471</v>
@@ -14926,16 +14980,16 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1165</v>
+        <v>1475</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1446</v>
+        <v>1409</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
@@ -14943,10 +14997,10 @@
         <v>1165</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>1476</v>
@@ -14957,10 +15011,10 @@
         <v>1165</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D694" s="3" t="s">
         <v>1476</v>
@@ -14971,10 +15025,10 @@
         <v>1165</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1476</v>
@@ -14982,16 +15036,16 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1510</v>
+        <v>1449</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1480</v>
+        <v>1458</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
@@ -14999,10 +15053,10 @@
         <v>1477</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>1539</v>
@@ -15013,10 +15067,10 @@
         <v>1477</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1539</v>
@@ -15027,10 +15081,10 @@
         <v>1477</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1539</v>
@@ -15041,10 +15095,10 @@
         <v>1477</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1539</v>
@@ -15055,10 +15109,10 @@
         <v>1477</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1539</v>
@@ -15069,10 +15123,10 @@
         <v>1477</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1539</v>
@@ -15083,10 +15137,10 @@
         <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1539</v>
@@ -15097,10 +15151,10 @@
         <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1539</v>
@@ -15111,10 +15165,10 @@
         <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1539</v>
@@ -15125,10 +15179,10 @@
         <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1539</v>
@@ -15139,10 +15193,10 @@
         <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1539</v>
@@ -15153,10 +15207,10 @@
         <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1539</v>
@@ -15167,10 +15221,10 @@
         <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1539</v>
@@ -15181,10 +15235,10 @@
         <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>1539</v>
@@ -15195,10 +15249,10 @@
         <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D711" s="3" t="s">
         <v>1539</v>
@@ -15209,10 +15263,10 @@
         <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1539</v>
@@ -15223,10 +15277,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15237,10 +15291,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15251,10 +15305,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15265,10 +15319,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15279,10 +15333,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15293,10 +15347,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15307,10 +15361,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15321,10 +15375,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15335,10 +15389,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15349,10 +15403,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15363,10 +15417,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15377,10 +15431,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -15388,16 +15442,128 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1479</v>
+        <v>1538</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A726" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D726" s="3" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A727" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D727" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A728" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D728" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A729" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D729" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A730" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C730" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D730" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A731" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D731" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A732" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C732" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D732" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A733" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C733" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D733" s="3" t="s">
+        <v>1596</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E73D5F-FCBF-488F-8009-834E3058FD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F975E1-3350-4195-B134-5F0323379A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="1611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1629">
   <si>
     <t>Company</t>
   </si>
@@ -4853,6 +4853,60 @@
   </si>
   <si>
     <t>78970155027722853</t>
+  </si>
+  <si>
+    <t>СИЙД ЕКСПРЕС ЕООД</t>
+  </si>
+  <si>
+    <t>ТХ1083АТ</t>
+  </si>
+  <si>
+    <t>ТХ4583АР</t>
+  </si>
+  <si>
+    <t>РР1216ВМ</t>
+  </si>
+  <si>
+    <t>СВ3438КМ</t>
+  </si>
+  <si>
+    <t>В2525НХ</t>
+  </si>
+  <si>
+    <t>Stefan SЕ</t>
+  </si>
+  <si>
+    <t>Plamen SE</t>
+  </si>
+  <si>
+    <t>78970153027721462</t>
+  </si>
+  <si>
+    <t>78970153027721470</t>
+  </si>
+  <si>
+    <t>78970153027721488</t>
+  </si>
+  <si>
+    <t>78970153027721496</t>
+  </si>
+  <si>
+    <t>78970153027721504</t>
+  </si>
+  <si>
+    <t>78970153027721512</t>
+  </si>
+  <si>
+    <t>ТХ4665МТ</t>
+  </si>
+  <si>
+    <t>78970153027721447</t>
+  </si>
+  <si>
+    <t>78970153027721454</t>
+  </si>
+  <si>
+    <t>205091212</t>
   </si>
 </sst>
 </file>
@@ -5266,7 +5320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E733"/>
+  <dimension ref="A1:E741"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
@@ -15566,6 +15620,118 @@
         <v>1596</v>
       </c>
     </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A734" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C734" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D734" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A735" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C735" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D735" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A736" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C736" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D736" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A737" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C737" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D737" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A738" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D738" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A739" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C739" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D739" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A740" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D740" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A741" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C741" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D741" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F975E1-3350-4195-B134-5F0323379A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1633">
   <si>
     <t>Company</t>
   </si>
@@ -4907,6 +4907,18 @@
   </si>
   <si>
     <t>205091212</t>
+  </si>
+  <si>
+    <t>ТУБА ОДЕСОС</t>
+  </si>
+  <si>
+    <t>78970155027722861</t>
+  </si>
+  <si>
+    <t>В4286ХМ</t>
+  </si>
+  <si>
+    <t>78970151027721052</t>
   </si>
 </sst>
 </file>
@@ -5320,7 +5332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E741"/>
+  <dimension ref="A1:E743"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
@@ -15023,10 +15035,10 @@
         <v>1592</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C691" s="9" t="s">
-        <v>1453</v>
+        <v>1631</v>
+      </c>
+      <c r="C691" s="10" t="s">
+        <v>1632</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1471</v>
@@ -15034,13 +15046,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1475</v>
+        <v>1592</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C692" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
+      </c>
+      <c r="C692" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D692" s="3" t="s">
         <v>1471</v>
@@ -15048,16 +15060,16 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1165</v>
+        <v>1475</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1446</v>
+        <v>1409</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
@@ -15065,10 +15077,10 @@
         <v>1165</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D694" s="3" t="s">
         <v>1476</v>
@@ -15079,10 +15091,10 @@
         <v>1165</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1476</v>
@@ -15093,10 +15105,10 @@
         <v>1165</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D696" s="3" t="s">
         <v>1476</v>
@@ -15104,30 +15116,30 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1510</v>
+        <v>1629</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1480</v>
+        <v>1630</v>
       </c>
       <c r="D697" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1511</v>
+        <v>1449</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1481</v>
+        <v>1458</v>
       </c>
       <c r="D698" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
@@ -15135,10 +15147,10 @@
         <v>1477</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1539</v>
@@ -15149,10 +15161,10 @@
         <v>1477</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1539</v>
@@ -15163,10 +15175,10 @@
         <v>1477</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1539</v>
@@ -15177,10 +15189,10 @@
         <v>1477</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1539</v>
@@ -15191,10 +15203,10 @@
         <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1539</v>
@@ -15205,10 +15217,10 @@
         <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1539</v>
@@ -15219,10 +15231,10 @@
         <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1539</v>
@@ -15233,10 +15245,10 @@
         <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1539</v>
@@ -15247,10 +15259,10 @@
         <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1539</v>
@@ -15261,10 +15273,10 @@
         <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1539</v>
@@ -15275,10 +15287,10 @@
         <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1539</v>
@@ -15289,10 +15301,10 @@
         <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>1539</v>
@@ -15303,10 +15315,10 @@
         <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D711" s="3" t="s">
         <v>1539</v>
@@ -15317,10 +15329,10 @@
         <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1539</v>
@@ -15331,10 +15343,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15345,10 +15357,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15359,10 +15371,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15373,10 +15385,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15387,10 +15399,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15401,10 +15413,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15415,10 +15427,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15429,10 +15441,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15443,10 +15455,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15457,10 +15469,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15471,10 +15483,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15485,10 +15497,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -15499,10 +15511,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -15510,13 +15522,13 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1479</v>
+        <v>1537</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -15524,30 +15536,30 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1597</v>
+        <v>1538</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1604</v>
+        <v>1508</v>
       </c>
       <c r="D727" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1598</v>
+        <v>1479</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1605</v>
+        <v>1509</v>
       </c>
       <c r="D728" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
@@ -15555,10 +15567,10 @@
         <v>1595</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>1596</v>
@@ -15569,10 +15581,10 @@
         <v>1595</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>1596</v>
@@ -15583,10 +15595,10 @@
         <v>1595</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>1596</v>
@@ -15597,10 +15609,10 @@
         <v>1595</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D732" s="3" t="s">
         <v>1596</v>
@@ -15611,10 +15623,10 @@
         <v>1595</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1596</v>
@@ -15622,30 +15634,30 @@
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1612</v>
+        <v>1602</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="D734" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1613</v>
+        <v>1603</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="D735" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.25">
@@ -15653,10 +15665,10 @@
         <v>1611</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D736" s="3" t="s">
         <v>1628</v>
@@ -15667,10 +15679,10 @@
         <v>1611</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>1628</v>
@@ -15681,10 +15693,10 @@
         <v>1611</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D738" s="3" t="s">
         <v>1628</v>
@@ -15695,10 +15707,10 @@
         <v>1611</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D739" s="3" t="s">
         <v>1628</v>
@@ -15709,10 +15721,10 @@
         <v>1611</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="D740" s="3" t="s">
         <v>1628</v>
@@ -15723,12 +15735,40 @@
         <v>1611</v>
       </c>
       <c r="B741" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C741" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D741" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A742" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C742" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D742" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A743" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B743" s="2" t="s">
         <v>1618</v>
       </c>
-      <c r="C741" s="2" t="s">
+      <c r="C743" s="2" t="s">
         <v>1627</v>
       </c>
-      <c r="D741" s="3" t="s">
+      <c r="D743" s="3" t="s">
         <v>1628</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07122F8D-1E62-45CD-8207-9892B54C90EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1634">
   <si>
     <t>Company</t>
   </si>
@@ -4919,6 +4919,9 @@
   </si>
   <si>
     <t>78970151027721052</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА % 5 - 5</t>
   </si>
 </sst>
 </file>
@@ -14752,86 +14755,86 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1163</v>
+        <v>1592</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C671" s="2" t="s">
-        <v>1412</v>
+        <v>1450</v>
+      </c>
+      <c r="C671" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D671" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1163</v>
+        <v>1592</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1479</v>
+        <v>1451</v>
       </c>
       <c r="C672" s="9" t="s">
-        <v>1575</v>
+        <v>1453</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1164</v>
+        <v>1633</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1414</v>
+        <v>1631</v>
       </c>
       <c r="C673" s="10" t="s">
-        <v>1429</v>
+        <v>1632</v>
       </c>
       <c r="D673" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1164</v>
+        <v>1475</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C674" s="9" t="s">
-        <v>1430</v>
+        <v>1409</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>1454</v>
       </c>
       <c r="D674" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C675" s="10" t="s">
-        <v>1431</v>
+        <v>1411</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D675" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1418</v>
+        <v>1479</v>
       </c>
       <c r="C676" s="9" t="s">
-        <v>1432</v>
+        <v>1575</v>
       </c>
       <c r="D676" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
@@ -14839,10 +14842,10 @@
         <v>1164</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="C677" s="10" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>1474</v>
@@ -14853,10 +14856,10 @@
         <v>1164</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C678" s="9" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>1474</v>
@@ -14867,10 +14870,10 @@
         <v>1164</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C679" s="10" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1474</v>
@@ -14881,10 +14884,10 @@
         <v>1164</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="C680" s="9" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1474</v>
@@ -14895,10 +14898,10 @@
         <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="C681" s="10" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1474</v>
@@ -14909,10 +14912,10 @@
         <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C682" s="9" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1474</v>
@@ -14923,10 +14926,10 @@
         <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="C683" s="10" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1474</v>
@@ -14937,10 +14940,10 @@
         <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="C684" s="9" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1474</v>
@@ -14951,10 +14954,10 @@
         <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="C685" s="10" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1474</v>
@@ -14965,10 +14968,10 @@
         <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="C686" s="9" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1474</v>
@@ -14979,10 +14982,10 @@
         <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C687" s="10" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1474</v>
@@ -14993,10 +14996,10 @@
         <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1413</v>
+        <v>1426</v>
       </c>
       <c r="C688" s="9" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1474</v>
@@ -15007,10 +15010,10 @@
         <v>1164</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
       <c r="C689" s="10" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="D689" s="3" t="s">
         <v>1474</v>
@@ -15018,58 +15021,58 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1592</v>
+        <v>1164</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C690" s="10" t="s">
-        <v>1452</v>
+        <v>1428</v>
+      </c>
+      <c r="C690" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D690" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1592</v>
+        <v>1164</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1631</v>
+        <v>1423</v>
       </c>
       <c r="C691" s="10" t="s">
-        <v>1632</v>
+        <v>1443</v>
       </c>
       <c r="D691" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1592</v>
+        <v>1164</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1451</v>
+        <v>1413</v>
       </c>
       <c r="C692" s="9" t="s">
-        <v>1453</v>
+        <v>1444</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1475</v>
+        <v>1164</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C693" s="2" t="s">
-        <v>1454</v>
+        <v>1415</v>
+      </c>
+      <c r="C693" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07122F8D-1E62-45CD-8207-9892B54C90EC}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FFCAE5A-E035-4A20-A048-E43202B979F9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4921,7 +4921,7 @@
     <t>78970151027721052</t>
   </si>
   <si>
-    <t>ОБЩИНА ВАРНА % 5 - 5</t>
+    <t>ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА</t>
   </si>
 </sst>
 </file>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FFCAE5A-E035-4A20-A048-E43202B979F9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4655FDE-E78C-4DED-A409-F7FBDC6E995A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="1636">
   <si>
     <t>Company</t>
   </si>
@@ -4922,6 +4922,12 @@
   </si>
   <si>
     <t>ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА</t>
+  </si>
+  <si>
+    <t>ТУБА ЗОО</t>
+  </si>
+  <si>
+    <t>78970155027722788</t>
   </si>
 </sst>
 </file>
@@ -4963,7 +4969,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4986,22 +4992,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -5029,10 +5024,6 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5335,7 +5326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E743"/>
+  <dimension ref="A1:E744"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
@@ -12625,14 +12616,14 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="519" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="B519" s="11" t="s">
+      <c r="B519" s="2" t="s">
         <v>1589</v>
       </c>
-      <c r="C519" s="12" t="s">
+      <c r="C519" s="3" t="s">
         <v>1590</v>
       </c>
       <c r="D519" s="3" t="s">
@@ -12641,16 +12632,16 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C520" s="6" t="s">
-        <v>1137</v>
+        <v>1634</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>1635</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
@@ -12658,10 +12649,10 @@
         <v>1076</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>1081</v>
@@ -12672,10 +12663,10 @@
         <v>1076</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>1081</v>
@@ -12686,10 +12677,10 @@
         <v>1076</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>1081</v>
@@ -12697,16 +12688,16 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
@@ -12714,10 +12705,10 @@
         <v>1082</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>1083</v>
@@ -12728,10 +12719,10 @@
         <v>1082</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>1083</v>
@@ -12742,10 +12733,10 @@
         <v>1082</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>1083</v>
@@ -12756,10 +12747,10 @@
         <v>1082</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D528" s="3" t="s">
         <v>1083</v>
@@ -12767,16 +12758,16 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
@@ -12784,10 +12775,10 @@
         <v>1540</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>1094</v>
@@ -12798,10 +12789,10 @@
         <v>1540</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D531" s="3" t="s">
         <v>1094</v>
@@ -12812,10 +12803,10 @@
         <v>1540</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>1094</v>
@@ -12826,10 +12817,10 @@
         <v>1540</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D533" s="3" t="s">
         <v>1094</v>
@@ -12837,16 +12828,16 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C534" s="2" t="s">
-        <v>1168</v>
+        <v>1093</v>
+      </c>
+      <c r="C534" s="6" t="s">
+        <v>1150</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
@@ -12854,10 +12845,10 @@
         <v>1151</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D535" s="3" t="s">
         <v>1459</v>
@@ -12865,16 +12856,16 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D536" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
@@ -12882,10 +12873,10 @@
         <v>1152</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D537" s="3" t="s">
         <v>1460</v>
@@ -12893,16 +12884,16 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
@@ -12910,10 +12901,10 @@
         <v>1153</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D539" s="3" t="s">
         <v>1461</v>
@@ -12921,16 +12912,16 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
@@ -12938,10 +12929,10 @@
         <v>1154</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D541" s="3" t="s">
         <v>1462</v>
@@ -12949,16 +12940,16 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
@@ -12966,10 +12957,10 @@
         <v>1155</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D543" s="3" t="s">
         <v>1463</v>
@@ -12977,16 +12968,16 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
@@ -12994,10 +12985,10 @@
         <v>1156</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D545" s="3" t="s">
         <v>1464</v>
@@ -13008,10 +12999,10 @@
         <v>1156</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D546" s="3" t="s">
         <v>1464</v>
@@ -13022,10 +13013,10 @@
         <v>1156</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D547" s="3" t="s">
         <v>1464</v>
@@ -13033,16 +13024,16 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
@@ -13050,10 +13041,10 @@
         <v>1157</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D549" s="3" t="s">
         <v>1465</v>
@@ -13061,16 +13052,16 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B550" s="7" t="s">
-        <v>1234</v>
+        <v>1157</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>1195</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
@@ -13078,10 +13069,10 @@
         <v>1158</v>
       </c>
       <c r="B551" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>1466</v>
@@ -13092,10 +13083,10 @@
         <v>1158</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D552" s="3" t="s">
         <v>1466</v>
@@ -13106,10 +13097,10 @@
         <v>1158</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D553" s="3" t="s">
         <v>1466</v>
@@ -13120,10 +13111,10 @@
         <v>1158</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D554" s="3" t="s">
         <v>1466</v>
@@ -13134,10 +13125,10 @@
         <v>1158</v>
       </c>
       <c r="B555" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>1466</v>
@@ -13148,10 +13139,10 @@
         <v>1158</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D556" s="3" t="s">
         <v>1466</v>
@@ -13162,10 +13153,10 @@
         <v>1158</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D557" s="3" t="s">
         <v>1466</v>
@@ -13176,10 +13167,10 @@
         <v>1158</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D558" s="3" t="s">
         <v>1466</v>
@@ -13190,10 +13181,10 @@
         <v>1158</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D559" s="3" t="s">
         <v>1466</v>
@@ -13204,10 +13195,10 @@
         <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D560" s="3" t="s">
         <v>1466</v>
@@ -13218,10 +13209,10 @@
         <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D561" s="3" t="s">
         <v>1466</v>
@@ -13232,10 +13223,10 @@
         <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D562" s="3" t="s">
         <v>1466</v>
@@ -13246,10 +13237,10 @@
         <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1466</v>
@@ -13260,10 +13251,10 @@
         <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>1466</v>
@@ -13274,10 +13265,10 @@
         <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>1466</v>
@@ -13288,10 +13279,10 @@
         <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1466</v>
@@ -13302,10 +13293,10 @@
         <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1466</v>
@@ -13316,10 +13307,10 @@
         <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>1466</v>
@@ -13330,10 +13321,10 @@
         <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>1466</v>
@@ -13344,10 +13335,10 @@
         <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>1466</v>
@@ -13358,10 +13349,10 @@
         <v>1158</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1466</v>
@@ -13371,11 +13362,11 @@
       <c r="A572" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B572" s="4" t="s">
-        <v>1256</v>
+      <c r="B572" s="7" t="s">
+        <v>1255</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1466</v>
@@ -13385,11 +13376,11 @@
       <c r="A573" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B573" s="7" t="s">
-        <v>1257</v>
+      <c r="B573" s="4" t="s">
+        <v>1256</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>1466</v>
@@ -13400,10 +13391,10 @@
         <v>1158</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1466</v>
@@ -13414,10 +13405,10 @@
         <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>1466</v>
@@ -13428,10 +13419,10 @@
         <v>1158</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>1466</v>
@@ -13442,10 +13433,10 @@
         <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>1466</v>
@@ -13456,10 +13447,10 @@
         <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>1466</v>
@@ -13470,10 +13461,10 @@
         <v>1158</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1232</v>
+        <v>1262</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>1466</v>
@@ -13484,10 +13475,10 @@
         <v>1158</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1263</v>
+        <v>1232</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>1466</v>
@@ -13498,10 +13489,10 @@
         <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>1466</v>
@@ -13512,10 +13503,10 @@
         <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>1466</v>
@@ -13526,10 +13517,10 @@
         <v>1158</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>1466</v>
@@ -13537,16 +13528,16 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1282</v>
+        <v>1231</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -13554,10 +13545,10 @@
         <v>1159</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>1467</v>
@@ -13568,10 +13559,10 @@
         <v>1159</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>1467</v>
@@ -13582,10 +13573,10 @@
         <v>1159</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>1467</v>
@@ -13596,10 +13587,10 @@
         <v>1159</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1467</v>
@@ -13610,10 +13601,10 @@
         <v>1159</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1467</v>
@@ -13624,10 +13615,10 @@
         <v>1159</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>1467</v>
@@ -13638,10 +13629,10 @@
         <v>1159</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>1467</v>
@@ -13652,10 +13643,10 @@
         <v>1159</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1467</v>
@@ -13666,10 +13657,10 @@
         <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>1467</v>
@@ -13680,10 +13671,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -13694,10 +13685,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -13708,10 +13699,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -13722,10 +13713,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -13736,10 +13727,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -13750,10 +13741,10 @@
         <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>1467</v>
@@ -13761,16 +13752,16 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="D600" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
@@ -13778,10 +13769,10 @@
         <v>1160</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D601" s="3" t="s">
         <v>1468</v>
@@ -13792,10 +13783,10 @@
         <v>1160</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1468</v>
@@ -13806,10 +13797,10 @@
         <v>1160</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1468</v>
@@ -13817,30 +13808,30 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B604" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B604" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1558</v>
+        <v>1305</v>
       </c>
       <c r="D604" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="D605" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
@@ -13848,10 +13839,10 @@
         <v>1162</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D606" s="3" t="s">
         <v>1470</v>
@@ -13859,16 +13850,16 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B607" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C607" s="8" t="s">
-        <v>1560</v>
+        <v>1162</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
@@ -13876,10 +13867,10 @@
         <v>1587</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C608" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1471</v>
@@ -13890,10 +13881,10 @@
         <v>1587</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1471</v>
@@ -13904,10 +13895,10 @@
         <v>1587</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1471</v>
@@ -13918,10 +13909,10 @@
         <v>1587</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1471</v>
@@ -13932,10 +13923,10 @@
         <v>1587</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1471</v>
@@ -13946,10 +13937,10 @@
         <v>1587</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1471</v>
@@ -13960,10 +13951,10 @@
         <v>1587</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1471</v>
@@ -13974,10 +13965,10 @@
         <v>1587</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1566</v>
+        <v>1553</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1471</v>
@@ -13988,10 +13979,10 @@
         <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -14002,10 +13993,10 @@
         <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -14016,10 +14007,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -14030,10 +14021,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -14044,10 +14035,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -14058,10 +14049,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C621" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -14072,10 +14063,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C622" s="9" t="s">
-        <v>1362</v>
+        <v>1323</v>
+      </c>
+      <c r="C622" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -14086,10 +14077,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C623" s="10" t="s">
-        <v>1363</v>
+        <v>1077</v>
+      </c>
+      <c r="C623" s="9" t="s">
+        <v>1362</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -14100,10 +14091,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C624" s="9" t="s">
-        <v>1364</v>
+        <v>1324</v>
+      </c>
+      <c r="C624" s="10" t="s">
+        <v>1363</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -14114,10 +14105,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C625" s="10" t="s">
-        <v>1365</v>
+        <v>1325</v>
+      </c>
+      <c r="C625" s="9" t="s">
+        <v>1364</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14128,10 +14119,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C626" s="9" t="s">
-        <v>1366</v>
+        <v>1326</v>
+      </c>
+      <c r="C626" s="10" t="s">
+        <v>1365</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14142,10 +14133,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C627" s="10" t="s">
-        <v>1367</v>
+        <v>1327</v>
+      </c>
+      <c r="C627" s="9" t="s">
+        <v>1366</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14156,10 +14147,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C628" s="9" t="s">
-        <v>1368</v>
+        <v>1328</v>
+      </c>
+      <c r="C628" s="10" t="s">
+        <v>1367</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14170,10 +14161,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C629" s="10" t="s">
-        <v>1369</v>
+        <v>1329</v>
+      </c>
+      <c r="C629" s="9" t="s">
+        <v>1368</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14184,10 +14175,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C630" s="9" t="s">
-        <v>1370</v>
+        <v>1330</v>
+      </c>
+      <c r="C630" s="10" t="s">
+        <v>1369</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14198,10 +14189,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C631" s="10" t="s">
-        <v>1371</v>
+        <v>1331</v>
+      </c>
+      <c r="C631" s="9" t="s">
+        <v>1370</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14212,10 +14203,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C632" s="9" t="s">
-        <v>1372</v>
+        <v>1332</v>
+      </c>
+      <c r="C632" s="10" t="s">
+        <v>1371</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14226,10 +14217,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C633" s="10" t="s">
-        <v>1373</v>
+        <v>1333</v>
+      </c>
+      <c r="C633" s="9" t="s">
+        <v>1372</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14240,10 +14231,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C634" s="9" t="s">
-        <v>1374</v>
+        <v>1334</v>
+      </c>
+      <c r="C634" s="10" t="s">
+        <v>1373</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14254,10 +14245,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C635" s="10" t="s">
-        <v>1375</v>
+        <v>1335</v>
+      </c>
+      <c r="C635" s="9" t="s">
+        <v>1374</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14268,10 +14259,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C636" s="9" t="s">
-        <v>1376</v>
+        <v>1336</v>
+      </c>
+      <c r="C636" s="10" t="s">
+        <v>1375</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14282,10 +14273,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C637" s="10" t="s">
-        <v>1377</v>
+        <v>1337</v>
+      </c>
+      <c r="C637" s="9" t="s">
+        <v>1376</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14296,10 +14287,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C638" s="9" t="s">
-        <v>1378</v>
+        <v>1338</v>
+      </c>
+      <c r="C638" s="10" t="s">
+        <v>1377</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14310,10 +14301,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C639" s="10" t="s">
-        <v>1379</v>
+        <v>1339</v>
+      </c>
+      <c r="C639" s="9" t="s">
+        <v>1378</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14324,10 +14315,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C640" s="9" t="s">
-        <v>1380</v>
+        <v>1340</v>
+      </c>
+      <c r="C640" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14338,10 +14329,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C641" s="10" t="s">
-        <v>1381</v>
+        <v>1341</v>
+      </c>
+      <c r="C641" s="9" t="s">
+        <v>1380</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14352,10 +14343,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C642" s="9" t="s">
-        <v>1382</v>
+        <v>1342</v>
+      </c>
+      <c r="C642" s="10" t="s">
+        <v>1381</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14366,10 +14357,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C643" s="10" t="s">
-        <v>1383</v>
+        <v>1343</v>
+      </c>
+      <c r="C643" s="9" t="s">
+        <v>1382</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14380,10 +14371,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C644" s="9" t="s">
-        <v>1384</v>
+        <v>1344</v>
+      </c>
+      <c r="C644" s="10" t="s">
+        <v>1383</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14394,10 +14385,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C645" s="10" t="s">
-        <v>1385</v>
+        <v>1345</v>
+      </c>
+      <c r="C645" s="9" t="s">
+        <v>1384</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14408,10 +14399,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C646" s="9" t="s">
-        <v>1386</v>
+        <v>1346</v>
+      </c>
+      <c r="C646" s="10" t="s">
+        <v>1385</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14422,10 +14413,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C647" s="10" t="s">
-        <v>1387</v>
+        <v>1347</v>
+      </c>
+      <c r="C647" s="9" t="s">
+        <v>1386</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14436,10 +14427,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C648" s="9" t="s">
-        <v>1388</v>
+        <v>1348</v>
+      </c>
+      <c r="C648" s="10" t="s">
+        <v>1387</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14450,10 +14441,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C649" s="10" t="s">
-        <v>1389</v>
+        <v>1349</v>
+      </c>
+      <c r="C649" s="9" t="s">
+        <v>1388</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14464,10 +14455,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C650" s="9" t="s">
-        <v>1390</v>
+        <v>1350</v>
+      </c>
+      <c r="C650" s="10" t="s">
+        <v>1389</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14478,10 +14469,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C651" s="10" t="s">
-        <v>1391</v>
+        <v>1351</v>
+      </c>
+      <c r="C651" s="9" t="s">
+        <v>1390</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14492,10 +14483,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C652" s="9" t="s">
-        <v>1392</v>
+        <v>1352</v>
+      </c>
+      <c r="C652" s="10" t="s">
+        <v>1391</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -14506,10 +14497,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C653" s="10" t="s">
-        <v>1393</v>
+        <v>1353</v>
+      </c>
+      <c r="C653" s="9" t="s">
+        <v>1392</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -14520,10 +14511,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C654" s="9" t="s">
-        <v>1394</v>
+        <v>1354</v>
+      </c>
+      <c r="C654" s="10" t="s">
+        <v>1393</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -14534,10 +14525,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C655" s="10" t="s">
-        <v>1395</v>
+        <v>1355</v>
+      </c>
+      <c r="C655" s="9" t="s">
+        <v>1394</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -14548,10 +14539,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C656" s="9" t="s">
-        <v>1396</v>
+        <v>1356</v>
+      </c>
+      <c r="C656" s="10" t="s">
+        <v>1395</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -14562,10 +14553,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C657" s="10" t="s">
-        <v>1397</v>
+        <v>1357</v>
+      </c>
+      <c r="C657" s="9" t="s">
+        <v>1396</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -14576,10 +14567,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C658" s="9" t="s">
-        <v>1398</v>
+        <v>1358</v>
+      </c>
+      <c r="C658" s="10" t="s">
+        <v>1397</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -14590,10 +14581,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C659" s="10" t="s">
-        <v>1399</v>
+        <v>1359</v>
+      </c>
+      <c r="C659" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -14604,10 +14595,10 @@
         <v>1587</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C660" s="2" t="s">
-        <v>1573</v>
+        <v>1360</v>
+      </c>
+      <c r="C660" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -14615,13 +14606,13 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B661" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C661" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -14632,10 +14623,10 @@
         <v>1472</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C662" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -14646,10 +14637,10 @@
         <v>1472</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -14660,10 +14651,10 @@
         <v>1472</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -14674,10 +14665,10 @@
         <v>1472</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -14688,10 +14679,10 @@
         <v>1472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -14702,10 +14693,10 @@
         <v>1472</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -14716,10 +14707,10 @@
         <v>1472</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -14727,13 +14718,13 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C669" s="8" t="s">
-        <v>1574</v>
+        <v>1552</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -14741,13 +14732,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C670" s="9" t="s">
-        <v>1410</v>
+        <v>1408</v>
+      </c>
+      <c r="C670" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D670" s="3" t="s">
         <v>1471</v>
@@ -14755,13 +14746,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C671" s="10" t="s">
-        <v>1452</v>
+        <v>1409</v>
+      </c>
+      <c r="C671" s="9" t="s">
+        <v>1410</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1471</v>
@@ -14772,10 +14763,10 @@
         <v>1592</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C672" s="9" t="s">
-        <v>1453</v>
+        <v>1450</v>
+      </c>
+      <c r="C672" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D672" s="3" t="s">
         <v>1471</v>
@@ -14783,13 +14774,13 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1633</v>
+        <v>1592</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C673" s="10" t="s">
-        <v>1632</v>
+        <v>1451</v>
+      </c>
+      <c r="C673" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1471</v>
@@ -14797,13 +14788,13 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1475</v>
+        <v>1633</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C674" s="2" t="s">
-        <v>1454</v>
+        <v>1631</v>
+      </c>
+      <c r="C674" s="10" t="s">
+        <v>1632</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1471</v>
@@ -14811,16 +14802,16 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1163</v>
+        <v>1475</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D675" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
@@ -14828,10 +14819,10 @@
         <v>1163</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C676" s="9" t="s">
-        <v>1575</v>
+        <v>1411</v>
+      </c>
+      <c r="C676" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D676" s="3" t="s">
         <v>1473</v>
@@ -14839,16 +14830,16 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C677" s="10" t="s">
-        <v>1429</v>
+        <v>1479</v>
+      </c>
+      <c r="C677" s="9" t="s">
+        <v>1575</v>
       </c>
       <c r="D677" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
@@ -14856,10 +14847,10 @@
         <v>1164</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C678" s="9" t="s">
-        <v>1430</v>
+        <v>1414</v>
+      </c>
+      <c r="C678" s="10" t="s">
+        <v>1429</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>1474</v>
@@ -14870,10 +14861,10 @@
         <v>1164</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C679" s="10" t="s">
-        <v>1431</v>
+        <v>1416</v>
+      </c>
+      <c r="C679" s="9" t="s">
+        <v>1430</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1474</v>
@@ -14884,10 +14875,10 @@
         <v>1164</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C680" s="9" t="s">
-        <v>1432</v>
+        <v>1417</v>
+      </c>
+      <c r="C680" s="10" t="s">
+        <v>1431</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1474</v>
@@ -14898,10 +14889,10 @@
         <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C681" s="10" t="s">
-        <v>1433</v>
+        <v>1418</v>
+      </c>
+      <c r="C681" s="9" t="s">
+        <v>1432</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1474</v>
@@ -14912,10 +14903,10 @@
         <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C682" s="9" t="s">
-        <v>1434</v>
+        <v>1419</v>
+      </c>
+      <c r="C682" s="10" t="s">
+        <v>1433</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1474</v>
@@ -14926,10 +14917,10 @@
         <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C683" s="10" t="s">
-        <v>1435</v>
+        <v>1420</v>
+      </c>
+      <c r="C683" s="9" t="s">
+        <v>1434</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1474</v>
@@ -14940,10 +14931,10 @@
         <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C684" s="9" t="s">
-        <v>1436</v>
+        <v>1421</v>
+      </c>
+      <c r="C684" s="10" t="s">
+        <v>1435</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1474</v>
@@ -14954,10 +14945,10 @@
         <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C685" s="10" t="s">
-        <v>1437</v>
+        <v>1422</v>
+      </c>
+      <c r="C685" s="9" t="s">
+        <v>1436</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1474</v>
@@ -14968,10 +14959,10 @@
         <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C686" s="9" t="s">
-        <v>1438</v>
+        <v>1423</v>
+      </c>
+      <c r="C686" s="10" t="s">
+        <v>1437</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1474</v>
@@ -14982,10 +14973,10 @@
         <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C687" s="10" t="s">
-        <v>1439</v>
+        <v>1424</v>
+      </c>
+      <c r="C687" s="9" t="s">
+        <v>1438</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1474</v>
@@ -14996,10 +14987,10 @@
         <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C688" s="9" t="s">
-        <v>1440</v>
+        <v>1425</v>
+      </c>
+      <c r="C688" s="10" t="s">
+        <v>1439</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1474</v>
@@ -15010,10 +15001,10 @@
         <v>1164</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C689" s="10" t="s">
-        <v>1441</v>
+        <v>1426</v>
+      </c>
+      <c r="C689" s="9" t="s">
+        <v>1440</v>
       </c>
       <c r="D689" s="3" t="s">
         <v>1474</v>
@@ -15024,10 +15015,10 @@
         <v>1164</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C690" s="9" t="s">
-        <v>1442</v>
+        <v>1427</v>
+      </c>
+      <c r="C690" s="10" t="s">
+        <v>1441</v>
       </c>
       <c r="D690" s="3" t="s">
         <v>1474</v>
@@ -15038,10 +15029,10 @@
         <v>1164</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C691" s="10" t="s">
-        <v>1443</v>
+        <v>1428</v>
+      </c>
+      <c r="C691" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1474</v>
@@ -15052,10 +15043,10 @@
         <v>1164</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C692" s="9" t="s">
-        <v>1444</v>
+        <v>1423</v>
+      </c>
+      <c r="C692" s="10" t="s">
+        <v>1443</v>
       </c>
       <c r="D692" s="3" t="s">
         <v>1474</v>
@@ -15066,10 +15057,10 @@
         <v>1164</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C693" s="10" t="s">
-        <v>1445</v>
+        <v>1413</v>
+      </c>
+      <c r="C693" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>1474</v>
@@ -15077,16 +15068,16 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C694" s="2" t="s">
-        <v>1455</v>
+        <v>1415</v>
+      </c>
+      <c r="C694" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
@@ -15094,10 +15085,10 @@
         <v>1165</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1476</v>
@@ -15108,10 +15099,10 @@
         <v>1165</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D696" s="3" t="s">
         <v>1476</v>
@@ -15122,10 +15113,10 @@
         <v>1165</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1629</v>
+        <v>1448</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1630</v>
+        <v>1457</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>1476</v>
@@ -15136,10 +15127,10 @@
         <v>1165</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1449</v>
+        <v>1629</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1458</v>
+        <v>1630</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1476</v>
@@ -15147,16 +15138,16 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1510</v>
+        <v>1449</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1480</v>
+        <v>1458</v>
       </c>
       <c r="D699" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
@@ -15164,10 +15155,10 @@
         <v>1477</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1539</v>
@@ -15178,10 +15169,10 @@
         <v>1477</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1539</v>
@@ -15192,10 +15183,10 @@
         <v>1477</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1539</v>
@@ -15206,10 +15197,10 @@
         <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1539</v>
@@ -15220,10 +15211,10 @@
         <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1539</v>
@@ -15234,10 +15225,10 @@
         <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1539</v>
@@ -15248,10 +15239,10 @@
         <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1539</v>
@@ -15262,10 +15253,10 @@
         <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1539</v>
@@ -15276,10 +15267,10 @@
         <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1539</v>
@@ -15290,10 +15281,10 @@
         <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1539</v>
@@ -15304,10 +15295,10 @@
         <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>1539</v>
@@ -15318,10 +15309,10 @@
         <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D711" s="3" t="s">
         <v>1539</v>
@@ -15332,10 +15323,10 @@
         <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1539</v>
@@ -15346,10 +15337,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15360,10 +15351,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15374,10 +15365,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15388,10 +15379,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15402,10 +15393,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15416,10 +15407,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15430,10 +15421,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15444,10 +15435,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15458,10 +15449,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15472,10 +15463,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15486,10 +15477,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15500,10 +15491,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -15514,10 +15505,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -15528,10 +15519,10 @@
         <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -15542,10 +15533,10 @@
         <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>1539</v>
@@ -15553,13 +15544,13 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1479</v>
+        <v>1538</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>1539</v>
@@ -15567,16 +15558,16 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1597</v>
+        <v>1479</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1604</v>
+        <v>1509</v>
       </c>
       <c r="D729" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
@@ -15584,10 +15575,10 @@
         <v>1595</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>1596</v>
@@ -15598,10 +15589,10 @@
         <v>1595</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>1596</v>
@@ -15612,10 +15603,10 @@
         <v>1595</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D732" s="3" t="s">
         <v>1596</v>
@@ -15626,10 +15617,10 @@
         <v>1595</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1596</v>
@@ -15640,10 +15631,10 @@
         <v>1595</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D734" s="3" t="s">
         <v>1596</v>
@@ -15654,10 +15645,10 @@
         <v>1595</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D735" s="3" t="s">
         <v>1596</v>
@@ -15665,16 +15656,16 @@
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1612</v>
+        <v>1603</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="D736" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
@@ -15682,10 +15673,10 @@
         <v>1611</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>1628</v>
@@ -15696,10 +15687,10 @@
         <v>1611</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D738" s="3" t="s">
         <v>1628</v>
@@ -15710,10 +15701,10 @@
         <v>1611</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D739" s="3" t="s">
         <v>1628</v>
@@ -15724,10 +15715,10 @@
         <v>1611</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D740" s="3" t="s">
         <v>1628</v>
@@ -15738,10 +15729,10 @@
         <v>1611</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D741" s="3" t="s">
         <v>1628</v>
@@ -15752,10 +15743,10 @@
         <v>1611</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D742" s="3" t="s">
         <v>1628</v>
@@ -15766,12 +15757,26 @@
         <v>1611</v>
       </c>
       <c r="B743" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C743" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D743" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A744" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B744" s="2" t="s">
         <v>1618</v>
       </c>
-      <c r="C743" s="2" t="s">
+      <c r="C744" s="2" t="s">
         <v>1627</v>
       </c>
-      <c r="D743" s="3" t="s">
+      <c r="D744" s="3" t="s">
         <v>1628</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{A90EF2EC-41C5-4C16-8C36-CA45D4AD502D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4655FDE-E78C-4DED-A409-F7FBDC6E995A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6455075D-4B34-4B11-856B-4C037200CE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="1720">
   <si>
     <t>Company</t>
   </si>
@@ -4928,6 +4928,258 @@
   </si>
   <si>
     <t>78970155027722788</t>
+  </si>
+  <si>
+    <t>СТЕФАН ИВАНОВ РУСИНЯШКИ</t>
+  </si>
+  <si>
+    <t>SIR 72</t>
+  </si>
+  <si>
+    <t>78970153027721520</t>
+  </si>
+  <si>
+    <t>7202114086</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА КАРТА</t>
+  </si>
+  <si>
+    <t>78970110027720308</t>
+  </si>
+  <si>
+    <t>78970110027720316</t>
+  </si>
+  <si>
+    <t>78970110027720324</t>
+  </si>
+  <si>
+    <t>78970110027720332</t>
+  </si>
+  <si>
+    <t>78970110027720340</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 1 - ФИЛИАЛ ХАСКОВО</t>
+  </si>
+  <si>
+    <t>СТ5415РС</t>
+  </si>
+  <si>
+    <t>78970153027721603</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 2 - ФТТ</t>
+  </si>
+  <si>
+    <t>Y6426BA</t>
+  </si>
+  <si>
+    <t>У3771АК</t>
+  </si>
+  <si>
+    <t>У9353ВА</t>
+  </si>
+  <si>
+    <t>У5775АМ</t>
+  </si>
+  <si>
+    <t>ТУ ТУБА 3 - ЯМБОЛ</t>
+  </si>
+  <si>
+    <t>78970153027721611</t>
+  </si>
+  <si>
+    <t>78970153027721629</t>
+  </si>
+  <si>
+    <t>78970153027721637</t>
+  </si>
+  <si>
+    <t>78970153027721645</t>
+  </si>
+  <si>
+    <t>78970153027721678</t>
+  </si>
+  <si>
+    <t>СТ 3223 АХ</t>
+  </si>
+  <si>
+    <t>ТУ ТУБА 1</t>
+  </si>
+  <si>
+    <t>ТУ ТУБА 2</t>
+  </si>
+  <si>
+    <t>СТ5559ВК</t>
+  </si>
+  <si>
+    <t>СТ8987КК</t>
+  </si>
+  <si>
+    <t>СТ5559РС</t>
+  </si>
+  <si>
+    <t>СТ5565РС</t>
+  </si>
+  <si>
+    <t>СТ7447РС</t>
+  </si>
+  <si>
+    <t>СТ5229РС</t>
+  </si>
+  <si>
+    <t>СТ7776РН</t>
+  </si>
+  <si>
+    <t>СТ9394АН</t>
+  </si>
+  <si>
+    <t>СТ5293РВ</t>
+  </si>
+  <si>
+    <t>СТ9898РР</t>
+  </si>
+  <si>
+    <t>СТ6336АН</t>
+  </si>
+  <si>
+    <t>СТ3413ВХ</t>
+  </si>
+  <si>
+    <t>СТ5232РС</t>
+  </si>
+  <si>
+    <t>СТ6813ВН</t>
+  </si>
+  <si>
+    <t>СТ8118РН</t>
+  </si>
+  <si>
+    <t>СТ9429РН</t>
+  </si>
+  <si>
+    <t>СТ9163РВ</t>
+  </si>
+  <si>
+    <t>СТ3232ВТ</t>
+  </si>
+  <si>
+    <t>СТ7287АВ</t>
+  </si>
+  <si>
+    <t>СТ8112АР</t>
+  </si>
+  <si>
+    <t>СТ3573НН</t>
+  </si>
+  <si>
+    <t>СТ8657РВ</t>
+  </si>
+  <si>
+    <t>СТ3385РА</t>
+  </si>
+  <si>
+    <t>СТ7753РТ</t>
+  </si>
+  <si>
+    <t>78970153027721652</t>
+  </si>
+  <si>
+    <t>78970153027721660</t>
+  </si>
+  <si>
+    <t>78970153027721686</t>
+  </si>
+  <si>
+    <t>78970153027721694</t>
+  </si>
+  <si>
+    <t>78970153027721702</t>
+  </si>
+  <si>
+    <t>78970153027721710</t>
+  </si>
+  <si>
+    <t>78970153027721728</t>
+  </si>
+  <si>
+    <t>78970153027721736</t>
+  </si>
+  <si>
+    <t>78970153027721744</t>
+  </si>
+  <si>
+    <t>78970153027721751</t>
+  </si>
+  <si>
+    <t>78970153027721769</t>
+  </si>
+  <si>
+    <t>78970153027721777</t>
+  </si>
+  <si>
+    <t>78970153027721785</t>
+  </si>
+  <si>
+    <t>78970153027721793</t>
+  </si>
+  <si>
+    <t>78970153027721801</t>
+  </si>
+  <si>
+    <t>78970153027721819</t>
+  </si>
+  <si>
+    <t>78970153027721827</t>
+  </si>
+  <si>
+    <t>78970153027721835</t>
+  </si>
+  <si>
+    <t>78970153027721843</t>
+  </si>
+  <si>
+    <t>78970153027721850</t>
+  </si>
+  <si>
+    <t>78970153027721868</t>
+  </si>
+  <si>
+    <t>78970153027721876</t>
+  </si>
+  <si>
+    <t>78970153027721884</t>
+  </si>
+  <si>
+    <t>78970153027721892</t>
+  </si>
+  <si>
+    <t>78970153027721900</t>
+  </si>
+  <si>
+    <t>78970153027721918</t>
+  </si>
+  <si>
+    <t>78970153027721926</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ</t>
+  </si>
+  <si>
+    <t>123024538</t>
+  </si>
+  <si>
+    <t>1230245380127</t>
+  </si>
+  <si>
+    <t>78970151027721060</t>
+  </si>
+  <si>
+    <t>В5454ХМ</t>
   </si>
 </sst>
 </file>
@@ -5326,7 +5578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E744"/>
+  <dimension ref="A1:E784"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
@@ -9914,16 +10166,16 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>1593</v>
+        <v>969</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1719</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>1594</v>
+        <v>1718</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -9931,10 +10183,10 @@
         <v>972</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>632</v>
+        <v>1593</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>633</v>
+        <v>1594</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>974</v>
@@ -9945,10 +10197,10 @@
         <v>972</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>974</v>
@@ -9959,10 +10211,10 @@
         <v>972</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>974</v>
@@ -9973,10 +10225,10 @@
         <v>972</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>974</v>
@@ -9987,10 +10239,10 @@
         <v>972</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>974</v>
@@ -10001,10 +10253,10 @@
         <v>972</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>974</v>
@@ -10015,10 +10267,10 @@
         <v>972</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>974</v>
@@ -10029,10 +10281,10 @@
         <v>972</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>974</v>
@@ -10043,10 +10295,10 @@
         <v>972</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>974</v>
@@ -10057,10 +10309,10 @@
         <v>972</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>1020</v>
+        <v>648</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1021</v>
+        <v>649</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>974</v>
@@ -10068,13 +10320,13 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>650</v>
+        <v>1020</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>651</v>
+        <v>1021</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>974</v>
@@ -10085,10 +10337,10 @@
         <v>971</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>974</v>
@@ -10099,10 +10351,10 @@
         <v>971</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>974</v>
@@ -10113,10 +10365,10 @@
         <v>971</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>974</v>
@@ -10127,10 +10379,10 @@
         <v>971</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>974</v>
@@ -10141,10 +10393,10 @@
         <v>971</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>974</v>
@@ -10155,10 +10407,10 @@
         <v>971</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>974</v>
@@ -10169,10 +10421,10 @@
         <v>971</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>974</v>
@@ -10180,16 +10432,16 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -10197,10 +10449,10 @@
         <v>973</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>975</v>
@@ -10211,10 +10463,10 @@
         <v>973</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>975</v>
@@ -10225,10 +10477,10 @@
         <v>973</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>975</v>
@@ -10236,16 +10488,16 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -10253,10 +10505,10 @@
         <v>976</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>987</v>
@@ -10267,10 +10519,10 @@
         <v>976</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>987</v>
@@ -10281,10 +10533,10 @@
         <v>976</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>987</v>
@@ -10295,10 +10547,10 @@
         <v>976</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>987</v>
@@ -10309,10 +10561,10 @@
         <v>976</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D356" s="3" t="s">
         <v>987</v>
@@ -10323,10 +10575,10 @@
         <v>976</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>987</v>
@@ -10337,10 +10589,10 @@
         <v>976</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>987</v>
@@ -10351,10 +10603,10 @@
         <v>976</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>987</v>
@@ -10365,10 +10617,10 @@
         <v>976</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>987</v>
@@ -10379,10 +10631,10 @@
         <v>976</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>987</v>
@@ -10393,10 +10645,10 @@
         <v>976</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>987</v>
@@ -10407,10 +10659,10 @@
         <v>976</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>987</v>
@@ -10421,10 +10673,10 @@
         <v>976</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>987</v>
@@ -10435,10 +10687,10 @@
         <v>976</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>987</v>
@@ -10449,10 +10701,10 @@
         <v>976</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>987</v>
@@ -10460,13 +10712,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>987</v>
@@ -10477,10 +10729,10 @@
         <v>977</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>987</v>
@@ -10491,10 +10743,10 @@
         <v>977</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>987</v>
@@ -10505,10 +10757,10 @@
         <v>977</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>987</v>
@@ -10519,10 +10771,10 @@
         <v>977</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>987</v>
@@ -10533,10 +10785,10 @@
         <v>977</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>987</v>
@@ -10547,10 +10799,10 @@
         <v>977</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>987</v>
@@ -10561,10 +10813,10 @@
         <v>977</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>987</v>
@@ -10575,10 +10827,10 @@
         <v>977</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>987</v>
@@ -10589,10 +10841,10 @@
         <v>977</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>987</v>
@@ -10603,10 +10855,10 @@
         <v>977</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>987</v>
@@ -10617,10 +10869,10 @@
         <v>977</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>987</v>
@@ -10631,10 +10883,10 @@
         <v>977</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>987</v>
@@ -10645,10 +10897,10 @@
         <v>977</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>987</v>
@@ -10659,10 +10911,10 @@
         <v>977</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>987</v>
@@ -10673,10 +10925,10 @@
         <v>977</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>987</v>
@@ -10684,27 +10936,27 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>893</v>
+        <v>737</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>740</v>
+        <v>893</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>986</v>
@@ -10715,10 +10967,10 @@
         <v>984</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>986</v>
@@ -10729,10 +10981,10 @@
         <v>984</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>986</v>
@@ -10746,7 +10998,7 @@
         <v>743</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>875</v>
+        <v>744</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>986</v>
@@ -10757,10 +11009,10 @@
         <v>984</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>986</v>
@@ -10771,10 +11023,10 @@
         <v>984</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>986</v>
@@ -10782,13 +11034,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>986</v>
@@ -10802,7 +11054,7 @@
         <v>745</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>746</v>
+        <v>878</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>986</v>
@@ -10810,16 +11062,16 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>788</v>
+        <v>746</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -10827,10 +11079,10 @@
         <v>978</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>810</v>
+        <v>788</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>988</v>
@@ -10841,10 +11093,10 @@
         <v>978</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>988</v>
@@ -10855,10 +11107,10 @@
         <v>978</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>988</v>
@@ -10869,10 +11121,10 @@
         <v>978</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>988</v>
@@ -10883,10 +11135,10 @@
         <v>978</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>988</v>
@@ -10897,10 +11149,10 @@
         <v>978</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>988</v>
@@ -10911,10 +11163,10 @@
         <v>978</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>988</v>
@@ -10925,10 +11177,10 @@
         <v>978</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>988</v>
@@ -10939,10 +11191,10 @@
         <v>978</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>988</v>
@@ -10953,10 +11205,10 @@
         <v>978</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>803</v>
+        <v>751</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>988</v>
@@ -10967,10 +11219,10 @@
         <v>978</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>988</v>
@@ -10981,10 +11233,10 @@
         <v>978</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>751</v>
+        <v>805</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>988</v>
@@ -10995,10 +11247,10 @@
         <v>978</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>988</v>
@@ -11009,10 +11261,10 @@
         <v>978</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>809</v>
+        <v>762</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>988</v>
@@ -11023,10 +11275,10 @@
         <v>978</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>898</v>
+        <v>809</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>988</v>
@@ -11037,10 +11289,10 @@
         <v>978</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>791</v>
+        <v>898</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>988</v>
@@ -11051,10 +11303,10 @@
         <v>978</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>988</v>
@@ -11065,10 +11317,10 @@
         <v>978</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="D410" s="3" t="s">
         <v>988</v>
@@ -11079,10 +11331,10 @@
         <v>978</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>838</v>
+        <v>792</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>988</v>
@@ -11093,10 +11345,10 @@
         <v>978</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="D412" s="3" t="s">
         <v>988</v>
@@ -11107,10 +11359,10 @@
         <v>978</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>988</v>
@@ -11121,10 +11373,10 @@
         <v>978</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11135,10 +11387,10 @@
         <v>978</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1583</v>
+        <v>793</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>988</v>
@@ -11149,10 +11401,10 @@
         <v>978</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>811</v>
+        <v>1583</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>988</v>
@@ -11163,10 +11415,10 @@
         <v>978</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11177,10 +11429,10 @@
         <v>978</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1578</v>
+        <v>802</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11191,10 +11443,10 @@
         <v>978</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11205,10 +11457,10 @@
         <v>978</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D420" s="3" t="s">
         <v>988</v>
@@ -11219,10 +11471,10 @@
         <v>978</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>804</v>
+        <v>1580</v>
       </c>
       <c r="D421" s="3" t="s">
         <v>988</v>
@@ -11233,10 +11485,10 @@
         <v>978</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>988</v>
@@ -11247,10 +11499,10 @@
         <v>978</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>988</v>
@@ -11261,10 +11513,10 @@
         <v>978</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>988</v>
@@ -11275,10 +11527,10 @@
         <v>978</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>988</v>
@@ -11288,11 +11540,11 @@
       <c r="A426" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B426" s="4" t="s">
-        <v>783</v>
+      <c r="B426" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>896</v>
+        <v>801</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>988</v>
@@ -11302,11 +11554,11 @@
       <c r="A427" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B427" s="2" t="s">
-        <v>784</v>
+      <c r="B427" s="4" t="s">
+        <v>783</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>796</v>
+        <v>896</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>988</v>
@@ -11317,10 +11569,10 @@
         <v>978</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11331,10 +11583,10 @@
         <v>978</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1581</v>
+        <v>798</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>988</v>
@@ -11345,10 +11597,10 @@
         <v>978</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1582</v>
+        <v>786</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>813</v>
+        <v>1581</v>
       </c>
       <c r="D430" s="3" t="s">
         <v>988</v>
@@ -11356,16 +11608,16 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B431" s="5" t="s">
-        <v>826</v>
+        <v>978</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>1582</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -11373,10 +11625,10 @@
         <v>979</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>980</v>
@@ -11387,10 +11639,10 @@
         <v>979</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>980</v>
@@ -11401,10 +11653,10 @@
         <v>979</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>980</v>
@@ -11415,10 +11667,10 @@
         <v>979</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D435" s="3" t="s">
         <v>980</v>
@@ -11429,10 +11681,10 @@
         <v>979</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D436" s="3" t="s">
         <v>980</v>
@@ -11443,10 +11695,10 @@
         <v>979</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D437" s="3" t="s">
         <v>980</v>
@@ -11457,10 +11709,10 @@
         <v>979</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>980</v>
@@ -11471,10 +11723,10 @@
         <v>979</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>980</v>
@@ -11485,10 +11737,10 @@
         <v>979</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D440" s="3" t="s">
         <v>980</v>
@@ -11499,10 +11751,10 @@
         <v>979</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D441" s="3" t="s">
         <v>980</v>
@@ -11513,10 +11765,10 @@
         <v>979</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D442" s="3" t="s">
         <v>980</v>
@@ -11524,16 +11776,16 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B443" s="2" t="s">
-        <v>843</v>
+        <v>979</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>837</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>884</v>
+        <v>825</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -11541,10 +11793,10 @@
         <v>839</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>981</v>
@@ -11555,10 +11807,10 @@
         <v>839</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>981</v>
@@ -11569,10 +11821,10 @@
         <v>839</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D446" s="3" t="s">
         <v>981</v>
@@ -11583,10 +11835,10 @@
         <v>839</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D447" s="3" t="s">
         <v>981</v>
@@ -11597,10 +11849,10 @@
         <v>839</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D448" s="3" t="s">
         <v>981</v>
@@ -11611,10 +11863,10 @@
         <v>839</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>871</v>
+        <v>844</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="D449" s="3" t="s">
         <v>981</v>
@@ -11622,36 +11874,33 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="B450" s="2">
-        <v>3</v>
+        <v>839</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E450" s="3" t="s">
-        <v>850</v>
+        <v>981</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B451" s="2" t="s">
-        <v>1584</v>
+      <c r="B451" s="2">
+        <v>3</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D451" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -11659,16 +11908,16 @@
         <v>880</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>856</v>
+        <v>1584</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -11676,16 +11925,16 @@
         <v>880</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D453" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -11693,16 +11942,16 @@
         <v>880</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>879</v>
+        <v>857</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -11710,16 +11959,16 @@
         <v>880</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>50</v>
+        <v>860</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -11727,16 +11976,16 @@
         <v>880</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
@@ -11744,78 +11993,81 @@
         <v>880</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B458" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C458" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B459" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="C459" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D459" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B460" s="4" t="s">
-        <v>883</v>
+      <c r="B460" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B461" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="C461" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -11823,13 +12075,13 @@
         <v>880</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D462" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -11837,27 +12089,27 @@
         <v>880</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D463" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B464" s="2" t="s">
-        <v>1005</v>
+        <v>880</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>993</v>
+        <v>894</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
+      </c>
+      <c r="E464" s="3" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -11865,10 +12117,10 @@
         <v>992</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D465" s="3" t="s">
         <v>1017</v>
@@ -11879,10 +12131,10 @@
         <v>992</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>1017</v>
@@ -11893,10 +12145,10 @@
         <v>992</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D467" s="3" t="s">
         <v>1017</v>
@@ -11907,10 +12159,10 @@
         <v>992</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D468" s="3" t="s">
         <v>1017</v>
@@ -11921,10 +12173,10 @@
         <v>992</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D469" s="3" t="s">
         <v>1017</v>
@@ -11935,10 +12187,10 @@
         <v>992</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D470" s="3" t="s">
         <v>1017</v>
@@ -11949,10 +12201,10 @@
         <v>992</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D471" s="3" t="s">
         <v>1017</v>
@@ -11963,10 +12215,10 @@
         <v>992</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D472" s="3" t="s">
         <v>1017</v>
@@ -11977,10 +12229,10 @@
         <v>992</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>1017</v>
@@ -11991,10 +12243,10 @@
         <v>992</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>1017</v>
@@ -12005,41 +12257,41 @@
         <v>992</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D475" s="3" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A476" s="3" t="s">
+      <c r="A476" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C476" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D476" s="3" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="B476" s="2" t="s">
+      <c r="B477" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C476" s="2" t="s">
+      <c r="C477" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="D476" s="3" t="s">
+      <c r="D477" s="3" t="s">
         <v>1019</v>
-      </c>
-    </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A477" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B477" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C477" s="6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D477" s="3" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -12047,10 +12299,10 @@
         <v>1034</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>1033</v>
@@ -12061,10 +12313,10 @@
         <v>1034</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>1033</v>
@@ -12075,10 +12327,10 @@
         <v>1034</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>1033</v>
@@ -12089,10 +12341,10 @@
         <v>1034</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D481" s="3" t="s">
         <v>1033</v>
@@ -12103,10 +12355,10 @@
         <v>1034</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>1033</v>
@@ -12117,10 +12369,10 @@
         <v>1034</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>1033</v>
@@ -12131,10 +12383,10 @@
         <v>1034</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D484" s="3" t="s">
         <v>1033</v>
@@ -12145,10 +12397,10 @@
         <v>1034</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1033</v>
@@ -12159,10 +12411,10 @@
         <v>1034</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1033</v>
@@ -12173,10 +12425,10 @@
         <v>1034</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D487" s="3" t="s">
         <v>1033</v>
@@ -12184,16 +12436,16 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -12201,10 +12453,10 @@
         <v>1035</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1036</v>
@@ -12215,10 +12467,10 @@
         <v>1035</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1036</v>
@@ -12229,10 +12481,10 @@
         <v>1035</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D491" s="3" t="s">
         <v>1036</v>
@@ -12243,10 +12495,10 @@
         <v>1035</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D492" s="3" t="s">
         <v>1036</v>
@@ -12257,10 +12509,10 @@
         <v>1035</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>1036</v>
@@ -12271,10 +12523,10 @@
         <v>1035</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1036</v>
@@ -12285,10 +12537,10 @@
         <v>1035</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>1036</v>
@@ -12299,10 +12551,10 @@
         <v>1035</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>1036</v>
@@ -12310,16 +12562,16 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -12327,10 +12579,10 @@
         <v>1591</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1046</v>
@@ -12341,10 +12593,10 @@
         <v>1591</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D499" s="3" t="s">
         <v>1046</v>
@@ -12352,16 +12604,16 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
@@ -12369,10 +12621,10 @@
         <v>1055</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>1050</v>
@@ -12383,10 +12635,10 @@
         <v>1055</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>1050</v>
@@ -12397,10 +12649,10 @@
         <v>1055</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D503" s="3" t="s">
         <v>1050</v>
@@ -12408,16 +12660,16 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -12425,10 +12677,10 @@
         <v>1056</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D505" s="3" t="s">
         <v>1057</v>
@@ -12442,7 +12694,7 @@
         <v>1059</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D506" s="3" t="s">
         <v>1057</v>
@@ -12450,16 +12702,16 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
@@ -12467,10 +12719,10 @@
         <v>1060</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>1061</v>
@@ -12481,10 +12733,10 @@
         <v>1060</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>1061</v>
@@ -12495,10 +12747,10 @@
         <v>1060</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D510" s="3" t="s">
         <v>1061</v>
@@ -12509,10 +12761,10 @@
         <v>1060</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>1061</v>
@@ -12523,10 +12775,10 @@
         <v>1060</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>1061</v>
@@ -12537,10 +12789,10 @@
         <v>1060</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D513" s="3" t="s">
         <v>1061</v>
@@ -12551,10 +12803,10 @@
         <v>1060</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D514" s="3" t="s">
         <v>1061</v>
@@ -12565,10 +12817,10 @@
         <v>1060</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>1061</v>
@@ -12579,10 +12831,10 @@
         <v>1060</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>1061</v>
@@ -12593,10 +12845,10 @@
         <v>1060</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D517" s="3" t="s">
         <v>1061</v>
@@ -12604,16 +12856,16 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
@@ -12621,10 +12873,10 @@
         <v>1073</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>1590</v>
+        <v>1074</v>
+      </c>
+      <c r="C519" s="6" t="s">
+        <v>1136</v>
       </c>
       <c r="D519" s="3" t="s">
         <v>1075</v>
@@ -12635,10 +12887,10 @@
         <v>1073</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1634</v>
+        <v>1589</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>1635</v>
+        <v>1590</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>1075</v>
@@ -12646,16 +12898,16 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C521" s="6" t="s">
-        <v>1137</v>
+        <v>1634</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>1635</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
@@ -12663,10 +12915,10 @@
         <v>1076</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>1081</v>
@@ -12677,10 +12929,10 @@
         <v>1076</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>1081</v>
@@ -12691,10 +12943,10 @@
         <v>1076</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>1081</v>
@@ -12702,16 +12954,16 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
@@ -12719,10 +12971,10 @@
         <v>1082</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>1083</v>
@@ -12733,10 +12985,10 @@
         <v>1082</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>1083</v>
@@ -12747,10 +12999,10 @@
         <v>1082</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D528" s="3" t="s">
         <v>1083</v>
@@ -12761,10 +13013,10 @@
         <v>1082</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>1083</v>
@@ -12772,16 +13024,16 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
@@ -12789,10 +13041,10 @@
         <v>1540</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D531" s="3" t="s">
         <v>1094</v>
@@ -12803,10 +13055,10 @@
         <v>1540</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>1094</v>
@@ -12817,10 +13069,10 @@
         <v>1540</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D533" s="3" t="s">
         <v>1094</v>
@@ -12831,10 +13083,10 @@
         <v>1540</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D534" s="3" t="s">
         <v>1094</v>
@@ -12842,16 +13094,16 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C535" s="2" t="s">
-        <v>1168</v>
+        <v>1093</v>
+      </c>
+      <c r="C535" s="6" t="s">
+        <v>1150</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
@@ -12859,10 +13111,10 @@
         <v>1151</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D536" s="3" t="s">
         <v>1459</v>
@@ -12870,16 +13122,16 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
@@ -12887,10 +13139,10 @@
         <v>1152</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D538" s="3" t="s">
         <v>1460</v>
@@ -12898,16 +13150,16 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
@@ -12915,10 +13167,10 @@
         <v>1153</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>1461</v>
@@ -12926,16 +13178,16 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
@@ -12943,10 +13195,10 @@
         <v>1154</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D542" s="3" t="s">
         <v>1462</v>
@@ -12954,16 +13206,16 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
@@ -12971,10 +13223,10 @@
         <v>1155</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D544" s="3" t="s">
         <v>1463</v>
@@ -12982,16 +13234,16 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
@@ -12999,10 +13251,10 @@
         <v>1156</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D546" s="3" t="s">
         <v>1464</v>
@@ -13013,10 +13265,10 @@
         <v>1156</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D547" s="3" t="s">
         <v>1464</v>
@@ -13027,10 +13279,10 @@
         <v>1156</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D548" s="3" t="s">
         <v>1464</v>
@@ -13038,16 +13290,16 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
@@ -13055,10 +13307,10 @@
         <v>1157</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D550" s="3" t="s">
         <v>1465</v>
@@ -13066,16 +13318,16 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B551" s="7" t="s">
-        <v>1234</v>
+        <v>1157</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>1195</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
@@ -13083,10 +13335,10 @@
         <v>1158</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D552" s="3" t="s">
         <v>1466</v>
@@ -13097,10 +13349,10 @@
         <v>1158</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D553" s="3" t="s">
         <v>1466</v>
@@ -13111,10 +13363,10 @@
         <v>1158</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D554" s="3" t="s">
         <v>1466</v>
@@ -13125,10 +13377,10 @@
         <v>1158</v>
       </c>
       <c r="B555" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>1466</v>
@@ -13139,10 +13391,10 @@
         <v>1158</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D556" s="3" t="s">
         <v>1466</v>
@@ -13153,10 +13405,10 @@
         <v>1158</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D557" s="3" t="s">
         <v>1466</v>
@@ -13167,10 +13419,10 @@
         <v>1158</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D558" s="3" t="s">
         <v>1466</v>
@@ -13181,10 +13433,10 @@
         <v>1158</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D559" s="3" t="s">
         <v>1466</v>
@@ -13195,10 +13447,10 @@
         <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D560" s="3" t="s">
         <v>1466</v>
@@ -13209,10 +13461,10 @@
         <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D561" s="3" t="s">
         <v>1466</v>
@@ -13223,10 +13475,10 @@
         <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D562" s="3" t="s">
         <v>1466</v>
@@ -13237,10 +13489,10 @@
         <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1466</v>
@@ -13251,10 +13503,10 @@
         <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>1466</v>
@@ -13265,10 +13517,10 @@
         <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>1466</v>
@@ -13279,10 +13531,10 @@
         <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1466</v>
@@ -13293,10 +13545,10 @@
         <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1466</v>
@@ -13307,10 +13559,10 @@
         <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>1466</v>
@@ -13321,10 +13573,10 @@
         <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>1466</v>
@@ -13335,10 +13587,10 @@
         <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>1466</v>
@@ -13349,10 +13601,10 @@
         <v>1158</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1466</v>
@@ -13363,10 +13615,10 @@
         <v>1158</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1466</v>
@@ -13376,11 +13628,11 @@
       <c r="A573" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B573" s="4" t="s">
-        <v>1256</v>
+      <c r="B573" s="7" t="s">
+        <v>1255</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>1466</v>
@@ -13390,11 +13642,11 @@
       <c r="A574" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B574" s="7" t="s">
-        <v>1257</v>
+      <c r="B574" s="4" t="s">
+        <v>1256</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1466</v>
@@ -13405,10 +13657,10 @@
         <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>1466</v>
@@ -13419,10 +13671,10 @@
         <v>1158</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>1466</v>
@@ -13433,10 +13685,10 @@
         <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>1466</v>
@@ -13447,10 +13699,10 @@
         <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>1466</v>
@@ -13461,10 +13713,10 @@
         <v>1158</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>1466</v>
@@ -13475,10 +13727,10 @@
         <v>1158</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1232</v>
+        <v>1262</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>1466</v>
@@ -13489,10 +13741,10 @@
         <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1263</v>
+        <v>1232</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>1466</v>
@@ -13503,10 +13755,10 @@
         <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>1466</v>
@@ -13517,10 +13769,10 @@
         <v>1158</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>1466</v>
@@ -13531,10 +13783,10 @@
         <v>1158</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>1466</v>
@@ -13542,16 +13794,16 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1282</v>
+        <v>1231</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
@@ -13559,10 +13811,10 @@
         <v>1159</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>1467</v>
@@ -13573,10 +13825,10 @@
         <v>1159</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>1467</v>
@@ -13587,10 +13839,10 @@
         <v>1159</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1467</v>
@@ -13601,10 +13853,10 @@
         <v>1159</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1467</v>
@@ -13615,10 +13867,10 @@
         <v>1159</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>1467</v>
@@ -13629,10 +13881,10 @@
         <v>1159</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>1467</v>
@@ -13643,10 +13895,10 @@
         <v>1159</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1467</v>
@@ -13657,10 +13909,10 @@
         <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>1467</v>
@@ -13671,10 +13923,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -13685,10 +13937,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -13699,10 +13951,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -13713,10 +13965,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -13727,10 +13979,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -13741,10 +13993,10 @@
         <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>1467</v>
@@ -13755,10 +14007,10 @@
         <v>1159</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D600" s="3" t="s">
         <v>1467</v>
@@ -13766,16 +14018,16 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="D601" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
@@ -13783,10 +14035,10 @@
         <v>1160</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1468</v>
@@ -13797,10 +14049,10 @@
         <v>1160</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1468</v>
@@ -13811,10 +14063,10 @@
         <v>1160</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1468</v>
@@ -13822,30 +14074,30 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B605" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B605" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1558</v>
+        <v>1305</v>
       </c>
       <c r="D605" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="D606" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
@@ -13853,10 +14105,10 @@
         <v>1162</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D607" s="3" t="s">
         <v>1470</v>
@@ -13864,16 +14116,16 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B608" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C608" s="8" t="s">
-        <v>1560</v>
+        <v>1162</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
@@ -13881,10 +14133,10 @@
         <v>1587</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C609" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1471</v>
@@ -13895,10 +14147,10 @@
         <v>1587</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C610" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1471</v>
@@ -13909,10 +14161,10 @@
         <v>1587</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1471</v>
@@ -13923,10 +14175,10 @@
         <v>1587</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1471</v>
@@ -13937,10 +14189,10 @@
         <v>1587</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1471</v>
@@ -13951,10 +14203,10 @@
         <v>1587</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1471</v>
@@ -13965,10 +14217,10 @@
         <v>1587</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1471</v>
@@ -13979,10 +14231,10 @@
         <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1566</v>
+        <v>1553</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -13993,10 +14245,10 @@
         <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -14007,10 +14259,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -14021,10 +14273,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -14035,10 +14287,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -14049,10 +14301,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C621" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -14063,10 +14315,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C622" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -14077,10 +14329,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C623" s="9" t="s">
-        <v>1362</v>
+        <v>1323</v>
+      </c>
+      <c r="C623" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -14091,10 +14343,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C624" s="10" t="s">
-        <v>1363</v>
+        <v>1077</v>
+      </c>
+      <c r="C624" s="9" t="s">
+        <v>1362</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -14105,10 +14357,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C625" s="9" t="s">
-        <v>1364</v>
+        <v>1324</v>
+      </c>
+      <c r="C625" s="10" t="s">
+        <v>1363</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14119,10 +14371,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C626" s="10" t="s">
-        <v>1365</v>
+        <v>1325</v>
+      </c>
+      <c r="C626" s="9" t="s">
+        <v>1364</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14133,10 +14385,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C627" s="9" t="s">
-        <v>1366</v>
+        <v>1326</v>
+      </c>
+      <c r="C627" s="10" t="s">
+        <v>1365</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14147,10 +14399,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C628" s="10" t="s">
-        <v>1367</v>
+        <v>1327</v>
+      </c>
+      <c r="C628" s="9" t="s">
+        <v>1366</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14161,10 +14413,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C629" s="9" t="s">
-        <v>1368</v>
+        <v>1328</v>
+      </c>
+      <c r="C629" s="10" t="s">
+        <v>1367</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14175,10 +14427,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C630" s="10" t="s">
-        <v>1369</v>
+        <v>1329</v>
+      </c>
+      <c r="C630" s="9" t="s">
+        <v>1368</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14189,10 +14441,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C631" s="9" t="s">
-        <v>1370</v>
+        <v>1330</v>
+      </c>
+      <c r="C631" s="10" t="s">
+        <v>1369</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14203,10 +14455,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C632" s="10" t="s">
-        <v>1371</v>
+        <v>1331</v>
+      </c>
+      <c r="C632" s="9" t="s">
+        <v>1370</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14217,10 +14469,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C633" s="9" t="s">
-        <v>1372</v>
+        <v>1332</v>
+      </c>
+      <c r="C633" s="10" t="s">
+        <v>1371</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14231,10 +14483,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C634" s="10" t="s">
-        <v>1373</v>
+        <v>1333</v>
+      </c>
+      <c r="C634" s="9" t="s">
+        <v>1372</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14245,10 +14497,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C635" s="9" t="s">
-        <v>1374</v>
+        <v>1334</v>
+      </c>
+      <c r="C635" s="10" t="s">
+        <v>1373</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14259,10 +14511,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C636" s="10" t="s">
-        <v>1375</v>
+        <v>1335</v>
+      </c>
+      <c r="C636" s="9" t="s">
+        <v>1374</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14273,10 +14525,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C637" s="9" t="s">
-        <v>1376</v>
+        <v>1336</v>
+      </c>
+      <c r="C637" s="10" t="s">
+        <v>1375</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14287,10 +14539,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C638" s="10" t="s">
-        <v>1377</v>
+        <v>1337</v>
+      </c>
+      <c r="C638" s="9" t="s">
+        <v>1376</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14301,10 +14553,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C639" s="9" t="s">
-        <v>1378</v>
+        <v>1338</v>
+      </c>
+      <c r="C639" s="10" t="s">
+        <v>1377</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14315,10 +14567,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C640" s="10" t="s">
-        <v>1379</v>
+        <v>1339</v>
+      </c>
+      <c r="C640" s="9" t="s">
+        <v>1378</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14329,10 +14581,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C641" s="9" t="s">
-        <v>1380</v>
+        <v>1340</v>
+      </c>
+      <c r="C641" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14343,10 +14595,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C642" s="10" t="s">
-        <v>1381</v>
+        <v>1341</v>
+      </c>
+      <c r="C642" s="9" t="s">
+        <v>1380</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14357,10 +14609,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C643" s="9" t="s">
-        <v>1382</v>
+        <v>1342</v>
+      </c>
+      <c r="C643" s="10" t="s">
+        <v>1381</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14371,10 +14623,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C644" s="10" t="s">
-        <v>1383</v>
+        <v>1343</v>
+      </c>
+      <c r="C644" s="9" t="s">
+        <v>1382</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14385,10 +14637,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C645" s="9" t="s">
-        <v>1384</v>
+        <v>1344</v>
+      </c>
+      <c r="C645" s="10" t="s">
+        <v>1383</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14399,10 +14651,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C646" s="10" t="s">
-        <v>1385</v>
+        <v>1345</v>
+      </c>
+      <c r="C646" s="9" t="s">
+        <v>1384</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14413,10 +14665,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C647" s="9" t="s">
-        <v>1386</v>
+        <v>1346</v>
+      </c>
+      <c r="C647" s="10" t="s">
+        <v>1385</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14427,10 +14679,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C648" s="10" t="s">
-        <v>1387</v>
+        <v>1347</v>
+      </c>
+      <c r="C648" s="9" t="s">
+        <v>1386</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14441,10 +14693,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C649" s="9" t="s">
-        <v>1388</v>
+        <v>1348</v>
+      </c>
+      <c r="C649" s="10" t="s">
+        <v>1387</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14455,10 +14707,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C650" s="10" t="s">
-        <v>1389</v>
+        <v>1349</v>
+      </c>
+      <c r="C650" s="9" t="s">
+        <v>1388</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14469,10 +14721,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C651" s="9" t="s">
-        <v>1390</v>
+        <v>1350</v>
+      </c>
+      <c r="C651" s="10" t="s">
+        <v>1389</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14483,10 +14735,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C652" s="10" t="s">
-        <v>1391</v>
+        <v>1351</v>
+      </c>
+      <c r="C652" s="9" t="s">
+        <v>1390</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -14497,10 +14749,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C653" s="9" t="s">
-        <v>1392</v>
+        <v>1352</v>
+      </c>
+      <c r="C653" s="10" t="s">
+        <v>1391</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -14511,10 +14763,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C654" s="10" t="s">
-        <v>1393</v>
+        <v>1353</v>
+      </c>
+      <c r="C654" s="9" t="s">
+        <v>1392</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -14525,10 +14777,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C655" s="9" t="s">
-        <v>1394</v>
+        <v>1354</v>
+      </c>
+      <c r="C655" s="10" t="s">
+        <v>1393</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -14539,10 +14791,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C656" s="10" t="s">
-        <v>1395</v>
+        <v>1355</v>
+      </c>
+      <c r="C656" s="9" t="s">
+        <v>1394</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -14553,10 +14805,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C657" s="9" t="s">
-        <v>1396</v>
+        <v>1356</v>
+      </c>
+      <c r="C657" s="10" t="s">
+        <v>1395</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -14567,10 +14819,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C658" s="10" t="s">
-        <v>1397</v>
+        <v>1357</v>
+      </c>
+      <c r="C658" s="9" t="s">
+        <v>1396</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -14581,10 +14833,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C659" s="9" t="s">
-        <v>1398</v>
+        <v>1358</v>
+      </c>
+      <c r="C659" s="10" t="s">
+        <v>1397</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -14595,10 +14847,10 @@
         <v>1587</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C660" s="10" t="s">
-        <v>1399</v>
+        <v>1359</v>
+      </c>
+      <c r="C660" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -14609,10 +14861,10 @@
         <v>1587</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C661" s="2" t="s">
-        <v>1573</v>
+        <v>1360</v>
+      </c>
+      <c r="C661" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -14620,13 +14872,13 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B662" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C662" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -14637,10 +14889,10 @@
         <v>1472</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C663" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -14651,10 +14903,10 @@
         <v>1472</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C664" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -14665,10 +14917,10 @@
         <v>1472</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -14679,10 +14931,10 @@
         <v>1472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -14693,10 +14945,10 @@
         <v>1472</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -14707,10 +14959,10 @@
         <v>1472</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -14721,10 +14973,10 @@
         <v>1472</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C669" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -14732,13 +14984,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C670" s="8" t="s">
-        <v>1574</v>
+        <v>1552</v>
       </c>
       <c r="D670" s="3" t="s">
         <v>1471</v>
@@ -14746,13 +14998,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C671" s="9" t="s">
-        <v>1410</v>
+        <v>1408</v>
+      </c>
+      <c r="C671" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1471</v>
@@ -14760,13 +15012,13 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C672" s="10" t="s">
-        <v>1452</v>
+        <v>1409</v>
+      </c>
+      <c r="C672" s="9" t="s">
+        <v>1410</v>
       </c>
       <c r="D672" s="3" t="s">
         <v>1471</v>
@@ -14777,10 +15029,10 @@
         <v>1592</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C673" s="9" t="s">
-        <v>1453</v>
+        <v>1450</v>
+      </c>
+      <c r="C673" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1471</v>
@@ -14788,13 +15040,13 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1633</v>
+        <v>1592</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C674" s="10" t="s">
-        <v>1632</v>
+        <v>1451</v>
+      </c>
+      <c r="C674" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1471</v>
@@ -14802,13 +15054,13 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1475</v>
+        <v>1633</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C675" s="2" t="s">
-        <v>1454</v>
+        <v>1631</v>
+      </c>
+      <c r="C675" s="10" t="s">
+        <v>1632</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>1471</v>
@@ -14816,16 +15068,16 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1163</v>
+        <v>1475</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D676" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
@@ -14833,10 +15085,10 @@
         <v>1163</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C677" s="9" t="s">
-        <v>1575</v>
+        <v>1411</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>1473</v>
@@ -14844,16 +15096,16 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C678" s="10" t="s">
-        <v>1429</v>
+        <v>1479</v>
+      </c>
+      <c r="C678" s="9" t="s">
+        <v>1575</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
@@ -14861,10 +15113,10 @@
         <v>1164</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C679" s="9" t="s">
-        <v>1430</v>
+        <v>1414</v>
+      </c>
+      <c r="C679" s="10" t="s">
+        <v>1429</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1474</v>
@@ -14875,10 +15127,10 @@
         <v>1164</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C680" s="10" t="s">
-        <v>1431</v>
+        <v>1416</v>
+      </c>
+      <c r="C680" s="9" t="s">
+        <v>1430</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1474</v>
@@ -14889,10 +15141,10 @@
         <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C681" s="9" t="s">
-        <v>1432</v>
+        <v>1417</v>
+      </c>
+      <c r="C681" s="10" t="s">
+        <v>1431</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1474</v>
@@ -14903,10 +15155,10 @@
         <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C682" s="10" t="s">
-        <v>1433</v>
+        <v>1418</v>
+      </c>
+      <c r="C682" s="9" t="s">
+        <v>1432</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1474</v>
@@ -14917,10 +15169,10 @@
         <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C683" s="9" t="s">
-        <v>1434</v>
+        <v>1419</v>
+      </c>
+      <c r="C683" s="10" t="s">
+        <v>1433</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1474</v>
@@ -14931,10 +15183,10 @@
         <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C684" s="10" t="s">
-        <v>1435</v>
+        <v>1420</v>
+      </c>
+      <c r="C684" s="9" t="s">
+        <v>1434</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1474</v>
@@ -14945,10 +15197,10 @@
         <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C685" s="9" t="s">
-        <v>1436</v>
+        <v>1421</v>
+      </c>
+      <c r="C685" s="10" t="s">
+        <v>1435</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1474</v>
@@ -14959,10 +15211,10 @@
         <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C686" s="10" t="s">
-        <v>1437</v>
+        <v>1422</v>
+      </c>
+      <c r="C686" s="9" t="s">
+        <v>1436</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1474</v>
@@ -14973,10 +15225,10 @@
         <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C687" s="9" t="s">
-        <v>1438</v>
+        <v>1423</v>
+      </c>
+      <c r="C687" s="10" t="s">
+        <v>1437</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1474</v>
@@ -14987,10 +15239,10 @@
         <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C688" s="10" t="s">
-        <v>1439</v>
+        <v>1424</v>
+      </c>
+      <c r="C688" s="9" t="s">
+        <v>1438</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1474</v>
@@ -15001,10 +15253,10 @@
         <v>1164</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C689" s="9" t="s">
-        <v>1440</v>
+        <v>1425</v>
+      </c>
+      <c r="C689" s="10" t="s">
+        <v>1439</v>
       </c>
       <c r="D689" s="3" t="s">
         <v>1474</v>
@@ -15015,10 +15267,10 @@
         <v>1164</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C690" s="10" t="s">
-        <v>1441</v>
+        <v>1426</v>
+      </c>
+      <c r="C690" s="9" t="s">
+        <v>1440</v>
       </c>
       <c r="D690" s="3" t="s">
         <v>1474</v>
@@ -15029,10 +15281,10 @@
         <v>1164</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C691" s="9" t="s">
-        <v>1442</v>
+        <v>1427</v>
+      </c>
+      <c r="C691" s="10" t="s">
+        <v>1441</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1474</v>
@@ -15043,10 +15295,10 @@
         <v>1164</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C692" s="10" t="s">
-        <v>1443</v>
+        <v>1428</v>
+      </c>
+      <c r="C692" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D692" s="3" t="s">
         <v>1474</v>
@@ -15057,10 +15309,10 @@
         <v>1164</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C693" s="9" t="s">
-        <v>1444</v>
+        <v>1423</v>
+      </c>
+      <c r="C693" s="10" t="s">
+        <v>1443</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>1474</v>
@@ -15071,10 +15323,10 @@
         <v>1164</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C694" s="10" t="s">
-        <v>1445</v>
+        <v>1413</v>
+      </c>
+      <c r="C694" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D694" s="3" t="s">
         <v>1474</v>
@@ -15082,16 +15334,16 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C695" s="2" t="s">
-        <v>1455</v>
+        <v>1415</v>
+      </c>
+      <c r="C695" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D695" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
@@ -15099,10 +15351,10 @@
         <v>1165</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D696" s="3" t="s">
         <v>1476</v>
@@ -15113,10 +15365,10 @@
         <v>1165</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>1476</v>
@@ -15127,10 +15379,10 @@
         <v>1165</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1629</v>
+        <v>1448</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1630</v>
+        <v>1457</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1476</v>
@@ -15141,10 +15393,10 @@
         <v>1165</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1449</v>
+        <v>1629</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1458</v>
+        <v>1630</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1476</v>
@@ -15152,16 +15404,16 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1510</v>
+        <v>1449</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1480</v>
+        <v>1458</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
@@ -15169,10 +15421,10 @@
         <v>1477</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1539</v>
@@ -15183,10 +15435,10 @@
         <v>1477</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1539</v>
@@ -15197,10 +15449,10 @@
         <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1539</v>
@@ -15211,10 +15463,10 @@
         <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1539</v>
@@ -15225,10 +15477,10 @@
         <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1539</v>
@@ -15239,10 +15491,10 @@
         <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1539</v>
@@ -15253,10 +15505,10 @@
         <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1539</v>
@@ -15267,10 +15519,10 @@
         <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1539</v>
@@ -15281,10 +15533,10 @@
         <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1539</v>
@@ -15295,10 +15547,10 @@
         <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>1539</v>
@@ -15309,10 +15561,10 @@
         <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D711" s="3" t="s">
         <v>1539</v>
@@ -15323,10 +15575,10 @@
         <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1539</v>
@@ -15337,10 +15589,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15351,10 +15603,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15365,10 +15617,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15379,10 +15631,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15393,10 +15645,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15407,10 +15659,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15421,10 +15673,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15435,10 +15687,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15449,10 +15701,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15463,10 +15715,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15477,10 +15729,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15491,10 +15743,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -15505,10 +15757,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -15519,10 +15771,10 @@
         <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -15533,10 +15785,10 @@
         <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>1539</v>
@@ -15547,10 +15799,10 @@
         <v>1477</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>1539</v>
@@ -15558,13 +15810,13 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1479</v>
+        <v>1538</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>1539</v>
@@ -15572,16 +15824,16 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1597</v>
+        <v>1479</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1604</v>
+        <v>1509</v>
       </c>
       <c r="D730" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
@@ -15589,10 +15841,10 @@
         <v>1595</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>1596</v>
@@ -15603,10 +15855,10 @@
         <v>1595</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D732" s="3" t="s">
         <v>1596</v>
@@ -15617,10 +15869,10 @@
         <v>1595</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1596</v>
@@ -15631,10 +15883,10 @@
         <v>1595</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D734" s="3" t="s">
         <v>1596</v>
@@ -15645,10 +15897,10 @@
         <v>1595</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D735" s="3" t="s">
         <v>1596</v>
@@ -15659,10 +15911,10 @@
         <v>1595</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D736" s="3" t="s">
         <v>1596</v>
@@ -15670,16 +15922,16 @@
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1612</v>
+        <v>1603</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="D737" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.25">
@@ -15687,10 +15939,10 @@
         <v>1611</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D738" s="3" t="s">
         <v>1628</v>
@@ -15701,10 +15953,10 @@
         <v>1611</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D739" s="3" t="s">
         <v>1628</v>
@@ -15715,10 +15967,10 @@
         <v>1611</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D740" s="3" t="s">
         <v>1628</v>
@@ -15729,10 +15981,10 @@
         <v>1611</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D741" s="3" t="s">
         <v>1628</v>
@@ -15743,10 +15995,10 @@
         <v>1611</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D742" s="3" t="s">
         <v>1628</v>
@@ -15757,10 +16009,10 @@
         <v>1611</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D743" s="3" t="s">
         <v>1628</v>
@@ -15771,13 +16023,573 @@
         <v>1611</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D744" s="3" t="s">
         <v>1628</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A745" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D745" s="3" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A746" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C746" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D746" s="3" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A747" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C747" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D747" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A748" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C748" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D748" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A749" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C749" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D749" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A750" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C750" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D750" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A751" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C751" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D751" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A752" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D752" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A753" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D753" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A754" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C754" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D754" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A755" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C755" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D755" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A756" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D756" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A757" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D757" s="3" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A758" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C758" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D758" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A759" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C759" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D759" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A760" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C760" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D760" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A761" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C761" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D761" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A762" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C762" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D762" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A763" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C763" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D763" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A764" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C764" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D764" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A765" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C765" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D765" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A766" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C766" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D766" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A767" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C767" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D767" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A768" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C768" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D768" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A769" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C769" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D769" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A770" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C770" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D770" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A771" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C771" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D771" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A772" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C772" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D772" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A773" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C773" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D773" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A774" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C774" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D774" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A775" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C775" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D775" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A776" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C776" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D776" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A777" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C777" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D777" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A778" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C778" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D778" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A779" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C779" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D779" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A780" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C780" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D780" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A781" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C781" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D781" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A782" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C782" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D782" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A783" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C783" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D783" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A784" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C784" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D784" s="3" t="s">
+        <v>1716</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6455075D-4B34-4B11-856B-4C037200CE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D6FCC0-D844-4C93-9112-60AAF09C00FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4963,18 +4963,12 @@
     <t>78970110027720340</t>
   </si>
   <si>
-    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 1 - ФИЛИАЛ ХАСКОВО</t>
-  </si>
-  <si>
     <t>СТ5415РС</t>
   </si>
   <si>
     <t>78970153027721603</t>
   </si>
   <si>
-    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 2 - ФТТ</t>
-  </si>
-  <si>
     <t>Y6426BA</t>
   </si>
   <si>
@@ -5180,6 +5174,12 @@
   </si>
   <si>
     <t>В5454ХМ</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 1 - ФИЛИАЛ ГР. ХАСКОВО</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 2 - ФАКУЛТЕТ ТЕХНИКА И ТЕХНОЛОГИИ</t>
   </si>
 </sst>
 </file>
@@ -10169,10 +10169,10 @@
         <v>969</v>
       </c>
       <c r="B328" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>970</v>
@@ -16071,7 +16071,7 @@
         <v>1642</v>
       </c>
       <c r="D747" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
@@ -16085,7 +16085,7 @@
         <v>1643</v>
       </c>
       <c r="D748" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
@@ -16099,7 +16099,7 @@
         <v>1644</v>
       </c>
       <c r="D749" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
@@ -16113,7 +16113,7 @@
         <v>1645</v>
       </c>
       <c r="D750" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
@@ -16127,469 +16127,469 @@
         <v>1646</v>
       </c>
       <c r="D751" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B752" s="2" t="s">
         <v>1647</v>
       </c>
-      <c r="B752" s="2" t="s">
+      <c r="C752" s="2" t="s">
         <v>1648</v>
       </c>
-      <c r="C752" s="2" t="s">
-        <v>1649</v>
-      </c>
       <c r="D752" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B753" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="B753" s="2" t="s">
-        <v>1652</v>
-      </c>
       <c r="C753" s="2" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="D753" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>1650</v>
+        <v>1719</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D754" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
-        <v>1650</v>
+        <v>1719</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="D755" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
-        <v>1650</v>
+        <v>1719</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="D756" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
-        <v>1650</v>
+        <v>1719</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="D757" s="3" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D758" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="D759" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D760" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="D761" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D762" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="D763" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D764" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="D765" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D766" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D767" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D768" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D769" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D770" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="D771" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="D772" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="D773" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="D774" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="D775" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D776" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="D777" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D778" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D779" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="D780" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D781" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D782" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="D783" s="3" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="C784" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D784" s="3" t="s">
         <v>1714</v>
-      </c>
-      <c r="D784" s="3" t="s">
-        <v>1716</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D6FCC0-D844-4C93-9112-60AAF09C00FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CCA0DF-82EE-4700-8192-D540B03EF44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CCA0DF-82EE-4700-8192-D540B03EF44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D249400A-ED79-439A-949F-6F94E1DE6245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="1770">
   <si>
     <t>Company</t>
   </si>
@@ -5180,6 +5180,156 @@
   </si>
   <si>
     <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 2 - ФАКУЛТЕТ ТЕХНИКА И ТЕХНОЛОГИИ</t>
+  </si>
+  <si>
+    <t>ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС</t>
+  </si>
+  <si>
+    <t>СТ3733ТК</t>
+  </si>
+  <si>
+    <t>СТ3633ТК</t>
+  </si>
+  <si>
+    <t>СТ9898РС</t>
+  </si>
+  <si>
+    <t>СТ7575СК</t>
+  </si>
+  <si>
+    <t>СТ5252НН</t>
+  </si>
+  <si>
+    <t>СТ9232ТМ</t>
+  </si>
+  <si>
+    <t>СТ5369АК</t>
+  </si>
+  <si>
+    <t>СТ2346РХ</t>
+  </si>
+  <si>
+    <t>ТУБА АТК</t>
+  </si>
+  <si>
+    <t>СТ9429РМ</t>
+  </si>
+  <si>
+    <t>СТ7447ВА</t>
+  </si>
+  <si>
+    <t>78970153027721934</t>
+  </si>
+  <si>
+    <t>78970153027721942</t>
+  </si>
+  <si>
+    <t>78970153027721959</t>
+  </si>
+  <si>
+    <t>78970153027721967</t>
+  </si>
+  <si>
+    <t>78970153027721975</t>
+  </si>
+  <si>
+    <t>78970153027721983</t>
+  </si>
+  <si>
+    <t>78970153027721991</t>
+  </si>
+  <si>
+    <t>78970153027722007</t>
+  </si>
+  <si>
+    <t>78970153027722015</t>
+  </si>
+  <si>
+    <t>78970153027722023</t>
+  </si>
+  <si>
+    <t>78970153027722031</t>
+  </si>
+  <si>
+    <t>ТЕМПО ТРАНС ЕООД</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА КАРТА 1</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА КАРТА 2</t>
+  </si>
+  <si>
+    <t>СЛУЖЕБНА КАРТА 3</t>
+  </si>
+  <si>
+    <t>148069808</t>
+  </si>
+  <si>
+    <t>СКАЙ РЕНТС ООД</t>
+  </si>
+  <si>
+    <t>207730267</t>
+  </si>
+  <si>
+    <t>78970153027721579</t>
+  </si>
+  <si>
+    <t>78970153027721587</t>
+  </si>
+  <si>
+    <t>78970153027721595</t>
+  </si>
+  <si>
+    <t>МИХНЕВИ ТРАНС ЕООД</t>
+  </si>
+  <si>
+    <t>78970153027721538</t>
+  </si>
+  <si>
+    <t>В3704ХЕ</t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>SR ТУБА</t>
+  </si>
+  <si>
+    <t>В4209ХЕ</t>
+  </si>
+  <si>
+    <t>В6613ВС</t>
+  </si>
+  <si>
+    <t>МТ 1</t>
+  </si>
+  <si>
+    <t>МТ 2</t>
+  </si>
+  <si>
+    <t>78970153027721546</t>
+  </si>
+  <si>
+    <t>78970153027721553</t>
+  </si>
+  <si>
+    <t>78970153027721561</t>
+  </si>
+  <si>
+    <t>203455425</t>
+  </si>
+  <si>
+    <t>В5346ХМ</t>
+  </si>
+  <si>
+    <t>В5350ХМ</t>
+  </si>
+  <si>
+    <t>78970155027722887</t>
+  </si>
+  <si>
+    <t>78970155027722895</t>
   </si>
 </sst>
 </file>
@@ -5578,10 +5728,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E784"/>
+  <dimension ref="A1:E807"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="3" bestFit="1" customWidth="1"/>
@@ -13797,10 +13947,10 @@
         <v>1158</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1233</v>
+        <v>1766</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1231</v>
+        <v>1768</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>1466</v>
@@ -13808,30 +13958,30 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1266</v>
+        <v>1767</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1282</v>
+        <v>1769</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1267</v>
+        <v>1233</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1283</v>
+        <v>1231</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
@@ -13839,10 +13989,10 @@
         <v>1159</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1467</v>
@@ -13853,10 +14003,10 @@
         <v>1159</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1467</v>
@@ -13867,10 +14017,10 @@
         <v>1159</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>1467</v>
@@ -13881,10 +14031,10 @@
         <v>1159</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>1467</v>
@@ -13895,10 +14045,10 @@
         <v>1159</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1467</v>
@@ -13909,10 +14059,10 @@
         <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>1467</v>
@@ -13923,10 +14073,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -13937,10 +14087,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -13951,10 +14101,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -13965,10 +14115,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -13979,10 +14129,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -13993,10 +14143,10 @@
         <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>1467</v>
@@ -14007,10 +14157,10 @@
         <v>1159</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D600" s="3" t="s">
         <v>1467</v>
@@ -14021,10 +14171,10 @@
         <v>1159</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D601" s="3" t="s">
         <v>1467</v>
@@ -14032,30 +14182,30 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1298</v>
+        <v>1280</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="D602" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1299</v>
+        <v>1281</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="D603" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
@@ -14063,10 +14213,10 @@
         <v>1160</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1468</v>
@@ -14077,10 +14227,10 @@
         <v>1160</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1468</v>
@@ -14088,72 +14238,72 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B606" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B606" s="7" t="s">
+        <v>1300</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1558</v>
+        <v>1304</v>
       </c>
       <c r="D606" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B607" s="2" t="s">
-        <v>1307</v>
+        <v>1160</v>
+      </c>
+      <c r="B607" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1576</v>
+        <v>1305</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1577</v>
+        <v>1558</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B609" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C609" s="8" t="s">
-        <v>1560</v>
+        <v>1162</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>1576</v>
       </c>
       <c r="D609" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B610" s="7" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C610" s="8" t="s">
-        <v>1561</v>
+        <v>1162</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D610" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
@@ -14161,10 +14311,10 @@
         <v>1587</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C611" s="8" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1471</v>
@@ -14175,10 +14325,10 @@
         <v>1587</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C612" s="8" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1471</v>
@@ -14189,10 +14339,10 @@
         <v>1587</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C613" s="8" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1471</v>
@@ -14203,10 +14353,10 @@
         <v>1587</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C614" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>1471</v>
@@ -14217,10 +14367,10 @@
         <v>1587</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C615" s="8" t="s">
-        <v>1565</v>
+        <v>1554</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1471</v>
@@ -14231,10 +14381,10 @@
         <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1553</v>
+        <v>1564</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -14245,10 +14395,10 @@
         <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -14259,10 +14409,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1567</v>
+        <v>1553</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -14273,10 +14423,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -14287,10 +14437,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -14301,10 +14451,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C621" s="8" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -14315,10 +14465,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C622" s="8" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -14329,10 +14479,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C623" s="8" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -14343,10 +14493,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C624" s="9" t="s">
-        <v>1362</v>
+        <v>1322</v>
+      </c>
+      <c r="C624" s="8" t="s">
+        <v>1571</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -14357,10 +14507,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C625" s="10" t="s">
-        <v>1363</v>
+        <v>1323</v>
+      </c>
+      <c r="C625" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14371,10 +14521,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1325</v>
+        <v>1077</v>
       </c>
       <c r="C626" s="9" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14385,10 +14535,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14399,10 +14549,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C628" s="9" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14413,10 +14563,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14427,10 +14577,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C630" s="9" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14441,10 +14591,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14455,10 +14605,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C632" s="9" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14469,10 +14619,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14483,10 +14633,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C634" s="9" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14497,10 +14647,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14511,10 +14661,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C636" s="9" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14525,10 +14675,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14539,10 +14689,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C638" s="9" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14553,10 +14703,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C639" s="10" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14567,10 +14717,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C640" s="9" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14581,10 +14731,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C641" s="10" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14595,10 +14745,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C642" s="9" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14609,10 +14759,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C643" s="10" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14623,10 +14773,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C644" s="9" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14637,10 +14787,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C645" s="10" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14651,10 +14801,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C646" s="9" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14665,10 +14815,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C647" s="10" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14679,10 +14829,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C648" s="9" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14693,10 +14843,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C649" s="10" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14707,10 +14857,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C650" s="9" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14721,10 +14871,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C651" s="10" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14735,10 +14885,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C652" s="9" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -14749,10 +14899,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C653" s="10" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -14763,10 +14913,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C654" s="9" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -14777,10 +14927,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C655" s="10" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -14791,10 +14941,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C656" s="9" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -14805,10 +14955,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C657" s="10" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -14819,10 +14969,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="C658" s="9" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -14833,10 +14983,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C659" s="10" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -14847,10 +14997,10 @@
         <v>1587</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C660" s="9" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -14861,10 +15011,10 @@
         <v>1587</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C661" s="10" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -14875,10 +15025,10 @@
         <v>1587</v>
       </c>
       <c r="B662" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C662" s="2" t="s">
-        <v>1573</v>
+        <v>1359</v>
+      </c>
+      <c r="C662" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -14886,13 +15036,13 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B663" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C663" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B663" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C663" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -14900,13 +15050,13 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C664" s="8" t="s">
-        <v>1546</v>
+        <v>1587</v>
+      </c>
+      <c r="B664" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C664" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -14917,10 +15067,10 @@
         <v>1472</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C665" s="8" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -14931,10 +15081,10 @@
         <v>1472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C666" s="8" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -14945,10 +15095,10 @@
         <v>1472</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C667" s="8" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -14959,10 +15109,10 @@
         <v>1472</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="C668" s="8" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -14973,10 +15123,10 @@
         <v>1472</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C669" s="8" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -14987,10 +15137,10 @@
         <v>1472</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="C670" s="8" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D670" s="3" t="s">
         <v>1471</v>
@@ -14998,13 +15148,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C671" s="8" t="s">
-        <v>1574</v>
+        <v>1551</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1471</v>
@@ -15012,13 +15162,13 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1586</v>
+        <v>1472</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C672" s="9" t="s">
-        <v>1410</v>
+        <v>1407</v>
+      </c>
+      <c r="C672" s="8" t="s">
+        <v>1552</v>
       </c>
       <c r="D672" s="3" t="s">
         <v>1471</v>
@@ -15026,13 +15176,13 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C673" s="10" t="s">
-        <v>1452</v>
+        <v>1408</v>
+      </c>
+      <c r="C673" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1471</v>
@@ -15040,13 +15190,13 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="C674" s="9" t="s">
-        <v>1453</v>
+        <v>1410</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1471</v>
@@ -15054,13 +15204,13 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1633</v>
+        <v>1592</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1631</v>
+        <v>1450</v>
       </c>
       <c r="C675" s="10" t="s">
-        <v>1632</v>
+        <v>1452</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>1471</v>
@@ -15068,13 +15218,13 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1475</v>
+        <v>1592</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C676" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
+      </c>
+      <c r="C676" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D676" s="3" t="s">
         <v>1471</v>
@@ -15082,58 +15232,58 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1163</v>
+        <v>1633</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C677" s="2" t="s">
-        <v>1412</v>
+        <v>1631</v>
+      </c>
+      <c r="C677" s="10" t="s">
+        <v>1632</v>
       </c>
       <c r="D677" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1163</v>
+        <v>1475</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C678" s="9" t="s">
-        <v>1575</v>
+        <v>1409</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>1454</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C679" s="10" t="s">
-        <v>1429</v>
+        <v>1411</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D679" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1416</v>
+        <v>1479</v>
       </c>
       <c r="C680" s="9" t="s">
-        <v>1430</v>
+        <v>1575</v>
       </c>
       <c r="D680" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
@@ -15141,10 +15291,10 @@
         <v>1164</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="C681" s="10" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1474</v>
@@ -15155,10 +15305,10 @@
         <v>1164</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C682" s="9" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1474</v>
@@ -15169,10 +15319,10 @@
         <v>1164</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="C683" s="10" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1474</v>
@@ -15183,10 +15333,10 @@
         <v>1164</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C684" s="9" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1474</v>
@@ -15197,10 +15347,10 @@
         <v>1164</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C685" s="10" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1474</v>
@@ -15211,10 +15361,10 @@
         <v>1164</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C686" s="9" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1474</v>
@@ -15225,10 +15375,10 @@
         <v>1164</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="C687" s="10" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1474</v>
@@ -15239,10 +15389,10 @@
         <v>1164</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C688" s="9" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1474</v>
@@ -15253,10 +15403,10 @@
         <v>1164</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C689" s="10" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="D689" s="3" t="s">
         <v>1474</v>
@@ -15267,10 +15417,10 @@
         <v>1164</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C690" s="9" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D690" s="3" t="s">
         <v>1474</v>
@@ -15281,10 +15431,10 @@
         <v>1164</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="C691" s="10" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1474</v>
@@ -15295,10 +15445,10 @@
         <v>1164</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="C692" s="9" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D692" s="3" t="s">
         <v>1474</v>
@@ -15309,10 +15459,10 @@
         <v>1164</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="C693" s="10" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>1474</v>
@@ -15323,10 +15473,10 @@
         <v>1164</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1413</v>
+        <v>1428</v>
       </c>
       <c r="C694" s="9" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D694" s="3" t="s">
         <v>1474</v>
@@ -15337,10 +15487,10 @@
         <v>1164</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="C695" s="10" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1474</v>
@@ -15348,30 +15498,30 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C696" s="2" t="s">
-        <v>1455</v>
+        <v>1413</v>
+      </c>
+      <c r="C696" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C697" s="2" t="s">
-        <v>1456</v>
+        <v>1415</v>
+      </c>
+      <c r="C697" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D697" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.25">
@@ -15379,10 +15529,10 @@
         <v>1165</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1476</v>
@@ -15393,10 +15543,10 @@
         <v>1165</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1629</v>
+        <v>1447</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1630</v>
+        <v>1456</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1476</v>
@@ -15407,10 +15557,10 @@
         <v>1165</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1476</v>
@@ -15418,30 +15568,30 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1510</v>
+        <v>1629</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1480</v>
+        <v>1630</v>
       </c>
       <c r="D701" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1511</v>
+        <v>1449</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1481</v>
+        <v>1458</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
@@ -15449,10 +15599,10 @@
         <v>1477</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1539</v>
@@ -15463,10 +15613,10 @@
         <v>1477</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1539</v>
@@ -15477,10 +15627,10 @@
         <v>1477</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1539</v>
@@ -15491,10 +15641,10 @@
         <v>1477</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1539</v>
@@ -15505,10 +15655,10 @@
         <v>1477</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1539</v>
@@ -15519,10 +15669,10 @@
         <v>1477</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1539</v>
@@ -15533,10 +15683,10 @@
         <v>1477</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1539</v>
@@ -15547,10 +15697,10 @@
         <v>1477</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>1539</v>
@@ -15561,10 +15711,10 @@
         <v>1477</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D711" s="3" t="s">
         <v>1539</v>
@@ -15575,10 +15725,10 @@
         <v>1477</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1539</v>
@@ -15589,10 +15739,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15603,10 +15753,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15617,10 +15767,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15631,10 +15781,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15645,10 +15795,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15659,10 +15809,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15673,10 +15823,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15687,10 +15837,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15701,10 +15851,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15715,10 +15865,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15729,10 +15879,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15743,10 +15893,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -15757,10 +15907,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -15771,10 +15921,10 @@
         <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -15785,10 +15935,10 @@
         <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>1539</v>
@@ -15799,10 +15949,10 @@
         <v>1477</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>1539</v>
@@ -15813,10 +15963,10 @@
         <v>1477</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>1539</v>
@@ -15824,13 +15974,13 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1479</v>
+        <v>1537</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>1539</v>
@@ -15838,30 +15988,30 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1597</v>
+        <v>1538</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1604</v>
+        <v>1508</v>
       </c>
       <c r="D731" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1598</v>
+        <v>1479</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1605</v>
+        <v>1509</v>
       </c>
       <c r="D732" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.25">
@@ -15869,10 +16019,10 @@
         <v>1595</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1596</v>
@@ -15883,10 +16033,10 @@
         <v>1595</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="D734" s="3" t="s">
         <v>1596</v>
@@ -15897,10 +16047,10 @@
         <v>1595</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="D735" s="3" t="s">
         <v>1596</v>
@@ -15911,10 +16061,10 @@
         <v>1595</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D736" s="3" t="s">
         <v>1596</v>
@@ -15925,10 +16075,10 @@
         <v>1595</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>1596</v>
@@ -15936,30 +16086,30 @@
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1612</v>
+        <v>1602</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="D738" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1613</v>
+        <v>1603</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="D739" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.25">
@@ -15967,10 +16117,10 @@
         <v>1611</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D740" s="3" t="s">
         <v>1628</v>
@@ -15981,10 +16131,10 @@
         <v>1611</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D741" s="3" t="s">
         <v>1628</v>
@@ -15995,10 +16145,10 @@
         <v>1611</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D742" s="3" t="s">
         <v>1628</v>
@@ -16009,10 +16159,10 @@
         <v>1611</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D743" s="3" t="s">
         <v>1628</v>
@@ -16023,10 +16173,10 @@
         <v>1611</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="D744" s="3" t="s">
         <v>1628</v>
@@ -16037,10 +16187,10 @@
         <v>1611</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>1618</v>
+        <v>1625</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="D745" s="3" t="s">
         <v>1628</v>
@@ -16048,44 +16198,44 @@
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
-        <v>1636</v>
+        <v>1611</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>1637</v>
+        <v>1617</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>1638</v>
+        <v>1626</v>
       </c>
       <c r="D746" s="3" t="s">
-        <v>1639</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
-        <v>1640</v>
+        <v>1611</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>1641</v>
+        <v>1618</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="D747" s="3" t="s">
-        <v>1714</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="D748" s="3" t="s">
-        <v>1714</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
@@ -16096,7 +16246,7 @@
         <v>1641</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="D749" s="3" t="s">
         <v>1714</v>
@@ -16110,7 +16260,7 @@
         <v>1641</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="D750" s="3" t="s">
         <v>1714</v>
@@ -16124,7 +16274,7 @@
         <v>1641</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="D751" s="3" t="s">
         <v>1714</v>
@@ -16132,13 +16282,13 @@
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
-        <v>1718</v>
+        <v>1640</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1647</v>
+        <v>1641</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="D752" s="3" t="s">
         <v>1714</v>
@@ -16146,30 +16296,30 @@
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
-        <v>1719</v>
+        <v>1640</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>1650</v>
+        <v>1641</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="D753" s="3" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="D754" s="3" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
@@ -16177,10 +16327,10 @@
         <v>1719</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="D755" s="3" t="s">
         <v>1715</v>
@@ -16191,10 +16341,10 @@
         <v>1719</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D756" s="3" t="s">
         <v>1715</v>
@@ -16205,10 +16355,10 @@
         <v>1719</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="D757" s="3" t="s">
         <v>1715</v>
@@ -16216,30 +16366,30 @@
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>1686</v>
+        <v>1657</v>
       </c>
       <c r="D758" s="3" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>1687</v>
+        <v>1658</v>
       </c>
       <c r="D759" s="3" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
@@ -16247,10 +16397,10 @@
         <v>1713</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D760" s="3" t="s">
         <v>1714</v>
@@ -16261,10 +16411,10 @@
         <v>1713</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="D761" s="3" t="s">
         <v>1714</v>
@@ -16275,10 +16425,10 @@
         <v>1713</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D762" s="3" t="s">
         <v>1714</v>
@@ -16289,10 +16439,10 @@
         <v>1713</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="D763" s="3" t="s">
         <v>1714</v>
@@ -16303,10 +16453,10 @@
         <v>1713</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D764" s="3" t="s">
         <v>1714</v>
@@ -16317,10 +16467,10 @@
         <v>1713</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="D765" s="3" t="s">
         <v>1714</v>
@@ -16331,10 +16481,10 @@
         <v>1713</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D766" s="3" t="s">
         <v>1714</v>
@@ -16345,10 +16495,10 @@
         <v>1713</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="D767" s="3" t="s">
         <v>1714</v>
@@ -16359,10 +16509,10 @@
         <v>1713</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D768" s="3" t="s">
         <v>1714</v>
@@ -16373,10 +16523,10 @@
         <v>1713</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D769" s="3" t="s">
         <v>1714</v>
@@ -16387,10 +16537,10 @@
         <v>1713</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D770" s="3" t="s">
         <v>1714</v>
@@ -16401,10 +16551,10 @@
         <v>1713</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D771" s="3" t="s">
         <v>1714</v>
@@ -16415,10 +16565,10 @@
         <v>1713</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D772" s="3" t="s">
         <v>1714</v>
@@ -16429,10 +16579,10 @@
         <v>1713</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="D773" s="3" t="s">
         <v>1714</v>
@@ -16443,10 +16593,10 @@
         <v>1713</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="D774" s="3" t="s">
         <v>1714</v>
@@ -16457,10 +16607,10 @@
         <v>1713</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="D775" s="3" t="s">
         <v>1714</v>
@@ -16471,10 +16621,10 @@
         <v>1713</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="D776" s="3" t="s">
         <v>1714</v>
@@ -16485,10 +16635,10 @@
         <v>1713</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="D777" s="3" t="s">
         <v>1714</v>
@@ -16499,10 +16649,10 @@
         <v>1713</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D778" s="3" t="s">
         <v>1714</v>
@@ -16513,10 +16663,10 @@
         <v>1713</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="D779" s="3" t="s">
         <v>1714</v>
@@ -16527,10 +16677,10 @@
         <v>1713</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D780" s="3" t="s">
         <v>1714</v>
@@ -16541,10 +16691,10 @@
         <v>1713</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D781" s="3" t="s">
         <v>1714</v>
@@ -16555,10 +16705,10 @@
         <v>1713</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="D782" s="3" t="s">
         <v>1714</v>
@@ -16569,10 +16719,10 @@
         <v>1713</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D783" s="3" t="s">
         <v>1714</v>
@@ -16583,13 +16733,326 @@
         <v>1713</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D784" s="3" t="s">
         <v>1714</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A785" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D785" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A786" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C786" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D786" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A787" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C787" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D787" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A788" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C788" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D788" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A789" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C789" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D789" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A790" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C790" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D790" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A791" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C791" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D791" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A792" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C792" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D792" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A793" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C793" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D793" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A794" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C794" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D794" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A795" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C795" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D795" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A796" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C796" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D796" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A797" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C797" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D797" s="3" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A798" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D798" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A799" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D799" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A800" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D800" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A801" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C801" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D801" s="3" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A802" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C802" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D802" s="3" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A803" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D803" s="3" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A804" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D804" s="3" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A805" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D805" s="3" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A806" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D806" s="3" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A807" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D807" s="3" t="s">
+        <v>1765</v>
       </c>
     </row>
   </sheetData>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6591F0F7-F846-4781-B29F-7F722E6D9A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DA7789-ED23-47EF-8825-B49EC0E91616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DA7789-ED23-47EF-8825-B49EC0E91616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F042C22-7906-4FA4-918C-28884022F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16919,7 +16919,7 @@
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>1730</v>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F042C22-7906-4FA4-918C-28884022F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16933,7 +16933,7 @@
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B794" s="2" t="s">
         <v>1729</v>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\3_PROJECT_DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05D6B8DB-6546-4382-ABC6-B7A0C114B4F4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="1791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3284" uniqueCount="1801">
   <si>
     <t>Company</t>
   </si>
@@ -5393,6 +5393,36 @@
   </si>
   <si>
     <t>ОБЩИНА ВАРНА % 6 - КДР</t>
+  </si>
+  <si>
+    <t>МАЙ БЮТИ ДЖЪРНИ ЕООД</t>
+  </si>
+  <si>
+    <t>БЮТИ 1</t>
+  </si>
+  <si>
+    <t>БЮТИ 2</t>
+  </si>
+  <si>
+    <t>БЮТИ ТУБА 1</t>
+  </si>
+  <si>
+    <t>БЮТИ ТУБА 2</t>
+  </si>
+  <si>
+    <t>78970153027722072</t>
+  </si>
+  <si>
+    <t>78970153027722080</t>
+  </si>
+  <si>
+    <t>78970153027722098</t>
+  </si>
+  <si>
+    <t>78970153027722106</t>
+  </si>
+  <si>
+    <t>206663561</t>
   </si>
 </sst>
 </file>
@@ -5791,7 +5821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E815"/>
+  <dimension ref="A1:E819"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -17239,6 +17269,62 @@
         <v>1777</v>
       </c>
     </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A816" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D816" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A817" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D817" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A818" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D818" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A819" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D819" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7EBE467-16A8-442E-B82E-E7DC3F683D78}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB63AD20-D347-49B1-B662-5B181EAEE62B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3299" uniqueCount="1806">
   <si>
     <t>Company</t>
   </si>
@@ -5426,6 +5426,18 @@
   </si>
   <si>
     <t>78970110027720225</t>
+  </si>
+  <si>
+    <t>ТУБА СПОРТ 2</t>
+  </si>
+  <si>
+    <t>78970155027722143</t>
+  </si>
+  <si>
+    <t>78970153027722064</t>
+  </si>
+  <si>
+    <t>78970110027720258</t>
   </si>
 </sst>
 </file>
@@ -5824,7 +5836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E820"/>
+  <dimension ref="A1:E823"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -8595,10 +8607,10 @@
         <v>941</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>371</v>
+        <v>1804</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>942</v>
@@ -8606,16 +8618,16 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -8623,10 +8635,10 @@
         <v>943</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>944</v>
@@ -8637,10 +8649,10 @@
         <v>943</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>944</v>
@@ -8651,10 +8663,10 @@
         <v>943</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>944</v>
@@ -8665,10 +8677,10 @@
         <v>943</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>944</v>
@@ -8679,10 +8691,10 @@
         <v>943</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>944</v>
@@ -8693,10 +8705,10 @@
         <v>943</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>944</v>
@@ -8704,16 +8716,16 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -8721,10 +8733,10 @@
         <v>945</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>946</v>
@@ -8732,16 +8744,16 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -8749,10 +8761,10 @@
         <v>947</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>948</v>
@@ -8763,10 +8775,10 @@
         <v>947</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>948</v>
@@ -8777,10 +8789,10 @@
         <v>947</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>948</v>
@@ -8791,10 +8803,10 @@
         <v>947</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>948</v>
@@ -8805,10 +8817,10 @@
         <v>947</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>948</v>
@@ -8819,10 +8831,10 @@
         <v>947</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>948</v>
@@ -8833,10 +8845,10 @@
         <v>947</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>948</v>
@@ -8847,10 +8859,10 @@
         <v>947</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>948</v>
@@ -8861,10 +8873,10 @@
         <v>947</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>948</v>
@@ -8875,10 +8887,10 @@
         <v>947</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>948</v>
@@ -8886,16 +8898,16 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -8903,10 +8915,10 @@
         <v>949</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>950</v>
@@ -8917,10 +8929,10 @@
         <v>949</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>950</v>
@@ -8931,10 +8943,10 @@
         <v>949</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>950</v>
@@ -8945,10 +8957,10 @@
         <v>949</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>950</v>
@@ -8959,10 +8971,10 @@
         <v>949</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>950</v>
@@ -8973,10 +8985,10 @@
         <v>949</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>950</v>
@@ -8987,10 +8999,10 @@
         <v>949</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>950</v>
@@ -9001,10 +9013,10 @@
         <v>949</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>950</v>
@@ -9015,10 +9027,10 @@
         <v>949</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>950</v>
@@ -9029,10 +9041,10 @@
         <v>949</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>950</v>
@@ -9043,10 +9055,10 @@
         <v>949</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>950</v>
@@ -9057,10 +9069,10 @@
         <v>949</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>950</v>
@@ -9071,10 +9083,10 @@
         <v>949</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>950</v>
@@ -9085,10 +9097,10 @@
         <v>949</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>950</v>
@@ -9099,10 +9111,10 @@
         <v>949</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>950</v>
@@ -9113,10 +9125,10 @@
         <v>949</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>950</v>
@@ -9127,10 +9139,10 @@
         <v>949</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>950</v>
@@ -9141,10 +9153,10 @@
         <v>949</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>950</v>
@@ -9155,10 +9167,10 @@
         <v>949</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>950</v>
@@ -9169,10 +9181,10 @@
         <v>949</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>950</v>
@@ -9183,10 +9195,10 @@
         <v>949</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>950</v>
@@ -9197,10 +9209,10 @@
         <v>949</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>950</v>
@@ -9211,10 +9223,10 @@
         <v>949</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>950</v>
@@ -9225,10 +9237,10 @@
         <v>949</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>950</v>
@@ -9239,10 +9251,10 @@
         <v>949</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>950</v>
@@ -9253,10 +9265,10 @@
         <v>949</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>950</v>
@@ -9267,10 +9279,10 @@
         <v>949</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>950</v>
@@ -9281,10 +9293,10 @@
         <v>949</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>950</v>
@@ -9295,10 +9307,10 @@
         <v>949</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>950</v>
@@ -9309,10 +9321,10 @@
         <v>949</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>950</v>
@@ -9320,16 +9332,16 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -9337,10 +9349,10 @@
         <v>951</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>952</v>
@@ -9348,16 +9360,16 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -9365,10 +9377,10 @@
         <v>953</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>954</v>
@@ -9376,30 +9388,30 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -9407,10 +9419,10 @@
         <v>957</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>958</v>
@@ -9418,16 +9430,16 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -9435,10 +9447,10 @@
         <v>959</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>960</v>
@@ -9449,10 +9461,10 @@
         <v>959</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>960</v>
@@ -9463,10 +9475,10 @@
         <v>959</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>960</v>
@@ -9477,10 +9489,10 @@
         <v>959</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>960</v>
@@ -9491,10 +9503,10 @@
         <v>959</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>960</v>
@@ -9505,10 +9517,10 @@
         <v>959</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>960</v>
@@ -9519,10 +9531,10 @@
         <v>959</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>960</v>
@@ -9530,16 +9542,16 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -9547,10 +9559,10 @@
         <v>961</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>962</v>
@@ -9561,10 +9573,10 @@
         <v>961</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>962</v>
@@ -9575,10 +9587,10 @@
         <v>961</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>962</v>
@@ -9589,10 +9601,10 @@
         <v>961</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D269" s="3" t="s">
         <v>962</v>
@@ -9603,10 +9615,10 @@
         <v>961</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>962</v>
@@ -9614,16 +9626,16 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -9631,10 +9643,10 @@
         <v>963</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>964</v>
@@ -9645,10 +9657,10 @@
         <v>963</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D273" s="3" t="s">
         <v>964</v>
@@ -9656,16 +9668,16 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -9673,10 +9685,10 @@
         <v>965</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>966</v>
@@ -9687,10 +9699,10 @@
         <v>965</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>966</v>
@@ -9701,10 +9713,10 @@
         <v>965</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>966</v>
@@ -9715,10 +9727,10 @@
         <v>965</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>966</v>
@@ -9729,10 +9741,10 @@
         <v>965</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>966</v>
@@ -9743,10 +9755,10 @@
         <v>965</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>966</v>
@@ -9757,10 +9769,10 @@
         <v>965</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>966</v>
@@ -9771,10 +9783,10 @@
         <v>965</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>966</v>
@@ -9785,10 +9797,10 @@
         <v>965</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>966</v>
@@ -9799,10 +9811,10 @@
         <v>965</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>966</v>
@@ -9813,10 +9825,10 @@
         <v>965</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>966</v>
@@ -9827,10 +9839,10 @@
         <v>965</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>966</v>
@@ -9841,10 +9853,10 @@
         <v>965</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>966</v>
@@ -9855,10 +9867,10 @@
         <v>965</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>966</v>
@@ -9869,10 +9881,10 @@
         <v>965</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>966</v>
@@ -9883,10 +9895,10 @@
         <v>965</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>1557</v>
+        <v>553</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>966</v>
@@ -9900,7 +9912,7 @@
         <v>554</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>555</v>
+        <v>1557</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>966</v>
@@ -9911,10 +9923,10 @@
         <v>965</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>966</v>
@@ -9925,10 +9937,10 @@
         <v>965</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>966</v>
@@ -9939,10 +9951,10 @@
         <v>965</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>966</v>
@@ -9953,10 +9965,10 @@
         <v>965</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D295" s="3" t="s">
         <v>966</v>
@@ -9967,10 +9979,10 @@
         <v>965</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>966</v>
@@ -9981,10 +9993,10 @@
         <v>965</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D297" s="3" t="s">
         <v>966</v>
@@ -9995,10 +10007,10 @@
         <v>965</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>966</v>
@@ -10009,10 +10021,10 @@
         <v>965</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>966</v>
@@ -10023,10 +10035,10 @@
         <v>965</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>966</v>
@@ -10037,10 +10049,10 @@
         <v>965</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D301" s="3" t="s">
         <v>966</v>
@@ -10051,10 +10063,10 @@
         <v>965</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>966</v>
@@ -10065,10 +10077,10 @@
         <v>965</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D303" s="3" t="s">
         <v>966</v>
@@ -10079,10 +10091,10 @@
         <v>965</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>966</v>
@@ -10093,10 +10105,10 @@
         <v>965</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>966</v>
@@ -10107,10 +10119,10 @@
         <v>965</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D306" s="3" t="s">
         <v>966</v>
@@ -10121,10 +10133,10 @@
         <v>965</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>966</v>
@@ -10135,10 +10147,10 @@
         <v>965</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>966</v>
@@ -10149,10 +10161,10 @@
         <v>965</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>966</v>
@@ -10163,10 +10175,10 @@
         <v>965</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>966</v>
@@ -10177,10 +10189,10 @@
         <v>965</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>966</v>
@@ -10191,10 +10203,10 @@
         <v>965</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>966</v>
@@ -10205,10 +10217,10 @@
         <v>965</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D313" s="3" t="s">
         <v>966</v>
@@ -10219,10 +10231,10 @@
         <v>965</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D314" s="3" t="s">
         <v>966</v>
@@ -10233,10 +10245,10 @@
         <v>965</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D315" s="3" t="s">
         <v>966</v>
@@ -10247,10 +10259,10 @@
         <v>965</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>966</v>
@@ -10258,16 +10270,16 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -10275,10 +10287,10 @@
         <v>967</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>968</v>
@@ -10289,10 +10301,10 @@
         <v>967</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>968</v>
@@ -10303,10 +10315,10 @@
         <v>967</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>968</v>
@@ -10317,10 +10329,10 @@
         <v>967</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D321" s="3" t="s">
         <v>968</v>
@@ -10331,10 +10343,10 @@
         <v>967</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>968</v>
@@ -10345,10 +10357,10 @@
         <v>967</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>968</v>
@@ -10359,10 +10371,10 @@
         <v>967</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>968</v>
@@ -10373,10 +10385,10 @@
         <v>967</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D325" s="3" t="s">
         <v>968</v>
@@ -10387,10 +10399,10 @@
         <v>967</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>968</v>
@@ -10398,16 +10410,16 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -10415,10 +10427,10 @@
         <v>969</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>970</v>
@@ -10429,10 +10441,10 @@
         <v>969</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>970</v>
@@ -10442,11 +10454,11 @@
       <c r="A330" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="B330" t="s">
-        <v>1716</v>
+      <c r="B330" s="2" t="s">
+        <v>630</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1715</v>
+        <v>631</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>970</v>
@@ -10454,16 +10466,16 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>1593</v>
+        <v>969</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1716</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1594</v>
+        <v>1715</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -10471,10 +10483,10 @@
         <v>972</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>632</v>
+        <v>1593</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>633</v>
+        <v>1594</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>974</v>
@@ -10485,10 +10497,10 @@
         <v>972</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>974</v>
@@ -10499,10 +10511,10 @@
         <v>972</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>974</v>
@@ -10513,10 +10525,10 @@
         <v>972</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>974</v>
@@ -10527,10 +10539,10 @@
         <v>972</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>974</v>
@@ -10541,10 +10553,10 @@
         <v>972</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>974</v>
@@ -10555,10 +10567,10 @@
         <v>972</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>974</v>
@@ -10569,10 +10581,10 @@
         <v>972</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>974</v>
@@ -10583,10 +10595,10 @@
         <v>972</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>974</v>
@@ -10597,10 +10609,10 @@
         <v>972</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>1020</v>
+        <v>648</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>1021</v>
+        <v>649</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>974</v>
@@ -10608,13 +10620,13 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>650</v>
+        <v>1020</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>651</v>
+        <v>1021</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>974</v>
@@ -10625,10 +10637,10 @@
         <v>971</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>974</v>
@@ -10639,10 +10651,10 @@
         <v>971</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>974</v>
@@ -10653,10 +10665,10 @@
         <v>971</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>974</v>
@@ -10667,10 +10679,10 @@
         <v>971</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>974</v>
@@ -10681,10 +10693,10 @@
         <v>971</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>974</v>
@@ -10695,10 +10707,10 @@
         <v>971</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>974</v>
@@ -10709,10 +10721,10 @@
         <v>971</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>974</v>
@@ -10720,16 +10732,16 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -10737,10 +10749,10 @@
         <v>973</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>975</v>
@@ -10751,10 +10763,10 @@
         <v>973</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>975</v>
@@ -10765,10 +10777,10 @@
         <v>973</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>975</v>
@@ -10776,16 +10788,16 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -10793,10 +10805,10 @@
         <v>976</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>987</v>
@@ -10807,10 +10819,10 @@
         <v>976</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D356" s="3" t="s">
         <v>987</v>
@@ -10821,10 +10833,10 @@
         <v>976</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>987</v>
@@ -10835,10 +10847,10 @@
         <v>976</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>987</v>
@@ -10849,10 +10861,10 @@
         <v>976</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>987</v>
@@ -10863,10 +10875,10 @@
         <v>976</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>987</v>
@@ -10877,10 +10889,10 @@
         <v>976</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>987</v>
@@ -10891,10 +10903,10 @@
         <v>976</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>987</v>
@@ -10905,10 +10917,10 @@
         <v>976</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>987</v>
@@ -10919,10 +10931,10 @@
         <v>976</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>987</v>
@@ -10933,10 +10945,10 @@
         <v>976</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>987</v>
@@ -10947,10 +10959,10 @@
         <v>976</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>987</v>
@@ -10961,10 +10973,10 @@
         <v>976</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>987</v>
@@ -10975,10 +10987,10 @@
         <v>976</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>987</v>
@@ -10989,10 +11001,10 @@
         <v>976</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>987</v>
@@ -11000,13 +11012,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>987</v>
@@ -11017,10 +11029,10 @@
         <v>977</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>987</v>
@@ -11031,10 +11043,10 @@
         <v>977</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>987</v>
@@ -11045,10 +11057,10 @@
         <v>977</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>987</v>
@@ -11059,10 +11071,10 @@
         <v>977</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>987</v>
@@ -11073,10 +11085,10 @@
         <v>977</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>987</v>
@@ -11087,10 +11099,10 @@
         <v>977</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>987</v>
@@ -11101,10 +11113,10 @@
         <v>977</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>987</v>
@@ -11115,10 +11127,10 @@
         <v>977</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>987</v>
@@ -11129,10 +11141,10 @@
         <v>977</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>987</v>
@@ -11143,10 +11155,10 @@
         <v>977</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>987</v>
@@ -11157,10 +11169,10 @@
         <v>977</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>987</v>
@@ -11171,10 +11183,10 @@
         <v>977</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>987</v>
@@ -11185,10 +11197,10 @@
         <v>977</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>987</v>
@@ -11199,10 +11211,10 @@
         <v>977</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>987</v>
@@ -11213,10 +11225,10 @@
         <v>977</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>987</v>
@@ -11224,27 +11236,27 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>893</v>
+        <v>737</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>740</v>
+        <v>893</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>986</v>
@@ -11255,10 +11267,10 @@
         <v>984</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>986</v>
@@ -11269,10 +11281,10 @@
         <v>984</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>986</v>
@@ -11286,7 +11298,7 @@
         <v>743</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>875</v>
+        <v>744</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>986</v>
@@ -11297,10 +11309,10 @@
         <v>984</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>986</v>
@@ -11311,10 +11323,10 @@
         <v>984</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>986</v>
@@ -11322,13 +11334,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>986</v>
@@ -11342,7 +11354,7 @@
         <v>745</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>746</v>
+        <v>878</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>986</v>
@@ -11350,16 +11362,16 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>788</v>
+        <v>746</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -11367,10 +11379,10 @@
         <v>978</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>810</v>
+        <v>788</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>988</v>
@@ -11381,10 +11393,10 @@
         <v>978</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>988</v>
@@ -11395,10 +11407,10 @@
         <v>978</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>988</v>
@@ -11409,10 +11421,10 @@
         <v>978</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>988</v>
@@ -11423,10 +11435,10 @@
         <v>978</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>988</v>
@@ -11437,10 +11449,10 @@
         <v>978</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>988</v>
@@ -11451,10 +11463,10 @@
         <v>978</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>988</v>
@@ -11465,10 +11477,10 @@
         <v>978</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>988</v>
@@ -11479,10 +11491,10 @@
         <v>978</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>988</v>
@@ -11493,10 +11505,10 @@
         <v>978</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>803</v>
+        <v>751</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>988</v>
@@ -11507,10 +11519,10 @@
         <v>978</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>988</v>
@@ -11521,10 +11533,10 @@
         <v>978</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>751</v>
+        <v>805</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>988</v>
@@ -11535,10 +11547,10 @@
         <v>978</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>988</v>
@@ -11549,10 +11561,10 @@
         <v>978</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>809</v>
+        <v>762</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>988</v>
@@ -11563,10 +11575,10 @@
         <v>978</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>898</v>
+        <v>809</v>
       </c>
       <c r="D410" s="3" t="s">
         <v>988</v>
@@ -11577,10 +11589,10 @@
         <v>978</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>791</v>
+        <v>898</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>988</v>
@@ -11591,10 +11603,10 @@
         <v>978</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="D412" s="3" t="s">
         <v>988</v>
@@ -11605,10 +11617,10 @@
         <v>978</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>988</v>
@@ -11619,10 +11631,10 @@
         <v>978</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>838</v>
+        <v>792</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11633,10 +11645,10 @@
         <v>978</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>988</v>
@@ -11647,10 +11659,10 @@
         <v>978</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>988</v>
@@ -11661,10 +11673,10 @@
         <v>978</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11675,10 +11687,10 @@
         <v>978</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1583</v>
+        <v>793</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11689,10 +11701,10 @@
         <v>978</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>811</v>
+        <v>1583</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11703,10 +11715,10 @@
         <v>978</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D420" s="3" t="s">
         <v>988</v>
@@ -11717,10 +11729,10 @@
         <v>978</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1578</v>
+        <v>802</v>
       </c>
       <c r="D421" s="3" t="s">
         <v>988</v>
@@ -11731,10 +11743,10 @@
         <v>978</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>988</v>
@@ -11745,10 +11757,10 @@
         <v>978</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>988</v>
@@ -11759,10 +11771,10 @@
         <v>978</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>804</v>
+        <v>1580</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>988</v>
@@ -11773,10 +11785,10 @@
         <v>978</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>988</v>
@@ -11787,10 +11799,10 @@
         <v>978</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>988</v>
@@ -11801,10 +11813,10 @@
         <v>978</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>988</v>
@@ -11815,10 +11827,10 @@
         <v>978</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11828,11 +11840,11 @@
       <c r="A429" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B429" s="4" t="s">
-        <v>783</v>
+      <c r="B429" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>896</v>
+        <v>801</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>988</v>
@@ -11842,11 +11854,11 @@
       <c r="A430" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B430" s="2" t="s">
-        <v>784</v>
+      <c r="B430" s="4" t="s">
+        <v>783</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>796</v>
+        <v>896</v>
       </c>
       <c r="D430" s="3" t="s">
         <v>988</v>
@@ -11857,10 +11869,10 @@
         <v>978</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D431" s="3" t="s">
         <v>988</v>
@@ -11871,10 +11883,10 @@
         <v>978</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1581</v>
+        <v>798</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>988</v>
@@ -11885,10 +11897,10 @@
         <v>978</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1582</v>
+        <v>786</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>813</v>
+        <v>1581</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>988</v>
@@ -11896,16 +11908,16 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B434" s="5" t="s">
-        <v>826</v>
+        <v>978</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>1582</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -11913,10 +11925,10 @@
         <v>979</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D435" s="3" t="s">
         <v>980</v>
@@ -11927,10 +11939,10 @@
         <v>979</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D436" s="3" t="s">
         <v>980</v>
@@ -11941,10 +11953,10 @@
         <v>979</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D437" s="3" t="s">
         <v>980</v>
@@ -11955,10 +11967,10 @@
         <v>979</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>980</v>
@@ -11969,10 +11981,10 @@
         <v>979</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>980</v>
@@ -11983,10 +11995,10 @@
         <v>979</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D440" s="3" t="s">
         <v>980</v>
@@ -11997,10 +12009,10 @@
         <v>979</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D441" s="3" t="s">
         <v>980</v>
@@ -12011,10 +12023,10 @@
         <v>979</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D442" s="3" t="s">
         <v>980</v>
@@ -12025,10 +12037,10 @@
         <v>979</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D443" s="3" t="s">
         <v>980</v>
@@ -12039,10 +12051,10 @@
         <v>979</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>980</v>
@@ -12053,10 +12065,10 @@
         <v>979</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>980</v>
@@ -12064,16 +12076,16 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B446" s="2" t="s">
-        <v>843</v>
+        <v>979</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>837</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>884</v>
+        <v>825</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -12081,10 +12093,10 @@
         <v>839</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="D447" s="3" t="s">
         <v>981</v>
@@ -12095,10 +12107,10 @@
         <v>839</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D448" s="3" t="s">
         <v>981</v>
@@ -12109,10 +12121,10 @@
         <v>839</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D449" s="3" t="s">
         <v>981</v>
@@ -12123,10 +12135,10 @@
         <v>839</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D450" s="3" t="s">
         <v>981</v>
@@ -12137,10 +12149,10 @@
         <v>839</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D451" s="3" t="s">
         <v>981</v>
@@ -12151,10 +12163,10 @@
         <v>839</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>871</v>
+        <v>844</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>981</v>
@@ -12162,36 +12174,33 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="B453" s="2">
-        <v>3</v>
+        <v>839</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E453" s="3" t="s">
-        <v>850</v>
+        <v>981</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B454" s="2" t="s">
-        <v>1584</v>
+      <c r="B454" s="2">
+        <v>3</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -12199,16 +12208,16 @@
         <v>880</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>856</v>
+        <v>1584</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -12216,16 +12225,16 @@
         <v>880</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
@@ -12233,16 +12242,16 @@
         <v>880</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>879</v>
+        <v>857</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -12250,16 +12259,16 @@
         <v>880</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>50</v>
+        <v>860</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -12267,16 +12276,16 @@
         <v>880</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D459" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -12284,78 +12293,81 @@
         <v>880</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B461" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C461" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B462" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="C462" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D462" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B463" s="4" t="s">
-        <v>883</v>
+      <c r="B463" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="D463" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B464" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="C464" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D464" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -12363,13 +12375,13 @@
         <v>880</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D465" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -12377,41 +12389,39 @@
         <v>880</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>1005</v>
+        <v>880</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>993</v>
+        <v>1805</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>1017</v>
-      </c>
+        <v>982</v>
+      </c>
+      <c r="E467" s="3"/>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B468" s="2" t="s">
-        <v>1006</v>
+        <v>880</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>994</v>
+        <v>894</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
+      </c>
+      <c r="E468" s="3" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -12419,10 +12429,10 @@
         <v>992</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D469" s="3" t="s">
         <v>1017</v>
@@ -12433,10 +12443,10 @@
         <v>992</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D470" s="3" t="s">
         <v>1017</v>
@@ -12447,10 +12457,10 @@
         <v>992</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D471" s="3" t="s">
         <v>1017</v>
@@ -12461,10 +12471,10 @@
         <v>992</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D472" s="3" t="s">
         <v>1017</v>
@@ -12475,10 +12485,10 @@
         <v>992</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>1017</v>
@@ -12489,10 +12499,10 @@
         <v>992</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>1017</v>
@@ -12503,10 +12513,10 @@
         <v>992</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D475" s="3" t="s">
         <v>1017</v>
@@ -12517,10 +12527,10 @@
         <v>992</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D476" s="3" t="s">
         <v>1017</v>
@@ -12531,10 +12541,10 @@
         <v>992</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1017</v>
@@ -12545,55 +12555,55 @@
         <v>992</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A479" s="3" t="s">
-        <v>1018</v>
+      <c r="A479" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>180</v>
+        <v>1015</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>872</v>
+        <v>1003</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
-        <v>1034</v>
+        <v>992</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C480" s="6" t="s">
-        <v>1095</v>
+        <v>1016</v>
+      </c>
+      <c r="C480" s="2" t="s">
+        <v>1004</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="1" t="s">
-        <v>1034</v>
+      <c r="A481" s="3" t="s">
+        <v>1018</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C481" s="6" t="s">
-        <v>1096</v>
+        <v>180</v>
+      </c>
+      <c r="C481" s="2" t="s">
+        <v>872</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -12601,10 +12611,10 @@
         <v>1034</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>1033</v>
@@ -12615,10 +12625,10 @@
         <v>1034</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>1033</v>
@@ -12629,10 +12639,10 @@
         <v>1034</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D484" s="3" t="s">
         <v>1033</v>
@@ -12643,10 +12653,10 @@
         <v>1034</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1033</v>
@@ -12657,10 +12667,10 @@
         <v>1034</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1033</v>
@@ -12671,10 +12681,10 @@
         <v>1034</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D487" s="3" t="s">
         <v>1033</v>
@@ -12685,10 +12695,10 @@
         <v>1034</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1033</v>
@@ -12699,10 +12709,10 @@
         <v>1034</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1033</v>
@@ -12713,10 +12723,10 @@
         <v>1034</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1033</v>
@@ -12724,30 +12734,30 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -12755,10 +12765,10 @@
         <v>1035</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>1036</v>
@@ -12769,10 +12779,10 @@
         <v>1035</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1036</v>
@@ -12783,10 +12793,10 @@
         <v>1035</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>1036</v>
@@ -12797,10 +12807,10 @@
         <v>1035</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>1036</v>
@@ -12811,10 +12821,10 @@
         <v>1035</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>1036</v>
@@ -12825,10 +12835,10 @@
         <v>1035</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1036</v>
@@ -12839,10 +12849,10 @@
         <v>1035</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D499" s="3" t="s">
         <v>1036</v>
@@ -12850,30 +12860,30 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
@@ -12881,10 +12891,10 @@
         <v>1591</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>1046</v>
@@ -12892,30 +12902,30 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -12923,10 +12933,10 @@
         <v>1055</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="D505" s="3" t="s">
         <v>1050</v>
@@ -12937,10 +12947,10 @@
         <v>1055</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D506" s="3" t="s">
         <v>1050</v>
@@ -12948,30 +12958,30 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
@@ -12979,10 +12989,10 @@
         <v>1056</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>1057</v>
@@ -12990,30 +13000,30 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
@@ -13021,10 +13031,10 @@
         <v>1060</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>1061</v>
@@ -13035,10 +13045,10 @@
         <v>1060</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D513" s="3" t="s">
         <v>1061</v>
@@ -13049,10 +13059,10 @@
         <v>1060</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="D514" s="3" t="s">
         <v>1061</v>
@@ -13063,10 +13073,10 @@
         <v>1060</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>1061</v>
@@ -13077,10 +13087,10 @@
         <v>1060</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>1061</v>
@@ -13091,10 +13101,10 @@
         <v>1060</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D517" s="3" t="s">
         <v>1061</v>
@@ -13105,10 +13115,10 @@
         <v>1060</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>1061</v>
@@ -13119,10 +13129,10 @@
         <v>1060</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C519" s="6" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="D519" s="3" t="s">
         <v>1061</v>
@@ -13133,10 +13143,10 @@
         <v>1060</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>1061</v>
@@ -13144,30 +13154,30 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1590</v>
+        <v>1072</v>
+      </c>
+      <c r="C522" s="6" t="s">
+        <v>1135</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
@@ -13175,10 +13185,10 @@
         <v>1073</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>1634</v>
+        <v>1074</v>
+      </c>
+      <c r="C523" s="6" t="s">
+        <v>1136</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>1075</v>
@@ -13186,30 +13196,30 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C524" s="6" t="s">
-        <v>1137</v>
+        <v>1589</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>1590</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C525" s="6" t="s">
-        <v>1138</v>
+        <v>1633</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>1634</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
@@ -13217,10 +13227,10 @@
         <v>1076</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>1081</v>
@@ -13231,10 +13241,10 @@
         <v>1076</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>1081</v>
@@ -13242,44 +13252,44 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1085</v>
+        <v>1802</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1142</v>
+        <v>1803</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
@@ -13287,10 +13297,10 @@
         <v>1082</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D531" s="3" t="s">
         <v>1083</v>
@@ -13301,10 +13311,10 @@
         <v>1082</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>1083</v>
@@ -13312,44 +13322,44 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
@@ -13357,10 +13367,10 @@
         <v>1540</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="D536" s="3" t="s">
         <v>1094</v>
@@ -13371,10 +13381,10 @@
         <v>1540</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D537" s="3" t="s">
         <v>1094</v>
@@ -13382,184 +13392,184 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C538" s="2" t="s">
-        <v>1168</v>
+        <v>1091</v>
+      </c>
+      <c r="C538" s="6" t="s">
+        <v>1148</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C539" s="2" t="s">
-        <v>1169</v>
+        <v>1092</v>
+      </c>
+      <c r="C539" s="6" t="s">
+        <v>1149</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>1152</v>
+        <v>1540</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C540" s="2" t="s">
-        <v>1172</v>
+        <v>1093</v>
+      </c>
+      <c r="C540" s="6" t="s">
+        <v>1150</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>1460</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1190</v>
+        <v>1181</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
@@ -13567,10 +13577,10 @@
         <v>1156</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>1464</v>
@@ -13578,72 +13588,72 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B554" s="7" t="s">
-        <v>1234</v>
+        <v>1156</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>1189</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B555" s="7" t="s">
-        <v>1235</v>
+        <v>1157</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>1194</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B556" s="7" t="s">
-        <v>1236</v>
+        <v>1157</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>1195</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
@@ -13651,10 +13661,10 @@
         <v>1158</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D557" s="3" t="s">
         <v>1466</v>
@@ -13665,10 +13675,10 @@
         <v>1158</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="D558" s="3" t="s">
         <v>1466</v>
@@ -13679,10 +13689,10 @@
         <v>1158</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="D559" s="3" t="s">
         <v>1466</v>
@@ -13693,10 +13703,10 @@
         <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="D560" s="3" t="s">
         <v>1466</v>
@@ -13707,10 +13717,10 @@
         <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="D561" s="3" t="s">
         <v>1466</v>
@@ -13721,10 +13731,10 @@
         <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="D562" s="3" t="s">
         <v>1466</v>
@@ -13735,10 +13745,10 @@
         <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1466</v>
@@ -13749,10 +13759,10 @@
         <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>1466</v>
@@ -13763,10 +13773,10 @@
         <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>1466</v>
@@ -13777,10 +13787,10 @@
         <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1466</v>
@@ -13791,10 +13801,10 @@
         <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1466</v>
@@ -13805,10 +13815,10 @@
         <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>1466</v>
@@ -13819,10 +13829,10 @@
         <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>1466</v>
@@ -13833,10 +13843,10 @@
         <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>1466</v>
@@ -13847,10 +13857,10 @@
         <v>1158</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1466</v>
@@ -13861,10 +13871,10 @@
         <v>1158</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1466</v>
@@ -13875,10 +13885,10 @@
         <v>1158</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>1466</v>
@@ -13889,10 +13899,10 @@
         <v>1158</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1466</v>
@@ -13903,10 +13913,10 @@
         <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>1466</v>
@@ -13916,11 +13926,11 @@
       <c r="A576" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B576" s="4" t="s">
-        <v>1256</v>
+      <c r="B576" s="7" t="s">
+        <v>1253</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>1466</v>
@@ -13931,10 +13941,10 @@
         <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>1466</v>
@@ -13945,10 +13955,10 @@
         <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>1466</v>
@@ -13958,11 +13968,11 @@
       <c r="A579" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B579" s="7" t="s">
-        <v>1259</v>
+      <c r="B579" s="4" t="s">
+        <v>1256</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>1466</v>
@@ -13973,10 +13983,10 @@
         <v>1158</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>1466</v>
@@ -13987,10 +13997,10 @@
         <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>1466</v>
@@ -14001,10 +14011,10 @@
         <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>1466</v>
@@ -14015,10 +14025,10 @@
         <v>1158</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1232</v>
+        <v>1260</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>1466</v>
@@ -14029,10 +14039,10 @@
         <v>1158</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>1466</v>
@@ -14043,10 +14053,10 @@
         <v>1158</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>1466</v>
@@ -14057,10 +14067,10 @@
         <v>1158</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1265</v>
+        <v>1232</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>1466</v>
@@ -14071,10 +14081,10 @@
         <v>1158</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1765</v>
+        <v>1263</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1767</v>
+        <v>1228</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>1466</v>
@@ -14085,10 +14095,10 @@
         <v>1158</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1766</v>
+        <v>1264</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1768</v>
+        <v>1229</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1466</v>
@@ -14099,10 +14109,10 @@
         <v>1158</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1466</v>
@@ -14110,44 +14120,44 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1266</v>
+        <v>1765</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1282</v>
+        <v>1767</v>
       </c>
       <c r="D590" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1267</v>
+        <v>1766</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1283</v>
+        <v>1768</v>
       </c>
       <c r="D591" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1268</v>
+        <v>1233</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1284</v>
+        <v>1231</v>
       </c>
       <c r="D592" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -14155,10 +14165,10 @@
         <v>1159</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>1467</v>
@@ -14169,10 +14179,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -14183,10 +14193,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -14197,10 +14207,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -14211,10 +14221,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -14225,10 +14235,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -14239,10 +14249,10 @@
         <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>1467</v>
@@ -14253,10 +14263,10 @@
         <v>1159</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="D600" s="3" t="s">
         <v>1467</v>
@@ -14267,10 +14277,10 @@
         <v>1159</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="D601" s="3" t="s">
         <v>1467</v>
@@ -14281,10 +14291,10 @@
         <v>1159</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1467</v>
@@ -14295,10 +14305,10 @@
         <v>1159</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1467</v>
@@ -14309,10 +14319,10 @@
         <v>1159</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1467</v>
@@ -14323,10 +14333,10 @@
         <v>1159</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1467</v>
@@ -14334,44 +14344,44 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1298</v>
+        <v>1279</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
       <c r="D606" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1299</v>
+        <v>1280</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1300</v>
+        <v>1281</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
@@ -14379,10 +14389,10 @@
         <v>1160</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="D609" s="3" t="s">
         <v>1468</v>
@@ -14390,86 +14400,86 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B610" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B610" s="7" t="s">
+        <v>1299</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1558</v>
+        <v>1303</v>
       </c>
       <c r="D610" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B611" s="2" t="s">
-        <v>1307</v>
+        <v>1160</v>
+      </c>
+      <c r="B611" s="7" t="s">
+        <v>1300</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1576</v>
+        <v>1304</v>
       </c>
       <c r="D611" s="3" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B612" s="2" t="s">
-        <v>1308</v>
+        <v>1160</v>
+      </c>
+      <c r="B612" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1577</v>
+        <v>1305</v>
       </c>
       <c r="D612" s="3" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B613" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C613" s="8" t="s">
-        <v>1560</v>
+        <v>1161</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>1558</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B614" s="7" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C614" s="8" t="s">
-        <v>1561</v>
+        <v>1162</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>1576</v>
       </c>
       <c r="D614" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B615" s="7" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C615" s="8" t="s">
-        <v>1562</v>
+        <v>1162</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D615" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
@@ -14477,10 +14487,10 @@
         <v>1587</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="C616" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1471</v>
@@ -14491,10 +14501,10 @@
         <v>1587</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -14505,10 +14515,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="C618" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -14519,10 +14529,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C619" s="8" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -14533,10 +14543,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -14547,10 +14557,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="C621" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -14561,10 +14571,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="C622" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -14575,10 +14585,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C623" s="8" t="s">
-        <v>1568</v>
+        <v>1553</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -14589,10 +14599,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="C624" s="8" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -14603,10 +14613,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C625" s="8" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14617,10 +14627,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C626" s="8" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14631,10 +14641,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C627" s="8" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14645,10 +14655,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C628" s="9" t="s">
-        <v>1362</v>
+        <v>1321</v>
+      </c>
+      <c r="C628" s="8" t="s">
+        <v>1570</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14659,10 +14669,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C629" s="10" t="s">
-        <v>1363</v>
+        <v>1322</v>
+      </c>
+      <c r="C629" s="8" t="s">
+        <v>1571</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14673,10 +14683,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C630" s="9" t="s">
-        <v>1364</v>
+        <v>1323</v>
+      </c>
+      <c r="C630" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14687,10 +14697,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C631" s="10" t="s">
-        <v>1365</v>
+        <v>1077</v>
+      </c>
+      <c r="C631" s="9" t="s">
+        <v>1362</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14701,10 +14711,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C632" s="9" t="s">
-        <v>1366</v>
+        <v>1324</v>
+      </c>
+      <c r="C632" s="10" t="s">
+        <v>1363</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14715,10 +14725,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C633" s="10" t="s">
-        <v>1367</v>
+        <v>1325</v>
+      </c>
+      <c r="C633" s="9" t="s">
+        <v>1364</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14729,10 +14739,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C634" s="9" t="s">
-        <v>1368</v>
+        <v>1326</v>
+      </c>
+      <c r="C634" s="10" t="s">
+        <v>1365</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14743,10 +14753,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C635" s="10" t="s">
-        <v>1369</v>
+        <v>1327</v>
+      </c>
+      <c r="C635" s="9" t="s">
+        <v>1366</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14757,10 +14767,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C636" s="9" t="s">
-        <v>1370</v>
+        <v>1328</v>
+      </c>
+      <c r="C636" s="10" t="s">
+        <v>1367</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14771,10 +14781,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C637" s="10" t="s">
-        <v>1371</v>
+        <v>1329</v>
+      </c>
+      <c r="C637" s="9" t="s">
+        <v>1368</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14785,10 +14795,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C638" s="9" t="s">
-        <v>1372</v>
+        <v>1330</v>
+      </c>
+      <c r="C638" s="10" t="s">
+        <v>1369</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14799,10 +14809,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C639" s="10" t="s">
-        <v>1373</v>
+        <v>1331</v>
+      </c>
+      <c r="C639" s="9" t="s">
+        <v>1370</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14813,10 +14823,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C640" s="9" t="s">
-        <v>1374</v>
+        <v>1332</v>
+      </c>
+      <c r="C640" s="10" t="s">
+        <v>1371</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14827,10 +14837,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C641" s="10" t="s">
-        <v>1375</v>
+        <v>1333</v>
+      </c>
+      <c r="C641" s="9" t="s">
+        <v>1372</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14841,10 +14851,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C642" s="9" t="s">
-        <v>1376</v>
+        <v>1334</v>
+      </c>
+      <c r="C642" s="10" t="s">
+        <v>1373</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14855,10 +14865,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C643" s="10" t="s">
-        <v>1377</v>
+        <v>1335</v>
+      </c>
+      <c r="C643" s="9" t="s">
+        <v>1374</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14869,10 +14879,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C644" s="9" t="s">
-        <v>1378</v>
+        <v>1336</v>
+      </c>
+      <c r="C644" s="10" t="s">
+        <v>1375</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14883,10 +14893,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C645" s="10" t="s">
-        <v>1379</v>
+        <v>1337</v>
+      </c>
+      <c r="C645" s="9" t="s">
+        <v>1376</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14897,10 +14907,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C646" s="9" t="s">
-        <v>1380</v>
+        <v>1338</v>
+      </c>
+      <c r="C646" s="10" t="s">
+        <v>1377</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14911,10 +14921,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C647" s="10" t="s">
-        <v>1381</v>
+        <v>1339</v>
+      </c>
+      <c r="C647" s="9" t="s">
+        <v>1378</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14925,10 +14935,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C648" s="9" t="s">
-        <v>1382</v>
+        <v>1340</v>
+      </c>
+      <c r="C648" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14939,10 +14949,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C649" s="10" t="s">
-        <v>1383</v>
+        <v>1341</v>
+      </c>
+      <c r="C649" s="9" t="s">
+        <v>1380</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14953,10 +14963,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C650" s="9" t="s">
-        <v>1384</v>
+        <v>1342</v>
+      </c>
+      <c r="C650" s="10" t="s">
+        <v>1381</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14967,10 +14977,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C651" s="10" t="s">
-        <v>1385</v>
+        <v>1343</v>
+      </c>
+      <c r="C651" s="9" t="s">
+        <v>1382</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14981,10 +14991,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C652" s="9" t="s">
-        <v>1386</v>
+        <v>1344</v>
+      </c>
+      <c r="C652" s="10" t="s">
+        <v>1383</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -14995,10 +15005,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C653" s="10" t="s">
-        <v>1387</v>
+        <v>1345</v>
+      </c>
+      <c r="C653" s="9" t="s">
+        <v>1384</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -15009,10 +15019,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C654" s="9" t="s">
-        <v>1388</v>
+        <v>1346</v>
+      </c>
+      <c r="C654" s="10" t="s">
+        <v>1385</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -15023,10 +15033,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C655" s="10" t="s">
-        <v>1389</v>
+        <v>1347</v>
+      </c>
+      <c r="C655" s="9" t="s">
+        <v>1386</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -15037,10 +15047,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C656" s="9" t="s">
-        <v>1390</v>
+        <v>1348</v>
+      </c>
+      <c r="C656" s="10" t="s">
+        <v>1387</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -15051,10 +15061,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C657" s="10" t="s">
-        <v>1391</v>
+        <v>1349</v>
+      </c>
+      <c r="C657" s="9" t="s">
+        <v>1388</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -15065,10 +15075,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C658" s="9" t="s">
-        <v>1392</v>
+        <v>1350</v>
+      </c>
+      <c r="C658" s="10" t="s">
+        <v>1389</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -15079,10 +15089,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C659" s="10" t="s">
-        <v>1393</v>
+        <v>1351</v>
+      </c>
+      <c r="C659" s="9" t="s">
+        <v>1390</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -15093,10 +15103,10 @@
         <v>1587</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C660" s="9" t="s">
-        <v>1394</v>
+        <v>1352</v>
+      </c>
+      <c r="C660" s="10" t="s">
+        <v>1391</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -15107,10 +15117,10 @@
         <v>1587</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C661" s="10" t="s">
-        <v>1395</v>
+        <v>1353</v>
+      </c>
+      <c r="C661" s="9" t="s">
+        <v>1392</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -15121,10 +15131,10 @@
         <v>1587</v>
       </c>
       <c r="B662" s="7" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C662" s="9" t="s">
-        <v>1396</v>
+        <v>1354</v>
+      </c>
+      <c r="C662" s="10" t="s">
+        <v>1393</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -15135,10 +15145,10 @@
         <v>1587</v>
       </c>
       <c r="B663" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C663" s="10" t="s">
-        <v>1397</v>
+        <v>1355</v>
+      </c>
+      <c r="C663" s="9" t="s">
+        <v>1394</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -15149,10 +15159,10 @@
         <v>1587</v>
       </c>
       <c r="B664" s="7" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C664" s="9" t="s">
-        <v>1398</v>
+        <v>1356</v>
+      </c>
+      <c r="C664" s="10" t="s">
+        <v>1395</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -15163,10 +15173,10 @@
         <v>1587</v>
       </c>
       <c r="B665" s="7" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C665" s="10" t="s">
-        <v>1399</v>
+        <v>1357</v>
+      </c>
+      <c r="C665" s="9" t="s">
+        <v>1396</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -15177,10 +15187,10 @@
         <v>1587</v>
       </c>
       <c r="B666" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C666" s="2" t="s">
-        <v>1573</v>
+        <v>1358</v>
+      </c>
+      <c r="C666" s="10" t="s">
+        <v>1397</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -15188,13 +15198,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B667" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C667" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B667" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C667" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -15202,13 +15212,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B668" s="2" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C668" s="8" t="s">
-        <v>1546</v>
+        <v>1587</v>
+      </c>
+      <c r="B668" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C668" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -15216,13 +15226,13 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B669" s="2" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C669" s="8" t="s">
-        <v>1547</v>
+        <v>1587</v>
+      </c>
+      <c r="B669" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -15233,10 +15243,10 @@
         <v>1472</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="C670" s="8" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="D670" s="3" t="s">
         <v>1471</v>
@@ -15247,10 +15257,10 @@
         <v>1472</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="C671" s="8" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1471</v>
@@ -15261,10 +15271,10 @@
         <v>1472</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="C672" s="8" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="D672" s="3" t="s">
         <v>1471</v>
@@ -15275,10 +15285,10 @@
         <v>1472</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="C673" s="8" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1471</v>
@@ -15289,10 +15299,10 @@
         <v>1472</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="C674" s="8" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1471</v>
@@ -15300,13 +15310,13 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="C675" s="8" t="s">
-        <v>1574</v>
+        <v>1550</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>1471</v>
@@ -15314,13 +15324,13 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1586</v>
+        <v>1472</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C676" s="9" t="s">
-        <v>1410</v>
+        <v>1406</v>
+      </c>
+      <c r="C676" s="8" t="s">
+        <v>1551</v>
       </c>
       <c r="D676" s="3" t="s">
         <v>1471</v>
@@ -15328,13 +15338,13 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1592</v>
+        <v>1472</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C677" s="10" t="s">
-        <v>1452</v>
+        <v>1407</v>
+      </c>
+      <c r="C677" s="8" t="s">
+        <v>1552</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>1471</v>
@@ -15342,13 +15352,13 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C678" s="9" t="s">
-        <v>1453</v>
+        <v>1408</v>
+      </c>
+      <c r="C678" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>1471</v>
@@ -15356,13 +15366,13 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1475</v>
+        <v>1586</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="C679" s="2" t="s">
-        <v>1454</v>
+      <c r="C679" s="9" t="s">
+        <v>1410</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1471</v>
@@ -15370,13 +15380,13 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1790</v>
+        <v>1592</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C680" s="2" t="s">
-        <v>1785</v>
+        <v>1450</v>
+      </c>
+      <c r="C680" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1471</v>
@@ -15384,13 +15394,13 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1790</v>
+        <v>1592</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C681" s="2" t="s">
-        <v>1786</v>
+        <v>1451</v>
+      </c>
+      <c r="C681" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1471</v>
@@ -15398,13 +15408,13 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1790</v>
+        <v>1475</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1781</v>
+        <v>1409</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1787</v>
+        <v>1454</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1471</v>
@@ -15415,10 +15425,10 @@
         <v>1790</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1778</v>
+        <v>1785</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1471</v>
@@ -15429,10 +15439,10 @@
         <v>1790</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1471</v>
@@ -15443,10 +15453,10 @@
         <v>1790</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1471</v>
@@ -15454,72 +15464,72 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1163</v>
+        <v>1790</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1411</v>
+        <v>1782</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1412</v>
+        <v>1778</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1163</v>
+        <v>1790</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C687" s="9" t="s">
-        <v>1575</v>
+        <v>1783</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>1788</v>
       </c>
       <c r="D687" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1164</v>
+        <v>1790</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C688" s="10" t="s">
-        <v>1429</v>
+        <v>1784</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>1789</v>
       </c>
       <c r="D688" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C689" s="9" t="s">
-        <v>1430</v>
+        <v>1411</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D689" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C690" s="10" t="s">
-        <v>1431</v>
+        <v>1479</v>
+      </c>
+      <c r="C690" s="9" t="s">
+        <v>1575</v>
       </c>
       <c r="D690" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
@@ -15527,10 +15537,10 @@
         <v>1164</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C691" s="9" t="s">
-        <v>1432</v>
+        <v>1414</v>
+      </c>
+      <c r="C691" s="10" t="s">
+        <v>1429</v>
       </c>
       <c r="D691" s="3" t="s">
         <v>1474</v>
@@ -15541,10 +15551,10 @@
         <v>1164</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C692" s="10" t="s">
-        <v>1433</v>
+        <v>1416</v>
+      </c>
+      <c r="C692" s="9" t="s">
+        <v>1430</v>
       </c>
       <c r="D692" s="3" t="s">
         <v>1474</v>
@@ -15555,10 +15565,10 @@
         <v>1164</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C693" s="9" t="s">
-        <v>1434</v>
+        <v>1417</v>
+      </c>
+      <c r="C693" s="10" t="s">
+        <v>1431</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>1474</v>
@@ -15569,10 +15579,10 @@
         <v>1164</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C694" s="10" t="s">
-        <v>1435</v>
+        <v>1418</v>
+      </c>
+      <c r="C694" s="9" t="s">
+        <v>1432</v>
       </c>
       <c r="D694" s="3" t="s">
         <v>1474</v>
@@ -15583,10 +15593,10 @@
         <v>1164</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C695" s="9" t="s">
-        <v>1436</v>
+        <v>1419</v>
+      </c>
+      <c r="C695" s="10" t="s">
+        <v>1433</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1474</v>
@@ -15597,10 +15607,10 @@
         <v>1164</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C696" s="10" t="s">
-        <v>1437</v>
+        <v>1420</v>
+      </c>
+      <c r="C696" s="9" t="s">
+        <v>1434</v>
       </c>
       <c r="D696" s="3" t="s">
         <v>1474</v>
@@ -15611,10 +15621,10 @@
         <v>1164</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C697" s="9" t="s">
-        <v>1438</v>
+        <v>1421</v>
+      </c>
+      <c r="C697" s="10" t="s">
+        <v>1435</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>1474</v>
@@ -15625,10 +15635,10 @@
         <v>1164</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C698" s="10" t="s">
-        <v>1439</v>
+        <v>1422</v>
+      </c>
+      <c r="C698" s="9" t="s">
+        <v>1436</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1474</v>
@@ -15639,10 +15649,10 @@
         <v>1164</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C699" s="9" t="s">
-        <v>1440</v>
+        <v>1423</v>
+      </c>
+      <c r="C699" s="10" t="s">
+        <v>1437</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1474</v>
@@ -15653,10 +15663,10 @@
         <v>1164</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C700" s="10" t="s">
-        <v>1441</v>
+        <v>1424</v>
+      </c>
+      <c r="C700" s="9" t="s">
+        <v>1438</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1474</v>
@@ -15667,10 +15677,10 @@
         <v>1164</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C701" s="9" t="s">
-        <v>1442</v>
+        <v>1425</v>
+      </c>
+      <c r="C701" s="10" t="s">
+        <v>1439</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1474</v>
@@ -15681,10 +15691,10 @@
         <v>1164</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C702" s="10" t="s">
-        <v>1443</v>
+        <v>1426</v>
+      </c>
+      <c r="C702" s="9" t="s">
+        <v>1440</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1474</v>
@@ -15695,10 +15705,10 @@
         <v>1164</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C703" s="9" t="s">
-        <v>1444</v>
+        <v>1427</v>
+      </c>
+      <c r="C703" s="10" t="s">
+        <v>1441</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1474</v>
@@ -15709,10 +15719,10 @@
         <v>1164</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C704" s="10" t="s">
-        <v>1445</v>
+        <v>1428</v>
+      </c>
+      <c r="C704" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1474</v>
@@ -15720,44 +15730,44 @@
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C705" s="2" t="s">
-        <v>1455</v>
+        <v>1423</v>
+      </c>
+      <c r="C705" s="10" t="s">
+        <v>1443</v>
       </c>
       <c r="D705" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C706" s="2" t="s">
-        <v>1456</v>
+        <v>1413</v>
+      </c>
+      <c r="C706" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1448</v>
-      </c>
-      <c r="C707" s="2" t="s">
-        <v>1457</v>
+        <v>1415</v>
+      </c>
+      <c r="C707" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D707" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
@@ -15765,10 +15775,10 @@
         <v>1165</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1629</v>
+        <v>1446</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1630</v>
+        <v>1455</v>
       </c>
       <c r="D708" s="3" t="s">
         <v>1476</v>
@@ -15779,10 +15789,10 @@
         <v>1165</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>1476</v>
@@ -15790,44 +15800,44 @@
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1510</v>
+        <v>1448</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1480</v>
+        <v>1457</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1511</v>
+        <v>1629</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1481</v>
+        <v>1630</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1512</v>
+        <v>1449</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1482</v>
+        <v>1458</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
@@ -15835,10 +15845,10 @@
         <v>1477</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>1539</v>
@@ -15849,10 +15859,10 @@
         <v>1477</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="D714" s="3" t="s">
         <v>1539</v>
@@ -15863,10 +15873,10 @@
         <v>1477</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="D715" s="3" t="s">
         <v>1539</v>
@@ -15877,10 +15887,10 @@
         <v>1477</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D716" s="3" t="s">
         <v>1539</v>
@@ -15891,10 +15901,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15905,10 +15915,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15919,10 +15929,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15933,10 +15943,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15947,10 +15957,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15961,10 +15971,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15975,10 +15985,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15989,10 +15999,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -16003,10 +16013,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -16017,10 +16027,10 @@
         <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -16031,10 +16041,10 @@
         <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>1539</v>
@@ -16045,10 +16055,10 @@
         <v>1477</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>1539</v>
@@ -16059,10 +16069,10 @@
         <v>1477</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>1539</v>
@@ -16073,10 +16083,10 @@
         <v>1477</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>1539</v>
@@ -16087,10 +16097,10 @@
         <v>1477</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>1539</v>
@@ -16101,10 +16111,10 @@
         <v>1477</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="D732" s="3" t="s">
         <v>1539</v>
@@ -16115,10 +16125,10 @@
         <v>1477</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1539</v>
@@ -16129,10 +16139,10 @@
         <v>1477</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="D734" s="3" t="s">
         <v>1539</v>
@@ -16143,10 +16153,10 @@
         <v>1477</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="D735" s="3" t="s">
         <v>1539</v>
@@ -16157,10 +16167,10 @@
         <v>1477</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="D736" s="3" t="s">
         <v>1539</v>
@@ -16171,10 +16181,10 @@
         <v>1477</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>1539</v>
@@ -16185,10 +16195,10 @@
         <v>1477</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="D738" s="3" t="s">
         <v>1539</v>
@@ -16196,13 +16206,13 @@
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1479</v>
+        <v>1536</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="D739" s="3" t="s">
         <v>1539</v>
@@ -16210,44 +16220,44 @@
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1597</v>
+        <v>1537</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1604</v>
+        <v>1507</v>
       </c>
       <c r="D740" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1598</v>
+        <v>1538</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1605</v>
+        <v>1508</v>
       </c>
       <c r="D741" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1599</v>
+        <v>1479</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1606</v>
+        <v>1509</v>
       </c>
       <c r="D742" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
@@ -16255,10 +16265,10 @@
         <v>1595</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="D743" s="3" t="s">
         <v>1596</v>
@@ -16269,10 +16279,10 @@
         <v>1595</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="D744" s="3" t="s">
         <v>1596</v>
@@ -16283,10 +16293,10 @@
         <v>1595</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="D745" s="3" t="s">
         <v>1596</v>
@@ -16297,10 +16307,10 @@
         <v>1595</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="D746" s="3" t="s">
         <v>1596</v>
@@ -16308,44 +16318,44 @@
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>1612</v>
+        <v>1601</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>1619</v>
+        <v>1608</v>
       </c>
       <c r="D747" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>1613</v>
+        <v>1602</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="D748" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>1621</v>
+        <v>1610</v>
       </c>
       <c r="D749" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
@@ -16353,10 +16363,10 @@
         <v>1611</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="D750" s="3" t="s">
         <v>1628</v>
@@ -16367,10 +16377,10 @@
         <v>1611</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="D751" s="3" t="s">
         <v>1628</v>
@@ -16381,10 +16391,10 @@
         <v>1611</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="D752" s="3" t="s">
         <v>1628</v>
@@ -16395,10 +16405,10 @@
         <v>1611</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="D753" s="3" t="s">
         <v>1628</v>
@@ -16409,10 +16419,10 @@
         <v>1611</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="D754" s="3" t="s">
         <v>1628</v>
@@ -16420,58 +16430,58 @@
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
-        <v>1635</v>
+        <v>1611</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1636</v>
+        <v>1625</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>1637</v>
+        <v>1624</v>
       </c>
       <c r="D755" s="3" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1640</v>
+        <v>1617</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="D756" s="3" t="s">
-        <v>1713</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1640</v>
+        <v>1618</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="D757" s="3" t="s">
-        <v>1713</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>1643</v>
+        <v>1637</v>
       </c>
       <c r="D758" s="3" t="s">
-        <v>1713</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
@@ -16482,7 +16492,7 @@
         <v>1640</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="D759" s="3" t="s">
         <v>1713</v>
@@ -16496,7 +16506,7 @@
         <v>1640</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="D760" s="3" t="s">
         <v>1713</v>
@@ -16504,13 +16514,13 @@
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
-        <v>1717</v>
+        <v>1639</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="D761" s="3" t="s">
         <v>1713</v>
@@ -16518,44 +16528,44 @@
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="D762" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="D763" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="D764" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
@@ -16563,10 +16573,10 @@
         <v>1718</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="D765" s="3" t="s">
         <v>1714</v>
@@ -16577,10 +16587,10 @@
         <v>1718</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="D766" s="3" t="s">
         <v>1714</v>
@@ -16588,44 +16598,44 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>1659</v>
+        <v>1648</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>1685</v>
+        <v>1655</v>
       </c>
       <c r="D767" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1660</v>
+        <v>1651</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>1686</v>
+        <v>1656</v>
       </c>
       <c r="D768" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>1687</v>
+        <v>1657</v>
       </c>
       <c r="D769" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
@@ -16633,10 +16643,10 @@
         <v>1712</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="D770" s="3" t="s">
         <v>1713</v>
@@ -16647,10 +16657,10 @@
         <v>1712</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="D771" s="3" t="s">
         <v>1713</v>
@@ -16661,10 +16671,10 @@
         <v>1712</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="D772" s="3" t="s">
         <v>1713</v>
@@ -16675,10 +16685,10 @@
         <v>1712</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="D773" s="3" t="s">
         <v>1713</v>
@@ -16689,10 +16699,10 @@
         <v>1712</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="D774" s="3" t="s">
         <v>1713</v>
@@ -16703,10 +16713,10 @@
         <v>1712</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="D775" s="3" t="s">
         <v>1713</v>
@@ -16717,10 +16727,10 @@
         <v>1712</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="D776" s="3" t="s">
         <v>1713</v>
@@ -16731,10 +16741,10 @@
         <v>1712</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="D777" s="3" t="s">
         <v>1713</v>
@@ -16745,10 +16755,10 @@
         <v>1712</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="D778" s="3" t="s">
         <v>1713</v>
@@ -16759,10 +16769,10 @@
         <v>1712</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="D779" s="3" t="s">
         <v>1713</v>
@@ -16773,10 +16783,10 @@
         <v>1712</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="D780" s="3" t="s">
         <v>1713</v>
@@ -16787,10 +16797,10 @@
         <v>1712</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="D781" s="3" t="s">
         <v>1713</v>
@@ -16801,10 +16811,10 @@
         <v>1712</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="D782" s="3" t="s">
         <v>1713</v>
@@ -16815,10 +16825,10 @@
         <v>1712</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="D783" s="3" t="s">
         <v>1713</v>
@@ -16829,10 +16839,10 @@
         <v>1712</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="D784" s="3" t="s">
         <v>1713</v>
@@ -16843,10 +16853,10 @@
         <v>1712</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="D785" s="3" t="s">
         <v>1713</v>
@@ -16857,10 +16867,10 @@
         <v>1712</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="D786" s="3" t="s">
         <v>1713</v>
@@ -16871,10 +16881,10 @@
         <v>1712</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="D787" s="3" t="s">
         <v>1713</v>
@@ -16885,10 +16895,10 @@
         <v>1712</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="D788" s="3" t="s">
         <v>1713</v>
@@ -16899,10 +16909,10 @@
         <v>1712</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="D789" s="3" t="s">
         <v>1713</v>
@@ -16913,10 +16923,10 @@
         <v>1712</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="D790" s="3" t="s">
         <v>1713</v>
@@ -16927,10 +16937,10 @@
         <v>1712</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="D791" s="3" t="s">
         <v>1713</v>
@@ -16941,10 +16951,10 @@
         <v>1712</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
       <c r="D792" s="3" t="s">
         <v>1713</v>
@@ -16955,10 +16965,10 @@
         <v>1712</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="D793" s="3" t="s">
         <v>1713</v>
@@ -16969,10 +16979,10 @@
         <v>1712</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>1730</v>
+        <v>1682</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>1731</v>
+        <v>1709</v>
       </c>
       <c r="D794" s="3" t="s">
         <v>1713</v>
@@ -16983,10 +16993,10 @@
         <v>1712</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>1729</v>
+        <v>1683</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>1732</v>
+        <v>1710</v>
       </c>
       <c r="D795" s="3" t="s">
         <v>1713</v>
@@ -16994,13 +17004,13 @@
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>1720</v>
+        <v>1684</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>1733</v>
+        <v>1711</v>
       </c>
       <c r="D796" s="3" t="s">
         <v>1713</v>
@@ -17008,13 +17018,13 @@
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="D797" s="3" t="s">
         <v>1713</v>
@@ -17022,13 +17032,13 @@
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="D798" s="3" t="s">
         <v>1713</v>
@@ -17039,10 +17049,10 @@
         <v>1719</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="D799" s="3" t="s">
         <v>1713</v>
@@ -17053,10 +17063,10 @@
         <v>1719</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="D800" s="3" t="s">
         <v>1713</v>
@@ -17067,10 +17077,10 @@
         <v>1719</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="D801" s="3" t="s">
         <v>1713</v>
@@ -17081,10 +17091,10 @@
         <v>1719</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="D802" s="3" t="s">
         <v>1713</v>
@@ -17095,10 +17105,10 @@
         <v>1719</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="D803" s="3" t="s">
         <v>1713</v>
@@ -17109,10 +17119,10 @@
         <v>1719</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="D804" s="3" t="s">
         <v>1713</v>
@@ -17120,128 +17130,128 @@
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1743</v>
+        <v>1726</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>1769</v>
+        <v>1739</v>
       </c>
       <c r="D805" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1744</v>
+        <v>1727</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>1770</v>
+        <v>1740</v>
       </c>
       <c r="D806" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>1745</v>
+        <v>1728</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>1771</v>
+        <v>1741</v>
       </c>
       <c r="D807" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>1749</v>
+        <v>1769</v>
       </c>
       <c r="D808" s="3" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>1755</v>
+        <v>1744</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>1750</v>
+        <v>1770</v>
       </c>
       <c r="D809" s="3" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1756</v>
+        <v>1745</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>1751</v>
+        <v>1771</v>
       </c>
       <c r="D810" s="3" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
       <c r="D811" s="3" t="s">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>1761</v>
+        <v>1750</v>
       </c>
       <c r="D812" s="3" t="s">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="C813" s="2" t="s">
-        <v>1762</v>
+        <v>1751</v>
       </c>
       <c r="D813" s="3" t="s">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.25">
@@ -17249,10 +17259,10 @@
         <v>1752</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>1763</v>
+        <v>1753</v>
       </c>
       <c r="D814" s="3" t="s">
         <v>1764</v>
@@ -17260,72 +17270,72 @@
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
-        <v>1772</v>
+        <v>1752</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>1773</v>
+        <v>1758</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>1775</v>
+        <v>1761</v>
       </c>
       <c r="D815" s="3" t="s">
-        <v>1777</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
-        <v>1772</v>
+        <v>1752</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>1774</v>
+        <v>1759</v>
       </c>
       <c r="C816" s="2" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
       <c r="D816" s="3" t="s">
-        <v>1777</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
-        <v>1791</v>
+        <v>1752</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>1792</v>
+        <v>1760</v>
       </c>
       <c r="C817" s="2" t="s">
-        <v>1796</v>
+        <v>1763</v>
       </c>
       <c r="D817" s="3" t="s">
-        <v>1800</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
-        <v>1791</v>
+        <v>1772</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>1793</v>
+        <v>1773</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>1797</v>
+        <v>1775</v>
       </c>
       <c r="D818" s="3" t="s">
-        <v>1800</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
-        <v>1791</v>
+        <v>1772</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>1794</v>
+        <v>1774</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>1798</v>
+        <v>1776</v>
       </c>
       <c r="D819" s="3" t="s">
-        <v>1800</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
@@ -17333,12 +17343,54 @@
         <v>1791</v>
       </c>
       <c r="B820" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D820" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A821" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D821" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A822" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D822" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A823" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B823" s="2" t="s">
         <v>1795</v>
       </c>
-      <c r="C820" s="2" t="s">
+      <c r="C823" s="2" t="s">
         <v>1799</v>
       </c>
-      <c r="D820" s="3" t="s">
+      <c r="D823" s="3" t="s">
         <v>1800</v>
       </c>
     </row>

--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB63AD20-D347-49B1-B662-5B181EAEE62B}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677F7910-0C46-45C8-BF71-42D3B904DAA3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5392,9 +5392,6 @@
     <t>78970155027722945</t>
   </si>
   <si>
-    <t>ОБЩИНА ВАРНА % 6 - КДР</t>
-  </si>
-  <si>
     <t>МАЙ БЮТИ ДЖЪРНИ ЕООД</t>
   </si>
   <si>
@@ -5438,6 +5435,9 @@
   </si>
   <si>
     <t>78970110027720258</t>
+  </si>
+  <si>
+    <t>ОБЩИНА ВАРНА - КДР</t>
   </si>
 </sst>
 </file>
@@ -6650,7 +6650,7 @@
         <v>176</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>914</v>
@@ -8610,7 +8610,7 @@
         <v>366</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>942</v>
@@ -12403,7 +12403,7 @@
         <v>880</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="D467" s="3" t="s">
         <v>982</v>
@@ -13269,10 +13269,10 @@
         <v>1076</v>
       </c>
       <c r="B529" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C529" s="6" t="s">
         <v>1802</v>
-      </c>
-      <c r="C529" s="6" t="s">
-        <v>1803</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>1081</v>
@@ -15422,7 +15422,7 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>1779</v>
@@ -15436,7 +15436,7 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>1780</v>
@@ -15450,7 +15450,7 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>1781</v>
@@ -15464,7 +15464,7 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>1782</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>1783</v>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>1784</v>
@@ -17340,58 +17340,58 @@
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B820" s="2" t="s">
         <v>1791</v>
       </c>
-      <c r="B820" s="2" t="s">
-        <v>1792</v>
-      </c>
       <c r="C820" s="2" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="D820" s="3" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="D821" s="3" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="C822" s="2" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="D822" s="3" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C823" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D823" s="3" t="s">
         <v>1799</v>
-      </c>
-      <c r="D823" s="3" t="s">
-        <v>1800</v>
       </c>
     </row>
   </sheetData>
